--- a/BIS_tr.xlsx
+++ b/BIS_tr.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -769,37 +769,37 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>74.5</v>
+        <v>56.5</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G5" s="3" t="n">
-        <v>39.2</v>
+        <v>46.4</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>D-N-D-U</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K5" s="3" t="n">
-        <v>78.90000000000001</v>
+        <v>50</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="N5" s="3" t="n">
-        <v>47.4</v>
+        <v>46.4</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6">
@@ -882,7 +882,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -891,25 +891,25 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>69.09999999999999</v>
+        <v>57.7</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>97</v>
+        <v>156</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G7" s="3" t="n">
-        <v>43.3</v>
+        <v>43.6</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>97</v>
+        <v>156</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-N</t>
+          <t>N-U-U-D</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -918,21 +918,21 @@
         </is>
       </c>
       <c r="K7" s="3" t="n">
-        <v>76.2</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N7" s="3" t="n">
-        <v>42.9</v>
+        <v>47.8</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1318,10 +1318,10 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>65.7</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>143</v>
+        <v>84</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1329,14 +1329,14 @@
         </is>
       </c>
       <c r="G14" s="3" t="n">
-        <v>39.2</v>
+        <v>38.1</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>143</v>
+        <v>84</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-U</t>
+          <t>U-U-U-N</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1345,21 +1345,21 @@
         </is>
       </c>
       <c r="K14" s="3" t="n">
-        <v>59.2</v>
+        <v>70.3</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N14" s="3" t="n">
-        <v>38.8</v>
+        <v>40.5</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>49</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1440,10 +1440,10 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>63.2</v>
+        <v>52.9</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1451,14 +1451,14 @@
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>42.1</v>
+        <v>51.5</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>N-N-U-N</t>
+          <t>N-N-U-U</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1467,21 +1467,21 @@
         </is>
       </c>
       <c r="K16" s="3" t="n">
-        <v>62.5</v>
+        <v>61.9</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N16" s="3" t="n">
-        <v>50</v>
+        <v>47.6</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1501,10 +1501,10 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>65.90000000000001</v>
+        <v>57.5</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>82</v>
+        <v>127</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1512,14 +1512,14 @@
         </is>
       </c>
       <c r="G17" s="3" t="n">
-        <v>43.9</v>
+        <v>41.7</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>82</v>
+        <v>127</v>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-N</t>
+          <t>N-D-D-U</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1528,21 +1528,21 @@
         </is>
       </c>
       <c r="K17" s="3" t="n">
-        <v>52.9</v>
+        <v>65</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N17" s="3" t="n">
-        <v>47.1</v>
+        <v>40</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1623,7 +1623,7 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>55.6</v>
+        <v>51.5</v>
       </c>
       <c r="E19" s="4" t="n">
         <v>99</v>
@@ -1634,14 +1634,14 @@
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>45.5</v>
+        <v>49.5</v>
       </c>
       <c r="H19" s="4" t="n">
         <v>99</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-D</t>
+          <t>U-D-U-U</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1650,21 +1650,21 @@
         </is>
       </c>
       <c r="K19" s="3" t="n">
-        <v>53.1</v>
+        <v>51.2</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N19" s="3" t="n">
-        <v>50</v>
+        <v>60.5</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>U-N-N</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1684,25 +1684,25 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>65.90000000000001</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>88</v>
+        <v>51</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>43.2</v>
+        <v>41.2</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>88</v>
+        <v>51</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-U</t>
+          <t>D-U-N-N</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1711,10 +1711,10 @@
         </is>
       </c>
       <c r="K20" s="3" t="n">
-        <v>56.8</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
@@ -1722,10 +1722,10 @@
         </is>
       </c>
       <c r="N20" s="3" t="n">
-        <v>51.4</v>
+        <v>45.5</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>37</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2050,25 +2050,25 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>49.2</v>
+        <v>51.2</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>187</v>
+        <v>82</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>43.9</v>
+        <v>45.1</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>187</v>
+        <v>82</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-U</t>
+          <t>D-U-U-N</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="K26" s="3" t="n">
-        <v>50</v>
+        <v>51.4</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>76</v>
+        <v>35</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
@@ -2088,10 +2088,10 @@
         </is>
       </c>
       <c r="N26" s="3" t="n">
-        <v>44.7</v>
+        <v>45.7</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>76</v>
+        <v>35</v>
       </c>
     </row>
     <row r="27">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2538,25 +2538,25 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>57.5</v>
+        <v>61.6</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>127</v>
+        <v>99</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>46.5</v>
+        <v>42.4</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>127</v>
+        <v>99</v>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-U</t>
+          <t>U-D-U-N</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -2565,21 +2565,21 @@
         </is>
       </c>
       <c r="K34" s="3" t="n">
-        <v>48.9</v>
+        <v>51.2</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N34" s="3" t="n">
-        <v>44.7</v>
+        <v>41.9</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="35">
@@ -3017,50 +3017,50 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>100</v>
+        <v>81.8</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G42" s="3" t="n">
-        <v>50</v>
+        <v>45.5</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-U</t>
+          <t>D-D-N-D</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K42" s="3" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="L42" s="4" t="n">
         <v>5</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="N42" s="3" t="n">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3148,10 +3148,10 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>80</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -3159,14 +3159,14 @@
         </is>
       </c>
       <c r="G44" s="3" t="n">
+        <v>57.8</v>
+      </c>
+      <c r="H44" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="H44" s="4" t="n">
-        <v>20</v>
-      </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-N</t>
+          <t>N-D-D-U</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -3178,18 +3178,18 @@
         <v>100</v>
       </c>
       <c r="L44" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N44" s="3" t="n">
-        <v>66.7</v>
+        <v>57.1</v>
       </c>
       <c r="O44" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3331,25 +3331,25 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>44.3</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G47" s="3" t="n">
-        <v>51.4</v>
+        <v>37.8</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-U</t>
+          <t>D-N-U-N</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -3358,21 +3358,21 @@
         </is>
       </c>
       <c r="K47" s="3" t="n">
-        <v>40</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="L47" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N47" s="3" t="n">
-        <v>45</v>
+        <v>42.1</v>
       </c>
       <c r="O47" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="48">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>U-N-N</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -3453,25 +3453,25 @@
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>58.3</v>
+        <v>63.8</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>84</v>
+        <v>47</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G49" s="3" t="n">
-        <v>40.5</v>
+        <v>42.6</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>84</v>
+        <v>47</v>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-U</t>
+          <t>D-U-N-N</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -3480,21 +3480,21 @@
         </is>
       </c>
       <c r="K49" s="3" t="n">
-        <v>70.40000000000001</v>
+        <v>68.2</v>
       </c>
       <c r="L49" s="4" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N49" s="3" t="n">
-        <v>40.7</v>
+        <v>40.9</v>
       </c>
       <c r="O49" s="4" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="50">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3636,10 +3636,10 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>60.4</v>
+        <v>61.1</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>164</v>
+        <v>90</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3647,14 +3647,14 @@
         </is>
       </c>
       <c r="G52" s="3" t="n">
-        <v>40.9</v>
+        <v>36.7</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>164</v>
+        <v>90</v>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-U</t>
+          <t>D-U-U-N</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -3663,21 +3663,21 @@
         </is>
       </c>
       <c r="K52" s="3" t="n">
-        <v>66.7</v>
+        <v>88</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N52" s="3" t="n">
-        <v>38.9</v>
+        <v>48</v>
       </c>
       <c r="O52" s="4" t="n">
-        <v>72</v>
+        <v>25</v>
       </c>
     </row>
     <row r="53">
@@ -3688,46 +3688,46 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>45.5</v>
+        <v>52.6</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G53" s="3" t="n">
-        <v>45.5</v>
+        <v>47.4</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="K53" s="3" t="n">
-        <v>47.6</v>
+        <v>42.9</v>
       </c>
       <c r="L53" s="4" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="N53" s="3" t="n">
-        <v>47.6</v>
+        <v>57.1</v>
       </c>
       <c r="O53" s="4" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3819,25 +3819,25 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>47.1</v>
+        <v>58.9</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>170</v>
+        <v>73</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G55" s="3" t="n">
-        <v>46.5</v>
+        <v>42.5</v>
       </c>
       <c r="H55" s="4" t="n">
-        <v>170</v>
+        <v>73</v>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-U</t>
+          <t>U-D-U-N</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -3846,10 +3846,10 @@
         </is>
       </c>
       <c r="K55" s="3" t="n">
-        <v>44.6</v>
+        <v>51.4</v>
       </c>
       <c r="L55" s="4" t="n">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
@@ -3857,10 +3857,10 @@
         </is>
       </c>
       <c r="N55" s="3" t="n">
-        <v>47.3</v>
+        <v>45.7</v>
       </c>
       <c r="O55" s="4" t="n">
-        <v>74</v>
+        <v>35</v>
       </c>
     </row>
     <row r="56">
@@ -4115,7 +4115,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4124,25 +4124,25 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>63.2</v>
+        <v>63.9</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>87</v>
+        <v>158</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G60" s="3" t="n">
-        <v>37.9</v>
+        <v>35.4</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>87</v>
+        <v>158</v>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -4151,10 +4151,10 @@
         </is>
       </c>
       <c r="K60" s="3" t="n">
-        <v>54.1</v>
+        <v>65</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
@@ -4162,10 +4162,10 @@
         </is>
       </c>
       <c r="N60" s="3" t="n">
-        <v>40.5</v>
+        <v>41.7</v>
       </c>
       <c r="O60" s="4" t="n">
-        <v>37</v>
+        <v>60</v>
       </c>
     </row>
     <row r="61">
@@ -4176,7 +4176,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4185,10 +4185,10 @@
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>56.3</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>119</v>
+        <v>28</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -4196,14 +4196,14 @@
         </is>
       </c>
       <c r="G61" s="3" t="n">
-        <v>44.5</v>
+        <v>57.1</v>
       </c>
       <c r="H61" s="4" t="n">
-        <v>119</v>
+        <v>28</v>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-D</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -4212,21 +4212,21 @@
         </is>
       </c>
       <c r="K61" s="3" t="n">
-        <v>51.9</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="L61" s="4" t="n">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N61" s="3" t="n">
-        <v>48.1</v>
+        <v>50</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>52</v>
+        <v>14</v>
       </c>
     </row>
     <row r="62">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>N-D-D</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -4368,25 +4368,25 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>51.2</v>
+        <v>64.5</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>86</v>
+        <v>31</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G64" s="3" t="n">
-        <v>44.2</v>
+        <v>45.2</v>
       </c>
       <c r="H64" s="4" t="n">
-        <v>86</v>
+        <v>31</v>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-D</t>
+          <t>U-N-D-N</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -4395,21 +4395,21 @@
         </is>
       </c>
       <c r="K64" s="3" t="n">
-        <v>59.4</v>
+        <v>66.7</v>
       </c>
       <c r="L64" s="4" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N64" s="3" t="n">
-        <v>40.6</v>
+        <v>58.3</v>
       </c>
       <c r="O64" s="4" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
     </row>
     <row r="65">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -5157,25 +5157,25 @@
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>74.7</v>
+        <v>64.7</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>83</v>
+        <v>116</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G77" s="3" t="n">
-        <v>38.6</v>
+        <v>44</v>
       </c>
       <c r="H77" s="4" t="n">
-        <v>83</v>
+        <v>116</v>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -5184,21 +5184,21 @@
         </is>
       </c>
       <c r="K77" s="3" t="n">
-        <v>75.8</v>
+        <v>60.4</v>
       </c>
       <c r="L77" s="4" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N77" s="3" t="n">
-        <v>39.4</v>
+        <v>45.3</v>
       </c>
       <c r="O77" s="4" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
     </row>
     <row r="78">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -5218,25 +5218,25 @@
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>52.7</v>
+        <v>54.5</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>74</v>
+        <v>191</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G78" s="3" t="n">
-        <v>43.2</v>
+        <v>41.9</v>
       </c>
       <c r="H78" s="4" t="n">
-        <v>74</v>
+        <v>191</v>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -5245,10 +5245,10 @@
         </is>
       </c>
       <c r="K78" s="3" t="n">
-        <v>54.5</v>
+        <v>58.2</v>
       </c>
       <c r="L78" s="4" t="n">
-        <v>33</v>
+        <v>79</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
@@ -5256,10 +5256,10 @@
         </is>
       </c>
       <c r="N78" s="3" t="n">
-        <v>48.5</v>
+        <v>45.6</v>
       </c>
       <c r="O78" s="4" t="n">
-        <v>33</v>
+        <v>79</v>
       </c>
     </row>
     <row r="79">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -5462,10 +5462,10 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>72</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -5473,14 +5473,14 @@
         </is>
       </c>
       <c r="G82" s="3" t="n">
-        <v>43.6</v>
+        <v>44</v>
       </c>
       <c r="H82" s="4" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -5489,21 +5489,21 @@
         </is>
       </c>
       <c r="K82" s="3" t="n">
-        <v>85</v>
+        <v>66.7</v>
       </c>
       <c r="L82" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N82" s="3" t="n">
-        <v>35</v>
+        <v>44.4</v>
       </c>
       <c r="O82" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="83">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -5523,10 +5523,10 @@
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>56.8</v>
+        <v>61.4</v>
       </c>
       <c r="E83" s="4" t="n">
-        <v>162</v>
+        <v>70</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -5534,14 +5534,14 @@
         </is>
       </c>
       <c r="G83" s="3" t="n">
-        <v>50.6</v>
+        <v>38.6</v>
       </c>
       <c r="H83" s="4" t="n">
-        <v>162</v>
+        <v>70</v>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-U</t>
+          <t>U-D-U-N</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
@@ -5550,10 +5550,10 @@
         </is>
       </c>
       <c r="K83" s="3" t="n">
-        <v>57.4</v>
+        <v>59.4</v>
       </c>
       <c r="L83" s="4" t="n">
-        <v>68</v>
+        <v>32</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
@@ -5561,10 +5561,10 @@
         </is>
       </c>
       <c r="N83" s="3" t="n">
-        <v>50</v>
+        <v>40.6</v>
       </c>
       <c r="O83" s="4" t="n">
-        <v>68</v>
+        <v>32</v>
       </c>
     </row>
     <row r="84">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -5584,25 +5584,25 @@
         </is>
       </c>
       <c r="D84" s="3" t="n">
-        <v>74.5</v>
+        <v>66.2</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G84" s="3" t="n">
-        <v>38.3</v>
+        <v>40</v>
       </c>
       <c r="H84" s="4" t="n">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-N-U-D</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -5611,21 +5611,21 @@
         </is>
       </c>
       <c r="K84" s="3" t="n">
-        <v>76.90000000000001</v>
+        <v>62.5</v>
       </c>
       <c r="L84" s="4" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N84" s="3" t="n">
-        <v>38.5</v>
+        <v>40.6</v>
       </c>
       <c r="O84" s="4" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
     </row>
     <row r="85">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -6255,25 +6255,25 @@
         </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>87.90000000000001</v>
+        <v>75.2</v>
       </c>
       <c r="E95" s="4" t="n">
-        <v>33</v>
+        <v>101</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G95" s="3" t="n">
-        <v>54.5</v>
+        <v>41.6</v>
       </c>
       <c r="H95" s="4" t="n">
-        <v>33</v>
+        <v>101</v>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-N</t>
+          <t>N-U-U-D</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
@@ -6282,10 +6282,10 @@
         </is>
       </c>
       <c r="K95" s="3" t="n">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="L95" s="4" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
@@ -6293,10 +6293,10 @@
         </is>
       </c>
       <c r="N95" s="3" t="n">
-        <v>66.7</v>
+        <v>43.8</v>
       </c>
       <c r="O95" s="4" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="96">
@@ -6307,7 +6307,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -6316,25 +6316,25 @@
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>64</v>
+        <v>50.6</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G96" s="3" t="n">
-        <v>46</v>
+        <v>44.6</v>
       </c>
       <c r="H96" s="4" t="n">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-N-U-U</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
@@ -6343,21 +6343,21 @@
         </is>
       </c>
       <c r="K96" s="3" t="n">
-        <v>52.2</v>
+        <v>45.9</v>
       </c>
       <c r="L96" s="4" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N96" s="3" t="n">
-        <v>56.5</v>
+        <v>56.8</v>
       </c>
       <c r="O96" s="4" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
     </row>
     <row r="97">
@@ -6429,7 +6429,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -6438,48 +6438,48 @@
         </is>
       </c>
       <c r="D98" s="3" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E98" s="4" t="n">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G98" s="3" t="n">
-        <v>45</v>
+        <v>39.7</v>
       </c>
       <c r="H98" s="4" t="n">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>N-N-U-N</t>
+          <t>N-N-U-D</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K98" s="3" t="n">
-        <v>42.9</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="L98" s="4" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="N98" s="3" t="n">
-        <v>57.1</v>
+        <v>36.8</v>
       </c>
       <c r="O98" s="4" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="99">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -6560,25 +6560,25 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>65.3</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G100" s="3" t="n">
-        <v>34.7</v>
+        <v>41.8</v>
       </c>
       <c r="H100" s="4" t="n">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-U</t>
+          <t>D-N-U-N</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
@@ -6587,21 +6587,21 @@
         </is>
       </c>
       <c r="K100" s="3" t="n">
-        <v>61.8</v>
+        <v>76.2</v>
       </c>
       <c r="L100" s="4" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N100" s="3" t="n">
-        <v>38.2</v>
+        <v>47.6</v>
       </c>
       <c r="O100" s="4" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
     </row>
     <row r="101">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>U-N-N</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -6743,10 +6743,10 @@
         </is>
       </c>
       <c r="D103" s="3" t="n">
-        <v>48.6</v>
+        <v>70.2</v>
       </c>
       <c r="E103" s="4" t="n">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -6754,14 +6754,14 @@
         </is>
       </c>
       <c r="G103" s="3" t="n">
-        <v>51.4</v>
+        <v>38.6</v>
       </c>
       <c r="H103" s="4" t="n">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-U</t>
+          <t>D-U-N-N</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
@@ -6770,10 +6770,10 @@
         </is>
       </c>
       <c r="K103" s="3" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="L103" s="4" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
@@ -6781,10 +6781,10 @@
         </is>
       </c>
       <c r="N103" s="3" t="n">
-        <v>53.6</v>
+        <v>41.7</v>
       </c>
       <c r="O103" s="4" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="104">
@@ -7244,7 +7244,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -7253,48 +7253,48 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I5" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>D-N-D-U</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M5" s="3" t="n">
-        <v>100</v>
+        <v>44.4</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P5" s="3" t="n">
-        <v>100</v>
+        <v>55.6</v>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -7386,7 +7386,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -7395,25 +7395,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>85.7</v>
+        <v>55.6</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I7" s="3" t="n">
-        <v>42.9</v>
+        <v>55.6</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-N</t>
+          <t>N-U-U-D</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -7425,7 +7425,7 @@
         <v>100</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
@@ -7433,10 +7433,10 @@
         </is>
       </c>
       <c r="P7" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -7879,7 +7879,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -7888,25 +7888,25 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>53.3</v>
+        <v>77.3</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I14" s="3" t="n">
-        <v>40</v>
+        <v>45.5</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-U</t>
+          <t>U-U-U-N</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -7915,10 +7915,10 @@
         </is>
       </c>
       <c r="M14" s="3" t="n">
-        <v>46.2</v>
+        <v>80</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -7926,10 +7926,10 @@
         </is>
       </c>
       <c r="P14" s="3" t="n">
-        <v>46.2</v>
+        <v>50</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -8021,57 +8021,57 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>66.7</v>
+        <v>57.1</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I16" s="3" t="n">
-        <v>33.3</v>
+        <v>57.1</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>N-N-U-N</t>
+          <t>N-N-U-U</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="M16" s="3" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P16" s="3" t="n">
         <v>50</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -8092,7 +8092,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -8101,48 +8101,48 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>82.40000000000001</v>
+        <v>74.3</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I17" s="3" t="n">
-        <v>41.2</v>
+        <v>45.7</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-N</t>
+          <t>N-D-D-U</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M17" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="P17" s="3" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -8234,7 +8234,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -8243,10 +8243,10 @@
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>53.8</v>
+        <v>68.8</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -8254,14 +8254,14 @@
         </is>
       </c>
       <c r="I19" s="3" t="n">
-        <v>61.5</v>
+        <v>56.2</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-D</t>
+          <t>U-D-U-U</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -8270,21 +8270,21 @@
         </is>
       </c>
       <c r="M19" s="3" t="n">
-        <v>60</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P19" s="3" t="n">
-        <v>60</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>U-N-N</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -8314,25 +8314,25 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>78.90000000000001</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I20" s="3" t="n">
-        <v>47.4</v>
+        <v>42.9</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-U</t>
+          <t>D-U-N-N</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -8341,10 +8341,10 @@
         </is>
       </c>
       <c r="M20" s="3" t="n">
-        <v>77.8</v>
+        <v>75</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -8352,10 +8352,10 @@
         </is>
       </c>
       <c r="P20" s="3" t="n">
-        <v>55.6</v>
+        <v>50</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -8740,25 +8740,25 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>58.3</v>
+        <v>70</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I26" s="3" t="n">
-        <v>47.2</v>
+        <v>50</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-U</t>
+          <t>D-U-U-N</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -8767,21 +8767,21 @@
         </is>
       </c>
       <c r="M26" s="3" t="n">
-        <v>62.5</v>
+        <v>66.7</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P26" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -9299,7 +9299,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -9308,25 +9308,25 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>52.6</v>
+        <v>69.2</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I34" s="3" t="n">
-        <v>68.40000000000001</v>
+        <v>53.8</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-U</t>
+          <t>U-D-U-N</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -9338,18 +9338,18 @@
         <v>60</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P34" s="3" t="n">
         <v>60</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35">
@@ -9867,57 +9867,53 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F42" s="3" t="n">
         <v>100</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I42" s="3" t="n">
         <v>100</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-U</t>
+          <t>D-D-N-D</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M42" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr"/>
       <c r="N42" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P42" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr"/>
       <c r="Q42" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -10009,7 +10005,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -10018,25 +10014,25 @@
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>83.3</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I44" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="J44" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-N</t>
+          <t>N-D-D-U</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
@@ -10048,18 +10044,18 @@
         <v>100</v>
       </c>
       <c r="N44" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P44" s="3" t="n">
         <v>100</v>
       </c>
       <c r="Q44" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -10222,54 +10218,54 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I47" s="3" t="n">
-        <v>41.7</v>
+        <v>75</v>
       </c>
       <c r="J47" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-U</t>
+          <t>D-N-U-N</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M47" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="N47" s="4" t="n">
         <v>3</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P47" s="3" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="Q47" s="4" t="n">
         <v>3</v>
@@ -10364,7 +10360,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>U-N-N</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -10373,25 +10369,25 @@
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>52.6</v>
+        <v>58.3</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I49" s="3" t="n">
-        <v>36.8</v>
+        <v>66.7</v>
       </c>
       <c r="J49" s="4" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-U</t>
+          <t>D-U-N-N</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
@@ -10400,10 +10396,10 @@
         </is>
       </c>
       <c r="M49" s="3" t="n">
-        <v>62.5</v>
+        <v>75</v>
       </c>
       <c r="N49" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
@@ -10411,10 +10407,10 @@
         </is>
       </c>
       <c r="P49" s="3" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="Q49" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50">
@@ -10573,7 +10569,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -10582,25 +10578,25 @@
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>54.3</v>
+        <v>87.5</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="I52" s="3" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="J52" s="4" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-U</t>
+          <t>D-U-U-N</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
@@ -10609,10 +10605,10 @@
         </is>
       </c>
       <c r="M52" s="3" t="n">
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
@@ -10620,10 +10616,10 @@
         </is>
       </c>
       <c r="P52" s="3" t="n">
-        <v>50</v>
+        <v>62.5</v>
       </c>
       <c r="Q52" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="53">
@@ -10644,57 +10640,57 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>55.6</v>
+        <v>40</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I53" s="3" t="n">
-        <v>44.4</v>
+        <v>40</v>
       </c>
       <c r="J53" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M53" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="N53" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P53" s="3" t="n">
         <v>50</v>
       </c>
       <c r="Q53" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -10786,7 +10782,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -10795,10 +10791,10 @@
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>48.4</v>
+        <v>40</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -10806,14 +10802,14 @@
         </is>
       </c>
       <c r="I55" s="3" t="n">
-        <v>54.8</v>
+        <v>50</v>
       </c>
       <c r="J55" s="4" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-U</t>
+          <t>U-D-U-N</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
@@ -10822,21 +10818,21 @@
         </is>
       </c>
       <c r="M55" s="3" t="n">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="N55" s="4" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="P55" s="3" t="n">
         <v>50</v>
       </c>
       <c r="Q55" s="4" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56">
@@ -11141,7 +11137,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -11150,48 +11146,48 @@
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>62.5</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="G60" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="J60" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>U-U-U-D</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="N60" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I60" s="3" t="n">
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>D/N</t>
+        </is>
+      </c>
+      <c r="P60" s="3" t="n">
         <v>37.5</v>
       </c>
-      <c r="J60" s="4" t="n">
+      <c r="Q60" s="4" t="n">
         <v>16</v>
-      </c>
-      <c r="K60" s="2" t="inlineStr">
-        <is>
-          <t>U-U-U-N</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="inlineStr">
-        <is>
-          <t>N/U</t>
-        </is>
-      </c>
-      <c r="M60" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="N60" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="O60" s="2" t="inlineStr">
-        <is>
-          <t>D/N/U</t>
-        </is>
-      </c>
-      <c r="P60" s="3" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="Q60" s="4" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="61">
@@ -11212,7 +11208,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -11221,25 +11217,25 @@
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>47.8</v>
+        <v>77.8</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I61" s="3" t="n">
-        <v>52.2</v>
+        <v>66.7</v>
       </c>
       <c r="J61" s="4" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-D</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
@@ -11248,21 +11244,21 @@
         </is>
       </c>
       <c r="M61" s="3" t="n">
-        <v>54.5</v>
+        <v>75</v>
       </c>
       <c r="N61" s="4" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P61" s="3" t="n">
-        <v>54.5</v>
+        <v>50</v>
       </c>
       <c r="Q61" s="4" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="62">
@@ -11425,57 +11421,57 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>N-D-D</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>54.5</v>
+        <v>60</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I64" s="3" t="n">
-        <v>63.6</v>
+        <v>40</v>
       </c>
       <c r="J64" s="4" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-D</t>
+          <t>U-N-D-N</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M64" s="3" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="N64" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="P64" s="3" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="Q64" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -12340,7 +12336,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -12349,25 +12345,25 @@
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>85.2</v>
+        <v>75</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I77" s="3" t="n">
-        <v>40.7</v>
+        <v>55</v>
       </c>
       <c r="J77" s="4" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
@@ -12376,21 +12372,21 @@
         </is>
       </c>
       <c r="M77" s="3" t="n">
-        <v>100</v>
+        <v>77.8</v>
       </c>
       <c r="N77" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P77" s="3" t="n">
-        <v>46.2</v>
+        <v>77.8</v>
       </c>
       <c r="Q77" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="78">
@@ -12411,7 +12407,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -12420,10 +12416,10 @@
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>66.7</v>
+        <v>52.5</v>
       </c>
       <c r="G78" s="4" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -12431,14 +12427,14 @@
         </is>
       </c>
       <c r="I78" s="3" t="n">
-        <v>55.6</v>
+        <v>47.5</v>
       </c>
       <c r="J78" s="4" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
@@ -12447,21 +12443,21 @@
         </is>
       </c>
       <c r="M78" s="3" t="n">
-        <v>60</v>
+        <v>43.8</v>
       </c>
       <c r="N78" s="4" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P78" s="3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="Q78" s="4" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="79">
@@ -12695,7 +12691,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -12704,10 +12700,10 @@
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -12715,14 +12711,14 @@
         </is>
       </c>
       <c r="I82" s="3" t="n">
-        <v>55.6</v>
+        <v>75</v>
       </c>
       <c r="J82" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
@@ -12731,21 +12727,21 @@
         </is>
       </c>
       <c r="M82" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="N82" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P82" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="Q82" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -12766,7 +12762,7 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -12775,10 +12771,10 @@
         </is>
       </c>
       <c r="F83" s="3" t="n">
-        <v>73.3</v>
+        <v>50</v>
       </c>
       <c r="G83" s="4" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
@@ -12786,37 +12782,37 @@
         </is>
       </c>
       <c r="I83" s="3" t="n">
-        <v>50</v>
+        <v>42.9</v>
       </c>
       <c r="J83" s="4" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-U</t>
+          <t>U-D-U-N</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M83" s="3" t="n">
-        <v>63.6</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="N83" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P83" s="3" t="n">
-        <v>45.5</v>
+        <v>57.1</v>
       </c>
       <c r="Q83" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="84">
@@ -12837,7 +12833,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -12846,25 +12842,25 @@
         </is>
       </c>
       <c r="F84" s="3" t="n">
-        <v>80</v>
+        <v>85.7</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I84" s="3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J84" s="4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-N-U-D</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
@@ -12873,21 +12869,21 @@
         </is>
       </c>
       <c r="M84" s="3" t="n">
-        <v>100</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="N84" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P84" s="3" t="n">
-        <v>100</v>
+        <v>57.1</v>
       </c>
       <c r="Q84" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="85">
@@ -13618,7 +13614,7 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -13627,48 +13623,48 @@
         </is>
       </c>
       <c r="F95" s="3" t="n">
-        <v>75</v>
+        <v>69.2</v>
       </c>
       <c r="G95" s="4" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I95" s="3" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="J95" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>N-U-U-D</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>N/U</t>
+        </is>
+      </c>
+      <c r="M95" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="J95" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="K95" s="2" t="inlineStr">
-        <is>
-          <t>N-U-U-N</t>
-        </is>
-      </c>
-      <c r="L95" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M95" s="3" t="n">
-        <v>100</v>
-      </c>
       <c r="N95" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P95" s="3" t="n">
         <v>100</v>
       </c>
       <c r="Q95" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96">
@@ -13689,7 +13685,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -13698,25 +13694,25 @@
         </is>
       </c>
       <c r="F96" s="3" t="n">
-        <v>70</v>
+        <v>61.5</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I96" s="3" t="n">
-        <v>40</v>
+        <v>53.8</v>
       </c>
       <c r="J96" s="4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-N-U-U</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
@@ -13725,21 +13721,21 @@
         </is>
       </c>
       <c r="M96" s="3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="N96" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P96" s="3" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="Q96" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="97">
@@ -13831,53 +13827,57 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F98" s="3" t="n">
         <v>50</v>
       </c>
       <c r="G98" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>D/N</t>
+        </is>
+      </c>
+      <c r="I98" s="3" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="J98" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>N-N-U-D</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M98" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N98" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="O98" s="2" t="inlineStr">
         <is>
           <t>D/N</t>
         </is>
       </c>
-      <c r="I98" s="3" t="n">
+      <c r="P98" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="J98" s="4" t="n">
+      <c r="Q98" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="K98" s="2" t="inlineStr">
-        <is>
-          <t>N-N-U-N</t>
-        </is>
-      </c>
-      <c r="L98" s="2" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M98" s="3" t="inlineStr"/>
-      <c r="N98" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O98" s="2" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P98" s="3" t="inlineStr"/>
-      <c r="Q98" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -13969,7 +13969,7 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -13978,37 +13978,37 @@
         </is>
       </c>
       <c r="F100" s="3" t="n">
-        <v>60.9</v>
+        <v>72.7</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I100" s="3" t="n">
-        <v>39.1</v>
+        <v>45.5</v>
       </c>
       <c r="J100" s="4" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-U</t>
+          <t>D-N-U-N</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M100" s="3" t="n">
-        <v>37.5</v>
+        <v>66.7</v>
       </c>
       <c r="N100" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
@@ -14016,10 +14016,10 @@
         </is>
       </c>
       <c r="P100" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="Q100" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="101">
@@ -14182,57 +14182,57 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>U-N-N</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F103" s="3" t="n">
-        <v>50</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="G103" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I103" s="3" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="J103" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>D-U-N-N</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M103" s="3" t="n">
         <v>66.7</v>
       </c>
-      <c r="J103" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="K103" s="2" t="inlineStr">
-        <is>
-          <t>D-U-N-U</t>
-        </is>
-      </c>
-      <c r="L103" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="M103" s="3" t="n">
-        <v>60</v>
-      </c>
       <c r="N103" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P103" s="3" t="n">
-        <v>80</v>
+        <v>66.7</v>
       </c>
       <c r="Q103" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="104">

--- a/BIS_tr.xlsx
+++ b/BIS_tr.xlsx
@@ -638,7 +638,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -647,25 +647,25 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>69.2</v>
+        <v>63.3</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>39</v>
+        <v>79</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G3" s="3" t="n">
-        <v>41</v>
+        <v>44.3</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>39</v>
+        <v>79</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-N</t>
+          <t>D-U-N-D</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -674,21 +674,21 @@
         </is>
       </c>
       <c r="K3" s="3" t="n">
-        <v>76.5</v>
+        <v>57.7</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N3" s="3" t="n">
-        <v>47.1</v>
+        <v>57.7</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
@@ -760,7 +760,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -769,37 +769,37 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>56.5</v>
+        <v>74.5</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G5" s="3" t="n">
-        <v>46.4</v>
+        <v>39.2</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-U</t>
+          <t>D-N-D-N</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K5" s="3" t="n">
-        <v>50</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="N5" s="3" t="n">
-        <v>46.4</v>
+        <v>47.4</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
@@ -821,7 +821,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -830,25 +830,25 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>70</v>
+        <v>63.2</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G6" s="3" t="n">
-        <v>42</v>
+        <v>45.6</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-N</t>
+          <t>D-U-N-D</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="K6" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>60.7</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="N6" s="3" t="n">
-        <v>41.2</v>
+        <v>57.1</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1318,10 +1318,10 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>67.90000000000001</v>
+        <v>65.7</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>84</v>
+        <v>143</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1329,14 +1329,14 @@
         </is>
       </c>
       <c r="G14" s="3" t="n">
-        <v>38.1</v>
+        <v>39.2</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>84</v>
+        <v>143</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-U</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1345,21 +1345,21 @@
         </is>
       </c>
       <c r="K14" s="3" t="n">
-        <v>70.3</v>
+        <v>59.2</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N14" s="3" t="n">
-        <v>40.5</v>
+        <v>38.8</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1440,10 +1440,10 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>52.9</v>
+        <v>63.2</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1451,14 +1451,14 @@
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>51.5</v>
+        <v>42.1</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>N-N-U-U</t>
+          <t>N-N-U-N</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1467,21 +1467,21 @@
         </is>
       </c>
       <c r="K16" s="3" t="n">
-        <v>61.9</v>
+        <v>62.5</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N16" s="3" t="n">
-        <v>47.6</v>
+        <v>50</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1623,25 +1623,25 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>51.5</v>
+        <v>60.6</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>49.5</v>
+        <v>48.5</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-U</t>
+          <t>U-D-U-N</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1650,21 +1650,21 @@
         </is>
       </c>
       <c r="K19" s="3" t="n">
-        <v>51.2</v>
+        <v>56.2</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N19" s="3" t="n">
-        <v>60.5</v>
+        <v>56.2</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>43</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20">
@@ -1858,57 +1858,57 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>D-N-D</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>65.59999999999999</v>
+        <v>58.3</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G23" s="3" t="n">
-        <v>46.9</v>
+        <v>41.7</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-D</t>
+          <t>U-D-N-N</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="K23" s="3" t="n">
-        <v>77.8</v>
+        <v>50</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N23" s="3" t="n">
-        <v>44.4</v>
+        <v>50</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2050,25 +2050,25 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>51.2</v>
+        <v>49.2</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>82</v>
+        <v>187</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>45.1</v>
+        <v>43.9</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>82</v>
+        <v>187</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="K26" s="3" t="n">
-        <v>51.4</v>
+        <v>50</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
@@ -2088,10 +2088,10 @@
         </is>
       </c>
       <c r="N26" s="3" t="n">
-        <v>45.7</v>
+        <v>44.7</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>35</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2477,25 +2477,25 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>59.6</v>
+        <v>71.3</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>136</v>
+        <v>94</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G33" s="3" t="n">
-        <v>47.1</v>
+        <v>43.6</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>136</v>
+        <v>94</v>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -2504,10 +2504,10 @@
         </is>
       </c>
       <c r="K33" s="3" t="n">
-        <v>63.2</v>
+        <v>69.7</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
@@ -2515,10 +2515,10 @@
         </is>
       </c>
       <c r="N33" s="3" t="n">
-        <v>50</v>
+        <v>39.4</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="34">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2538,25 +2538,25 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>61.6</v>
+        <v>60.7</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>99</v>
+        <v>145</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>42.4</v>
+        <v>39.3</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>99</v>
+        <v>145</v>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -2565,10 +2565,10 @@
         </is>
       </c>
       <c r="K34" s="3" t="n">
-        <v>51.2</v>
+        <v>59.7</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
@@ -2576,10 +2576,10 @@
         </is>
       </c>
       <c r="N34" s="3" t="n">
-        <v>41.9</v>
+        <v>37.3</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>43</v>
+        <v>67</v>
       </c>
     </row>
     <row r="35">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2599,48 +2599,48 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>50.7</v>
+        <v>55.6</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v>45.3</v>
+        <v>48.1</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-U</t>
+          <t>N-D-D-N</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="K35" s="3" t="n">
-        <v>87.5</v>
+        <v>50</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N35" s="3" t="n">
         <v>50</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>U-N-N</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2782,10 +2782,10 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>63</v>
+        <v>62.8</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2793,14 +2793,14 @@
         </is>
       </c>
       <c r="G38" s="3" t="n">
-        <v>45.7</v>
+        <v>39.5</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>N-U-N-U</t>
+          <t>N-U-N-N</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -2809,21 +2809,21 @@
         </is>
       </c>
       <c r="K38" s="3" t="n">
-        <v>52.2</v>
+        <v>57.1</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N38" s="3" t="n">
-        <v>43.5</v>
+        <v>42.9</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
     </row>
     <row r="39">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2843,25 +2843,25 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>64.59999999999999</v>
+        <v>57.5</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>79</v>
+        <v>40</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G39" s="3" t="n">
-        <v>41.8</v>
+        <v>37.5</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>79</v>
+        <v>40</v>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-U</t>
+          <t>D-N-U-N</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -2870,21 +2870,21 @@
         </is>
       </c>
       <c r="K39" s="3" t="n">
-        <v>69.40000000000001</v>
+        <v>45.5</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N39" s="3" t="n">
-        <v>47.2</v>
+        <v>45.5</v>
       </c>
       <c r="O39" s="4" t="n">
-        <v>36</v>
+        <v>11</v>
       </c>
     </row>
     <row r="40">
@@ -3017,57 +3017,57 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>D-N-D</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>81.8</v>
+        <v>75</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G42" s="3" t="n">
-        <v>45.5</v>
+        <v>50</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-D</t>
+          <t>D-D-N-N</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="K42" s="3" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="N42" s="3" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="O42" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3331,25 +3331,25 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>68.90000000000001</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G47" s="3" t="n">
-        <v>37.8</v>
+        <v>36.9</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-N-U-D</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -3358,10 +3358,10 @@
         </is>
       </c>
       <c r="K47" s="3" t="n">
-        <v>68.40000000000001</v>
+        <v>71</v>
       </c>
       <c r="L47" s="4" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
@@ -3369,10 +3369,10 @@
         </is>
       </c>
       <c r="N47" s="3" t="n">
-        <v>42.1</v>
+        <v>41.9</v>
       </c>
       <c r="O47" s="4" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
     </row>
     <row r="48">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3636,10 +3636,10 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>61.1</v>
+        <v>60.4</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>90</v>
+        <v>164</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3647,14 +3647,14 @@
         </is>
       </c>
       <c r="G52" s="3" t="n">
-        <v>36.7</v>
+        <v>40.9</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>90</v>
+        <v>164</v>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -3663,21 +3663,21 @@
         </is>
       </c>
       <c r="K52" s="3" t="n">
-        <v>88</v>
+        <v>66.7</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N52" s="3" t="n">
-        <v>48</v>
+        <v>38.9</v>
       </c>
       <c r="O52" s="4" t="n">
-        <v>25</v>
+        <v>72</v>
       </c>
     </row>
     <row r="53">
@@ -3688,46 +3688,46 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>52.6</v>
+        <v>45.5</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G53" s="3" t="n">
-        <v>47.4</v>
+        <v>45.5</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K53" s="3" t="n">
-        <v>42.9</v>
+        <v>47.6</v>
       </c>
       <c r="L53" s="4" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="N53" s="3" t="n">
-        <v>57.1</v>
+        <v>47.6</v>
       </c>
       <c r="O53" s="4" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="54">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3819,25 +3819,25 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>58.9</v>
+        <v>50.6</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>73</v>
+        <v>180</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G55" s="3" t="n">
-        <v>42.5</v>
+        <v>45.6</v>
       </c>
       <c r="H55" s="4" t="n">
-        <v>73</v>
+        <v>180</v>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -3846,21 +3846,21 @@
         </is>
       </c>
       <c r="K55" s="3" t="n">
-        <v>51.4</v>
+        <v>58.3</v>
       </c>
       <c r="L55" s="4" t="n">
-        <v>35</v>
+        <v>84</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N55" s="3" t="n">
-        <v>45.7</v>
+        <v>46.4</v>
       </c>
       <c r="O55" s="4" t="n">
-        <v>35</v>
+        <v>84</v>
       </c>
     </row>
     <row r="56">
@@ -4115,7 +4115,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4124,25 +4124,25 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>63.9</v>
+        <v>63.2</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>158</v>
+        <v>87</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G60" s="3" t="n">
-        <v>35.4</v>
+        <v>37.9</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>158</v>
+        <v>87</v>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-D</t>
+          <t>U-U-U-N</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -4151,10 +4151,10 @@
         </is>
       </c>
       <c r="K60" s="3" t="n">
-        <v>65</v>
+        <v>54.1</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
@@ -4162,10 +4162,10 @@
         </is>
       </c>
       <c r="N60" s="3" t="n">
-        <v>41.7</v>
+        <v>40.5</v>
       </c>
       <c r="O60" s="4" t="n">
-        <v>60</v>
+        <v>37</v>
       </c>
     </row>
     <row r="61">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -4368,25 +4368,25 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>64.5</v>
+        <v>51.2</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>31</v>
+        <v>86</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G64" s="3" t="n">
-        <v>45.2</v>
+        <v>44.2</v>
       </c>
       <c r="H64" s="4" t="n">
-        <v>31</v>
+        <v>86</v>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-N</t>
+          <t>U-N-D-D</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -4395,21 +4395,21 @@
         </is>
       </c>
       <c r="K64" s="3" t="n">
-        <v>66.7</v>
+        <v>59.4</v>
       </c>
       <c r="L64" s="4" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N64" s="3" t="n">
-        <v>58.3</v>
+        <v>40.6</v>
       </c>
       <c r="O64" s="4" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
     </row>
     <row r="65">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -4429,10 +4429,10 @@
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>79.5</v>
+        <v>64.2</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>78</v>
+        <v>173</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -4440,14 +4440,14 @@
         </is>
       </c>
       <c r="G65" s="3" t="n">
-        <v>41</v>
+        <v>41.6</v>
       </c>
       <c r="H65" s="4" t="n">
-        <v>78</v>
+        <v>173</v>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -4456,10 +4456,10 @@
         </is>
       </c>
       <c r="K65" s="3" t="n">
-        <v>83.3</v>
+        <v>68.7</v>
       </c>
       <c r="L65" s="4" t="n">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
@@ -4467,10 +4467,10 @@
         </is>
       </c>
       <c r="N65" s="3" t="n">
-        <v>47.2</v>
+        <v>46.3</v>
       </c>
       <c r="O65" s="4" t="n">
-        <v>36</v>
+        <v>67</v>
       </c>
     </row>
     <row r="66">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -4795,48 +4795,48 @@
         </is>
       </c>
       <c r="D71" s="3" t="n">
-        <v>55.4</v>
+        <v>52.9</v>
       </c>
       <c r="E71" s="4" t="n">
-        <v>168</v>
+        <v>70</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G71" s="3" t="n">
-        <v>36.3</v>
+        <v>40</v>
       </c>
       <c r="H71" s="4" t="n">
-        <v>168</v>
+        <v>70</v>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-U</t>
+          <t>N-D-D-N</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="K71" s="3" t="n">
-        <v>51.6</v>
+        <v>50</v>
       </c>
       <c r="L71" s="4" t="n">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N71" s="3" t="n">
-        <v>35.5</v>
+        <v>64.3</v>
       </c>
       <c r="O71" s="4" t="n">
-        <v>31</v>
+        <v>14</v>
       </c>
     </row>
     <row r="72">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -5462,25 +5462,25 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>72</v>
+        <v>73.2</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G82" s="3" t="n">
-        <v>44</v>
+        <v>43.9</v>
       </c>
       <c r="H82" s="4" t="n">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -5489,10 +5489,10 @@
         </is>
       </c>
       <c r="K82" s="3" t="n">
-        <v>66.7</v>
+        <v>81.2</v>
       </c>
       <c r="L82" s="4" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
@@ -5500,10 +5500,10 @@
         </is>
       </c>
       <c r="N82" s="3" t="n">
-        <v>44.4</v>
+        <v>43.8</v>
       </c>
       <c r="O82" s="4" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="83">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -5523,10 +5523,10 @@
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>61.4</v>
+        <v>55.5</v>
       </c>
       <c r="E83" s="4" t="n">
-        <v>70</v>
+        <v>155</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -5534,14 +5534,14 @@
         </is>
       </c>
       <c r="G83" s="3" t="n">
-        <v>38.6</v>
+        <v>42.6</v>
       </c>
       <c r="H83" s="4" t="n">
-        <v>70</v>
+        <v>155</v>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
@@ -5550,10 +5550,10 @@
         </is>
       </c>
       <c r="K83" s="3" t="n">
-        <v>59.4</v>
+        <v>62.5</v>
       </c>
       <c r="L83" s="4" t="n">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
@@ -5561,10 +5561,10 @@
         </is>
       </c>
       <c r="N83" s="3" t="n">
-        <v>40.6</v>
+        <v>48.4</v>
       </c>
       <c r="O83" s="4" t="n">
-        <v>32</v>
+        <v>64</v>
       </c>
     </row>
     <row r="84">
@@ -6002,7 +6002,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>U-N-N</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -6011,25 +6011,25 @@
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>63.5</v>
+        <v>60.5</v>
       </c>
       <c r="E91" s="4" t="n">
-        <v>85</v>
+        <v>43</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G91" s="3" t="n">
-        <v>42.4</v>
+        <v>37.2</v>
       </c>
       <c r="H91" s="4" t="n">
-        <v>85</v>
+        <v>43</v>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-U</t>
+          <t>D-U-N-N</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
@@ -6038,10 +6038,10 @@
         </is>
       </c>
       <c r="K91" s="3" t="n">
-        <v>76.5</v>
+        <v>86.7</v>
       </c>
       <c r="L91" s="4" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
@@ -6049,10 +6049,10 @@
         </is>
       </c>
       <c r="N91" s="3" t="n">
-        <v>52.9</v>
+        <v>46.7</v>
       </c>
       <c r="O91" s="4" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
     </row>
     <row r="92">
@@ -6307,7 +6307,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -6316,25 +6316,25 @@
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>50.6</v>
+        <v>64</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G96" s="3" t="n">
-        <v>44.6</v>
+        <v>46</v>
       </c>
       <c r="H96" s="4" t="n">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-U</t>
+          <t>D-N-U-N</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
@@ -6343,21 +6343,21 @@
         </is>
       </c>
       <c r="K96" s="3" t="n">
-        <v>45.9</v>
+        <v>52.2</v>
       </c>
       <c r="L96" s="4" t="n">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N96" s="3" t="n">
-        <v>56.8</v>
+        <v>56.5</v>
       </c>
       <c r="O96" s="4" t="n">
-        <v>37</v>
+        <v>23</v>
       </c>
     </row>
     <row r="97">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -6560,10 +6560,10 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>69.09999999999999</v>
+        <v>48.1</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -6571,14 +6571,14 @@
         </is>
       </c>
       <c r="G100" s="3" t="n">
-        <v>41.8</v>
+        <v>48.1</v>
       </c>
       <c r="H100" s="4" t="n">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-N-U-D</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
@@ -6587,10 +6587,10 @@
         </is>
       </c>
       <c r="K100" s="3" t="n">
-        <v>76.2</v>
+        <v>47.8</v>
       </c>
       <c r="L100" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
@@ -6598,10 +6598,10 @@
         </is>
       </c>
       <c r="N100" s="3" t="n">
-        <v>47.6</v>
+        <v>52.2</v>
       </c>
       <c r="O100" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="101">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -6621,25 +6621,25 @@
         </is>
       </c>
       <c r="D101" s="3" t="n">
-        <v>80</v>
+        <v>58.4</v>
       </c>
       <c r="E101" s="4" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G101" s="3" t="n">
-        <v>40</v>
+        <v>37.7</v>
       </c>
       <c r="H101" s="4" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>N-N-U-N</t>
+          <t>N-N-U-D</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
@@ -6648,10 +6648,10 @@
         </is>
       </c>
       <c r="K101" s="3" t="n">
-        <v>88</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L101" s="4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
@@ -6659,10 +6659,10 @@
         </is>
       </c>
       <c r="N101" s="3" t="n">
-        <v>40</v>
+        <v>40.7</v>
       </c>
       <c r="O101" s="4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="102">
@@ -7102,46 +7102,46 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>75</v>
+        <v>58.3</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I3" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-N</t>
+          <t>D-U-N-D</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M3" s="3" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
@@ -7149,10 +7149,10 @@
         </is>
       </c>
       <c r="P3" s="3" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="Q3" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -7244,7 +7244,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -7253,48 +7253,48 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I5" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-U</t>
+          <t>D-N-D-N</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M5" s="3" t="n">
-        <v>44.4</v>
+        <v>100</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P5" s="3" t="n">
-        <v>55.6</v>
+        <v>100</v>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -7324,48 +7324,48 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>80</v>
+        <v>57.1</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I6" s="3" t="n">
-        <v>40</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-N</t>
+          <t>D-U-N-D</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M6" s="3" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="P6" s="3" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -7879,7 +7879,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -7888,25 +7888,25 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>77.3</v>
+        <v>53.3</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I14" s="3" t="n">
-        <v>45.5</v>
+        <v>40</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-U</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -7915,10 +7915,10 @@
         </is>
       </c>
       <c r="M14" s="3" t="n">
-        <v>80</v>
+        <v>46.2</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -7926,10 +7926,10 @@
         </is>
       </c>
       <c r="P14" s="3" t="n">
-        <v>50</v>
+        <v>46.2</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
@@ -8021,57 +8021,57 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>57.1</v>
+        <v>66.7</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="I16" s="3" t="n">
-        <v>57.1</v>
+        <v>33.3</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>N-N-U-U</t>
+          <t>N-N-U-N</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M16" s="3" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P16" s="3" t="n">
         <v>50</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -8234,7 +8234,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -8243,25 +8243,25 @@
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>68.8</v>
+        <v>75</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I19" s="3" t="n">
-        <v>56.2</v>
+        <v>50</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-U</t>
+          <t>U-D-U-N</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -8270,10 +8270,10 @@
         </is>
       </c>
       <c r="M19" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -8281,10 +8281,10 @@
         </is>
       </c>
       <c r="P19" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -8518,57 +8518,57 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>D-N-D</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="G23" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="J23" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>U-D-N-N</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="N23" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="n">
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="n">
         <v>66.7</v>
       </c>
-      <c r="J23" s="4" t="n">
+      <c r="Q23" s="4" t="n">
         <v>3</v>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>U-D-N-D</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M23" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="N23" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P23" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q23" s="4" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -8740,48 +8740,48 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>70</v>
+        <v>58.3</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I26" s="3" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="J26" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>D-U-U-U</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="N26" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>D/U</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="J26" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>D-U-U-N</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="N26" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P26" s="3" t="n">
-        <v>66.7</v>
-      </c>
       <c r="Q26" s="4" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="27">
@@ -9228,7 +9228,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -9237,37 +9237,37 @@
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>69.7</v>
+        <v>76.2</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I33" s="3" t="n">
-        <v>48.5</v>
+        <v>61.9</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M33" s="3" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -9275,10 +9275,10 @@
         </is>
       </c>
       <c r="P33" s="3" t="n">
-        <v>62.5</v>
+        <v>50</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34">
@@ -9299,7 +9299,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -9308,25 +9308,25 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>69.2</v>
+        <v>46.4</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I34" s="3" t="n">
-        <v>53.8</v>
+        <v>53.6</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -9335,21 +9335,21 @@
         </is>
       </c>
       <c r="M34" s="3" t="n">
-        <v>60</v>
+        <v>58.8</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P34" s="3" t="n">
-        <v>60</v>
+        <v>58.8</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="35">
@@ -9370,7 +9370,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -9379,48 +9379,48 @@
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I35" s="3" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-U</t>
+          <t>N-D-D-N</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M35" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="N35" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="N35" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P35" s="3" t="n">
-        <v>66.7</v>
-      </c>
       <c r="Q35" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>U-N-N</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -9592,10 +9592,10 @@
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>62.5</v>
+        <v>60</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -9603,14 +9603,14 @@
         </is>
       </c>
       <c r="I38" s="3" t="n">
-        <v>45.8</v>
+        <v>60</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>N-U-N-U</t>
+          <t>N-U-N-N</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -9619,21 +9619,21 @@
         </is>
       </c>
       <c r="M38" s="3" t="n">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P38" s="3" t="n">
-        <v>57.1</v>
+        <v>100</v>
       </c>
       <c r="Q38" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -9654,7 +9654,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -9663,48 +9663,48 @@
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>81.2</v>
+        <v>57.1</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I39" s="3" t="n">
-        <v>37.5</v>
+        <v>42.9</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-U</t>
+          <t>D-N-U-N</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="M39" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="P39" s="3" t="n">
-        <v>44.4</v>
+        <v>50</v>
       </c>
       <c r="Q39" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -9867,34 +9867,34 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>D-N-D</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F42" s="3" t="n">
         <v>100</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="I42" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-D</t>
+          <t>D-D-N-N</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -10218,7 +10218,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -10227,45 +10227,45 @@
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>100</v>
+        <v>73.3</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I47" s="3" t="n">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="J47" s="4" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-N-U-D</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M47" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="N47" s="4" t="n">
         <v>3</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P47" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="Q47" s="4" t="n">
         <v>3</v>
@@ -10569,7 +10569,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -10578,25 +10578,25 @@
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>87.5</v>
+        <v>54.3</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I52" s="3" t="n">
-        <v>37.5</v>
+        <v>40</v>
       </c>
       <c r="J52" s="4" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
@@ -10605,10 +10605,10 @@
         </is>
       </c>
       <c r="M52" s="3" t="n">
-        <v>87.5</v>
+        <v>75</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
@@ -10616,10 +10616,10 @@
         </is>
       </c>
       <c r="P52" s="3" t="n">
-        <v>62.5</v>
+        <v>50</v>
       </c>
       <c r="Q52" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="53">
@@ -10640,57 +10640,57 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>40</v>
+        <v>55.6</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I53" s="3" t="n">
-        <v>40</v>
+        <v>44.4</v>
       </c>
       <c r="J53" s="4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M53" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="N53" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P53" s="3" t="n">
         <v>50</v>
       </c>
       <c r="Q53" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54">
@@ -10782,7 +10782,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -10791,25 +10791,25 @@
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>40</v>
+        <v>45.9</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I55" s="3" t="n">
-        <v>50</v>
+        <v>59.5</v>
       </c>
       <c r="J55" s="4" t="n">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
@@ -10818,21 +10818,21 @@
         </is>
       </c>
       <c r="M55" s="3" t="n">
-        <v>50</v>
+        <v>58.8</v>
       </c>
       <c r="N55" s="4" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P55" s="3" t="n">
-        <v>50</v>
+        <v>58.8</v>
       </c>
       <c r="Q55" s="4" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
     </row>
     <row r="56">
@@ -11137,7 +11137,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -11146,48 +11146,48 @@
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>78.59999999999999</v>
+        <v>62.5</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I60" s="3" t="n">
-        <v>39.3</v>
+        <v>37.5</v>
       </c>
       <c r="J60" s="4" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-D</t>
+          <t>U-U-U-N</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M60" s="3" t="n">
-        <v>87.5</v>
+        <v>50</v>
       </c>
       <c r="N60" s="4" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="P60" s="3" t="n">
-        <v>37.5</v>
+        <v>33.3</v>
       </c>
       <c r="Q60" s="4" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="61">
@@ -11421,57 +11421,57 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>60</v>
+        <v>54.5</v>
       </c>
       <c r="G64" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="J64" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>U-N-D-D</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="N64" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>D/U</t>
-        </is>
-      </c>
-      <c r="I64" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="J64" s="4" t="n">
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P64" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q64" s="4" t="n">
         <v>5</v>
-      </c>
-      <c r="K64" s="2" t="inlineStr">
-        <is>
-          <t>U-N-D-N</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="inlineStr">
-        <is>
-          <t>N/U</t>
-        </is>
-      </c>
-      <c r="M64" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="N64" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="O64" s="2" t="inlineStr">
-        <is>
-          <t>D/N</t>
-        </is>
-      </c>
-      <c r="P64" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q64" s="4" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -11492,7 +11492,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -11501,25 +11501,25 @@
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>77.8</v>
+        <v>72.7</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I65" s="3" t="n">
-        <v>44.4</v>
+        <v>45.5</v>
       </c>
       <c r="J65" s="4" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
@@ -11528,21 +11528,21 @@
         </is>
       </c>
       <c r="M65" s="3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="N65" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P65" s="3" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="Q65" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66">
@@ -11918,7 +11918,7 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -11927,25 +11927,25 @@
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>54.8</v>
+        <v>53.3</v>
       </c>
       <c r="G71" s="4" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I71" s="3" t="n">
-        <v>38.1</v>
+        <v>40</v>
       </c>
       <c r="J71" s="4" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-U</t>
+          <t>N-D-D-N</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
@@ -11954,21 +11954,21 @@
         </is>
       </c>
       <c r="M71" s="3" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="N71" s="4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P71" s="3" t="n">
         <v>50</v>
       </c>
       <c r="Q71" s="4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -12691,7 +12691,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -12700,25 +12700,25 @@
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>75</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I82" s="3" t="n">
-        <v>75</v>
+        <v>44.4</v>
       </c>
       <c r="J82" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
@@ -12727,21 +12727,21 @@
         </is>
       </c>
       <c r="M82" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="N82" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P82" s="3" t="n">
-        <v>66.7</v>
+        <v>42.9</v>
       </c>
       <c r="Q82" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="83">
@@ -12762,7 +12762,7 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -12774,7 +12774,7 @@
         <v>50</v>
       </c>
       <c r="G83" s="4" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
@@ -12782,26 +12782,26 @@
         </is>
       </c>
       <c r="I83" s="3" t="n">
-        <v>42.9</v>
+        <v>41.2</v>
       </c>
       <c r="J83" s="4" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M83" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>54.5</v>
       </c>
       <c r="N83" s="4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
@@ -12809,10 +12809,10 @@
         </is>
       </c>
       <c r="P83" s="3" t="n">
-        <v>57.1</v>
+        <v>45.5</v>
       </c>
       <c r="Q83" s="4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="84">
@@ -13330,7 +13330,7 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>U-N-N</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -13339,10 +13339,10 @@
         </is>
       </c>
       <c r="F91" s="3" t="n">
-        <v>76.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="G91" s="4" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
@@ -13350,14 +13350,14 @@
         </is>
       </c>
       <c r="I91" s="3" t="n">
-        <v>42.3</v>
+        <v>57.1</v>
       </c>
       <c r="J91" s="4" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-U</t>
+          <t>D-U-N-N</t>
         </is>
       </c>
       <c r="L91" s="2" t="inlineStr">
@@ -13366,21 +13366,21 @@
         </is>
       </c>
       <c r="M91" s="3" t="n">
-        <v>81.8</v>
+        <v>100</v>
       </c>
       <c r="N91" s="4" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P91" s="3" t="n">
-        <v>54.5</v>
+        <v>50</v>
       </c>
       <c r="Q91" s="4" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
@@ -13685,7 +13685,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -13694,25 +13694,25 @@
         </is>
       </c>
       <c r="F96" s="3" t="n">
-        <v>61.5</v>
+        <v>70</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I96" s="3" t="n">
-        <v>53.8</v>
+        <v>40</v>
       </c>
       <c r="J96" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-U</t>
+          <t>D-N-U-N</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
@@ -13721,21 +13721,21 @@
         </is>
       </c>
       <c r="M96" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="N96" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P96" s="3" t="n">
-        <v>62.5</v>
+        <v>60</v>
       </c>
       <c r="Q96" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97">
@@ -13969,7 +13969,7 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -13978,48 +13978,48 @@
         </is>
       </c>
       <c r="F100" s="3" t="n">
-        <v>72.7</v>
+        <v>70</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="I100" s="3" t="n">
-        <v>45.5</v>
+        <v>40</v>
       </c>
       <c r="J100" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-N-U-D</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="M100" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="N100" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="P100" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="Q100" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="101">
@@ -14040,7 +14040,7 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -14049,25 +14049,25 @@
         </is>
       </c>
       <c r="F101" s="3" t="n">
-        <v>92.90000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G101" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I101" s="3" t="n">
-        <v>78.59999999999999</v>
+        <v>54.5</v>
       </c>
       <c r="J101" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>N-N-U-N</t>
+          <t>N-N-U-D</t>
         </is>
       </c>
       <c r="L101" s="2" t="inlineStr">
@@ -14087,7 +14087,7 @@
         </is>
       </c>
       <c r="P101" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="Q101" s="4" t="n">
         <v>3</v>

--- a/BIS_tr.xlsx
+++ b/BIS_tr.xlsx
@@ -699,7 +699,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -708,25 +708,25 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>61.4</v>
+        <v>55.6</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G4" s="3" t="n">
-        <v>45.7</v>
+        <v>41.8</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-U</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -735,21 +735,21 @@
         </is>
       </c>
       <c r="K4" s="3" t="n">
-        <v>66.7</v>
+        <v>44.8</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N4" s="3" t="n">
-        <v>48.5</v>
+        <v>37.9</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1501,10 +1501,10 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>57.5</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>127</v>
+        <v>82</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1512,14 +1512,14 @@
         </is>
       </c>
       <c r="G17" s="3" t="n">
-        <v>41.7</v>
+        <v>43.9</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>127</v>
+        <v>82</v>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-U</t>
+          <t>N-D-D-N</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1528,21 +1528,21 @@
         </is>
       </c>
       <c r="K17" s="3" t="n">
-        <v>65</v>
+        <v>52.9</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N17" s="3" t="n">
-        <v>40</v>
+        <v>47.1</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1623,25 +1623,25 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>60.6</v>
+        <v>55.6</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>48.5</v>
+        <v>45.5</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1650,10 +1650,10 @@
         </is>
       </c>
       <c r="K19" s="3" t="n">
-        <v>56.2</v>
+        <v>53.1</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
@@ -1661,10 +1661,10 @@
         </is>
       </c>
       <c r="N19" s="3" t="n">
-        <v>56.2</v>
+        <v>50</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1684,25 +1684,25 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>80.40000000000001</v>
+        <v>70.8</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>51</v>
+        <v>96</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>41.2</v>
+        <v>41.7</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>51</v>
+        <v>96</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-N</t>
+          <t>D-U-N-D</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="K20" s="3" t="n">
-        <v>86.40000000000001</v>
+        <v>77.8</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N20" s="3" t="n">
-        <v>45.5</v>
+        <v>38.9</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1745,25 +1745,25 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="E21" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="E21" s="4" t="n">
-        <v>77</v>
-      </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G21" s="3" t="n">
-        <v>49.4</v>
+        <v>45.9</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>N-D-N-U</t>
+          <t>N-D-N-D</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1772,21 +1772,21 @@
         </is>
       </c>
       <c r="K21" s="3" t="n">
-        <v>63.6</v>
+        <v>86.7</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N21" s="3" t="n">
-        <v>63.6</v>
+        <v>53.3</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
@@ -1858,57 +1858,57 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>58.3</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G23" s="3" t="n">
-        <v>41.7</v>
+        <v>46.9</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-N</t>
+          <t>U-D-N-D</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K23" s="3" t="n">
-        <v>50</v>
+        <v>77.8</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N23" s="3" t="n">
-        <v>50</v>
+        <v>44.4</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1928,48 +1928,48 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>77.8</v>
+        <v>62.5</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="G24" s="3" t="n">
-        <v>55.6</v>
+        <v>41.7</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-U</t>
+          <t>D-D-N-N</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="K24" s="3" t="n">
-        <v>100</v>
+        <v>45.5</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N24" s="3" t="n">
-        <v>85.7</v>
+        <v>45.5</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25">
@@ -2407,7 +2407,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2416,25 +2416,25 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>74.09999999999999</v>
+        <v>79.2</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G32" s="3" t="n">
-        <v>44.4</v>
+        <v>47.2</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>U-U-N-U</t>
+          <t>U-U-N-D</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -2443,21 +2443,21 @@
         </is>
       </c>
       <c r="K32" s="3" t="n">
-        <v>72.2</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N32" s="3" t="n">
-        <v>50</v>
+        <v>55.9</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
     </row>
     <row r="33">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2599,48 +2599,48 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>55.6</v>
+        <v>50.7</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>27</v>
+        <v>75</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v>48.1</v>
+        <v>45.3</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>27</v>
+        <v>75</v>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-N</t>
+          <t>N-D-D-U</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K35" s="3" t="n">
-        <v>50</v>
+        <v>87.5</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N35" s="3" t="n">
         <v>50</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-U</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2782,10 +2782,10 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>62.8</v>
+        <v>63</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>43</v>
+        <v>81</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2793,14 +2793,14 @@
         </is>
       </c>
       <c r="G38" s="3" t="n">
-        <v>39.5</v>
+        <v>45.7</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>43</v>
+        <v>81</v>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>N-U-N-N</t>
+          <t>N-U-N-U</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -2809,21 +2809,21 @@
         </is>
       </c>
       <c r="K38" s="3" t="n">
-        <v>57.1</v>
+        <v>52.2</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N38" s="3" t="n">
-        <v>42.9</v>
+        <v>43.5</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="39">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2843,25 +2843,25 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>57.5</v>
+        <v>60.4</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>40</v>
+        <v>91</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G39" s="3" t="n">
-        <v>37.5</v>
+        <v>39.6</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>40</v>
+        <v>91</v>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-N-U-D</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -2870,21 +2870,21 @@
         </is>
       </c>
       <c r="K39" s="3" t="n">
-        <v>45.5</v>
+        <v>72.2</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N39" s="3" t="n">
-        <v>45.5</v>
+        <v>36.1</v>
       </c>
       <c r="O39" s="4" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
     </row>
     <row r="40">
@@ -3017,57 +3017,57 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>75</v>
+        <v>81.8</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G42" s="3" t="n">
-        <v>50</v>
+        <v>45.5</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-N</t>
+          <t>D-D-N-D</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="L42" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
           <t>N/U</t>
         </is>
       </c>
-      <c r="K42" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="L42" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>D/N</t>
-        </is>
-      </c>
       <c r="N42" s="3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="O42" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3270,25 +3270,25 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>51.6</v>
+        <v>60</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>153</v>
+        <v>65</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G46" s="3" t="n">
-        <v>41.8</v>
+        <v>47.7</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>153</v>
+        <v>65</v>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-U</t>
+          <t>U-D-U-N</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -3297,21 +3297,21 @@
         </is>
       </c>
       <c r="K46" s="3" t="n">
-        <v>52.5</v>
+        <v>64.3</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>61</v>
+        <v>28</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N46" s="3" t="n">
-        <v>36.1</v>
+        <v>50</v>
       </c>
       <c r="O46" s="4" t="n">
-        <v>61</v>
+        <v>28</v>
       </c>
     </row>
     <row r="47">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -3453,25 +3453,25 @@
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>63.8</v>
+        <v>61</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G49" s="3" t="n">
-        <v>42.6</v>
+        <v>40.3</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-N</t>
+          <t>D-U-N-D</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -3480,21 +3480,21 @@
         </is>
       </c>
       <c r="K49" s="3" t="n">
-        <v>68.2</v>
+        <v>55.6</v>
       </c>
       <c r="L49" s="4" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N49" s="3" t="n">
-        <v>40.9</v>
+        <v>40.7</v>
       </c>
       <c r="O49" s="4" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="50">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -3514,10 +3514,10 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>68.8</v>
+        <v>74</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>93</v>
+        <v>50</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3525,14 +3525,14 @@
         </is>
       </c>
       <c r="G50" s="3" t="n">
-        <v>44.1</v>
+        <v>46</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>93</v>
+        <v>50</v>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-U</t>
+          <t>D-N-U-N</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -3541,21 +3541,21 @@
         </is>
       </c>
       <c r="K50" s="3" t="n">
-        <v>76.5</v>
+        <v>69.2</v>
       </c>
       <c r="L50" s="4" t="n">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N50" s="3" t="n">
-        <v>38.2</v>
+        <v>69.2</v>
       </c>
       <c r="O50" s="4" t="n">
-        <v>34</v>
+        <v>13</v>
       </c>
     </row>
     <row r="51">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>N-N-D</t>
+          <t>N-N-N</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -3575,25 +3575,25 @@
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G51" s="3" t="n">
-        <v>44.4</v>
+        <v>50</v>
       </c>
       <c r="H51" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>U-N-N-D</t>
+          <t>U-N-N-N</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -3605,7 +3605,7 @@
         <v>100</v>
       </c>
       <c r="L51" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="N51" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="O51" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3758,10 +3758,10 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>53.1</v>
+        <v>83.3</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3769,37 +3769,37 @@
         </is>
       </c>
       <c r="G54" s="3" t="n">
-        <v>53.1</v>
+        <v>50</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-U</t>
+          <t>D-N-D-N</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K54" s="3" t="n">
-        <v>52.9</v>
+        <v>100</v>
       </c>
       <c r="L54" s="4" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N54" s="3" t="n">
-        <v>52.9</v>
+        <v>57.1</v>
       </c>
       <c r="O54" s="4" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="55">
@@ -4054,7 +4054,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4063,25 +4063,25 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>67.90000000000001</v>
+        <v>55.2</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>140</v>
+        <v>58</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G59" s="3" t="n">
-        <v>40</v>
+        <v>44.8</v>
       </c>
       <c r="H59" s="4" t="n">
-        <v>140</v>
+        <v>58</v>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-U</t>
+          <t>N-D-D-N</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -4090,21 +4090,21 @@
         </is>
       </c>
       <c r="K59" s="3" t="n">
-        <v>48.1</v>
+        <v>57.1</v>
       </c>
       <c r="L59" s="4" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N59" s="3" t="n">
-        <v>40.7</v>
+        <v>50</v>
       </c>
       <c r="O59" s="4" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
     </row>
     <row r="60">
@@ -4115,7 +4115,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4124,25 +4124,25 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>63.2</v>
+        <v>63.9</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>87</v>
+        <v>158</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G60" s="3" t="n">
-        <v>37.9</v>
+        <v>35.4</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>87</v>
+        <v>158</v>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -4151,10 +4151,10 @@
         </is>
       </c>
       <c r="K60" s="3" t="n">
-        <v>54.1</v>
+        <v>65</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
@@ -4162,10 +4162,10 @@
         </is>
       </c>
       <c r="N60" s="3" t="n">
-        <v>40.5</v>
+        <v>41.7</v>
       </c>
       <c r="O60" s="4" t="n">
-        <v>37</v>
+        <v>60</v>
       </c>
     </row>
     <row r="61">
@@ -4176,7 +4176,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4185,10 +4185,10 @@
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>56.3</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>28</v>
+        <v>119</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -4196,14 +4196,14 @@
         </is>
       </c>
       <c r="G61" s="3" t="n">
-        <v>57.1</v>
+        <v>44.5</v>
       </c>
       <c r="H61" s="4" t="n">
-        <v>28</v>
+        <v>119</v>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -4212,21 +4212,21 @@
         </is>
       </c>
       <c r="K61" s="3" t="n">
-        <v>78.59999999999999</v>
+        <v>51.9</v>
       </c>
       <c r="L61" s="4" t="n">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N61" s="3" t="n">
-        <v>50</v>
+        <v>48.1</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>14</v>
+        <v>52</v>
       </c>
     </row>
     <row r="62">
@@ -4542,57 +4542,57 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>76.90000000000001</v>
+        <v>37.5</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="H67" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>U-D-U-N</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="L67" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
           <t>D/U</t>
-        </is>
-      </c>
-      <c r="G67" s="3" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="H67" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>U-D-U-U</t>
-        </is>
-      </c>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="K67" s="3" t="n">
-        <v>83.3</v>
-      </c>
-      <c r="L67" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="M67" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
         </is>
       </c>
       <c r="N67" s="3" t="n">
         <v>50</v>
       </c>
       <c r="O67" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -4673,10 +4673,10 @@
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>57.7</v>
+        <v>53.4</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4684,14 +4684,14 @@
         </is>
       </c>
       <c r="G69" s="3" t="n">
-        <v>52.1</v>
+        <v>60.3</v>
       </c>
       <c r="H69" s="4" t="n">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-D</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -4700,10 +4700,10 @@
         </is>
       </c>
       <c r="K69" s="3" t="n">
-        <v>52.8</v>
+        <v>54.5</v>
       </c>
       <c r="L69" s="4" t="n">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
@@ -4711,10 +4711,10 @@
         </is>
       </c>
       <c r="N69" s="3" t="n">
-        <v>47.2</v>
+        <v>59.1</v>
       </c>
       <c r="O69" s="4" t="n">
-        <v>36</v>
+        <v>22</v>
       </c>
     </row>
     <row r="70">
@@ -5030,7 +5030,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5039,44 +5039,48 @@
         </is>
       </c>
       <c r="D75" s="3" t="n">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="E75" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="H75" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>N-N-U-D</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K75" s="3" t="n">
         <v>75</v>
       </c>
-      <c r="E75" s="4" t="n">
+      <c r="L75" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G75" s="3" t="n">
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>D/U</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="H75" s="4" t="n">
+      <c r="O75" s="4" t="n">
         <v>4</v>
-      </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>N-N-U-N</t>
-        </is>
-      </c>
-      <c r="J75" s="2" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="K75" s="3" t="inlineStr"/>
-      <c r="L75" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M75" s="2" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N75" s="3" t="inlineStr"/>
-      <c r="O75" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -5453,7 +5457,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -5462,25 +5466,25 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>73.2</v>
+        <v>72</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G82" s="3" t="n">
-        <v>43.9</v>
+        <v>44</v>
       </c>
       <c r="H82" s="4" t="n">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-D</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -5489,10 +5493,10 @@
         </is>
       </c>
       <c r="K82" s="3" t="n">
-        <v>81.2</v>
+        <v>66.7</v>
       </c>
       <c r="L82" s="4" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
@@ -5500,10 +5504,10 @@
         </is>
       </c>
       <c r="N82" s="3" t="n">
-        <v>43.8</v>
+        <v>44.4</v>
       </c>
       <c r="O82" s="4" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="83">
@@ -5697,7 +5701,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -5706,25 +5710,25 @@
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>56.4</v>
+        <v>57.4</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>163</v>
+        <v>68</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G86" s="3" t="n">
-        <v>47.2</v>
+        <v>44.1</v>
       </c>
       <c r="H86" s="4" t="n">
-        <v>163</v>
+        <v>68</v>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -5733,10 +5737,10 @@
         </is>
       </c>
       <c r="K86" s="3" t="n">
-        <v>61.5</v>
+        <v>54.5</v>
       </c>
       <c r="L86" s="4" t="n">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
@@ -5744,10 +5748,10 @@
         </is>
       </c>
       <c r="N86" s="3" t="n">
-        <v>53.8</v>
+        <v>54.5</v>
       </c>
       <c r="O86" s="4" t="n">
-        <v>65</v>
+        <v>22</v>
       </c>
     </row>
     <row r="87">
@@ -6002,7 +6006,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -6011,25 +6015,25 @@
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>60.5</v>
+        <v>51.3</v>
       </c>
       <c r="E91" s="4" t="n">
-        <v>43</v>
+        <v>78</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G91" s="3" t="n">
-        <v>37.2</v>
+        <v>41</v>
       </c>
       <c r="H91" s="4" t="n">
-        <v>43</v>
+        <v>78</v>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-N</t>
+          <t>D-U-N-D</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
@@ -6038,21 +6042,21 @@
         </is>
       </c>
       <c r="K91" s="3" t="n">
-        <v>86.7</v>
+        <v>40.5</v>
       </c>
       <c r="L91" s="4" t="n">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N91" s="3" t="n">
-        <v>46.7</v>
+        <v>43.2</v>
       </c>
       <c r="O91" s="4" t="n">
-        <v>15</v>
+        <v>37</v>
       </c>
     </row>
     <row r="92">
@@ -6063,7 +6067,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -6072,10 +6076,10 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>62.9</v>
+        <v>55.6</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>70</v>
+        <v>180</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -6083,14 +6087,14 @@
         </is>
       </c>
       <c r="G92" s="3" t="n">
-        <v>41.4</v>
+        <v>45.6</v>
       </c>
       <c r="H92" s="4" t="n">
-        <v>70</v>
+        <v>180</v>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
@@ -6099,10 +6103,10 @@
         </is>
       </c>
       <c r="K92" s="3" t="n">
-        <v>54.5</v>
+        <v>52.5</v>
       </c>
       <c r="L92" s="4" t="n">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
@@ -6110,10 +6114,10 @@
         </is>
       </c>
       <c r="N92" s="3" t="n">
-        <v>36.4</v>
+        <v>45.9</v>
       </c>
       <c r="O92" s="4" t="n">
-        <v>22</v>
+        <v>61</v>
       </c>
     </row>
     <row r="93">
@@ -6490,7 +6494,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -6499,10 +6503,10 @@
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>56.3</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="E99" s="4" t="n">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -6510,14 +6514,14 @@
         </is>
       </c>
       <c r="G99" s="3" t="n">
-        <v>38</v>
+        <v>40.4</v>
       </c>
       <c r="H99" s="4" t="n">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-U</t>
+          <t>D-D-N-N</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
@@ -6526,21 +6530,21 @@
         </is>
       </c>
       <c r="K99" s="3" t="n">
-        <v>54.8</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="L99" s="4" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N99" s="3" t="n">
-        <v>38.7</v>
+        <v>42.1</v>
       </c>
       <c r="O99" s="4" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
     </row>
     <row r="100">
@@ -6734,7 +6738,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -6743,10 +6747,10 @@
         </is>
       </c>
       <c r="D103" s="3" t="n">
-        <v>70.2</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="E103" s="4" t="n">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -6754,14 +6758,14 @@
         </is>
       </c>
       <c r="G103" s="3" t="n">
-        <v>38.6</v>
+        <v>42</v>
       </c>
       <c r="H103" s="4" t="n">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-N</t>
+          <t>D-U-N-D</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
@@ -6770,10 +6774,10 @@
         </is>
       </c>
       <c r="K103" s="3" t="n">
-        <v>75</v>
+        <v>62.1</v>
       </c>
       <c r="L103" s="4" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
@@ -6781,10 +6785,10 @@
         </is>
       </c>
       <c r="N103" s="3" t="n">
-        <v>41.7</v>
+        <v>48.3</v>
       </c>
       <c r="O103" s="4" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="104">
@@ -6795,7 +6799,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-N-N</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -6804,25 +6808,25 @@
         </is>
       </c>
       <c r="D104" s="3" t="n">
-        <v>66.7</v>
+        <v>61.9</v>
       </c>
       <c r="E104" s="4" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G104" s="3" t="n">
-        <v>38.5</v>
+        <v>35.7</v>
       </c>
       <c r="H104" s="4" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>N-N-N-U</t>
+          <t>N-N-N-N</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
@@ -6831,10 +6835,10 @@
         </is>
       </c>
       <c r="K104" s="3" t="n">
-        <v>69.2</v>
+        <v>57.1</v>
       </c>
       <c r="L104" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
@@ -6842,10 +6846,10 @@
         </is>
       </c>
       <c r="N104" s="3" t="n">
-        <v>46.2</v>
+        <v>50</v>
       </c>
       <c r="O104" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -7173,7 +7177,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -7182,10 +7186,10 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>76</v>
+        <v>48.4</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -7193,14 +7197,14 @@
         </is>
       </c>
       <c r="I4" s="3" t="n">
-        <v>56</v>
+        <v>48.4</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-U</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -7209,10 +7213,10 @@
         </is>
       </c>
       <c r="M4" s="3" t="n">
-        <v>87.5</v>
+        <v>50</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
@@ -7220,10 +7224,10 @@
         </is>
       </c>
       <c r="P4" s="3" t="n">
-        <v>75</v>
+        <v>57.1</v>
       </c>
       <c r="Q4" s="4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
@@ -8092,7 +8096,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -8101,48 +8105,48 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>74.3</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="I17" s="3" t="n">
-        <v>45.7</v>
+        <v>41.2</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-U</t>
+          <t>N-D-D-N</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M17" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P17" s="3" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -8234,7 +8238,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -8243,25 +8247,25 @@
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>75</v>
+        <v>53.8</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I19" s="3" t="n">
-        <v>50</v>
+        <v>61.5</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -8270,21 +8274,21 @@
         </is>
       </c>
       <c r="M19" s="3" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P19" s="3" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -8305,7 +8309,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -8314,10 +8318,10 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -8325,14 +8329,14 @@
         </is>
       </c>
       <c r="I20" s="3" t="n">
-        <v>42.9</v>
+        <v>46.2</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-N</t>
+          <t>D-U-N-D</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -8341,10 +8345,10 @@
         </is>
       </c>
       <c r="M20" s="3" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -8352,10 +8356,10 @@
         </is>
       </c>
       <c r="P20" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -8376,7 +8380,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -8385,10 +8389,10 @@
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>53.8</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -8396,14 +8400,14 @@
         </is>
       </c>
       <c r="I21" s="3" t="n">
-        <v>42.9</v>
+        <v>53.8</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>N-D-N-U</t>
+          <t>N-D-N-D</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -8412,21 +8416,21 @@
         </is>
       </c>
       <c r="M21" s="3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="P21" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -8518,19 +8522,19 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -8538,37 +8542,37 @@
         </is>
       </c>
       <c r="I23" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-N</t>
+          <t>U-D-N-D</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M23" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P23" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -8589,7 +8593,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -8598,48 +8602,48 @@
         </is>
       </c>
       <c r="F24" s="3" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="J24" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>D-D-N-N</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="n">
         <v>66.7</v>
       </c>
-      <c r="G24" s="4" t="n">
+      <c r="N24" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="n">
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="n">
         <v>66.7</v>
       </c>
-      <c r="J24" s="4" t="n">
+      <c r="Q24" s="4" t="n">
         <v>3</v>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>D-D-N-U</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="N24" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P24" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q24" s="4" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -9157,7 +9161,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -9166,25 +9170,25 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>77.8</v>
+        <v>75</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I32" s="3" t="n">
-        <v>44.4</v>
+        <v>66.7</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>U-U-N-U</t>
+          <t>U-U-N-D</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -9196,18 +9200,18 @@
         <v>100</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P32" s="3" t="n">
-        <v>50</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33">
@@ -9370,7 +9374,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -9379,48 +9383,48 @@
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I35" s="3" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-N</t>
+          <t>N-D-D-U</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M35" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P35" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -9583,7 +9587,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-U</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -9592,10 +9596,10 @@
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -9603,14 +9607,14 @@
         </is>
       </c>
       <c r="I38" s="3" t="n">
-        <v>60</v>
+        <v>45.8</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>N-U-N-N</t>
+          <t>N-U-N-U</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -9619,21 +9623,21 @@
         </is>
       </c>
       <c r="M38" s="3" t="n">
-        <v>50</v>
+        <v>42.9</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P38" s="3" t="n">
-        <v>100</v>
+        <v>57.1</v>
       </c>
       <c r="Q38" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39">
@@ -9654,7 +9658,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -9663,48 +9667,48 @@
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>57.1</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="I39" s="3" t="n">
-        <v>42.9</v>
+        <v>33.3</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-N-U-D</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M39" s="3" t="n">
-        <v>50</v>
+        <v>83.3</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="P39" s="3" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="Q39" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40">
@@ -9867,34 +9871,34 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F42" s="3" t="n">
         <v>100</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I42" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-N</t>
+          <t>D-D-N-D</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -10147,7 +10151,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -10156,25 +10160,25 @@
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>51.7</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I46" s="3" t="n">
-        <v>51.7</v>
+        <v>53.8</v>
       </c>
       <c r="J46" s="4" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-U</t>
+          <t>U-D-U-N</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -10183,21 +10187,21 @@
         </is>
       </c>
       <c r="M46" s="3" t="n">
-        <v>57.1</v>
+        <v>75</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P46" s="3" t="n">
-        <v>35.7</v>
+        <v>62.5</v>
       </c>
       <c r="Q46" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="47">
@@ -10360,7 +10364,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -10369,48 +10373,48 @@
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>58.3</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I49" s="3" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="J49" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>D-U-N-D</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="n">
         <v>66.7</v>
       </c>
-      <c r="J49" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>D-U-N-N</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M49" s="3" t="n">
-        <v>75</v>
-      </c>
       <c r="N49" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P49" s="3" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="Q49" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50">
@@ -10431,7 +10435,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -10440,48 +10444,48 @@
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>75</v>
+        <v>62.5</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I50" s="3" t="n">
-        <v>50</v>
+        <v>62.5</v>
       </c>
       <c r="J50" s="4" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-U</t>
+          <t>D-N-U-N</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M50" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P50" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q50" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -10502,7 +10506,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>N-N-D</t>
+          <t>N-N-N</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -10514,41 +10518,45 @@
         <v>100</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I51" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="J51" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>U-N-N-N</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="J51" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>U-N-N-D</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M51" s="3" t="inlineStr"/>
       <c r="N51" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P51" s="3" t="inlineStr"/>
+          <t>N/U</t>
+        </is>
+      </c>
+      <c r="P51" s="3" t="n">
+        <v>50</v>
+      </c>
       <c r="Q51" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -10711,7 +10719,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -10720,10 +10728,10 @@
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -10731,14 +10739,14 @@
         </is>
       </c>
       <c r="I54" s="3" t="n">
-        <v>57.1</v>
+        <v>100</v>
       </c>
       <c r="J54" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-U</t>
+          <t>D-N-D-N</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
@@ -10747,10 +10755,10 @@
         </is>
       </c>
       <c r="M54" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
@@ -10758,10 +10766,10 @@
         </is>
       </c>
       <c r="P54" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q54" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -11066,7 +11074,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -11075,48 +11083,48 @@
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>57.7</v>
+        <v>56.2</v>
       </c>
       <c r="G59" s="4" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I59" s="3" t="n">
-        <v>42.3</v>
+        <v>50</v>
       </c>
       <c r="J59" s="4" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-U</t>
+          <t>N-D-D-N</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M59" s="3" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="N59" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="P59" s="3" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="Q59" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60">
@@ -11137,7 +11145,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -11146,48 +11154,48 @@
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>62.5</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="G60" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="J60" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>U-U-U-D</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="N60" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I60" s="3" t="n">
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>D/N</t>
+        </is>
+      </c>
+      <c r="P60" s="3" t="n">
         <v>37.5</v>
       </c>
-      <c r="J60" s="4" t="n">
+      <c r="Q60" s="4" t="n">
         <v>16</v>
-      </c>
-      <c r="K60" s="2" t="inlineStr">
-        <is>
-          <t>U-U-U-N</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="inlineStr">
-        <is>
-          <t>N/U</t>
-        </is>
-      </c>
-      <c r="M60" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="N60" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="O60" s="2" t="inlineStr">
-        <is>
-          <t>D/N/U</t>
-        </is>
-      </c>
-      <c r="P60" s="3" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="Q60" s="4" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="61">
@@ -11208,7 +11216,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -11217,25 +11225,25 @@
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>77.8</v>
+        <v>47.8</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I61" s="3" t="n">
-        <v>66.7</v>
+        <v>52.2</v>
       </c>
       <c r="J61" s="4" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
@@ -11244,21 +11252,21 @@
         </is>
       </c>
       <c r="M61" s="3" t="n">
-        <v>75</v>
+        <v>54.5</v>
       </c>
       <c r="N61" s="4" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P61" s="3" t="n">
-        <v>50</v>
+        <v>54.5</v>
       </c>
       <c r="Q61" s="4" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="62">
@@ -11634,12 +11642,12 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F67" s="3" t="n">
@@ -11650,7 +11658,7 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I67" s="3" t="n">
@@ -11661,12 +11669,12 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-U</t>
+          <t>U-D-U-N</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M67" s="3" t="n">
@@ -11677,7 +11685,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P67" s="3" t="n">
@@ -11776,19 +11784,19 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>64.7</v>
+        <v>50</v>
       </c>
       <c r="G69" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -11796,14 +11804,14 @@
         </is>
       </c>
       <c r="I69" s="3" t="n">
-        <v>47.1</v>
+        <v>72.2</v>
       </c>
       <c r="J69" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-D</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
@@ -11812,21 +11820,21 @@
         </is>
       </c>
       <c r="M69" s="3" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
       <c r="N69" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P69" s="3" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
       <c r="Q69" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="70">
@@ -12202,49 +12210,57 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="F75" s="3" t="inlineStr"/>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="G75" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="I75" s="3" t="inlineStr"/>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I75" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="J75" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>N-N-U-N</t>
+          <t>N-N-U-D</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M75" s="3" t="inlineStr"/>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="M75" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="N75" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P75" s="3" t="inlineStr"/>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P75" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="Q75" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -12691,7 +12707,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -12700,25 +12716,25 @@
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>75</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I82" s="3" t="n">
-        <v>44.4</v>
+        <v>75</v>
       </c>
       <c r="J82" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-D</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
@@ -12727,21 +12743,21 @@
         </is>
       </c>
       <c r="M82" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="N82" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P82" s="3" t="n">
-        <v>42.9</v>
+        <v>66.7</v>
       </c>
       <c r="Q82" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -12975,7 +12991,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -12984,48 +13000,48 @@
         </is>
       </c>
       <c r="F86" s="3" t="n">
-        <v>63.3</v>
+        <v>69.2</v>
       </c>
       <c r="G86" s="4" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I86" s="3" t="n">
-        <v>46.7</v>
+        <v>53.8</v>
       </c>
       <c r="J86" s="4" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="M86" s="3" t="n">
-        <v>62.5</v>
+        <v>33.3</v>
       </c>
       <c r="N86" s="4" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P86" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q86" s="4" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87">
@@ -13330,7 +13346,7 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -13339,48 +13355,48 @@
         </is>
       </c>
       <c r="F91" s="3" t="n">
-        <v>100</v>
+        <v>38.9</v>
       </c>
       <c r="G91" s="4" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I91" s="3" t="n">
-        <v>57.1</v>
+        <v>38.9</v>
       </c>
       <c r="J91" s="4" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-N</t>
+          <t>D-U-N-D</t>
         </is>
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="M91" s="3" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="N91" s="4" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P91" s="3" t="n">
         <v>50</v>
       </c>
       <c r="Q91" s="4" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="92">
@@ -13401,7 +13417,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -13410,30 +13426,30 @@
         </is>
       </c>
       <c r="F92" s="3" t="n">
-        <v>64.7</v>
+        <v>42.9</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I92" s="3" t="n">
-        <v>47.1</v>
+        <v>52.4</v>
       </c>
       <c r="J92" s="4" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M92" s="3" t="n">
@@ -13444,11 +13460,11 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P92" s="3" t="n">
-        <v>42.9</v>
+        <v>57.1</v>
       </c>
       <c r="Q92" s="4" t="n">
         <v>7</v>
@@ -13898,7 +13914,7 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -13907,25 +13923,25 @@
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>72.7</v>
+        <v>75</v>
       </c>
       <c r="G99" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I99" s="3" t="n">
-        <v>45.5</v>
+        <v>50</v>
       </c>
       <c r="J99" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-U</t>
+          <t>D-D-N-N</t>
         </is>
       </c>
       <c r="L99" s="2" t="inlineStr">
@@ -13934,21 +13950,21 @@
         </is>
       </c>
       <c r="M99" s="3" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="N99" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="P99" s="3" t="n">
-        <v>66.7</v>
+        <v>40</v>
       </c>
       <c r="Q99" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="100">
@@ -14182,7 +14198,7 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -14191,25 +14207,25 @@
         </is>
       </c>
       <c r="F103" s="3" t="n">
-        <v>84.59999999999999</v>
+        <v>80</v>
       </c>
       <c r="G103" s="4" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I103" s="3" t="n">
-        <v>38.5</v>
+        <v>45</v>
       </c>
       <c r="J103" s="4" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-N</t>
+          <t>D-U-N-D</t>
         </is>
       </c>
       <c r="L103" s="2" t="inlineStr">
@@ -14218,21 +14234,21 @@
         </is>
       </c>
       <c r="M103" s="3" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
       <c r="N103" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P103" s="3" t="n">
-        <v>66.7</v>
+        <v>40</v>
       </c>
       <c r="Q103" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="104">
@@ -14253,7 +14269,7 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-N-N</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -14262,10 +14278,10 @@
         </is>
       </c>
       <c r="F104" s="3" t="n">
-        <v>66.7</v>
+        <v>73.3</v>
       </c>
       <c r="G104" s="4" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
@@ -14273,37 +14289,37 @@
         </is>
       </c>
       <c r="I104" s="3" t="n">
-        <v>44.4</v>
+        <v>40</v>
       </c>
       <c r="J104" s="4" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>N-N-N-U</t>
+          <t>N-N-N-N</t>
         </is>
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="M104" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N104" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="P104" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="Q104" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/BIS_tr.xlsx
+++ b/BIS_tr.xlsx
@@ -699,7 +699,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -708,25 +708,25 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>55.6</v>
+        <v>58.1</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>153</v>
+        <v>86</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G4" s="3" t="n">
-        <v>41.8</v>
+        <v>39.5</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>153</v>
+        <v>86</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-D</t>
+          <t>D-U-U-N</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -735,21 +735,21 @@
         </is>
       </c>
       <c r="K4" s="3" t="n">
-        <v>44.8</v>
+        <v>44.1</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N4" s="3" t="n">
-        <v>37.9</v>
+        <v>35.3</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>58</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5">
@@ -760,7 +760,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -769,48 +769,48 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>74.5</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>51</v>
+        <v>78</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>78</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>D-N-D-D</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="G5" s="3" t="n">
-        <v>39.2</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>D-N-D-N</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="n">
-        <v>78.90000000000001</v>
-      </c>
-      <c r="L5" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
       <c r="N5" s="3" t="n">
-        <v>47.4</v>
+        <v>40.5</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>63.9</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -1024,14 +1024,14 @@
         </is>
       </c>
       <c r="G9" s="3" t="n">
-        <v>34.7</v>
+        <v>41.5</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-U</t>
+          <t>D-D-N-N</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1040,21 +1040,21 @@
         </is>
       </c>
       <c r="K9" s="3" t="n">
-        <v>66.7</v>
+        <v>85.7</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N9" s="3" t="n">
-        <v>33.3</v>
+        <v>38.1</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1318,10 +1318,10 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>65.7</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>143</v>
+        <v>84</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1329,14 +1329,14 @@
         </is>
       </c>
       <c r="G14" s="3" t="n">
-        <v>39.2</v>
+        <v>38.1</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>143</v>
+        <v>84</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-U</t>
+          <t>U-U-U-N</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1345,21 +1345,21 @@
         </is>
       </c>
       <c r="K14" s="3" t="n">
-        <v>59.2</v>
+        <v>70.3</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N14" s="3" t="n">
-        <v>38.8</v>
+        <v>40.5</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>49</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1501,10 +1501,10 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>65.90000000000001</v>
+        <v>57.5</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>82</v>
+        <v>127</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1512,14 +1512,14 @@
         </is>
       </c>
       <c r="G17" s="3" t="n">
-        <v>43.9</v>
+        <v>41.7</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>82</v>
+        <v>127</v>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-N</t>
+          <t>N-D-D-U</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1528,21 +1528,21 @@
         </is>
       </c>
       <c r="K17" s="3" t="n">
-        <v>52.9</v>
+        <v>65</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N17" s="3" t="n">
-        <v>47.1</v>
+        <v>40</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>D-N-D</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1745,25 +1745,25 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>67.2</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G21" s="3" t="n">
-        <v>45.9</v>
+        <v>36.2</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>N-D-N-D</t>
+          <t>N-D-N-N</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1772,21 +1772,21 @@
         </is>
       </c>
       <c r="K21" s="3" t="n">
-        <v>86.7</v>
+        <v>76.5</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N21" s="3" t="n">
-        <v>53.3</v>
+        <v>41.2</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22">
@@ -2407,7 +2407,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>U-N-D</t>
+          <t>U-N-N</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2416,25 +2416,25 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>79.2</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G32" s="3" t="n">
-        <v>47.2</v>
+        <v>41.2</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>U-U-N-D</t>
+          <t>U-U-N-N</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -2443,21 +2443,21 @@
         </is>
       </c>
       <c r="K32" s="3" t="n">
-        <v>82.40000000000001</v>
+        <v>66.7</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N32" s="3" t="n">
-        <v>55.9</v>
+        <v>41.7</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2538,10 +2538,10 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>60.7</v>
+        <v>57.5</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2549,14 +2549,14 @@
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>39.3</v>
+        <v>46.5</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-D</t>
+          <t>U-D-U-U</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -2565,21 +2565,21 @@
         </is>
       </c>
       <c r="K34" s="3" t="n">
-        <v>59.7</v>
+        <v>48.9</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N34" s="3" t="n">
-        <v>37.3</v>
+        <v>44.7</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>67</v>
+        <v>47</v>
       </c>
     </row>
     <row r="35">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2599,48 +2599,48 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>50.7</v>
+        <v>55.6</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v>45.3</v>
+        <v>48.1</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-U</t>
+          <t>N-D-D-N</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="K35" s="3" t="n">
-        <v>87.5</v>
+        <v>50</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N35" s="3" t="n">
         <v>50</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36">
@@ -4542,57 +4542,57 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>37.5</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G67" s="3" t="n">
-        <v>62.5</v>
+        <v>38.5</v>
       </c>
       <c r="H67" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-U</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K67" s="3" t="n">
-        <v>50</v>
+        <v>83.3</v>
       </c>
       <c r="L67" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N67" s="3" t="n">
         <v>50</v>
       </c>
       <c r="O67" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="68">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -5222,48 +5222,48 @@
         </is>
       </c>
       <c r="D78" s="3" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="E78" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="H78" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>D-D-D-N</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K78" s="3" t="n">
         <v>54.5</v>
       </c>
-      <c r="E78" s="4" t="n">
-        <v>191</v>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="L78" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="G78" s="3" t="n">
-        <v>41.9</v>
-      </c>
-      <c r="H78" s="4" t="n">
-        <v>191</v>
-      </c>
-      <c r="I78" s="2" t="inlineStr">
-        <is>
-          <t>D-D-D-D</t>
-        </is>
-      </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K78" s="3" t="n">
-        <v>58.2</v>
-      </c>
-      <c r="L78" s="4" t="n">
-        <v>79</v>
-      </c>
-      <c r="M78" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
       <c r="N78" s="3" t="n">
-        <v>45.6</v>
+        <v>48.5</v>
       </c>
       <c r="O78" s="4" t="n">
-        <v>79</v>
+        <v>33</v>
       </c>
     </row>
     <row r="79">
@@ -5335,19 +5335,19 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>70</v>
+        <v>45.2</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -5355,37 +5355,37 @@
         </is>
       </c>
       <c r="G80" s="3" t="n">
-        <v>38</v>
+        <v>52.1</v>
       </c>
       <c r="H80" s="4" t="n">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-N</t>
+          <t>U-N-D-D</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K80" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>52.2</v>
       </c>
       <c r="L80" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N80" s="3" t="n">
-        <v>42.9</v>
+        <v>47.8</v>
       </c>
       <c r="O80" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="81">
@@ -6494,7 +6494,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -6503,10 +6503,10 @@
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>68.09999999999999</v>
+        <v>56.3</v>
       </c>
       <c r="E99" s="4" t="n">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -6514,14 +6514,14 @@
         </is>
       </c>
       <c r="G99" s="3" t="n">
-        <v>40.4</v>
+        <v>38</v>
       </c>
       <c r="H99" s="4" t="n">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-N</t>
+          <t>D-D-N-U</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
@@ -6530,21 +6530,21 @@
         </is>
       </c>
       <c r="K99" s="3" t="n">
-        <v>68.40000000000001</v>
+        <v>54.8</v>
       </c>
       <c r="L99" s="4" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N99" s="3" t="n">
-        <v>42.1</v>
+        <v>38.7</v>
       </c>
       <c r="O99" s="4" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
     </row>
     <row r="100">
@@ -7177,7 +7177,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -7186,10 +7186,10 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>48.4</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -7197,37 +7197,37 @@
         </is>
       </c>
       <c r="I4" s="3" t="n">
-        <v>48.4</v>
+        <v>52.9</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-D</t>
+          <t>D-U-U-N</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="M4" s="3" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="N4" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="N4" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="n">
-        <v>57.1</v>
-      </c>
       <c r="Q4" s="4" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -7248,7 +7248,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -7257,25 +7257,25 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>66.7</v>
+        <v>78.3</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I5" s="3" t="n">
-        <v>66.7</v>
+        <v>39.1</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>D-N-D-D</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -7284,21 +7284,21 @@
         </is>
       </c>
       <c r="M5" s="3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P5" s="3" t="n">
-        <v>100</v>
+        <v>41.7</v>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
@@ -7528,7 +7528,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -7537,48 +7537,48 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>85</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="I9" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>D-D-N-N</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="N9" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>D/N</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="J9" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>D-D-N-U</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="N9" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>D/N</t>
-        </is>
-      </c>
-      <c r="P9" s="3" t="n">
-        <v>40</v>
-      </c>
       <c r="Q9" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -7892,25 +7892,25 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>53.3</v>
+        <v>77.3</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I14" s="3" t="n">
-        <v>40</v>
+        <v>45.5</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-U</t>
+          <t>U-U-U-N</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -7919,10 +7919,10 @@
         </is>
       </c>
       <c r="M14" s="3" t="n">
-        <v>46.2</v>
+        <v>80</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -7930,10 +7930,10 @@
         </is>
       </c>
       <c r="P14" s="3" t="n">
-        <v>46.2</v>
+        <v>50</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -8105,48 +8105,48 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>82.40000000000001</v>
+        <v>74.3</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I17" s="3" t="n">
-        <v>41.2</v>
+        <v>45.7</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-N</t>
+          <t>N-D-D-U</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M17" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="P17" s="3" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -8380,7 +8380,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>D-N-D</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -8389,25 +8389,25 @@
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>53.8</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="G21" s="4" t="n">
         <v>13</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I21" s="3" t="n">
-        <v>53.8</v>
+        <v>46.2</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>N-D-N-D</t>
+          <t>N-D-N-N</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -8416,10 +8416,10 @@
         </is>
       </c>
       <c r="M21" s="3" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="P21" s="3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
@@ -9161,7 +9161,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>U-N-D</t>
+          <t>U-N-N</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -9177,18 +9177,18 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I32" s="3" t="n">
-        <v>66.7</v>
+        <v>41.7</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>U-U-N-D</t>
+          <t>U-U-N-N</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -9197,21 +9197,21 @@
         </is>
       </c>
       <c r="M32" s="3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P32" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>75</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
@@ -9303,7 +9303,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -9312,10 +9312,10 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>46.4</v>
+        <v>52.6</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -9323,14 +9323,14 @@
         </is>
       </c>
       <c r="I34" s="3" t="n">
-        <v>53.6</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-D</t>
+          <t>U-D-U-U</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -9339,10 +9339,10 @@
         </is>
       </c>
       <c r="M34" s="3" t="n">
-        <v>58.8</v>
+        <v>60</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -9350,10 +9350,10 @@
         </is>
       </c>
       <c r="P34" s="3" t="n">
-        <v>58.8</v>
+        <v>60</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35">
@@ -9374,7 +9374,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -9383,48 +9383,48 @@
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I35" s="3" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-U</t>
+          <t>N-D-D-N</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M35" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="N35" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="N35" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P35" s="3" t="n">
-        <v>66.7</v>
-      </c>
       <c r="Q35" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -11642,12 +11642,12 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F67" s="3" t="n">
@@ -11658,7 +11658,7 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I67" s="3" t="n">
@@ -11669,12 +11669,12 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-U</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M67" s="3" t="n">
@@ -11685,7 +11685,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P67" s="3" t="n">
@@ -12423,7 +12423,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -12432,10 +12432,10 @@
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>52.5</v>
+        <v>66.7</v>
       </c>
       <c r="G78" s="4" t="n">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -12443,14 +12443,14 @@
         </is>
       </c>
       <c r="I78" s="3" t="n">
-        <v>47.5</v>
+        <v>55.6</v>
       </c>
       <c r="J78" s="4" t="n">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-D</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
@@ -12459,21 +12459,21 @@
         </is>
       </c>
       <c r="M78" s="3" t="n">
-        <v>43.8</v>
+        <v>60</v>
       </c>
       <c r="N78" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P78" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="Q78" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="79">
@@ -12565,57 +12565,57 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F80" s="3" t="n">
-        <v>81.8</v>
+        <v>41.7</v>
       </c>
       <c r="G80" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I80" s="3" t="n">
-        <v>54.5</v>
+        <v>58.3</v>
       </c>
       <c r="J80" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-N</t>
+          <t>U-N-D-D</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M80" s="3" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="N80" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P80" s="3" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="Q80" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="81">
@@ -13914,7 +13914,7 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -13923,25 +13923,25 @@
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>75</v>
+        <v>72.7</v>
       </c>
       <c r="G99" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I99" s="3" t="n">
-        <v>50</v>
+        <v>45.5</v>
       </c>
       <c r="J99" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-N</t>
+          <t>D-D-N-U</t>
         </is>
       </c>
       <c r="L99" s="2" t="inlineStr">
@@ -13950,21 +13950,21 @@
         </is>
       </c>
       <c r="M99" s="3" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="N99" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P99" s="3" t="n">
-        <v>40</v>
+        <v>66.7</v>
       </c>
       <c r="Q99" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="100">

--- a/BIS_tr.xlsx
+++ b/BIS_tr.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -586,25 +586,25 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>65.40000000000001</v>
+        <v>63.1</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>81</v>
+        <v>149</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G2" s="3" t="n">
-        <v>45.7</v>
+        <v>43</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>81</v>
+        <v>149</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-N</t>
+          <t>U-U-D-U</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -613,21 +613,21 @@
         </is>
       </c>
       <c r="K2" s="3" t="n">
-        <v>61.3</v>
+        <v>67.2</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N2" s="3" t="n">
-        <v>38.7</v>
+        <v>42.2</v>
       </c>
       <c r="O2" s="4" t="n">
-        <v>31</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3">
@@ -699,7 +699,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-U</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -708,25 +708,25 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>76.09999999999999</v>
+        <v>65.8</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G4" s="3" t="n">
-        <v>34.8</v>
+        <v>43.8</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>U-U-N-N</t>
+          <t>U-U-N-U</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -735,21 +735,21 @@
         </is>
       </c>
       <c r="K4" s="3" t="n">
-        <v>75</v>
+        <v>68.8</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N4" s="3" t="n">
-        <v>40</v>
+        <v>43.8</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5">
@@ -760,7 +760,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>62.4</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -780,14 +780,14 @@
         </is>
       </c>
       <c r="G5" s="3" t="n">
-        <v>45.5</v>
+        <v>46.3</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-N</t>
+          <t>N-D-D-U</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -796,21 +796,21 @@
         </is>
       </c>
       <c r="K5" s="3" t="n">
-        <v>78.3</v>
+        <v>57.1</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N5" s="3" t="n">
-        <v>39.1</v>
+        <v>57.1</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6">
@@ -821,7 +821,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -830,25 +830,25 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>59.7</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G6" s="3" t="n">
-        <v>40.5</v>
+        <v>46.8</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-N</t>
+          <t>U-N-D-U</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -857,21 +857,21 @@
         </is>
       </c>
       <c r="K6" s="3" t="n">
-        <v>61.5</v>
+        <v>64.5</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N6" s="3" t="n">
-        <v>38.5</v>
+        <v>48.4</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7">
@@ -882,7 +882,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -891,10 +891,10 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>63.6</v>
+        <v>58.4</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>77</v>
+        <v>161</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -902,14 +902,14 @@
         </is>
       </c>
       <c r="G7" s="3" t="n">
-        <v>40.3</v>
+        <v>45.3</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>77</v>
+        <v>161</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-N</t>
+          <t>U-U-D-U</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -918,10 +918,10 @@
         </is>
       </c>
       <c r="K7" s="3" t="n">
-        <v>63</v>
+        <v>66.2</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="N7" s="3" t="n">
-        <v>37</v>
+        <v>41.2</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8">
@@ -943,57 +943,57 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>63.2</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G8" s="3" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>47</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>N-U-U-U</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>N/U</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="H8" s="4" t="n">
-        <v>38</v>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>N-U-U-D</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>D/U</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="n">
-        <v>40</v>
-      </c>
       <c r="L8" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N8" s="3" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-U</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>77</v>
+        <v>69.7</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>248</v>
+        <v>109</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -1024,14 +1024,14 @@
         </is>
       </c>
       <c r="G9" s="3" t="n">
-        <v>60.9</v>
+        <v>46.8</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>248</v>
+        <v>109</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-N</t>
+          <t>D-N-N-U</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="K9" s="3" t="n">
-        <v>71.8</v>
+        <v>60</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="N9" s="3" t="n">
-        <v>51.3</v>
+        <v>44</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1074,25 +1074,25 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>71.7</v>
+        <v>66.3</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G10" s="3" t="n">
-        <v>35.8</v>
+        <v>41.9</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>N-D-N-N</t>
+          <t>N-D-N-U</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1101,21 +1101,21 @@
         </is>
       </c>
       <c r="K10" s="3" t="n">
-        <v>64.3</v>
+        <v>61.1</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N10" s="3" t="n">
-        <v>35.7</v>
+        <v>44.4</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>72.40000000000001</v>
+        <v>56.7</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>58</v>
+        <v>171</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1146,14 +1146,14 @@
         </is>
       </c>
       <c r="G11" s="3" t="n">
-        <v>46.6</v>
+        <v>43.9</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>58</v>
+        <v>171</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1162,21 +1162,21 @@
         </is>
       </c>
       <c r="K11" s="3" t="n">
-        <v>72.7</v>
+        <v>56.5</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N11" s="3" t="n">
-        <v>50</v>
+        <v>48.4</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>22</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1379,25 +1379,25 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G15" s="3" t="n">
-        <v>43.3</v>
+        <v>39.2</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-U</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1406,21 +1406,21 @@
         </is>
       </c>
       <c r="K15" s="3" t="n">
-        <v>47.5</v>
+        <v>58.4</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N15" s="3" t="n">
-        <v>44.3</v>
+        <v>37.7</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>61</v>
+        <v>77</v>
       </c>
     </row>
     <row r="16">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1562,25 +1562,25 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>83.09999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>89</v>
+        <v>60</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G18" s="3" t="n">
-        <v>50.6</v>
+        <v>43.3</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>89</v>
+        <v>60</v>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>N-N-N-N</t>
+          <t>N-N-N-D</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1589,21 +1589,21 @@
         </is>
       </c>
       <c r="K18" s="3" t="n">
-        <v>84.09999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="N18" s="3" t="n">
-        <v>50</v>
+        <v>35.3</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>44</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1623,25 +1623,25 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>56.4</v>
+        <v>50</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>39</v>
+        <v>92</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>46.2</v>
+        <v>46.7</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>39</v>
+        <v>92</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1650,21 +1650,21 @@
         </is>
       </c>
       <c r="K19" s="3" t="n">
-        <v>61.1</v>
+        <v>50</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N19" s="3" t="n">
-        <v>44.4</v>
+        <v>41.7</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-U</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1745,25 +1745,25 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>82.8</v>
+        <v>75</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>93</v>
+        <v>60</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G21" s="3" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>93</v>
+        <v>60</v>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-N</t>
+          <t>D-N-N-U</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1772,21 +1772,21 @@
         </is>
       </c>
       <c r="K21" s="3" t="n">
-        <v>85.7</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N21" s="3" t="n">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22">
@@ -1797,57 +1797,57 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>49.3</v>
+        <v>67.8</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G22" s="3" t="n">
-        <v>49.3</v>
+        <v>50.8</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K22" s="3" t="n">
-        <v>50</v>
+        <v>81.5</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N22" s="3" t="n">
-        <v>50</v>
+        <v>51.9</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23">
@@ -1858,19 +1858,19 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>57.7</v>
+        <v>46.2</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1881,34 +1881,34 @@
         <v>46.2</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-U</t>
+          <t>D-N-D-N</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K23" s="3" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N23" s="3" t="n">
-        <v>58.3</v>
+        <v>60</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2233,48 +2233,48 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>88.5</v>
+        <v>76.2</v>
       </c>
       <c r="E29" s="4" t="n">
+        <v>105</v>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="H29" s="4" t="n">
+        <v>105</v>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>D-U-U-U</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="L29" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>53.8</v>
-      </c>
-      <c r="H29" s="4" t="n">
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="O29" s="4" t="n">
         <v>26</v>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>D-U-U-N</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="n">
-        <v>85.7</v>
-      </c>
-      <c r="L29" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="N29" s="3" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="O29" s="4" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="30">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2355,10 +2355,10 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>67.7</v>
+        <v>63.6</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2366,14 +2366,14 @@
         </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>40</v>
+        <v>54.5</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-U</t>
+          <t>U-D-U-N</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -2382,21 +2382,21 @@
         </is>
       </c>
       <c r="K31" s="3" t="n">
-        <v>72.7</v>
+        <v>100</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N31" s="3" t="n">
-        <v>51.5</v>
+        <v>50</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
@@ -2407,7 +2407,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-U</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2416,48 +2416,48 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>84</v>
+        <v>62.5</v>
       </c>
       <c r="E32" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>U-N-N-U</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="n">
-        <v>44</v>
-      </c>
-      <c r="H32" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>U-N-N-N</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="n">
-        <v>85</v>
-      </c>
       <c r="L32" s="4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N32" s="3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-U</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2477,25 +2477,25 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>76.40000000000001</v>
+        <v>63.4</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G33" s="3" t="n">
-        <v>40.3</v>
+        <v>39.8</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-N</t>
+          <t>D-U-N-U</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -2504,21 +2504,21 @@
         </is>
       </c>
       <c r="K33" s="3" t="n">
-        <v>75</v>
+        <v>58.5</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N33" s="3" t="n">
-        <v>37.5</v>
+        <v>39</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>24</v>
+        <v>41</v>
       </c>
     </row>
     <row r="34">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2538,10 +2538,10 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>63.2</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>152</v>
+        <v>68</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2549,14 +2549,14 @@
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>37.5</v>
+        <v>42.6</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>152</v>
+        <v>68</v>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-U</t>
+          <t>D-U-U-N</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -2565,10 +2565,10 @@
         </is>
       </c>
       <c r="K34" s="3" t="n">
-        <v>72.90000000000001</v>
+        <v>75</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
@@ -2576,10 +2576,10 @@
         </is>
       </c>
       <c r="N34" s="3" t="n">
-        <v>40.7</v>
+        <v>56.2</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>59</v>
+        <v>16</v>
       </c>
     </row>
     <row r="35">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2599,10 +2599,10 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>72.40000000000001</v>
+        <v>77.8</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2610,14 +2610,14 @@
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v>55.2</v>
+        <v>55.6</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-U</t>
+          <t>D-D-N-N</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -2626,21 +2626,21 @@
         </is>
       </c>
       <c r="K35" s="3" t="n">
-        <v>76.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N35" s="3" t="n">
-        <v>53.8</v>
+        <v>50</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2721,25 +2721,25 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>58.8</v>
+        <v>57.4</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>153</v>
+        <v>61</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G37" s="3" t="n">
-        <v>47.7</v>
+        <v>37.7</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>153</v>
+        <v>61</v>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-D</t>
+          <t>U-D-U-N</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -2748,21 +2748,21 @@
         </is>
       </c>
       <c r="K37" s="3" t="n">
-        <v>58.6</v>
+        <v>54.2</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N37" s="3" t="n">
-        <v>50</v>
+        <v>58.3</v>
       </c>
       <c r="O37" s="4" t="n">
-        <v>58</v>
+        <v>24</v>
       </c>
     </row>
     <row r="38">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2843,25 +2843,25 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>58.3</v>
+        <v>59</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>84</v>
+        <v>156</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G39" s="3" t="n">
-        <v>40.5</v>
+        <v>42.9</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>84</v>
+        <v>156</v>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-N</t>
+          <t>N-U-D-U</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -2870,10 +2870,10 @@
         </is>
       </c>
       <c r="K39" s="3" t="n">
-        <v>70.8</v>
+        <v>74.2</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
@@ -2881,10 +2881,10 @@
         </is>
       </c>
       <c r="N39" s="3" t="n">
-        <v>45.8</v>
+        <v>48.4</v>
       </c>
       <c r="O39" s="4" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="40">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2965,25 +2965,25 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>48</v>
+        <v>68.2</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>98</v>
+        <v>22</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G41" s="3" t="n">
-        <v>44.9</v>
+        <v>54.5</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>98</v>
+        <v>22</v>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -2992,21 +2992,21 @@
         </is>
       </c>
       <c r="K41" s="3" t="n">
-        <v>45.5</v>
+        <v>75</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N41" s="3" t="n">
-        <v>52.3</v>
+        <v>62.5</v>
       </c>
       <c r="O41" s="4" t="n">
-        <v>44</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3026,25 +3026,25 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>77.8</v>
+        <v>73.3</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G42" s="3" t="n">
-        <v>44.4</v>
+        <v>53.3</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>D-N-D-U</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -3053,21 +3053,21 @@
         </is>
       </c>
       <c r="K42" s="3" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N42" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="O42" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3148,10 +3148,10 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>66.7</v>
+        <v>80</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -3159,14 +3159,14 @@
         </is>
       </c>
       <c r="G44" s="3" t="n">
-        <v>55.6</v>
+        <v>60</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -3175,10 +3175,10 @@
         </is>
       </c>
       <c r="K44" s="3" t="n">
-        <v>100</v>
+        <v>81.2</v>
       </c>
       <c r="L44" s="4" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
@@ -3186,10 +3186,10 @@
         </is>
       </c>
       <c r="N44" s="3" t="n">
-        <v>66.7</v>
+        <v>56.2</v>
       </c>
       <c r="O44" s="4" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="45">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3331,25 +3331,25 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>57.1</v>
+        <v>54.4</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>98</v>
+        <v>149</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G47" s="3" t="n">
-        <v>40.8</v>
+        <v>48.3</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>98</v>
+        <v>149</v>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-N</t>
+          <t>N-U-D-U</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -3358,21 +3358,21 @@
         </is>
       </c>
       <c r="K47" s="3" t="n">
-        <v>59.1</v>
+        <v>58.1</v>
       </c>
       <c r="L47" s="4" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N47" s="3" t="n">
-        <v>45.5</v>
+        <v>45.2</v>
       </c>
       <c r="O47" s="4" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
     </row>
     <row r="48">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3392,37 +3392,37 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>70</v>
+        <v>54.5</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>40</v>
+        <v>40.3</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-N-U-U</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="K48" s="3" t="n">
-        <v>69.2</v>
+        <v>45.2</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
@@ -3430,10 +3430,10 @@
         </is>
       </c>
       <c r="N48" s="3" t="n">
-        <v>46.2</v>
+        <v>48.4</v>
       </c>
       <c r="O48" s="4" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
     </row>
     <row r="49">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-U</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -3514,25 +3514,25 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>71.90000000000001</v>
+        <v>70.7</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G50" s="3" t="n">
-        <v>42.1</v>
+        <v>42.7</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>N-U-N-N</t>
+          <t>N-U-N-U</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -3541,21 +3541,21 @@
         </is>
       </c>
       <c r="K50" s="3" t="n">
-        <v>80</v>
+        <v>56.5</v>
       </c>
       <c r="L50" s="4" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N50" s="3" t="n">
-        <v>46.7</v>
+        <v>56.5</v>
       </c>
       <c r="O50" s="4" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="51">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3636,10 +3636,10 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>61.1</v>
+        <v>60</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>90</v>
+        <v>165</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3647,14 +3647,14 @@
         </is>
       </c>
       <c r="G52" s="3" t="n">
-        <v>36.7</v>
+        <v>41.2</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>90</v>
+        <v>165</v>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-U</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -3663,10 +3663,10 @@
         </is>
       </c>
       <c r="K52" s="3" t="n">
-        <v>50</v>
+        <v>55.2</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
@@ -3674,10 +3674,10 @@
         </is>
       </c>
       <c r="N52" s="3" t="n">
-        <v>37.5</v>
+        <v>43.3</v>
       </c>
       <c r="O52" s="4" t="n">
-        <v>40</v>
+        <v>67</v>
       </c>
     </row>
     <row r="53">
@@ -3688,7 +3688,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3697,48 +3697,48 @@
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>58</v>
+        <v>56.2</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G53" s="3" t="n">
-        <v>52</v>
+        <v>56.2</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K53" s="3" t="n">
-        <v>45</v>
+        <v>57.1</v>
       </c>
       <c r="L53" s="4" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N53" s="3" t="n">
-        <v>70</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="O53" s="4" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3819,25 +3819,25 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>51.3</v>
+        <v>60.7</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>193</v>
+        <v>61</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G55" s="3" t="n">
-        <v>44</v>
+        <v>39.3</v>
       </c>
       <c r="H55" s="4" t="n">
-        <v>193</v>
+        <v>61</v>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -3846,10 +3846,10 @@
         </is>
       </c>
       <c r="K55" s="3" t="n">
-        <v>51.2</v>
+        <v>54.5</v>
       </c>
       <c r="L55" s="4" t="n">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
@@ -3857,10 +3857,10 @@
         </is>
       </c>
       <c r="N55" s="3" t="n">
-        <v>43.9</v>
+        <v>45.5</v>
       </c>
       <c r="O55" s="4" t="n">
-        <v>82</v>
+        <v>22</v>
       </c>
     </row>
     <row r="56">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3941,10 +3941,10 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>49.7</v>
+        <v>73</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>159</v>
+        <v>74</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3952,14 +3952,14 @@
         </is>
       </c>
       <c r="G57" s="3" t="n">
-        <v>45.9</v>
+        <v>40.5</v>
       </c>
       <c r="H57" s="4" t="n">
-        <v>159</v>
+        <v>74</v>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -3968,10 +3968,10 @@
         </is>
       </c>
       <c r="K57" s="3" t="n">
-        <v>47.9</v>
+        <v>70</v>
       </c>
       <c r="L57" s="4" t="n">
-        <v>71</v>
+        <v>30</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
@@ -3979,10 +3979,10 @@
         </is>
       </c>
       <c r="N57" s="3" t="n">
-        <v>47.9</v>
+        <v>43.3</v>
       </c>
       <c r="O57" s="4" t="n">
-        <v>71</v>
+        <v>30</v>
       </c>
     </row>
     <row r="58">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4002,25 +4002,25 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>57.4</v>
+        <v>60.9</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>94</v>
+        <v>69</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G58" s="3" t="n">
-        <v>50</v>
+        <v>43.5</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>94</v>
+        <v>69</v>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-U</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -4029,10 +4029,10 @@
         </is>
       </c>
       <c r="K58" s="3" t="n">
-        <v>52.8</v>
+        <v>53.3</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
@@ -4040,10 +4040,10 @@
         </is>
       </c>
       <c r="N58" s="3" t="n">
-        <v>52.8</v>
+        <v>43.3</v>
       </c>
       <c r="O58" s="4" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="59">
@@ -4115,7 +4115,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4124,25 +4124,25 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>70.2</v>
+        <v>63.6</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>94</v>
+        <v>143</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G60" s="3" t="n">
-        <v>42.6</v>
+        <v>41.3</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>94</v>
+        <v>143</v>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-N</t>
+          <t>U-U-D-U</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -4151,21 +4151,21 @@
         </is>
       </c>
       <c r="K60" s="3" t="n">
-        <v>58.7</v>
+        <v>60.7</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N60" s="3" t="n">
-        <v>41.3</v>
+        <v>42.9</v>
       </c>
       <c r="O60" s="4" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
     </row>
     <row r="61">
@@ -4298,7 +4298,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -4310,22 +4310,22 @@
         <v>76.5</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G63" s="3" t="n">
         <v>41.2</v>
       </c>
       <c r="H63" s="4" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-N</t>
+          <t>U-U-D-U</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -4334,21 +4334,21 @@
         </is>
       </c>
       <c r="K63" s="3" t="n">
-        <v>75</v>
+        <v>85.7</v>
       </c>
       <c r="L63" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N63" s="3" t="n">
         <v>50</v>
       </c>
       <c r="O63" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="64">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -4368,25 +4368,25 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>53.6</v>
+        <v>42.5</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>69</v>
+        <v>181</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G64" s="3" t="n">
-        <v>47.8</v>
+        <v>47</v>
       </c>
       <c r="H64" s="4" t="n">
-        <v>69</v>
+        <v>181</v>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-N</t>
+          <t>N-D-D-D</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -4395,21 +4395,21 @@
         </is>
       </c>
       <c r="K64" s="3" t="n">
-        <v>62.5</v>
+        <v>50</v>
       </c>
       <c r="L64" s="4" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N64" s="3" t="n">
-        <v>50</v>
+        <v>47.4</v>
       </c>
       <c r="O64" s="4" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
     </row>
     <row r="65">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -4673,48 +4673,48 @@
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>53.3</v>
+        <v>51.1</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G69" s="3" t="n">
-        <v>66.7</v>
+        <v>44.4</v>
       </c>
       <c r="H69" s="4" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-U</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K69" s="3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="L69" s="4" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N69" s="3" t="n">
-        <v>60</v>
+        <v>44.4</v>
       </c>
       <c r="O69" s="4" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="70">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -4734,10 +4734,10 @@
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>63.1</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>160</v>
+        <v>73</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4745,14 +4745,14 @@
         </is>
       </c>
       <c r="G70" s="3" t="n">
-        <v>43.1</v>
+        <v>47.9</v>
       </c>
       <c r="H70" s="4" t="n">
-        <v>160</v>
+        <v>73</v>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-D</t>
+          <t>U-U-U-N</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -4761,10 +4761,10 @@
         </is>
       </c>
       <c r="K70" s="3" t="n">
-        <v>59.4</v>
+        <v>62.1</v>
       </c>
       <c r="L70" s="4" t="n">
-        <v>69</v>
+        <v>29</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
@@ -4772,10 +4772,10 @@
         </is>
       </c>
       <c r="N70" s="3" t="n">
-        <v>44.9</v>
+        <v>58.6</v>
       </c>
       <c r="O70" s="4" t="n">
-        <v>69</v>
+        <v>29</v>
       </c>
     </row>
     <row r="71">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -4795,25 +4795,25 @@
         </is>
       </c>
       <c r="D71" s="3" t="n">
-        <v>62.2</v>
+        <v>73.7</v>
       </c>
       <c r="E71" s="4" t="n">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G71" s="3" t="n">
-        <v>45.9</v>
+        <v>39.5</v>
       </c>
       <c r="H71" s="4" t="n">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-U</t>
+          <t>D-D-N-N</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -4822,10 +4822,10 @@
         </is>
       </c>
       <c r="K71" s="3" t="n">
-        <v>55.6</v>
+        <v>80</v>
       </c>
       <c r="L71" s="4" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
@@ -4833,10 +4833,10 @@
         </is>
       </c>
       <c r="N71" s="3" t="n">
-        <v>48.1</v>
+        <v>46.7</v>
       </c>
       <c r="O71" s="4" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
     </row>
     <row r="72">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -4978,37 +4978,37 @@
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>56.1</v>
+        <v>47.9</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>66</v>
+        <v>144</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G74" s="3" t="n">
-        <v>39.4</v>
+        <v>42.4</v>
       </c>
       <c r="H74" s="4" t="n">
-        <v>66</v>
+        <v>144</v>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K74" s="3" t="n">
-        <v>52</v>
+        <v>46.3</v>
       </c>
       <c r="L74" s="4" t="n">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
@@ -5016,10 +5016,10 @@
         </is>
       </c>
       <c r="N74" s="3" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="O74" s="4" t="n">
-        <v>25</v>
+        <v>54</v>
       </c>
     </row>
     <row r="75">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -5222,48 +5222,48 @@
         </is>
       </c>
       <c r="D78" s="3" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="E78" s="4" t="n">
+        <v>69</v>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="H78" s="4" t="n">
+        <v>69</v>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>D-D-N-U</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K78" s="3" t="n">
         <v>62.5</v>
       </c>
-      <c r="E78" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>D/U</t>
-        </is>
-      </c>
-      <c r="G78" s="3" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H78" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="I78" s="2" t="inlineStr">
-        <is>
-          <t>D-D-N-N</t>
-        </is>
-      </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K78" s="3" t="n">
-        <v>66.7</v>
-      </c>
       <c r="L78" s="4" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N78" s="3" t="n">
-        <v>41.7</v>
+        <v>43.8</v>
       </c>
       <c r="O78" s="4" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
     </row>
     <row r="79">
@@ -5457,7 +5457,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-U</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -5466,10 +5466,10 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>88.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -5477,14 +5477,14 @@
         </is>
       </c>
       <c r="G82" s="3" t="n">
-        <v>52.9</v>
+        <v>37</v>
       </c>
       <c r="H82" s="4" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-N</t>
+          <t>D-U-N-U</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -5493,10 +5493,10 @@
         </is>
       </c>
       <c r="K82" s="3" t="n">
-        <v>100</v>
+        <v>81.8</v>
       </c>
       <c r="L82" s="4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
@@ -5504,10 +5504,10 @@
         </is>
       </c>
       <c r="N82" s="3" t="n">
-        <v>66.7</v>
+        <v>54.5</v>
       </c>
       <c r="O82" s="4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="83">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -5527,25 +5527,25 @@
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>68.2</v>
+        <v>54.5</v>
       </c>
       <c r="E83" s="4" t="n">
-        <v>85</v>
+        <v>165</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G83" s="3" t="n">
         <v>41.2</v>
       </c>
       <c r="H83" s="4" t="n">
-        <v>85</v>
+        <v>165</v>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
@@ -5554,21 +5554,21 @@
         </is>
       </c>
       <c r="K83" s="3" t="n">
-        <v>70.8</v>
+        <v>50</v>
       </c>
       <c r="L83" s="4" t="n">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N83" s="3" t="n">
-        <v>45.8</v>
+        <v>48.5</v>
       </c>
       <c r="O83" s="4" t="n">
-        <v>24</v>
+        <v>66</v>
       </c>
     </row>
     <row r="84">
@@ -5579,7 +5579,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -5588,25 +5588,25 @@
         </is>
       </c>
       <c r="D84" s="3" t="n">
-        <v>67.8</v>
+        <v>62.8</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>90</v>
+        <v>129</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G84" s="3" t="n">
-        <v>38.9</v>
+        <v>39.5</v>
       </c>
       <c r="H84" s="4" t="n">
-        <v>90</v>
+        <v>129</v>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-N</t>
+          <t>N-U-D-U</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -5615,21 +5615,21 @@
         </is>
       </c>
       <c r="K84" s="3" t="n">
-        <v>69.2</v>
+        <v>81.8</v>
       </c>
       <c r="L84" s="4" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N84" s="3" t="n">
-        <v>50</v>
+        <v>40.9</v>
       </c>
       <c r="O84" s="4" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="85">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -5710,25 +5710,25 @@
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>85.7</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G86" s="3" t="n">
-        <v>42.9</v>
+        <v>42.3</v>
       </c>
       <c r="H86" s="4" t="n">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-N</t>
+          <t>D-D-N-D</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -5737,21 +5737,21 @@
         </is>
       </c>
       <c r="K86" s="3" t="n">
-        <v>77.8</v>
+        <v>53.3</v>
       </c>
       <c r="L86" s="4" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N86" s="3" t="n">
-        <v>44.4</v>
+        <v>43.3</v>
       </c>
       <c r="O86" s="4" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="87">
@@ -5762,7 +5762,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -5771,10 +5771,10 @@
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>66.7</v>
+        <v>56.6</v>
       </c>
       <c r="E87" s="4" t="n">
-        <v>39</v>
+        <v>76</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5782,14 +5782,14 @@
         </is>
       </c>
       <c r="G87" s="3" t="n">
-        <v>38.5</v>
+        <v>50</v>
       </c>
       <c r="H87" s="4" t="n">
-        <v>39</v>
+        <v>76</v>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>N-N-U-N</t>
+          <t>N-N-U-U</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
@@ -5798,10 +5798,10 @@
         </is>
       </c>
       <c r="K87" s="3" t="n">
-        <v>66.7</v>
+        <v>61.9</v>
       </c>
       <c r="L87" s="4" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
@@ -5809,10 +5809,10 @@
         </is>
       </c>
       <c r="N87" s="3" t="n">
-        <v>50</v>
+        <v>61.9</v>
       </c>
       <c r="O87" s="4" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
     </row>
     <row r="88">
@@ -6067,7 +6067,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -6076,25 +6076,25 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>60.7</v>
+        <v>59.3</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>89</v>
+        <v>182</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G92" s="3" t="n">
-        <v>42.7</v>
+        <v>42.9</v>
       </c>
       <c r="H92" s="4" t="n">
-        <v>89</v>
+        <v>182</v>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-N</t>
+          <t>U-U-D-U</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
@@ -6103,21 +6103,21 @@
         </is>
       </c>
       <c r="K92" s="3" t="n">
-        <v>68.8</v>
+        <v>58.5</v>
       </c>
       <c r="L92" s="4" t="n">
-        <v>32</v>
+        <v>82</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N92" s="3" t="n">
-        <v>40.6</v>
+        <v>45.1</v>
       </c>
       <c r="O92" s="4" t="n">
-        <v>32</v>
+        <v>82</v>
       </c>
     </row>
     <row r="93">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -6198,25 +6198,25 @@
         </is>
       </c>
       <c r="D94" s="3" t="n">
-        <v>61.8</v>
+        <v>64.7</v>
       </c>
       <c r="E94" s="4" t="n">
-        <v>102</v>
+        <v>153</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G94" s="3" t="n">
-        <v>37.3</v>
+        <v>38.6</v>
       </c>
       <c r="H94" s="4" t="n">
-        <v>102</v>
+        <v>153</v>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-N</t>
+          <t>N-U-U-U</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
@@ -6225,21 +6225,21 @@
         </is>
       </c>
       <c r="K94" s="3" t="n">
-        <v>81</v>
+        <v>61.3</v>
       </c>
       <c r="L94" s="4" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N94" s="3" t="n">
-        <v>47.6</v>
+        <v>45.2</v>
       </c>
       <c r="O94" s="4" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
     </row>
     <row r="95">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -6259,25 +6259,25 @@
         </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>73.90000000000001</v>
+        <v>67.8</v>
       </c>
       <c r="E95" s="4" t="n">
-        <v>46</v>
+        <v>87</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G95" s="3" t="n">
-        <v>41.3</v>
+        <v>50.6</v>
       </c>
       <c r="H95" s="4" t="n">
-        <v>46</v>
+        <v>87</v>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-N</t>
+          <t>U-U-D-D</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
@@ -6286,21 +6286,21 @@
         </is>
       </c>
       <c r="K95" s="3" t="n">
-        <v>80</v>
+        <v>66.7</v>
       </c>
       <c r="L95" s="4" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N95" s="3" t="n">
-        <v>56</v>
+        <v>47.6</v>
       </c>
       <c r="O95" s="4" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
     </row>
     <row r="96">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -6442,25 +6442,25 @@
         </is>
       </c>
       <c r="D98" s="3" t="n">
-        <v>63.5</v>
+        <v>46.7</v>
       </c>
       <c r="E98" s="4" t="n">
-        <v>96</v>
+        <v>169</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G98" s="3" t="n">
-        <v>42.7</v>
+        <v>44.4</v>
       </c>
       <c r="H98" s="4" t="n">
-        <v>96</v>
+        <v>169</v>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-N</t>
+          <t>N-U-D-U</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
@@ -6469,10 +6469,10 @@
         </is>
       </c>
       <c r="K98" s="3" t="n">
-        <v>61.5</v>
+        <v>45.2</v>
       </c>
       <c r="L98" s="4" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
@@ -6480,10 +6480,10 @@
         </is>
       </c>
       <c r="N98" s="3" t="n">
-        <v>38.5</v>
+        <v>48.4</v>
       </c>
       <c r="O98" s="4" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="99">
@@ -6555,7 +6555,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -6564,10 +6564,10 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>54.1</v>
+        <v>61.5</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>74</v>
+        <v>161</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -6575,14 +6575,14 @@
         </is>
       </c>
       <c r="G100" s="3" t="n">
-        <v>40.5</v>
+        <v>40.4</v>
       </c>
       <c r="H100" s="4" t="n">
-        <v>74</v>
+        <v>161</v>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-N</t>
+          <t>N-U-D-U</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
@@ -6591,21 +6591,21 @@
         </is>
       </c>
       <c r="K100" s="3" t="n">
-        <v>66.7</v>
+        <v>68</v>
       </c>
       <c r="L100" s="4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="N100" s="3" t="n">
-        <v>53.3</v>
+        <v>36</v>
       </c>
       <c r="O100" s="4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="101">
@@ -6616,7 +6616,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-U</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -6625,25 +6625,25 @@
         </is>
       </c>
       <c r="D101" s="3" t="n">
-        <v>80.2</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="E101" s="4" t="n">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G101" s="3" t="n">
-        <v>34.4</v>
+        <v>41.7</v>
       </c>
       <c r="H101" s="4" t="n">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>N-U-N-N</t>
+          <t>N-U-N-U</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
@@ -6652,21 +6652,21 @@
         </is>
       </c>
       <c r="K101" s="3" t="n">
-        <v>84.40000000000001</v>
+        <v>66.7</v>
       </c>
       <c r="L101" s="4" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N101" s="3" t="n">
-        <v>34.4</v>
+        <v>52.4</v>
       </c>
       <c r="O101" s="4" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
     </row>
     <row r="102">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-U</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -6686,25 +6686,25 @@
         </is>
       </c>
       <c r="D102" s="3" t="n">
-        <v>85.59999999999999</v>
+        <v>74.8</v>
       </c>
       <c r="E102" s="4" t="n">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G102" s="3" t="n">
-        <v>39.8</v>
+        <v>40.7</v>
       </c>
       <c r="H102" s="4" t="n">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-N</t>
+          <t>D-U-N-U</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
@@ -6713,21 +6713,21 @@
         </is>
       </c>
       <c r="K102" s="3" t="n">
-        <v>90.5</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="L102" s="4" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N102" s="3" t="n">
-        <v>47.6</v>
+        <v>46.4</v>
       </c>
       <c r="O102" s="4" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="103">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -6747,10 +6747,10 @@
         </is>
       </c>
       <c r="D103" s="3" t="n">
-        <v>62.7</v>
+        <v>60.5</v>
       </c>
       <c r="E103" s="4" t="n">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -6758,14 +6758,14 @@
         </is>
       </c>
       <c r="G103" s="3" t="n">
-        <v>49</v>
+        <v>40.7</v>
       </c>
       <c r="H103" s="4" t="n">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-N</t>
+          <t>U-N-D-U</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
@@ -6774,10 +6774,10 @@
         </is>
       </c>
       <c r="K103" s="3" t="n">
-        <v>61.1</v>
+        <v>50</v>
       </c>
       <c r="L103" s="4" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
@@ -6785,10 +6785,10 @@
         </is>
       </c>
       <c r="N103" s="3" t="n">
-        <v>55.6</v>
+        <v>50</v>
       </c>
       <c r="O103" s="4" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
     </row>
     <row r="104">
@@ -7035,7 +7035,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -7047,22 +7047,22 @@
         <v>50</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I2" s="3" t="n">
-        <v>42.9</v>
+        <v>46.2</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-N</t>
+          <t>U-U-D-U</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -7071,21 +7071,21 @@
         </is>
       </c>
       <c r="M2" s="3" t="n">
-        <v>50</v>
+        <v>54.5</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P2" s="3" t="n">
-        <v>33.3</v>
+        <v>36.4</v>
       </c>
       <c r="Q2" s="4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -7177,57 +7177,57 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-U</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>85.7</v>
+        <v>45.5</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I4" s="3" t="n">
-        <v>42.9</v>
+        <v>54.5</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>U-U-N-N</t>
+          <t>U-U-N-U</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="M4" s="3" t="n">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P4" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q4" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -7248,7 +7248,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -7257,10 +7257,10 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>82.40000000000001</v>
+        <v>62.2</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -7268,14 +7268,14 @@
         </is>
       </c>
       <c r="I5" s="3" t="n">
-        <v>47.1</v>
+        <v>45.9</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-N</t>
+          <t>N-D-D-U</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -7284,10 +7284,10 @@
         </is>
       </c>
       <c r="M5" s="3" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
@@ -7295,10 +7295,10 @@
         </is>
       </c>
       <c r="P5" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -7319,57 +7319,57 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>40</v>
+        <v>72.7</v>
       </c>
       <c r="G6" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>U-N-D-U</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="N6" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="n">
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="J6" s="4" t="n">
+      <c r="Q6" s="4" t="n">
         <v>5</v>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>U-N-D-N</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="N6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P6" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q6" s="4" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -7399,48 +7399,48 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>38.5</v>
+        <v>55.2</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I7" s="3" t="n">
-        <v>46.2</v>
+        <v>48.3</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-N</t>
+          <t>U-U-D-U</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M7" s="3" t="n">
-        <v>33.3</v>
+        <v>53.3</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P7" s="3" t="n">
-        <v>66.7</v>
+        <v>53.3</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
@@ -7461,57 +7461,53 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>66.7</v>
+        <v>85.7</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I8" s="3" t="n">
-        <v>83.3</v>
+        <v>57.1</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-D</t>
+          <t>N-U-U-U</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr"/>
       <c r="N8" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr"/>
       <c r="Q8" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -7532,34 +7528,34 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-U</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>75.5</v>
+        <v>47.6</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I9" s="3" t="n">
-        <v>65.3</v>
+        <v>47.6</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-N</t>
+          <t>D-N-N-U</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -7568,21 +7564,21 @@
         </is>
       </c>
       <c r="M9" s="3" t="n">
-        <v>85.7</v>
+        <v>60</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P9" s="3" t="n">
-        <v>42.9</v>
+        <v>60</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -7603,57 +7599,57 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>65</v>
+        <v>47.4</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I10" s="3" t="n">
-        <v>50</v>
+        <v>52.6</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>N-D-N-N</t>
+          <t>N-D-N-U</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M10" s="3" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P10" s="3" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -7674,57 +7670,57 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>72.7</v>
+        <v>50</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I11" s="3" t="n">
-        <v>45.5</v>
+        <v>64.3</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M11" s="3" t="n">
-        <v>100</v>
+        <v>53.8</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P11" s="3" t="n">
-        <v>50</v>
+        <v>69.2</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
@@ -7958,19 +7954,19 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>57.1</v>
+        <v>54.5</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -7978,19 +7974,19 @@
         </is>
       </c>
       <c r="I15" s="3" t="n">
-        <v>53.6</v>
+        <v>40.9</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-U</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M15" s="3" t="n">
@@ -8005,7 +8001,7 @@
         </is>
       </c>
       <c r="P15" s="3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>10</v>
@@ -8171,7 +8167,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -8180,48 +8176,48 @@
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>76.5</v>
+        <v>90</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I18" s="3" t="n">
-        <v>58.8</v>
+        <v>40</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>N-N-N-N</t>
+          <t>N-N-N-D</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M18" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="P18" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -8242,7 +8238,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -8251,44 +8247,48 @@
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>100</v>
+        <v>52.4</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I19" s="3" t="n">
-        <v>100</v>
+        <v>57.1</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M19" s="3" t="inlineStr"/>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="n">
+        <v>50</v>
+      </c>
       <c r="N19" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P19" s="3" t="inlineStr"/>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>50</v>
+      </c>
       <c r="Q19" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20">
@@ -8380,19 +8380,19 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-U</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -8400,14 +8400,14 @@
         </is>
       </c>
       <c r="I21" s="3" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-N</t>
+          <t>D-N-N-U</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -8419,7 +8419,7 @@
         <v>66.7</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="P21" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -8451,19 +8451,19 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>56</v>
+        <v>58.8</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -8471,37 +8471,37 @@
         </is>
       </c>
       <c r="I22" s="3" t="n">
-        <v>52</v>
+        <v>52.9</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M22" s="3" t="n">
-        <v>61.5</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P22" s="3" t="n">
-        <v>46.2</v>
+        <v>57.1</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
@@ -8522,12 +8522,12 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F23" s="3" t="n">
@@ -8538,7 +8538,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I23" s="3" t="n">
@@ -8549,30 +8549,30 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-U</t>
+          <t>D-N-D-N</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M23" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P23" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -8957,44 +8957,48 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>100</v>
+        <v>78.3</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="J29" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>D-U-U-U</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="N29" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
           <t>D/U</t>
         </is>
       </c>
-      <c r="I29" s="3" t="n">
+      <c r="P29" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="J29" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>D-U-U-N</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M29" s="3" t="inlineStr"/>
-      <c r="N29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P29" s="3" t="inlineStr"/>
       <c r="Q29" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30">
@@ -9086,19 +9090,19 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -9106,37 +9110,33 @@
         </is>
       </c>
       <c r="I31" s="3" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-U</t>
+          <t>U-D-U-N</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M31" s="3" t="n">
-        <v>75</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr"/>
       <c r="N31" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P31" s="3" t="n">
-        <v>62.5</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr"/>
       <c r="Q31" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -9157,19 +9157,19 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-U</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>81.8</v>
+        <v>53.8</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -9177,14 +9177,14 @@
         </is>
       </c>
       <c r="I32" s="3" t="n">
-        <v>63.6</v>
+        <v>53.8</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>U-N-N-N</t>
+          <t>U-N-N-U</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -9193,21 +9193,21 @@
         </is>
       </c>
       <c r="M32" s="3" t="n">
-        <v>80</v>
+        <v>66.7</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="P32" s="3" t="n">
-        <v>40</v>
+        <v>33.3</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -9228,7 +9228,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-U</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -9237,48 +9237,48 @@
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>50</v>
+        <v>58.3</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I33" s="3" t="n">
-        <v>43.8</v>
+        <v>41.7</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-N</t>
+          <t>D-U-N-U</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M33" s="3" t="n">
-        <v>50</v>
+        <v>61.5</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P33" s="3" t="n">
-        <v>75</v>
+        <v>38.5</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="34">
@@ -9299,7 +9299,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -9308,25 +9308,25 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>56.7</v>
+        <v>77.8</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="I34" s="3" t="n">
-        <v>46.7</v>
+        <v>44.4</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-U</t>
+          <t>D-U-U-N</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -9335,21 +9335,21 @@
         </is>
       </c>
       <c r="M34" s="3" t="n">
-        <v>46.2</v>
+        <v>100</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P34" s="3" t="n">
-        <v>53.8</v>
+        <v>100</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -9370,7 +9370,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -9379,25 +9379,25 @@
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I35" s="3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-U</t>
+          <t>D-D-N-N</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -9409,18 +9409,18 @@
         <v>100</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P35" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -9512,19 +9512,19 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>37.9</v>
+        <v>50</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -9532,26 +9532,26 @@
         </is>
       </c>
       <c r="I37" s="3" t="n">
-        <v>51.7</v>
+        <v>57.1</v>
       </c>
       <c r="J37" s="4" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-D</t>
+          <t>U-D-U-N</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M37" s="3" t="n">
-        <v>42.9</v>
+        <v>66.7</v>
       </c>
       <c r="N37" s="4" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
@@ -9559,10 +9559,10 @@
         </is>
       </c>
       <c r="P37" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="Q37" s="4" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
@@ -9654,7 +9654,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -9663,34 +9663,34 @@
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>62.5</v>
+        <v>46.4</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I39" s="3" t="n">
-        <v>37.5</v>
+        <v>39.3</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-N</t>
+          <t>N-U-D-U</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M39" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="N39" s="4" t="n">
         <v>6</v>
@@ -9701,7 +9701,7 @@
         </is>
       </c>
       <c r="P39" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="Q39" s="4" t="n">
         <v>6</v>
@@ -9796,7 +9796,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -9805,10 +9805,10 @@
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>41.4</v>
+        <v>50</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -9816,37 +9816,37 @@
         </is>
       </c>
       <c r="I41" s="3" t="n">
-        <v>48.3</v>
+        <v>50</v>
       </c>
       <c r="J41" s="4" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M41" s="3" t="n">
-        <v>46.2</v>
+        <v>50</v>
       </c>
       <c r="N41" s="4" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P41" s="3" t="n">
-        <v>53.8</v>
+        <v>50</v>
       </c>
       <c r="Q41" s="4" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F42" s="3" t="n">
@@ -9894,26 +9894,30 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>D-N-D-U</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M42" s="3" t="inlineStr"/>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="N42" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P42" s="3" t="inlineStr"/>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="Q42" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -10005,7 +10009,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -10014,44 +10018,48 @@
         </is>
       </c>
       <c r="F44" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="J44" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>D-D-U-D</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="G44" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I44" s="3" t="n">
+      <c r="N44" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P44" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="J44" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>D-D-U-N</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M44" s="3" t="inlineStr"/>
-      <c r="N44" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P44" s="3" t="inlineStr"/>
       <c r="Q44" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45">
@@ -10214,7 +10222,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -10223,30 +10231,30 @@
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I47" s="3" t="n">
-        <v>44.4</v>
+        <v>40.9</v>
       </c>
       <c r="J47" s="4" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-N</t>
+          <t>N-U-D-U</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="M47" s="3" t="n">
@@ -10285,57 +10293,57 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>83.3</v>
+        <v>41.2</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I48" s="3" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="J48" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>D-N-U-U</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="N48" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P48" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="J48" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>D-N-U-N</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M48" s="3" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="N48" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="O48" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P48" s="3" t="n">
-        <v>66.7</v>
-      </c>
       <c r="Q48" s="4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="49">
@@ -10427,7 +10435,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-U</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -10436,44 +10444,48 @@
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>60</v>
+        <v>64.7</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I50" s="3" t="n">
-        <v>60</v>
+        <v>47.1</v>
       </c>
       <c r="J50" s="4" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>N-U-N-N</t>
+          <t>N-U-N-U</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M50" s="3" t="inlineStr"/>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="n">
+        <v>66.7</v>
+      </c>
       <c r="N50" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P50" s="3" t="inlineStr"/>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P50" s="3" t="n">
+        <v>66.7</v>
+      </c>
       <c r="Q50" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
@@ -10565,7 +10577,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -10574,48 +10586,48 @@
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>42.1</v>
+        <v>54.3</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I52" s="3" t="n">
-        <v>42.1</v>
+        <v>42.9</v>
       </c>
       <c r="J52" s="4" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-U</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M52" s="3" t="n">
-        <v>44.4</v>
+        <v>50</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P52" s="3" t="n">
-        <v>55.6</v>
+        <v>50</v>
       </c>
       <c r="Q52" s="4" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="53">
@@ -10636,7 +10648,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -10645,37 +10657,37 @@
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>77.8</v>
+        <v>57.1</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I53" s="3" t="n">
-        <v>66.7</v>
+        <v>42.9</v>
       </c>
       <c r="J53" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M53" s="3" t="n">
-        <v>66.7</v>
+        <v>75</v>
       </c>
       <c r="N53" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
@@ -10683,10 +10695,10 @@
         </is>
       </c>
       <c r="P53" s="3" t="n">
-        <v>66.7</v>
+        <v>75</v>
       </c>
       <c r="Q53" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54">
@@ -10774,19 +10786,19 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>43.2</v>
+        <v>70</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -10794,37 +10806,37 @@
         </is>
       </c>
       <c r="I55" s="3" t="n">
-        <v>51.4</v>
+        <v>40</v>
       </c>
       <c r="J55" s="4" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M55" s="3" t="n">
-        <v>42.1</v>
+        <v>80</v>
       </c>
       <c r="N55" s="4" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="P55" s="3" t="n">
-        <v>52.6</v>
+        <v>40</v>
       </c>
       <c r="Q55" s="4" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56">
@@ -10916,7 +10928,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -10925,10 +10937,10 @@
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>54.3</v>
+        <v>85.7</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -10936,37 +10948,37 @@
         </is>
       </c>
       <c r="I57" s="3" t="n">
-        <v>45.7</v>
+        <v>50</v>
       </c>
       <c r="J57" s="4" t="n">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M57" s="3" t="n">
-        <v>42.9</v>
+        <v>83.3</v>
       </c>
       <c r="N57" s="4" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P57" s="3" t="n">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="Q57" s="4" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58">
@@ -10987,7 +10999,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -10996,48 +11008,48 @@
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>52.4</v>
+        <v>68.8</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I58" s="3" t="n">
-        <v>47.6</v>
+        <v>56.2</v>
       </c>
       <c r="J58" s="4" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-U</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M58" s="3" t="n">
-        <v>54.5</v>
+        <v>66.7</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="P58" s="3" t="n">
-        <v>45.5</v>
+        <v>50</v>
       </c>
       <c r="Q58" s="4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="59">
@@ -11129,7 +11141,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -11138,25 +11150,25 @@
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>64.7</v>
+        <v>63.6</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I60" s="3" t="n">
-        <v>47.1</v>
+        <v>54.5</v>
       </c>
       <c r="J60" s="4" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-N</t>
+          <t>U-U-D-U</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
@@ -11165,21 +11177,21 @@
         </is>
       </c>
       <c r="M60" s="3" t="n">
-        <v>55.6</v>
+        <v>57.1</v>
       </c>
       <c r="N60" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P60" s="3" t="n">
-        <v>44.4</v>
+        <v>57.1</v>
       </c>
       <c r="Q60" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61">
@@ -11342,7 +11354,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -11351,25 +11363,25 @@
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I63" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="J63" s="4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-N</t>
+          <t>U-U-D-U</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
@@ -11381,18 +11393,18 @@
         <v>100</v>
       </c>
       <c r="N63" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P63" s="3" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
       <c r="Q63" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64">
@@ -11413,7 +11425,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -11422,48 +11434,48 @@
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>44.4</v>
+        <v>38.7</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I64" s="3" t="n">
-        <v>44.4</v>
+        <v>38.7</v>
       </c>
       <c r="J64" s="4" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-N</t>
+          <t>N-D-D-D</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M64" s="3" t="n">
-        <v>50</v>
+        <v>42.9</v>
       </c>
       <c r="N64" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P64" s="3" t="n">
-        <v>50</v>
+        <v>42.9</v>
       </c>
       <c r="Q64" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65">
@@ -11768,7 +11780,7 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -11777,44 +11789,48 @@
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>100</v>
+        <v>62.5</v>
       </c>
       <c r="G69" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="I69" s="3" t="n">
-        <v>100</v>
+        <v>37.5</v>
       </c>
       <c r="J69" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-U</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M69" s="3" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M69" s="3" t="n">
+        <v>75</v>
+      </c>
       <c r="N69" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P69" s="3" t="inlineStr"/>
+          <t>N/U</t>
+        </is>
+      </c>
+      <c r="P69" s="3" t="n">
+        <v>50</v>
+      </c>
       <c r="Q69" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70">
@@ -11835,7 +11851,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -11844,10 +11860,10 @@
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>46.2</v>
+        <v>50</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -11855,37 +11871,37 @@
         </is>
       </c>
       <c r="I70" s="3" t="n">
-        <v>46.2</v>
+        <v>50</v>
       </c>
       <c r="J70" s="4" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-D</t>
+          <t>U-U-U-N</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M70" s="3" t="n">
-        <v>41.7</v>
+        <v>50</v>
       </c>
       <c r="N70" s="4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P70" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="Q70" s="4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71">
@@ -11906,7 +11922,7 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -11915,25 +11931,25 @@
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>45.5</v>
+        <v>60</v>
       </c>
       <c r="G71" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I71" s="3" t="n">
-        <v>63.6</v>
+        <v>60</v>
       </c>
       <c r="J71" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-U</t>
+          <t>D-D-N-N</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
@@ -11942,21 +11958,21 @@
         </is>
       </c>
       <c r="M71" s="3" t="n">
-        <v>66.7</v>
+        <v>75</v>
       </c>
       <c r="N71" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="P71" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="Q71" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="72">
@@ -12119,7 +12135,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -12128,25 +12144,25 @@
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>52.9</v>
+        <v>55.2</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I74" s="3" t="n">
-        <v>64.7</v>
+        <v>44.8</v>
       </c>
       <c r="J74" s="4" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
@@ -12158,18 +12174,18 @@
         <v>50</v>
       </c>
       <c r="N74" s="4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P74" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="Q74" s="4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="75">
@@ -12399,57 +12415,57 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F78" s="3" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="G78" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I78" s="3" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="J78" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>D-D-N-U</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M78" s="3" t="n">
         <v>71.40000000000001</v>
       </c>
-      <c r="G78" s="4" t="n">
+      <c r="N78" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>D/U</t>
-        </is>
-      </c>
-      <c r="I78" s="3" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="J78" s="4" t="n">
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P78" s="3" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="Q78" s="4" t="n">
         <v>7</v>
-      </c>
-      <c r="K78" s="2" t="inlineStr">
-        <is>
-          <t>D-D-N-N</t>
-        </is>
-      </c>
-      <c r="L78" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="M78" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="N78" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O78" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P78" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q78" s="4" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -12683,7 +12699,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-U</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -12692,10 +12708,10 @@
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -12703,33 +12719,37 @@
         </is>
       </c>
       <c r="I82" s="3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="J82" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-N</t>
+          <t>D-U-N-U</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M82" s="3" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M82" s="3" t="n">
+        <v>66.7</v>
+      </c>
       <c r="N82" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P82" s="3" t="inlineStr"/>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P82" s="3" t="n">
+        <v>66.7</v>
+      </c>
       <c r="Q82" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -12750,57 +12770,57 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F83" s="3" t="n">
-        <v>44</v>
+        <v>53.1</v>
       </c>
       <c r="G83" s="4" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I83" s="3" t="n">
-        <v>44</v>
+        <v>59.4</v>
       </c>
       <c r="J83" s="4" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M83" s="3" t="n">
         <v>66.7</v>
       </c>
       <c r="N83" s="4" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P83" s="3" t="n">
-        <v>55.6</v>
+        <v>66.7</v>
       </c>
       <c r="Q83" s="4" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="84">
@@ -12821,7 +12841,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -12830,10 +12850,10 @@
         </is>
       </c>
       <c r="F84" s="3" t="n">
-        <v>73.3</v>
+        <v>43.5</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -12841,37 +12861,37 @@
         </is>
       </c>
       <c r="I84" s="3" t="n">
-        <v>40</v>
+        <v>47.8</v>
       </c>
       <c r="J84" s="4" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-N</t>
+          <t>N-U-D-U</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M84" s="3" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="N84" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P84" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="Q84" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="85">
@@ -12963,57 +12983,57 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F86" s="3" t="n">
-        <v>80</v>
+        <v>47.1</v>
       </c>
       <c r="G86" s="4" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I86" s="3" t="n">
-        <v>60</v>
+        <v>41.2</v>
       </c>
       <c r="J86" s="4" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-N</t>
+          <t>D-D-N-D</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M86" s="3" t="n">
-        <v>75</v>
+        <v>83.3</v>
       </c>
       <c r="N86" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P86" s="3" t="n">
         <v>50</v>
       </c>
       <c r="Q86" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="87">
@@ -13034,7 +13054,7 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -13043,25 +13063,25 @@
         </is>
       </c>
       <c r="F87" s="3" t="n">
-        <v>62.5</v>
+        <v>60</v>
       </c>
       <c r="G87" s="4" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I87" s="3" t="n">
-        <v>37.5</v>
+        <v>40</v>
       </c>
       <c r="J87" s="4" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>N-N-U-N</t>
+          <t>N-N-U-U</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
@@ -13070,10 +13090,10 @@
         </is>
       </c>
       <c r="M87" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="N87" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
@@ -13081,10 +13101,10 @@
         </is>
       </c>
       <c r="P87" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="Q87" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
@@ -13389,19 +13409,19 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F92" s="3" t="n">
-        <v>44.4</v>
+        <v>45.2</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -13409,33 +13429,37 @@
         </is>
       </c>
       <c r="I92" s="3" t="n">
-        <v>55.6</v>
+        <v>45.2</v>
       </c>
       <c r="J92" s="4" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-N</t>
+          <t>U-U-D-U</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M92" s="3" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M92" s="3" t="n">
+        <v>54.5</v>
+      </c>
       <c r="N92" s="4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P92" s="3" t="inlineStr"/>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P92" s="3" t="n">
+        <v>63.6</v>
+      </c>
       <c r="Q92" s="4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="93">
@@ -13527,7 +13551,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -13536,37 +13560,37 @@
         </is>
       </c>
       <c r="F94" s="3" t="n">
-        <v>59.1</v>
+        <v>58.6</v>
       </c>
       <c r="G94" s="4" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I94" s="3" t="n">
-        <v>40.9</v>
+        <v>41.4</v>
       </c>
       <c r="J94" s="4" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-N</t>
+          <t>N-U-U-U</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M94" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N94" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
@@ -13574,10 +13598,10 @@
         </is>
       </c>
       <c r="P94" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="Q94" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="95">
@@ -13598,34 +13622,34 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F95" s="3" t="n">
-        <v>33.3</v>
+        <v>56.2</v>
       </c>
       <c r="G95" s="4" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I95" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="J95" s="4" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-N</t>
+          <t>U-U-D-D</t>
         </is>
       </c>
       <c r="L95" s="2" t="inlineStr">
@@ -13634,21 +13658,21 @@
         </is>
       </c>
       <c r="M95" s="3" t="n">
-        <v>50</v>
+        <v>42.9</v>
       </c>
       <c r="N95" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P95" s="3" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
       <c r="Q95" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="96">
@@ -13811,57 +13835,57 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F98" s="3" t="n">
-        <v>53.3</v>
+        <v>66.7</v>
       </c>
       <c r="G98" s="4" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I98" s="3" t="n">
-        <v>53.3</v>
+        <v>54.2</v>
       </c>
       <c r="J98" s="4" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-N</t>
+          <t>N-U-D-U</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M98" s="3" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="N98" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P98" s="3" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="Q98" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="99">
@@ -13953,57 +13977,57 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F100" s="3" t="n">
-        <v>66.7</v>
+        <v>46.7</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I100" s="3" t="n">
-        <v>46.7</v>
+        <v>56.7</v>
       </c>
       <c r="J100" s="4" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-N</t>
+          <t>N-U-D-U</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="M100" s="3" t="n">
         <v>50</v>
       </c>
       <c r="N100" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="P100" s="3" t="n">
         <v>50</v>
       </c>
       <c r="Q100" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101">
@@ -14024,19 +14048,19 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-U</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F101" s="3" t="n">
-        <v>47.6</v>
+        <v>50</v>
       </c>
       <c r="G101" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
@@ -14044,14 +14068,14 @@
         </is>
       </c>
       <c r="I101" s="3" t="n">
-        <v>47.6</v>
+        <v>66.7</v>
       </c>
       <c r="J101" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>N-U-N-N</t>
+          <t>N-U-N-U</t>
         </is>
       </c>
       <c r="L101" s="2" t="inlineStr">
@@ -14060,10 +14084,10 @@
         </is>
       </c>
       <c r="M101" s="3" t="n">
-        <v>54.5</v>
+        <v>100</v>
       </c>
       <c r="N101" s="4" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
@@ -14071,10 +14095,10 @@
         </is>
       </c>
       <c r="P101" s="3" t="n">
-        <v>45.5</v>
+        <v>100</v>
       </c>
       <c r="Q101" s="4" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
@@ -14095,7 +14119,7 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-U</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -14104,10 +14128,10 @@
         </is>
       </c>
       <c r="F102" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="G102" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
@@ -14115,14 +14139,14 @@
         </is>
       </c>
       <c r="I102" s="3" t="n">
-        <v>52.9</v>
+        <v>44.4</v>
       </c>
       <c r="J102" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-N</t>
+          <t>D-U-N-U</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
@@ -14131,21 +14155,21 @@
         </is>
       </c>
       <c r="M102" s="3" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="N102" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P102" s="3" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="Q102" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103">
@@ -14166,7 +14190,7 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -14175,37 +14199,37 @@
         </is>
       </c>
       <c r="F103" s="3" t="n">
-        <v>57.1</v>
+        <v>43.8</v>
       </c>
       <c r="G103" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I103" s="3" t="n">
-        <v>57.1</v>
+        <v>43.8</v>
       </c>
       <c r="J103" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-N</t>
+          <t>U-N-D-U</t>
         </is>
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M103" s="3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="N103" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
@@ -14213,10 +14237,10 @@
         </is>
       </c>
       <c r="P103" s="3" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="Q103" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="104">

--- a/BIS_tr.xlsx
+++ b/BIS_tr.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>62.4</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>149</v>
+        <v>77</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -780,14 +780,14 @@
         </is>
       </c>
       <c r="G5" s="3" t="n">
-        <v>46.3</v>
+        <v>45.5</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>149</v>
+        <v>77</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-U</t>
+          <t>N-D-D-N</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -796,21 +796,21 @@
         </is>
       </c>
       <c r="K5" s="3" t="n">
-        <v>57.1</v>
+        <v>78.3</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N5" s="3" t="n">
-        <v>57.1</v>
+        <v>39.1</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
@@ -882,7 +882,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -891,10 +891,10 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>58.4</v>
+        <v>63.6</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>161</v>
+        <v>77</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -902,14 +902,14 @@
         </is>
       </c>
       <c r="G7" s="3" t="n">
-        <v>45.3</v>
+        <v>40.3</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>161</v>
+        <v>77</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-U</t>
+          <t>U-U-D-N</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -918,10 +918,10 @@
         </is>
       </c>
       <c r="K7" s="3" t="n">
-        <v>66.2</v>
+        <v>63</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="N7" s="3" t="n">
-        <v>41.2</v>
+        <v>37</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>68</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-N-N</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>69.7</v>
+        <v>77</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>109</v>
+        <v>248</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -1024,14 +1024,14 @@
         </is>
       </c>
       <c r="G9" s="3" t="n">
-        <v>46.8</v>
+        <v>60.9</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>109</v>
+        <v>248</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-U</t>
+          <t>D-N-N-N</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="K9" s="3" t="n">
-        <v>60</v>
+        <v>71.8</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="N9" s="3" t="n">
-        <v>44</v>
+        <v>51.3</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>25</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1074,25 +1074,25 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>66.3</v>
+        <v>71.7</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G10" s="3" t="n">
-        <v>41.9</v>
+        <v>35.8</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>N-D-N-U</t>
+          <t>N-D-N-N</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1101,21 +1101,21 @@
         </is>
       </c>
       <c r="K10" s="3" t="n">
-        <v>61.1</v>
+        <v>64.3</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="N10" s="3" t="n">
-        <v>44.4</v>
+        <v>35.7</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1501,10 +1501,10 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>64.40000000000001</v>
+        <v>59.6</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>73</v>
+        <v>146</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1512,14 +1512,14 @@
         </is>
       </c>
       <c r="G17" s="3" t="n">
-        <v>42.5</v>
+        <v>39.7</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>73</v>
+        <v>146</v>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1528,10 +1528,10 @@
         </is>
       </c>
       <c r="K17" s="3" t="n">
-        <v>70.8</v>
+        <v>56.6</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
@@ -1539,10 +1539,10 @@
         </is>
       </c>
       <c r="N17" s="3" t="n">
-        <v>41.7</v>
+        <v>45.3</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>24</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18">
@@ -1858,46 +1858,46 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>46.2</v>
+        <v>67.7</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="G23" s="3" t="n">
-        <v>46.2</v>
+        <v>35.5</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>D-N-D-D</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K23" s="3" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
@@ -1905,10 +1905,10 @@
         </is>
       </c>
       <c r="N23" s="3" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2050,48 +2050,48 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>51.2</v>
+        <v>49.5</v>
       </c>
       <c r="E26" s="4" t="n">
+        <v>188</v>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>188</v>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>U-U-U-U</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="L26" s="4" t="n">
         <v>82</v>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="n">
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="n">
         <v>45.1</v>
       </c>
-      <c r="H26" s="4" t="n">
+      <c r="O26" s="4" t="n">
         <v>82</v>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>U-U-U-N</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="n">
-        <v>51.4</v>
-      </c>
-      <c r="L26" s="4" t="n">
-        <v>37</v>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="N26" s="3" t="n">
-        <v>51.4</v>
-      </c>
-      <c r="O26" s="4" t="n">
-        <v>37</v>
       </c>
     </row>
     <row r="27">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2721,25 +2721,25 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>57.4</v>
+        <v>58.8</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>61</v>
+        <v>153</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G37" s="3" t="n">
-        <v>37.7</v>
+        <v>47.7</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>61</v>
+        <v>153</v>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -2748,21 +2748,21 @@
         </is>
       </c>
       <c r="K37" s="3" t="n">
-        <v>54.2</v>
+        <v>58.6</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N37" s="3" t="n">
-        <v>58.3</v>
+        <v>50</v>
       </c>
       <c r="O37" s="4" t="n">
-        <v>24</v>
+        <v>58</v>
       </c>
     </row>
     <row r="38">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2965,25 +2965,25 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>68.2</v>
+        <v>50.9</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>22</v>
+        <v>108</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G41" s="3" t="n">
-        <v>54.5</v>
+        <v>51.9</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>22</v>
+        <v>108</v>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -2992,10 +2992,10 @@
         </is>
       </c>
       <c r="K41" s="3" t="n">
-        <v>75</v>
+        <v>49.2</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>8</v>
+        <v>61</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
@@ -3003,10 +3003,10 @@
         </is>
       </c>
       <c r="N41" s="3" t="n">
-        <v>62.5</v>
+        <v>45.9</v>
       </c>
       <c r="O41" s="4" t="n">
-        <v>8</v>
+        <v>61</v>
       </c>
     </row>
     <row r="42">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>62</v>
+        <v>70.3</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>79</v>
+        <v>37</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3464,14 +3464,14 @@
         </is>
       </c>
       <c r="G49" s="3" t="n">
-        <v>44.3</v>
+        <v>54.1</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>79</v>
+        <v>37</v>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-U</t>
+          <t>U-N-D-N</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -3480,10 +3480,10 @@
         </is>
       </c>
       <c r="K49" s="3" t="n">
-        <v>74.09999999999999</v>
+        <v>57.9</v>
       </c>
       <c r="L49" s="4" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
@@ -3491,10 +3491,10 @@
         </is>
       </c>
       <c r="N49" s="3" t="n">
-        <v>51.9</v>
+        <v>57.9</v>
       </c>
       <c r="O49" s="4" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="50">
@@ -3688,7 +3688,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3697,10 +3697,10 @@
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>56.2</v>
+        <v>60.5</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3708,26 +3708,26 @@
         </is>
       </c>
       <c r="G53" s="3" t="n">
-        <v>56.2</v>
+        <v>44.7</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K53" s="3" t="n">
-        <v>57.1</v>
+        <v>58.8</v>
       </c>
       <c r="L53" s="4" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="N53" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>52.9</v>
       </c>
       <c r="O53" s="4" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="54">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3941,10 +3941,10 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>73</v>
+        <v>49.4</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>74</v>
+        <v>156</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3952,26 +3952,26 @@
         </is>
       </c>
       <c r="G57" s="3" t="n">
-        <v>40.5</v>
+        <v>41.7</v>
       </c>
       <c r="H57" s="4" t="n">
-        <v>74</v>
+        <v>156</v>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K57" s="3" t="n">
-        <v>70</v>
+        <v>46.7</v>
       </c>
       <c r="L57" s="4" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
@@ -3979,10 +3979,10 @@
         </is>
       </c>
       <c r="N57" s="3" t="n">
-        <v>43.3</v>
+        <v>41.7</v>
       </c>
       <c r="O57" s="4" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
     </row>
     <row r="58">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -4551,48 +4551,48 @@
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>55.6</v>
+        <v>75</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="G67" s="3" t="n">
-        <v>55.6</v>
+        <v>50</v>
       </c>
       <c r="H67" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-U</t>
+          <t>D-U-U-N</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K67" s="3" t="n">
-        <v>40</v>
+        <v>66.7</v>
       </c>
       <c r="L67" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N67" s="3" t="n">
-        <v>40</v>
+        <v>66.7</v>
       </c>
       <c r="O67" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -4734,25 +4734,25 @@
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>69.90000000000001</v>
+        <v>61.1</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>73</v>
+        <v>167</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G70" s="3" t="n">
-        <v>47.9</v>
+        <v>41.3</v>
       </c>
       <c r="H70" s="4" t="n">
-        <v>73</v>
+        <v>167</v>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-U</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -4761,21 +4761,21 @@
         </is>
       </c>
       <c r="K70" s="3" t="n">
-        <v>62.1</v>
+        <v>57.4</v>
       </c>
       <c r="L70" s="4" t="n">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N70" s="3" t="n">
-        <v>58.6</v>
+        <v>47.1</v>
       </c>
       <c r="O70" s="4" t="n">
-        <v>29</v>
+        <v>68</v>
       </c>
     </row>
     <row r="71">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -5161,10 +5161,10 @@
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>56.2</v>
+        <v>74.7</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>130</v>
+        <v>83</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -5172,14 +5172,14 @@
         </is>
       </c>
       <c r="G77" s="3" t="n">
-        <v>44.6</v>
+        <v>38.6</v>
       </c>
       <c r="H77" s="4" t="n">
-        <v>130</v>
+        <v>83</v>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -5188,10 +5188,10 @@
         </is>
       </c>
       <c r="K77" s="3" t="n">
-        <v>60.8</v>
+        <v>72</v>
       </c>
       <c r="L77" s="4" t="n">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
@@ -5199,10 +5199,10 @@
         </is>
       </c>
       <c r="N77" s="3" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="O77" s="4" t="n">
-        <v>51</v>
+        <v>25</v>
       </c>
     </row>
     <row r="78">
@@ -7248,7 +7248,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -7257,10 +7257,10 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>62.2</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -7268,14 +7268,14 @@
         </is>
       </c>
       <c r="I5" s="3" t="n">
-        <v>45.9</v>
+        <v>47.1</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-U</t>
+          <t>N-D-D-N</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -7284,10 +7284,10 @@
         </is>
       </c>
       <c r="M5" s="3" t="n">
-        <v>66.7</v>
+        <v>75</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
@@ -7295,10 +7295,10 @@
         </is>
       </c>
       <c r="P5" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -7399,48 +7399,48 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>55.2</v>
+        <v>38.5</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I7" s="3" t="n">
-        <v>48.3</v>
+        <v>46.2</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-U</t>
+          <t>U-U-D-N</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="M7" s="3" t="n">
-        <v>53.3</v>
+        <v>33.3</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P7" s="3" t="n">
-        <v>53.3</v>
+        <v>66.7</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -7528,34 +7528,34 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-N-N</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>47.6</v>
+        <v>75.5</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I9" s="3" t="n">
-        <v>47.6</v>
+        <v>65.3</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-U</t>
+          <t>D-N-N-N</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -7564,21 +7564,21 @@
         </is>
       </c>
       <c r="M9" s="3" t="n">
-        <v>60</v>
+        <v>85.7</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P9" s="3" t="n">
-        <v>60</v>
+        <v>42.9</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -7599,57 +7599,57 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>47.4</v>
+        <v>65</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I10" s="3" t="n">
-        <v>52.6</v>
+        <v>50</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>N-D-N-U</t>
+          <t>N-D-N-N</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M10" s="3" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P10" s="3" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -8105,10 +8105,10 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>61.1</v>
+        <v>62.9</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -8116,14 +8116,14 @@
         </is>
       </c>
       <c r="I17" s="3" t="n">
-        <v>55.6</v>
+        <v>57.1</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -8132,10 +8132,10 @@
         </is>
       </c>
       <c r="M17" s="3" t="n">
-        <v>57.1</v>
+        <v>66.7</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -8143,10 +8143,10 @@
         </is>
       </c>
       <c r="P17" s="3" t="n">
-        <v>42.9</v>
+        <v>46.7</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
@@ -8522,57 +8522,53 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I23" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>D-N-D-D</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
-        </is>
-      </c>
-      <c r="M23" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr"/>
       <c r="N23" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
-        </is>
-      </c>
-      <c r="P23" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr"/>
       <c r="Q23" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -8735,57 +8731,57 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>45.5</v>
+        <v>54.8</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I26" s="3" t="n">
-        <v>40.9</v>
+        <v>61.3</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-U</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M26" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>46.7</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P26" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>60</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27">
@@ -9512,57 +9508,57 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="F37" s="3" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="J37" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>U-D-U-D</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="N37" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P37" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="G37" s="4" t="n">
+      <c r="Q37" s="4" t="n">
         <v>14</v>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I37" s="3" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="J37" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>U-D-U-N</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="M37" s="3" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="N37" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P37" s="3" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="Q37" s="4" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="38">
@@ -9796,57 +9792,57 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>50</v>
+        <v>53.1</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I41" s="3" t="n">
-        <v>50</v>
+        <v>68.8</v>
       </c>
       <c r="J41" s="4" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M41" s="3" t="n">
-        <v>50</v>
+        <v>52.6</v>
       </c>
       <c r="N41" s="4" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P41" s="3" t="n">
-        <v>50</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="Q41" s="4" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="42">
@@ -10364,7 +10360,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -10376,22 +10372,22 @@
         <v>50</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I49" s="3" t="n">
-        <v>41.7</v>
+        <v>83.3</v>
       </c>
       <c r="J49" s="4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-U</t>
+          <t>U-N-D-N</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
@@ -10400,21 +10396,21 @@
         </is>
       </c>
       <c r="M49" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="N49" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P49" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="N49" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="O49" s="2" t="inlineStr">
-        <is>
-          <t>N/U</t>
-        </is>
-      </c>
-      <c r="P49" s="3" t="n">
-        <v>50</v>
-      </c>
       <c r="Q49" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50">
@@ -10648,19 +10644,19 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>57.1</v>
+        <v>40</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -10668,37 +10664,37 @@
         </is>
       </c>
       <c r="I53" s="3" t="n">
-        <v>42.9</v>
+        <v>40</v>
       </c>
       <c r="J53" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M53" s="3" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="N53" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P53" s="3" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="Q53" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -10928,7 +10924,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -10937,10 +10933,10 @@
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>85.7</v>
+        <v>42.5</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -10948,37 +10944,37 @@
         </is>
       </c>
       <c r="I57" s="3" t="n">
-        <v>50</v>
+        <v>42.5</v>
       </c>
       <c r="J57" s="4" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M57" s="3" t="n">
-        <v>83.3</v>
+        <v>63.6</v>
       </c>
       <c r="N57" s="4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="P57" s="3" t="n">
-        <v>50</v>
+        <v>36.4</v>
       </c>
       <c r="Q57" s="4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="58">
@@ -11638,57 +11634,49 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F67" s="3" t="n">
-        <v>66.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr"/>
       <c r="G67" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I67" s="3" t="n">
-        <v>66.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="inlineStr"/>
       <c r="J67" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-U</t>
+          <t>D-U-U-N</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="M67" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M67" s="3" t="inlineStr"/>
       <c r="N67" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P67" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P67" s="3" t="inlineStr"/>
       <c r="Q67" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -11851,7 +11839,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -11863,7 +11851,7 @@
         <v>50</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -11871,26 +11859,26 @@
         </is>
       </c>
       <c r="I70" s="3" t="n">
-        <v>50</v>
+        <v>42.9</v>
       </c>
       <c r="J70" s="4" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-U</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M70" s="3" t="n">
         <v>50</v>
       </c>
       <c r="N70" s="4" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
@@ -11898,10 +11886,10 @@
         </is>
       </c>
       <c r="P70" s="3" t="n">
-        <v>66.7</v>
+        <v>57.1</v>
       </c>
       <c r="Q70" s="4" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="71">
@@ -12344,7 +12332,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -12353,25 +12341,25 @@
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>48</v>
+        <v>66.7</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I77" s="3" t="n">
-        <v>56</v>
+        <v>53.3</v>
       </c>
       <c r="J77" s="4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
@@ -12380,21 +12368,21 @@
         </is>
       </c>
       <c r="M77" s="3" t="n">
-        <v>54.5</v>
+        <v>100</v>
       </c>
       <c r="N77" s="4" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P77" s="3" t="n">
-        <v>63.6</v>
+        <v>50</v>
       </c>
       <c r="Q77" s="4" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78">

--- a/BIS_tr.xlsx
+++ b/BIS_tr.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -769,48 +769,48 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>65.7</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>105</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>N-D-D-D</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="G5" s="3" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>77</v>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>N-D-D-N</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="n">
-        <v>78.3</v>
-      </c>
-      <c r="L5" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>D/U</t>
-        </is>
-      </c>
       <c r="N5" s="3" t="n">
-        <v>39.1</v>
+        <v>48.1</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6">
@@ -821,7 +821,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -830,25 +830,25 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>59.7</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G6" s="3" t="n">
-        <v>46.8</v>
+        <v>40.5</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-U</t>
+          <t>U-N-D-N</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -857,21 +857,21 @@
         </is>
       </c>
       <c r="K6" s="3" t="n">
-        <v>64.5</v>
+        <v>61.5</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N6" s="3" t="n">
-        <v>48.4</v>
+        <v>38.5</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
@@ -882,7 +882,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -891,10 +891,10 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>63.6</v>
+        <v>69</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>77</v>
+        <v>158</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -902,14 +902,14 @@
         </is>
       </c>
       <c r="G7" s="3" t="n">
-        <v>40.3</v>
+        <v>42.4</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>77</v>
+        <v>158</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-N</t>
+          <t>U-U-D-D</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -918,10 +918,10 @@
         </is>
       </c>
       <c r="K7" s="3" t="n">
-        <v>63</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>27</v>
+        <v>61</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="N7" s="3" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>27</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1379,25 +1379,25 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>58</v>
+        <v>47.9</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>176</v>
+        <v>71</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G15" s="3" t="n">
-        <v>39.2</v>
+        <v>43.7</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>176</v>
+        <v>71</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-D</t>
+          <t>D-U-U-N</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1406,21 +1406,21 @@
         </is>
       </c>
       <c r="K15" s="3" t="n">
-        <v>58.4</v>
+        <v>66.7</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N15" s="3" t="n">
-        <v>37.7</v>
+        <v>48.1</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>77</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1623,25 +1623,25 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>50</v>
+        <v>56.4</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>92</v>
+        <v>39</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>46.7</v>
+        <v>46.2</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>92</v>
+        <v>39</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1650,21 +1650,21 @@
         </is>
       </c>
       <c r="K19" s="3" t="n">
-        <v>50</v>
+        <v>61.1</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N19" s="3" t="n">
-        <v>41.7</v>
+        <v>44.4</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20">
@@ -1919,39 +1919,39 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-U</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>50</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G24" s="3" t="n">
-        <v>42.9</v>
+        <v>55</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-N</t>
+          <t>D-N-N-U</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K24" s="3" t="n">
@@ -1966,7 +1966,7 @@
         </is>
       </c>
       <c r="N24" s="3" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="O24" s="4" t="n">
         <v>10</v>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>59.3</v>
+        <v>56.9</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>54</v>
+        <v>153</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -2000,14 +2000,14 @@
         </is>
       </c>
       <c r="G25" s="3" t="n">
-        <v>37</v>
+        <v>45.1</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>54</v>
+        <v>153</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -2016,21 +2016,21 @@
         </is>
       </c>
       <c r="K25" s="3" t="n">
-        <v>52.2</v>
+        <v>62.3</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N25" s="3" t="n">
-        <v>43.5</v>
+        <v>42.6</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>23</v>
+        <v>61</v>
       </c>
     </row>
     <row r="26">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>59</v>
+        <v>63.6</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -2183,14 +2183,14 @@
         </is>
       </c>
       <c r="G28" s="3" t="n">
-        <v>43.6</v>
+        <v>43.2</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-U</t>
+          <t>D-N-U-N</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="K28" s="3" t="n">
-        <v>53.8</v>
+        <v>64.7</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
@@ -2210,10 +2210,10 @@
         </is>
       </c>
       <c r="N28" s="3" t="n">
-        <v>46.2</v>
+        <v>41.2</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>U-N-N</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2477,25 +2477,25 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>63.4</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G33" s="3" t="n">
-        <v>39.8</v>
+        <v>40.3</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-U</t>
+          <t>D-U-N-N</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -2504,21 +2504,21 @@
         </is>
       </c>
       <c r="K33" s="3" t="n">
-        <v>58.5</v>
+        <v>75</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N33" s="3" t="n">
-        <v>39</v>
+        <v>37.5</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>41</v>
+        <v>24</v>
       </c>
     </row>
     <row r="34">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2721,25 +2721,25 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>58.8</v>
+        <v>57.4</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>153</v>
+        <v>61</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G37" s="3" t="n">
-        <v>47.7</v>
+        <v>37.7</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>153</v>
+        <v>61</v>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-D</t>
+          <t>U-D-U-N</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -2748,21 +2748,21 @@
         </is>
       </c>
       <c r="K37" s="3" t="n">
-        <v>58.6</v>
+        <v>54.2</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N37" s="3" t="n">
-        <v>50</v>
+        <v>58.3</v>
       </c>
       <c r="O37" s="4" t="n">
-        <v>58</v>
+        <v>24</v>
       </c>
     </row>
     <row r="38">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -3575,14 +3575,14 @@
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="E51" s="4" t="n">
         <v>9</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G51" s="3" t="n">
@@ -3593,30 +3593,30 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>N-N-N-N</t>
+          <t>N-N-N-D</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K51" s="3" t="n">
         <v>100</v>
       </c>
       <c r="L51" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N51" s="3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="O51" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3941,10 +3941,10 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>49.4</v>
+        <v>73</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>156</v>
+        <v>74</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3952,37 +3952,37 @@
         </is>
       </c>
       <c r="G57" s="3" t="n">
-        <v>41.7</v>
+        <v>40.5</v>
       </c>
       <c r="H57" s="4" t="n">
-        <v>156</v>
+        <v>74</v>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-D</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="L57" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
           <t>U</t>
         </is>
       </c>
-      <c r="K57" s="3" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="L57" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="M57" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
       <c r="N57" s="3" t="n">
-        <v>41.7</v>
+        <v>43.3</v>
       </c>
       <c r="O57" s="4" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
     </row>
     <row r="58">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -4429,10 +4429,10 @@
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>68.09999999999999</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>94</v>
+        <v>142</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -4440,14 +4440,14 @@
         </is>
       </c>
       <c r="G65" s="3" t="n">
-        <v>43.6</v>
+        <v>43</v>
       </c>
       <c r="H65" s="4" t="n">
-        <v>94</v>
+        <v>142</v>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-N</t>
+          <t>U-U-D-D</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -4456,10 +4456,10 @@
         </is>
       </c>
       <c r="K65" s="3" t="n">
-        <v>68.59999999999999</v>
+        <v>63.6</v>
       </c>
       <c r="L65" s="4" t="n">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
@@ -4467,10 +4467,10 @@
         </is>
       </c>
       <c r="N65" s="3" t="n">
-        <v>48.6</v>
+        <v>53</v>
       </c>
       <c r="O65" s="4" t="n">
-        <v>35</v>
+        <v>66</v>
       </c>
     </row>
     <row r="66">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -4490,10 +4490,10 @@
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>45.6</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>85</v>
+        <v>136</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -4501,26 +4501,26 @@
         </is>
       </c>
       <c r="G66" s="3" t="n">
-        <v>41.2</v>
+        <v>44.9</v>
       </c>
       <c r="H66" s="4" t="n">
-        <v>85</v>
+        <v>136</v>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-N</t>
+          <t>N-D-U-D</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K66" s="3" t="n">
-        <v>70.40000000000001</v>
+        <v>43.8</v>
       </c>
       <c r="L66" s="4" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
@@ -4528,10 +4528,10 @@
         </is>
       </c>
       <c r="N66" s="3" t="n">
-        <v>48.1</v>
+        <v>43.8</v>
       </c>
       <c r="O66" s="4" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
     </row>
     <row r="67">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -4734,25 +4734,25 @@
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>61.1</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>167</v>
+        <v>73</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G70" s="3" t="n">
-        <v>41.3</v>
+        <v>47.9</v>
       </c>
       <c r="H70" s="4" t="n">
-        <v>167</v>
+        <v>73</v>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-U</t>
+          <t>U-U-U-N</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -4761,21 +4761,21 @@
         </is>
       </c>
       <c r="K70" s="3" t="n">
-        <v>57.4</v>
+        <v>62.1</v>
       </c>
       <c r="L70" s="4" t="n">
-        <v>68</v>
+        <v>29</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N70" s="3" t="n">
-        <v>47.1</v>
+        <v>58.6</v>
       </c>
       <c r="O70" s="4" t="n">
-        <v>68</v>
+        <v>29</v>
       </c>
     </row>
     <row r="71">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -4978,48 +4978,48 @@
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>47.9</v>
+        <v>56.1</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>144</v>
+        <v>66</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="H74" s="4" t="n">
+        <v>66</v>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>U-D-U-N</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K74" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="L74" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
           <t>U</t>
         </is>
       </c>
-      <c r="G74" s="3" t="n">
-        <v>42.4</v>
-      </c>
-      <c r="H74" s="4" t="n">
-        <v>144</v>
-      </c>
-      <c r="I74" s="2" t="inlineStr">
-        <is>
-          <t>U-D-U-D</t>
-        </is>
-      </c>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="K74" s="3" t="n">
-        <v>46.3</v>
-      </c>
-      <c r="L74" s="4" t="n">
-        <v>54</v>
-      </c>
-      <c r="M74" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
       <c r="N74" s="3" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="O74" s="4" t="n">
-        <v>54</v>
+        <v>25</v>
       </c>
     </row>
     <row r="75">
@@ -6372,7 +6372,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -6381,48 +6381,48 @@
         </is>
       </c>
       <c r="D97" s="3" t="n">
-        <v>73</v>
+        <v>61.9</v>
       </c>
       <c r="E97" s="4" t="n">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
+          <t>D/U</t>
+        </is>
+      </c>
+      <c r="G97" s="3" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="H97" s="4" t="n">
+        <v>134</v>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>U-U-D-U</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K97" s="3" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="L97" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="G97" s="3" t="n">
-        <v>36.5</v>
-      </c>
-      <c r="H97" s="4" t="n">
-        <v>74</v>
-      </c>
-      <c r="I97" s="2" t="inlineStr">
-        <is>
-          <t>U-U-D-N</t>
-        </is>
-      </c>
-      <c r="J97" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K97" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="L97" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="M97" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
       <c r="N97" s="3" t="n">
-        <v>40</v>
+        <v>47.1</v>
       </c>
       <c r="O97" s="4" t="n">
-        <v>25</v>
+        <v>51</v>
       </c>
     </row>
     <row r="98">
@@ -6494,7 +6494,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -6503,25 +6503,25 @@
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>48.6</v>
+        <v>64.8</v>
       </c>
       <c r="E99" s="4" t="n">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G99" s="3" t="n">
-        <v>36.5</v>
+        <v>42.6</v>
       </c>
       <c r="H99" s="4" t="n">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-U</t>
+          <t>D-N-U-N</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
@@ -6530,10 +6530,10 @@
         </is>
       </c>
       <c r="K99" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="L99" s="4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
         </is>
       </c>
       <c r="N99" s="3" t="n">
-        <v>54.2</v>
+        <v>45</v>
       </c>
       <c r="O99" s="4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="100">
@@ -6799,7 +6799,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-N-N</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -6808,25 +6808,25 @@
         </is>
       </c>
       <c r="D104" s="3" t="n">
-        <v>66.7</v>
+        <v>62.8</v>
       </c>
       <c r="E104" s="4" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G104" s="3" t="n">
-        <v>38.5</v>
+        <v>37.2</v>
       </c>
       <c r="H104" s="4" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>N-N-N-U</t>
+          <t>N-N-N-N</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
@@ -6835,10 +6835,10 @@
         </is>
       </c>
       <c r="K104" s="3" t="n">
-        <v>69.2</v>
+        <v>60</v>
       </c>
       <c r="L104" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
@@ -6846,10 +6846,10 @@
         </is>
       </c>
       <c r="N104" s="3" t="n">
-        <v>46.2</v>
+        <v>53.3</v>
       </c>
       <c r="O104" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -7025,7 +7025,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -7040,25 +7040,21 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr"/>
       <c r="G2" s="4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="n">
-        <v>46.2</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr"/>
       <c r="J2" s="4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
@@ -7067,25 +7063,21 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="n">
-        <v>54.5</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr"/>
       <c r="N2" s="4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
-        </is>
-      </c>
-      <c r="P2" s="3" t="n">
-        <v>36.4</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P2" s="3" t="inlineStr"/>
       <c r="Q2" s="4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -7096,7 +7088,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -7111,25 +7103,21 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>70.59999999999999</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr"/>
       <c r="G3" s="4" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="n">
-        <v>41.2</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr"/>
       <c r="J3" s="4" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
@@ -7138,25 +7126,21 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="n">
-        <v>75</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P3" s="3" t="n">
-        <v>75</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr"/>
       <c r="Q3" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -7167,7 +7151,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -7182,25 +7166,21 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>45.5</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr"/>
       <c r="G4" s="4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>54.5</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr"/>
       <c r="J4" s="4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
@@ -7209,25 +7189,21 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="n">
-        <v>33.3</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr"/>
       <c r="N4" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr"/>
       <c r="Q4" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -7238,7 +7214,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -7248,57 +7224,49 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>82.40000000000001</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr"/>
       <c r="G5" s="4" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>47.1</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="4" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-N</t>
+          <t>N-D-D-D</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="n">
-        <v>75</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr"/>
       <c r="Q5" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -7309,7 +7277,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -7319,57 +7287,49 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>72.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr"/>
       <c r="G6" s="4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>54.5</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr"/>
       <c r="J6" s="4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-U</t>
+          <t>U-N-D-N</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v>80</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr"/>
       <c r="N6" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P6" s="3" t="n">
-        <v>60</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr"/>
       <c r="Q6" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -7380,7 +7340,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -7390,57 +7350,49 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>38.5</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr"/>
       <c r="G7" s="4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>46.2</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-N</t>
+          <t>U-U-D-D</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="n">
-        <v>33.3</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr"/>
       <c r="N7" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P7" s="3" t="n">
-        <v>66.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr"/>
       <c r="Q7" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -7451,7 +7403,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -7466,25 +7418,21 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>85.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr"/>
       <c r="G8" s="4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="n">
-        <v>57.1</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
@@ -7518,7 +7466,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -7533,25 +7481,21 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>75.5</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="4" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>65.3</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="4" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
@@ -7560,25 +7504,21 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="n">
-        <v>85.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr"/>
       <c r="N9" s="4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P9" s="3" t="n">
-        <v>42.9</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr"/>
       <c r="Q9" s="4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -7589,7 +7529,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -7604,25 +7544,21 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>65</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr"/>
       <c r="G10" s="4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr"/>
       <c r="J10" s="4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
@@ -7631,25 +7567,21 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M10" s="3" t="n">
-        <v>60</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr"/>
       <c r="N10" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P10" s="3" t="n">
-        <v>60</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr"/>
       <c r="Q10" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -7660,7 +7592,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -7675,25 +7607,21 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr"/>
       <c r="G11" s="4" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="n">
-        <v>64.3</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr"/>
       <c r="J11" s="4" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
@@ -7702,25 +7630,21 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="n">
-        <v>53.8</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr"/>
       <c r="N11" s="4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P11" s="3" t="n">
-        <v>69.2</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr"/>
       <c r="Q11" s="4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -7731,7 +7655,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -7746,25 +7670,21 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>47.4</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr"/>
       <c r="G12" s="4" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="n">
-        <v>73.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr"/>
       <c r="J12" s="4" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
@@ -7773,25 +7693,21 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="M12" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr"/>
       <c r="N12" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P12" s="3" t="n">
-        <v>83.3</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr"/>
       <c r="Q12" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -7802,7 +7718,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -7817,25 +7733,21 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>66.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr"/>
       <c r="G13" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="n">
-        <v>66.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr"/>
       <c r="J13" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
@@ -7844,25 +7756,21 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
-        </is>
-      </c>
-      <c r="M13" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr"/>
       <c r="N13" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
-        </is>
-      </c>
-      <c r="P13" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr"/>
       <c r="Q13" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -7873,7 +7781,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -7888,25 +7796,21 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>73.3</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr"/>
       <c r="G14" s="4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="n">
-        <v>60</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr"/>
       <c r="J14" s="4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
@@ -7915,25 +7819,21 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M14" s="3" t="n">
-        <v>75</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr"/>
       <c r="N14" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P14" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr"/>
       <c r="Q14" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -7944,7 +7844,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -7954,57 +7854,49 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>54.5</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr"/>
       <c r="G15" s="4" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="n">
-        <v>40.9</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr"/>
       <c r="J15" s="4" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-D</t>
+          <t>D-U-U-N</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M15" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr"/>
       <c r="N15" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P15" s="3" t="n">
-        <v>40</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr"/>
       <c r="Q15" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -8015,7 +7907,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -8030,25 +7922,21 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>86.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr"/>
       <c r="G16" s="4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>60</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr"/>
       <c r="J16" s="4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
@@ -8057,25 +7945,21 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M16" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr"/>
       <c r="N16" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P16" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr"/>
       <c r="Q16" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -8086,7 +7970,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -8101,25 +7985,21 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>62.9</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr"/>
       <c r="G17" s="4" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="n">
-        <v>57.1</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr"/>
       <c r="J17" s="4" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
@@ -8128,25 +8008,21 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M17" s="3" t="n">
-        <v>66.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr"/>
       <c r="N17" s="4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
-        </is>
-      </c>
-      <c r="P17" s="3" t="n">
-        <v>46.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr"/>
       <c r="Q17" s="4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -8157,7 +8033,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -8172,25 +8048,21 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>90</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr"/>
       <c r="G18" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="n">
-        <v>40</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr"/>
       <c r="J18" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
@@ -8199,25 +8071,21 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
-        </is>
-      </c>
-      <c r="M18" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr"/>
       <c r="N18" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
-        </is>
-      </c>
-      <c r="P18" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr"/>
       <c r="Q18" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -8228,7 +8096,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -8238,57 +8106,49 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>52.4</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr"/>
       <c r="G19" s="4" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="n">
-        <v>57.1</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr"/>
       <c r="J19" s="4" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="M19" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr"/>
       <c r="N19" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P19" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr"/>
       <c r="Q19" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -8299,7 +8159,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -8314,25 +8174,21 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr"/>
       <c r="G20" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="n">
-        <v>40</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr"/>
       <c r="J20" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
@@ -8341,25 +8197,21 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M20" s="3" t="n">
-        <v>66.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr"/>
       <c r="N20" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P20" s="3" t="n">
-        <v>66.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr"/>
       <c r="Q20" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -8370,7 +8222,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -8385,25 +8237,21 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>40</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="n">
-        <v>60</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr"/>
       <c r="J21" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
@@ -8412,25 +8260,21 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M21" s="3" t="n">
-        <v>66.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr"/>
       <c r="N21" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P21" s="3" t="n">
-        <v>66.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr"/>
       <c r="Q21" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -8441,7 +8285,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -8456,25 +8300,21 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>58.8</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr"/>
       <c r="G22" s="4" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="n">
-        <v>52.9</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr"/>
       <c r="J22" s="4" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
@@ -8483,25 +8323,21 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="n">
-        <v>71.40000000000001</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr"/>
       <c r="N22" s="4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P22" s="3" t="n">
-        <v>57.1</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr"/>
       <c r="Q22" s="4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -8512,7 +8348,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -8527,25 +8363,21 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr"/>
       <c r="G23" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr"/>
       <c r="J23" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
@@ -8579,7 +8411,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -8589,57 +8421,49 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-U</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="n">
-        <v>62.5</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr"/>
       <c r="G24" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="n">
-        <v>37.5</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr"/>
       <c r="J24" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-N</t>
+          <t>D-N-N-U</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr"/>
       <c r="N24" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
-        </is>
-      </c>
-      <c r="P24" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr"/>
       <c r="Q24" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -8650,7 +8474,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -8660,57 +8484,49 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>62.5</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr"/>
       <c r="G25" s="4" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr"/>
       <c r="J25" s="4" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M25" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr"/>
       <c r="N25" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P25" s="3" t="n">
-        <v>60</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr"/>
       <c r="Q25" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -8721,7 +8537,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -8736,25 +8552,21 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>54.8</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr"/>
       <c r="G26" s="4" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="n">
-        <v>61.3</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr"/>
       <c r="J26" s="4" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
@@ -8763,25 +8575,21 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="n">
-        <v>46.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr"/>
       <c r="N26" s="4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P26" s="3" t="n">
-        <v>60</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr"/>
       <c r="Q26" s="4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -8792,7 +8600,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -8807,25 +8615,21 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>52.6</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr"/>
       <c r="G27" s="4" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="n">
-        <v>68.40000000000001</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr"/>
       <c r="J27" s="4" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
@@ -8834,25 +8638,21 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
-        </is>
-      </c>
-      <c r="M27" s="3" t="n">
-        <v>46.2</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr"/>
       <c r="N27" s="4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P27" s="3" t="n">
-        <v>69.2</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr"/>
       <c r="Q27" s="4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -8863,7 +8663,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -8873,57 +8673,49 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr"/>
       <c r="G28" s="4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="n">
-        <v>60</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr"/>
       <c r="J28" s="4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-U</t>
+          <t>D-N-U-N</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M28" s="3" t="n">
-        <v>66.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr"/>
       <c r="N28" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P28" s="3" t="n">
-        <v>66.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="inlineStr"/>
       <c r="Q28" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -8934,7 +8726,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -8949,25 +8741,21 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>78.3</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr"/>
       <c r="G29" s="4" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="n">
-        <v>52.2</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr"/>
       <c r="J29" s="4" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
@@ -8976,25 +8764,21 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M29" s="3" t="n">
-        <v>66.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr"/>
       <c r="N29" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
-        </is>
-      </c>
-      <c r="P29" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr"/>
       <c r="Q29" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -9005,7 +8789,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -9020,25 +8804,21 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="n">
-        <v>60</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr"/>
       <c r="G30" s="4" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I30" s="3" t="n">
-        <v>42.9</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr"/>
       <c r="J30" s="4" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
@@ -9047,25 +8827,21 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M30" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr"/>
       <c r="N30" s="4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
-        </is>
-      </c>
-      <c r="P30" s="3" t="n">
-        <v>44.4</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr"/>
       <c r="Q30" s="4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -9076,7 +8852,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -9091,25 +8867,21 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr"/>
       <c r="G31" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I31" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr"/>
       <c r="J31" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
@@ -9143,7 +8915,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -9158,25 +8930,21 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>53.8</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr"/>
       <c r="G32" s="4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="n">
-        <v>53.8</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr"/>
       <c r="J32" s="4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
@@ -9185,25 +8953,21 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M32" s="3" t="n">
-        <v>66.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr"/>
       <c r="N32" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
-        </is>
-      </c>
-      <c r="P32" s="3" t="n">
-        <v>33.3</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr"/>
       <c r="Q32" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -9214,7 +8978,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -9224,57 +8988,49 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>U-N-N</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>58.3</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr"/>
       <c r="G33" s="4" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="n">
-        <v>41.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr"/>
       <c r="J33" s="4" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-U</t>
+          <t>D-U-N-N</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M33" s="3" t="n">
-        <v>61.5</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr"/>
       <c r="N33" s="4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P33" s="3" t="n">
-        <v>38.5</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr"/>
       <c r="Q33" s="4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -9285,7 +9041,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -9300,25 +9056,21 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="n">
-        <v>77.8</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr"/>
       <c r="G34" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="n">
-        <v>44.4</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr"/>
       <c r="J34" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
@@ -9327,25 +9079,21 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M34" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr"/>
       <c r="N34" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P34" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr"/>
       <c r="Q34" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -9356,7 +9104,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -9371,25 +9119,21 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr"/>
       <c r="G35" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
-        </is>
-      </c>
-      <c r="I35" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr"/>
       <c r="J35" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
@@ -9398,25 +9142,21 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M35" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr"/>
       <c r="N35" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
-        </is>
-      </c>
-      <c r="P35" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr"/>
       <c r="Q35" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -9427,7 +9167,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -9442,25 +9182,21 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="n">
-        <v>53.3</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr"/>
       <c r="G36" s="4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I36" s="3" t="n">
-        <v>60</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr"/>
       <c r="J36" s="4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
@@ -9469,25 +9205,21 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M36" s="3" t="n">
-        <v>66.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr"/>
       <c r="N36" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
-        </is>
-      </c>
-      <c r="P36" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr"/>
       <c r="Q36" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -9498,7 +9230,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -9508,57 +9240,49 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>37.9</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr"/>
       <c r="G37" s="4" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I37" s="3" t="n">
-        <v>51.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr"/>
       <c r="J37" s="4" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-D</t>
+          <t>U-D-U-N</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="M37" s="3" t="n">
-        <v>42.9</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr"/>
       <c r="N37" s="4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P37" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P37" s="3" t="inlineStr"/>
       <c r="Q37" s="4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -9569,7 +9293,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -9584,25 +9308,21 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F38" s="3" t="n">
-        <v>65</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr"/>
       <c r="G38" s="4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I38" s="3" t="n">
-        <v>40</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr"/>
       <c r="J38" s="4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
@@ -9611,25 +9331,21 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M38" s="3" t="n">
-        <v>62.5</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr"/>
       <c r="N38" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
-        </is>
-      </c>
-      <c r="P38" s="3" t="n">
-        <v>37.5</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr"/>
       <c r="Q38" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -9640,7 +9356,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -9655,25 +9371,21 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>46.4</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr"/>
       <c r="G39" s="4" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="n">
-        <v>39.3</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr"/>
       <c r="J39" s="4" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
@@ -9682,25 +9394,21 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
-        </is>
-      </c>
-      <c r="M39" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr"/>
       <c r="N39" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P39" s="3" t="n">
-        <v>66.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr"/>
       <c r="Q39" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -9711,7 +9419,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -9726,25 +9434,21 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="n">
-        <v>52.4</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr"/>
       <c r="G40" s="4" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
-        </is>
-      </c>
-      <c r="I40" s="3" t="n">
-        <v>38.1</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr"/>
       <c r="J40" s="4" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
@@ -9753,25 +9457,21 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="M40" s="3" t="n">
-        <v>66.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr"/>
       <c r="N40" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P40" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr"/>
       <c r="Q40" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -9782,7 +9482,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -9797,25 +9497,21 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>53.1</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr"/>
       <c r="G41" s="4" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I41" s="3" t="n">
-        <v>68.8</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr"/>
       <c r="J41" s="4" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
@@ -9824,25 +9520,21 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M41" s="3" t="n">
-        <v>52.6</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr"/>
       <c r="N41" s="4" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P41" s="3" t="n">
-        <v>68.40000000000001</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr"/>
       <c r="Q41" s="4" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -9853,7 +9545,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -9868,25 +9560,21 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="F42" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr"/>
       <c r="G42" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I42" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr"/>
       <c r="J42" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
@@ -9895,25 +9583,21 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="M42" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr"/>
       <c r="N42" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P42" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr"/>
       <c r="Q42" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -9924,7 +9608,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -9939,25 +9623,21 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>45.5</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr"/>
       <c r="G43" s="4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="n">
-        <v>81.8</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr"/>
       <c r="J43" s="4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
@@ -9966,25 +9646,21 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M43" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr"/>
       <c r="N43" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P43" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr"/>
       <c r="Q43" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -9995,7 +9671,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -10010,25 +9686,21 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F44" s="3" t="n">
-        <v>90</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr"/>
       <c r="G44" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I44" s="3" t="n">
-        <v>90</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr"/>
       <c r="J44" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
@@ -10037,25 +9709,21 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M44" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr"/>
       <c r="N44" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P44" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P44" s="3" t="inlineStr"/>
       <c r="Q44" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -10066,7 +9734,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -10081,25 +9749,21 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
-        </is>
-      </c>
-      <c r="F45" s="3" t="n">
-        <v>35.3</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr"/>
       <c r="G45" s="4" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I45" s="3" t="n">
-        <v>64.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr"/>
       <c r="J45" s="4" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
@@ -10108,25 +9772,21 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M45" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr"/>
       <c r="N45" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P45" s="3" t="n">
-        <v>83.3</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="inlineStr"/>
       <c r="Q45" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -10137,7 +9797,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -10152,25 +9812,21 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="F46" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr"/>
       <c r="G46" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I46" s="3" t="n">
-        <v>80</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr"/>
       <c r="J46" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
@@ -10179,25 +9835,21 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="M46" s="3" t="n">
-        <v>57.1</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr"/>
       <c r="N46" s="4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P46" s="3" t="n">
-        <v>71.40000000000001</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr"/>
       <c r="Q46" s="4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -10208,7 +9860,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -10223,25 +9875,21 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="F47" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr"/>
       <c r="G47" s="4" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
-        </is>
-      </c>
-      <c r="I47" s="3" t="n">
-        <v>40.9</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr"/>
       <c r="J47" s="4" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
@@ -10250,25 +9898,21 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
-        </is>
-      </c>
-      <c r="M47" s="3" t="n">
-        <v>40</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr"/>
       <c r="N47" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P47" s="3" t="n">
-        <v>60</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P47" s="3" t="inlineStr"/>
       <c r="Q47" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -10279,7 +9923,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -10294,25 +9938,21 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
-        </is>
-      </c>
-      <c r="F48" s="3" t="n">
-        <v>41.2</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr"/>
       <c r="G48" s="4" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I48" s="3" t="n">
-        <v>58.8</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr"/>
       <c r="J48" s="4" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
@@ -10321,25 +9961,21 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="M48" s="3" t="n">
-        <v>75</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr"/>
       <c r="N48" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P48" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P48" s="3" t="inlineStr"/>
       <c r="Q48" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -10350,7 +9986,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -10365,25 +10001,21 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="F49" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr"/>
       <c r="G49" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I49" s="3" t="n">
-        <v>83.3</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr"/>
       <c r="J49" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
@@ -10392,25 +10024,21 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="M49" s="3" t="n">
-        <v>60</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr"/>
       <c r="N49" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P49" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P49" s="3" t="inlineStr"/>
       <c r="Q49" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -10421,7 +10049,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -10436,25 +10064,21 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F50" s="3" t="n">
-        <v>64.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr"/>
       <c r="G50" s="4" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I50" s="3" t="n">
-        <v>47.1</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr"/>
       <c r="J50" s="4" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
@@ -10463,25 +10087,21 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="M50" s="3" t="n">
-        <v>66.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr"/>
       <c r="N50" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P50" s="3" t="n">
-        <v>66.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P50" s="3" t="inlineStr"/>
       <c r="Q50" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -10492,7 +10112,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -10502,57 +10122,49 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="F51" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr"/>
       <c r="G51" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I51" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr"/>
       <c r="J51" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>N-N-N-N</t>
+          <t>N-N-N-D</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="M51" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr"/>
       <c r="N51" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P51" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P51" s="3" t="inlineStr"/>
       <c r="Q51" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -10563,7 +10175,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -10578,25 +10190,21 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F52" s="3" t="n">
-        <v>54.3</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr"/>
       <c r="G52" s="4" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I52" s="3" t="n">
-        <v>42.9</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr"/>
       <c r="J52" s="4" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
@@ -10605,25 +10213,21 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M52" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr"/>
       <c r="N52" s="4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P52" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P52" s="3" t="inlineStr"/>
       <c r="Q52" s="4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -10634,7 +10238,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -10649,25 +10253,21 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
-        </is>
-      </c>
-      <c r="F53" s="3" t="n">
-        <v>40</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr"/>
       <c r="G53" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
-        </is>
-      </c>
-      <c r="I53" s="3" t="n">
-        <v>40</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr"/>
       <c r="J53" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
@@ -10676,25 +10276,21 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
-        </is>
-      </c>
-      <c r="M53" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr"/>
       <c r="N53" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
-        </is>
-      </c>
-      <c r="P53" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P53" s="3" t="inlineStr"/>
       <c r="Q53" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -10705,7 +10301,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -10720,25 +10316,21 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="F54" s="3" t="n">
-        <v>62.5</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr"/>
       <c r="G54" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I54" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr"/>
       <c r="J54" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
@@ -10772,7 +10364,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -10787,25 +10379,21 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F55" s="3" t="n">
-        <v>70</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr"/>
       <c r="G55" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I55" s="3" t="n">
-        <v>40</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr"/>
       <c r="J55" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
@@ -10814,25 +10402,21 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M55" s="3" t="n">
-        <v>80</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr"/>
       <c r="N55" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
-        </is>
-      </c>
-      <c r="P55" s="3" t="n">
-        <v>40</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P55" s="3" t="inlineStr"/>
       <c r="Q55" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -10843,7 +10427,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -10858,25 +10442,21 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F56" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr"/>
       <c r="G56" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I56" s="3" t="n">
-        <v>75</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr"/>
       <c r="J56" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
@@ -10885,25 +10465,21 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M56" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr"/>
       <c r="N56" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P56" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P56" s="3" t="inlineStr"/>
       <c r="Q56" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -10914,7 +10490,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -10924,57 +10500,49 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F57" s="3" t="n">
-        <v>42.5</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr"/>
       <c r="G57" s="4" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I57" s="3" t="n">
-        <v>42.5</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr"/>
       <c r="J57" s="4" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-D</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="M57" s="3" t="n">
-        <v>63.6</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr"/>
       <c r="N57" s="4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
-        </is>
-      </c>
-      <c r="P57" s="3" t="n">
-        <v>36.4</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P57" s="3" t="inlineStr"/>
       <c r="Q57" s="4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -10985,7 +10553,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -11000,25 +10568,21 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F58" s="3" t="n">
-        <v>68.8</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr"/>
       <c r="G58" s="4" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I58" s="3" t="n">
-        <v>56.2</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr"/>
       <c r="J58" s="4" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
@@ -11027,25 +10591,21 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M58" s="3" t="n">
-        <v>66.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr"/>
       <c r="N58" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
-        </is>
-      </c>
-      <c r="P58" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P58" s="3" t="inlineStr"/>
       <c r="Q58" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -11056,7 +10616,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -11071,25 +10631,21 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F59" s="3" t="n">
-        <v>66.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr"/>
       <c r="G59" s="4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
-        </is>
-      </c>
-      <c r="I59" s="3" t="n">
-        <v>40</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="inlineStr"/>
       <c r="J59" s="4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
@@ -11098,25 +10654,21 @@
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M59" s="3" t="n">
-        <v>77.8</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr"/>
       <c r="N59" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P59" s="3" t="n">
-        <v>44.4</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P59" s="3" t="inlineStr"/>
       <c r="Q59" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -11127,7 +10679,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -11142,25 +10694,21 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F60" s="3" t="n">
-        <v>63.6</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr"/>
       <c r="G60" s="4" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I60" s="3" t="n">
-        <v>54.5</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="inlineStr"/>
       <c r="J60" s="4" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
@@ -11169,25 +10717,21 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M60" s="3" t="n">
-        <v>57.1</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr"/>
       <c r="N60" s="4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P60" s="3" t="n">
-        <v>57.1</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P60" s="3" t="inlineStr"/>
       <c r="Q60" s="4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -11198,7 +10742,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -11213,25 +10757,21 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F61" s="3" t="n">
-        <v>44.4</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr"/>
       <c r="G61" s="4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I61" s="3" t="n">
-        <v>55.6</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr"/>
       <c r="J61" s="4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
@@ -11240,25 +10780,21 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="M61" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M61" s="3" t="inlineStr"/>
       <c r="N61" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
-        </is>
-      </c>
-      <c r="P61" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P61" s="3" t="inlineStr"/>
       <c r="Q61" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -11269,7 +10805,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -11284,25 +10820,21 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F62" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr"/>
       <c r="G62" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
-        </is>
-      </c>
-      <c r="I62" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr"/>
       <c r="J62" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
@@ -11311,25 +10843,21 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="M62" s="3" t="n">
-        <v>66.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr"/>
       <c r="N62" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P62" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P62" s="3" t="inlineStr"/>
       <c r="Q62" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -11340,7 +10868,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -11355,25 +10883,21 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F63" s="3" t="n">
-        <v>87.5</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr"/>
       <c r="G63" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I63" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="inlineStr"/>
       <c r="J63" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
@@ -11382,25 +10906,21 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M63" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M63" s="3" t="inlineStr"/>
       <c r="N63" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P63" s="3" t="n">
-        <v>60</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P63" s="3" t="inlineStr"/>
       <c r="Q63" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -11411,7 +10931,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -11426,25 +10946,21 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F64" s="3" t="n">
-        <v>38.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr"/>
       <c r="G64" s="4" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I64" s="3" t="n">
-        <v>38.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="inlineStr"/>
       <c r="J64" s="4" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
@@ -11453,25 +10969,21 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
-        </is>
-      </c>
-      <c r="M64" s="3" t="n">
-        <v>42.9</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr"/>
       <c r="N64" s="4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
-        </is>
-      </c>
-      <c r="P64" s="3" t="n">
-        <v>42.9</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P64" s="3" t="inlineStr"/>
       <c r="Q64" s="4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -11482,7 +10994,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -11492,57 +11004,49 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F65" s="3" t="n">
-        <v>52.6</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr"/>
       <c r="G65" s="4" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I65" s="3" t="n">
-        <v>52.6</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I65" s="3" t="inlineStr"/>
       <c r="J65" s="4" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-N</t>
+          <t>U-U-D-D</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M65" s="3" t="n">
-        <v>66.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M65" s="3" t="inlineStr"/>
       <c r="N65" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P65" s="3" t="n">
-        <v>66.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P65" s="3" t="inlineStr"/>
       <c r="Q65" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -11553,7 +11057,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -11563,57 +11067,49 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F66" s="3" t="n">
-        <v>80</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr"/>
       <c r="G66" s="4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I66" s="3" t="n">
-        <v>53.3</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I66" s="3" t="inlineStr"/>
       <c r="J66" s="4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-N</t>
+          <t>N-D-U-D</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M66" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M66" s="3" t="inlineStr"/>
       <c r="N66" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P66" s="3" t="n">
-        <v>66.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P66" s="3" t="inlineStr"/>
       <c r="Q66" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -11624,7 +11120,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -11687,7 +11183,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -11702,25 +11198,21 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F68" s="3" t="n">
-        <v>61.5</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr"/>
       <c r="G68" s="4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I68" s="3" t="n">
-        <v>53.8</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I68" s="3" t="inlineStr"/>
       <c r="J68" s="4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
@@ -11729,25 +11221,21 @@
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
-        </is>
-      </c>
-      <c r="M68" s="3" t="n">
-        <v>42.9</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr"/>
       <c r="N68" s="4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P68" s="3" t="n">
-        <v>42.9</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P68" s="3" t="inlineStr"/>
       <c r="Q68" s="4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -11758,7 +11246,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -11773,25 +11261,21 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F69" s="3" t="n">
-        <v>62.5</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr"/>
       <c r="G69" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
-        </is>
-      </c>
-      <c r="I69" s="3" t="n">
-        <v>37.5</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="inlineStr"/>
       <c r="J69" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
@@ -11800,25 +11284,21 @@
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M69" s="3" t="n">
-        <v>75</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M69" s="3" t="inlineStr"/>
       <c r="N69" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
-        </is>
-      </c>
-      <c r="P69" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P69" s="3" t="inlineStr"/>
       <c r="Q69" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -11829,7 +11309,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -11839,57 +11319,49 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F70" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="inlineStr"/>
       <c r="G70" s="4" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I70" s="3" t="n">
-        <v>42.9</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I70" s="3" t="inlineStr"/>
       <c r="J70" s="4" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-U</t>
+          <t>U-U-U-N</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M70" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M70" s="3" t="inlineStr"/>
       <c r="N70" s="4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P70" s="3" t="n">
-        <v>57.1</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P70" s="3" t="inlineStr"/>
       <c r="Q70" s="4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -11900,7 +11372,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -11915,25 +11387,21 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F71" s="3" t="n">
-        <v>60</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr"/>
       <c r="G71" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I71" s="3" t="n">
-        <v>60</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I71" s="3" t="inlineStr"/>
       <c r="J71" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
@@ -11942,25 +11410,21 @@
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M71" s="3" t="n">
-        <v>75</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M71" s="3" t="inlineStr"/>
       <c r="N71" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
-        </is>
-      </c>
-      <c r="P71" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P71" s="3" t="inlineStr"/>
       <c r="Q71" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -11971,7 +11435,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -11986,25 +11450,21 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F72" s="3" t="n">
-        <v>60</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr"/>
       <c r="G72" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
-        </is>
-      </c>
-      <c r="I72" s="3" t="n">
-        <v>40</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I72" s="3" t="inlineStr"/>
       <c r="J72" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
@@ -12013,25 +11473,21 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
-        </is>
-      </c>
-      <c r="M72" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M72" s="3" t="inlineStr"/>
       <c r="N72" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
-        </is>
-      </c>
-      <c r="P72" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P72" s="3" t="inlineStr"/>
       <c r="Q72" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -12042,7 +11498,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -12057,25 +11513,21 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F73" s="3" t="n">
-        <v>46.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="inlineStr"/>
       <c r="G73" s="4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I73" s="3" t="n">
-        <v>46.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I73" s="3" t="inlineStr"/>
       <c r="J73" s="4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
@@ -12084,25 +11536,21 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M73" s="3" t="n">
-        <v>80</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M73" s="3" t="inlineStr"/>
       <c r="N73" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P73" s="3" t="n">
-        <v>60</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P73" s="3" t="inlineStr"/>
       <c r="Q73" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -12113,7 +11561,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -12123,57 +11571,49 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F74" s="3" t="n">
-        <v>55.2</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr"/>
       <c r="G74" s="4" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I74" s="3" t="n">
-        <v>44.8</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I74" s="3" t="inlineStr"/>
       <c r="J74" s="4" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-D</t>
+          <t>U-D-U-N</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M74" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M74" s="3" t="inlineStr"/>
       <c r="N74" s="4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P74" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P74" s="3" t="inlineStr"/>
       <c r="Q74" s="4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -12184,7 +11624,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -12199,25 +11639,21 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="F75" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="inlineStr"/>
       <c r="G75" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I75" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I75" s="3" t="inlineStr"/>
       <c r="J75" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
@@ -12251,7 +11687,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -12266,25 +11702,21 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="F76" s="3" t="n">
-        <v>58.3</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr"/>
       <c r="G76" s="4" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I76" s="3" t="n">
-        <v>54.2</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I76" s="3" t="inlineStr"/>
       <c r="J76" s="4" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
@@ -12293,25 +11725,21 @@
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="M76" s="3" t="n">
-        <v>57.1</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M76" s="3" t="inlineStr"/>
       <c r="N76" s="4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P76" s="3" t="n">
-        <v>57.1</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P76" s="3" t="inlineStr"/>
       <c r="Q76" s="4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -12322,7 +11750,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -12337,25 +11765,21 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F77" s="3" t="n">
-        <v>66.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="inlineStr"/>
       <c r="G77" s="4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I77" s="3" t="n">
-        <v>53.3</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I77" s="3" t="inlineStr"/>
       <c r="J77" s="4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
@@ -12364,25 +11788,21 @@
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M77" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M77" s="3" t="inlineStr"/>
       <c r="N77" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P77" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P77" s="3" t="inlineStr"/>
       <c r="Q77" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -12393,7 +11813,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -12408,25 +11828,21 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F78" s="3" t="n">
-        <v>68.8</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="inlineStr"/>
       <c r="G78" s="4" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I78" s="3" t="n">
-        <v>68.8</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I78" s="3" t="inlineStr"/>
       <c r="J78" s="4" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
@@ -12435,25 +11851,21 @@
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M78" s="3" t="n">
-        <v>71.40000000000001</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M78" s="3" t="inlineStr"/>
       <c r="N78" s="4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P78" s="3" t="n">
-        <v>57.1</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P78" s="3" t="inlineStr"/>
       <c r="Q78" s="4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -12464,7 +11876,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -12479,25 +11891,21 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="F79" s="3" t="n">
-        <v>61.1</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="inlineStr"/>
       <c r="G79" s="4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I79" s="3" t="n">
-        <v>55.6</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I79" s="3" t="inlineStr"/>
       <c r="J79" s="4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
@@ -12506,25 +11914,21 @@
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="M79" s="3" t="n">
-        <v>70</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M79" s="3" t="inlineStr"/>
       <c r="N79" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P79" s="3" t="n">
-        <v>60</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P79" s="3" t="inlineStr"/>
       <c r="Q79" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -12535,7 +11939,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -12550,25 +11954,21 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F80" s="3" t="n">
-        <v>45.5</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="inlineStr"/>
       <c r="G80" s="4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I80" s="3" t="n">
-        <v>63.6</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I80" s="3" t="inlineStr"/>
       <c r="J80" s="4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
@@ -12577,25 +11977,21 @@
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="M80" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M80" s="3" t="inlineStr"/>
       <c r="N80" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P80" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P80" s="3" t="inlineStr"/>
       <c r="Q80" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -12606,7 +12002,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -12621,25 +12017,21 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="F81" s="3" t="n">
-        <v>56.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="inlineStr"/>
       <c r="G81" s="4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I81" s="3" t="n">
-        <v>46.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I81" s="3" t="inlineStr"/>
       <c r="J81" s="4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
@@ -12648,25 +12040,21 @@
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="M81" s="3" t="n">
-        <v>60</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M81" s="3" t="inlineStr"/>
       <c r="N81" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P81" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P81" s="3" t="inlineStr"/>
       <c r="Q81" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -12677,7 +12065,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -12692,25 +12080,21 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F82" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="inlineStr"/>
       <c r="G82" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I82" s="3" t="n">
-        <v>75</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I82" s="3" t="inlineStr"/>
       <c r="J82" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
@@ -12719,25 +12103,21 @@
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M82" s="3" t="n">
-        <v>66.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M82" s="3" t="inlineStr"/>
       <c r="N82" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P82" s="3" t="n">
-        <v>66.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P82" s="3" t="inlineStr"/>
       <c r="Q82" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -12748,7 +12128,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -12763,25 +12143,21 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="F83" s="3" t="n">
-        <v>53.1</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="inlineStr"/>
       <c r="G83" s="4" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I83" s="3" t="n">
-        <v>59.4</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I83" s="3" t="inlineStr"/>
       <c r="J83" s="4" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
@@ -12790,25 +12166,21 @@
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="M83" s="3" t="n">
-        <v>66.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M83" s="3" t="inlineStr"/>
       <c r="N83" s="4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P83" s="3" t="n">
-        <v>66.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P83" s="3" t="inlineStr"/>
       <c r="Q83" s="4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -12819,7 +12191,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -12834,25 +12206,21 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F84" s="3" t="n">
-        <v>43.5</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F84" s="3" t="inlineStr"/>
       <c r="G84" s="4" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I84" s="3" t="n">
-        <v>47.8</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I84" s="3" t="inlineStr"/>
       <c r="J84" s="4" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
@@ -12861,25 +12229,21 @@
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M84" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M84" s="3" t="inlineStr"/>
       <c r="N84" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P84" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P84" s="3" t="inlineStr"/>
       <c r="Q84" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -12890,7 +12254,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -12905,25 +12269,21 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F85" s="3" t="n">
-        <v>66.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="inlineStr"/>
       <c r="G85" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I85" s="3" t="n">
-        <v>55.6</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I85" s="3" t="inlineStr"/>
       <c r="J85" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
@@ -12932,25 +12292,21 @@
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="M85" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M85" s="3" t="inlineStr"/>
       <c r="N85" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P85" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P85" s="3" t="inlineStr"/>
       <c r="Q85" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -12961,7 +12317,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -12976,25 +12332,21 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
-        </is>
-      </c>
-      <c r="F86" s="3" t="n">
-        <v>47.1</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F86" s="3" t="inlineStr"/>
       <c r="G86" s="4" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I86" s="3" t="n">
-        <v>41.2</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I86" s="3" t="inlineStr"/>
       <c r="J86" s="4" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
@@ -13003,25 +12355,21 @@
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="M86" s="3" t="n">
-        <v>83.3</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M86" s="3" t="inlineStr"/>
       <c r="N86" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P86" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P86" s="3" t="inlineStr"/>
       <c r="Q86" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -13032,7 +12380,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -13047,25 +12395,21 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F87" s="3" t="n">
-        <v>60</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F87" s="3" t="inlineStr"/>
       <c r="G87" s="4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
-        </is>
-      </c>
-      <c r="I87" s="3" t="n">
-        <v>40</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I87" s="3" t="inlineStr"/>
       <c r="J87" s="4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
@@ -13074,25 +12418,21 @@
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M87" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M87" s="3" t="inlineStr"/>
       <c r="N87" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P87" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P87" s="3" t="inlineStr"/>
       <c r="Q87" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -13103,7 +12443,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -13118,25 +12458,21 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="F88" s="3" t="n">
-        <v>63.6</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="inlineStr"/>
       <c r="G88" s="4" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I88" s="3" t="n">
-        <v>54.5</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I88" s="3" t="inlineStr"/>
       <c r="J88" s="4" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
@@ -13145,25 +12481,21 @@
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="M88" s="3" t="n">
-        <v>68.40000000000001</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M88" s="3" t="inlineStr"/>
       <c r="N88" s="4" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P88" s="3" t="n">
-        <v>52.6</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P88" s="3" t="inlineStr"/>
       <c r="Q88" s="4" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -13174,7 +12506,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -13189,25 +12521,21 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="F89" s="3" t="n">
-        <v>57.1</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="inlineStr"/>
       <c r="G89" s="4" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I89" s="3" t="n">
-        <v>62.9</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I89" s="3" t="inlineStr"/>
       <c r="J89" s="4" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
@@ -13216,25 +12544,21 @@
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="M89" s="3" t="n">
-        <v>46.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M89" s="3" t="inlineStr"/>
       <c r="N89" s="4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P89" s="3" t="n">
-        <v>46.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P89" s="3" t="inlineStr"/>
       <c r="Q89" s="4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -13245,7 +12569,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -13260,25 +12584,21 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="F90" s="3" t="n">
-        <v>67.59999999999999</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F90" s="3" t="inlineStr"/>
       <c r="G90" s="4" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I90" s="3" t="n">
-        <v>64.90000000000001</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I90" s="3" t="inlineStr"/>
       <c r="J90" s="4" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
@@ -13287,25 +12607,21 @@
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="M90" s="3" t="n">
-        <v>60</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M90" s="3" t="inlineStr"/>
       <c r="N90" s="4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P90" s="3" t="n">
-        <v>53.3</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P90" s="3" t="inlineStr"/>
       <c r="Q90" s="4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -13316,7 +12632,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -13331,25 +12647,21 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F91" s="3" t="n">
-        <v>46.2</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F91" s="3" t="inlineStr"/>
       <c r="G91" s="4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I91" s="3" t="n">
-        <v>46.2</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I91" s="3" t="inlineStr"/>
       <c r="J91" s="4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
@@ -13358,25 +12670,21 @@
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M91" s="3" t="n">
-        <v>66.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M91" s="3" t="inlineStr"/>
       <c r="N91" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
-        </is>
-      </c>
-      <c r="P91" s="3" t="n">
-        <v>33.3</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P91" s="3" t="inlineStr"/>
       <c r="Q91" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -13387,7 +12695,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -13402,25 +12710,21 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F92" s="3" t="n">
-        <v>45.2</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F92" s="3" t="inlineStr"/>
       <c r="G92" s="4" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I92" s="3" t="n">
-        <v>45.2</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I92" s="3" t="inlineStr"/>
       <c r="J92" s="4" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
@@ -13429,25 +12733,21 @@
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M92" s="3" t="n">
-        <v>54.5</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M92" s="3" t="inlineStr"/>
       <c r="N92" s="4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P92" s="3" t="n">
-        <v>63.6</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P92" s="3" t="inlineStr"/>
       <c r="Q92" s="4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -13458,7 +12758,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -13473,25 +12773,21 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F93" s="3" t="n">
-        <v>70</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F93" s="3" t="inlineStr"/>
       <c r="G93" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
-        </is>
-      </c>
-      <c r="I93" s="3" t="n">
-        <v>40</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I93" s="3" t="inlineStr"/>
       <c r="J93" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
@@ -13500,25 +12796,21 @@
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M93" s="3" t="n">
-        <v>66.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M93" s="3" t="inlineStr"/>
       <c r="N93" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P93" s="3" t="n">
-        <v>66.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P93" s="3" t="inlineStr"/>
       <c r="Q93" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -13529,7 +12821,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -13544,25 +12836,21 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F94" s="3" t="n">
-        <v>58.6</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="inlineStr"/>
       <c r="G94" s="4" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I94" s="3" t="n">
-        <v>41.4</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I94" s="3" t="inlineStr"/>
       <c r="J94" s="4" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
@@ -13571,25 +12859,21 @@
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
-        </is>
-      </c>
-      <c r="M94" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M94" s="3" t="inlineStr"/>
       <c r="N94" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P94" s="3" t="n">
-        <v>66.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P94" s="3" t="inlineStr"/>
       <c r="Q94" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -13600,7 +12884,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -13615,25 +12899,21 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F95" s="3" t="n">
-        <v>56.2</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F95" s="3" t="inlineStr"/>
       <c r="G95" s="4" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I95" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I95" s="3" t="inlineStr"/>
       <c r="J95" s="4" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
@@ -13642,25 +12922,21 @@
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
-        </is>
-      </c>
-      <c r="M95" s="3" t="n">
-        <v>42.9</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M95" s="3" t="inlineStr"/>
       <c r="N95" s="4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P95" s="3" t="n">
-        <v>57.1</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P95" s="3" t="inlineStr"/>
       <c r="Q95" s="4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -13671,7 +12947,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -13686,25 +12962,21 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F96" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F96" s="3" t="inlineStr"/>
       <c r="G96" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
-        </is>
-      </c>
-      <c r="I96" s="3" t="n">
-        <v>40</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I96" s="3" t="inlineStr"/>
       <c r="J96" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
@@ -13713,25 +12985,21 @@
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M96" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M96" s="3" t="inlineStr"/>
       <c r="N96" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P96" s="3" t="n">
-        <v>66.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P96" s="3" t="inlineStr"/>
       <c r="Q96" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -13742,7 +13010,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -13752,57 +13020,49 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F97" s="3" t="n">
-        <v>70</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F97" s="3" t="inlineStr"/>
       <c r="G97" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I97" s="3" t="n">
-        <v>60</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I97" s="3" t="inlineStr"/>
       <c r="J97" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-N</t>
+          <t>U-U-D-U</t>
         </is>
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M97" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M97" s="3" t="inlineStr"/>
       <c r="N97" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P97" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P97" s="3" t="inlineStr"/>
       <c r="Q97" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -13813,7 +13073,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -13828,25 +13088,21 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="F98" s="3" t="n">
-        <v>66.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F98" s="3" t="inlineStr"/>
       <c r="G98" s="4" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I98" s="3" t="n">
-        <v>54.2</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I98" s="3" t="inlineStr"/>
       <c r="J98" s="4" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
@@ -13855,25 +13111,21 @@
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="M98" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M98" s="3" t="inlineStr"/>
       <c r="N98" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P98" s="3" t="n">
-        <v>75</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P98" s="3" t="inlineStr"/>
       <c r="Q98" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -13884,7 +13136,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -13894,57 +13146,49 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
-        </is>
-      </c>
-      <c r="F99" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F99" s="3" t="inlineStr"/>
       <c r="G99" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I99" s="3" t="n">
-        <v>62.5</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I99" s="3" t="inlineStr"/>
       <c r="J99" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-U</t>
+          <t>D-N-U-N</t>
         </is>
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M99" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M99" s="3" t="inlineStr"/>
       <c r="N99" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P99" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P99" s="3" t="inlineStr"/>
       <c r="Q99" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -13955,7 +13199,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -13970,25 +13214,21 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="F100" s="3" t="n">
-        <v>46.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F100" s="3" t="inlineStr"/>
       <c r="G100" s="4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I100" s="3" t="n">
-        <v>56.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I100" s="3" t="inlineStr"/>
       <c r="J100" s="4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
@@ -13997,25 +13237,21 @@
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
-        </is>
-      </c>
-      <c r="M100" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M100" s="3" t="inlineStr"/>
       <c r="N100" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
-        </is>
-      </c>
-      <c r="P100" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P100" s="3" t="inlineStr"/>
       <c r="Q100" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -14026,7 +13262,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -14041,25 +13277,21 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="F101" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="inlineStr"/>
       <c r="G101" s="4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I101" s="3" t="n">
-        <v>66.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I101" s="3" t="inlineStr"/>
       <c r="J101" s="4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
@@ -14068,25 +13300,21 @@
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M101" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M101" s="3" t="inlineStr"/>
       <c r="N101" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P101" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P101" s="3" t="inlineStr"/>
       <c r="Q101" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -14097,7 +13325,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -14112,25 +13340,21 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F102" s="3" t="n">
-        <v>72.2</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F102" s="3" t="inlineStr"/>
       <c r="G102" s="4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I102" s="3" t="n">
-        <v>44.4</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I102" s="3" t="inlineStr"/>
       <c r="J102" s="4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
@@ -14139,25 +13363,21 @@
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M102" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M102" s="3" t="inlineStr"/>
       <c r="N102" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P102" s="3" t="n">
-        <v>80</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P102" s="3" t="inlineStr"/>
       <c r="Q102" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -14168,7 +13388,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -14183,25 +13403,21 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F103" s="3" t="n">
-        <v>43.8</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F103" s="3" t="inlineStr"/>
       <c r="G103" s="4" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I103" s="3" t="n">
-        <v>43.8</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I103" s="3" t="inlineStr"/>
       <c r="J103" s="4" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
@@ -14210,25 +13426,21 @@
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M103" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M103" s="3" t="inlineStr"/>
       <c r="N103" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P103" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P103" s="3" t="inlineStr"/>
       <c r="Q103" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -14239,7 +13451,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Cumartesi</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -14249,57 +13461,49 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-N-N</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
-        </is>
-      </c>
-      <c r="F104" s="3" t="n">
-        <v>42.9</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F104" s="3" t="inlineStr"/>
       <c r="G104" s="4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I104" s="3" t="n">
-        <v>57.1</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I104" s="3" t="inlineStr"/>
       <c r="J104" s="4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>N-N-N-U</t>
+          <t>N-N-N-N</t>
         </is>
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M104" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M104" s="3" t="inlineStr"/>
       <c r="N104" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P104" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P104" s="3" t="inlineStr"/>
       <c r="Q104" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/BIS_tr.xlsx
+++ b/BIS_tr.xlsx
@@ -7025,7 +7025,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -7151,7 +7151,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -7277,7 +7277,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -7403,7 +7403,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -7529,7 +7529,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -7592,7 +7592,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -7655,7 +7655,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -7718,7 +7718,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -7844,7 +7844,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -7907,7 +7907,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -8033,7 +8033,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -8159,7 +8159,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -8222,7 +8222,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -8285,7 +8285,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -8348,7 +8348,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -8411,7 +8411,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -8537,7 +8537,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -8600,7 +8600,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -8663,7 +8663,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -8726,7 +8726,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -8852,7 +8852,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -8915,7 +8915,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -8978,7 +8978,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -9041,7 +9041,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -9104,7 +9104,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -9230,7 +9230,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -9293,7 +9293,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -9356,7 +9356,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -9419,7 +9419,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -9482,7 +9482,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -9545,7 +9545,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -9608,7 +9608,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -9671,7 +9671,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -9734,7 +9734,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -9797,7 +9797,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -9860,7 +9860,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -9923,7 +9923,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -9986,7 +9986,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -10049,7 +10049,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -10175,7 +10175,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -10238,7 +10238,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -10301,7 +10301,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -10364,7 +10364,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -10427,7 +10427,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -10490,7 +10490,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -10553,7 +10553,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -10616,7 +10616,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -10679,7 +10679,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -10805,7 +10805,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -10868,7 +10868,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -10931,7 +10931,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -10994,7 +10994,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -11057,7 +11057,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -11120,7 +11120,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -11183,7 +11183,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -11246,7 +11246,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -11309,7 +11309,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -11372,7 +11372,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -11435,7 +11435,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -11498,7 +11498,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -11561,7 +11561,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -11624,7 +11624,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -11687,7 +11687,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -11750,7 +11750,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -11813,7 +11813,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -11876,7 +11876,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -11939,7 +11939,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -12002,7 +12002,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -12065,7 +12065,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -12128,7 +12128,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -12191,7 +12191,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -12254,7 +12254,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -12317,7 +12317,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -12380,7 +12380,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -12443,7 +12443,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -12506,7 +12506,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -12569,7 +12569,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -12632,7 +12632,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -12695,7 +12695,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -12758,7 +12758,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -12821,7 +12821,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -12884,7 +12884,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -12947,7 +12947,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -13010,7 +13010,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -13073,7 +13073,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -13136,7 +13136,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -13199,7 +13199,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -13262,7 +13262,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -13325,7 +13325,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -13388,7 +13388,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -13451,7 +13451,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">

--- a/BIS_tr.xlsx
+++ b/BIS_tr.xlsx
@@ -568,7 +568,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -577,10 +577,10 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>55.6</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -588,14 +588,14 @@
         </is>
       </c>
       <c r="G2" s="3" t="n">
-        <v>42</v>
+        <v>42.6</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-U</t>
+          <t>D-N-D-N</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="K2" s="3" t="n">
-        <v>51.6</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
@@ -615,10 +615,10 @@
         </is>
       </c>
       <c r="N2" s="3" t="n">
-        <v>48.4</v>
+        <v>42.9</v>
       </c>
       <c r="O2" s="4" t="n">
-        <v>31</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -629,7 +629,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>56.2</v>
+        <v>61.8</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>80</v>
+        <v>157</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -649,14 +649,14 @@
         </is>
       </c>
       <c r="G3" s="3" t="n">
-        <v>41.2</v>
+        <v>43.3</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>80</v>
+        <v>157</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-N</t>
+          <t>N-U-D-D</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -665,10 +665,10 @@
         </is>
       </c>
       <c r="K3" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>56</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="N3" s="3" t="n">
-        <v>41.2</v>
+        <v>40</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
@@ -751,7 +751,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -760,25 +760,25 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>65.09999999999999</v>
+        <v>57.1</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>63</v>
+        <v>163</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G5" s="3" t="n">
-        <v>46</v>
+        <v>44.2</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>63</v>
+        <v>163</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-N</t>
+          <t>N-D-U-D</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="K5" s="3" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N5" s="3" t="n">
-        <v>66.7</v>
+        <v>40</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
@@ -873,7 +873,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -882,10 +882,10 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>55.7</v>
+        <v>58</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>61</v>
+        <v>176</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -893,14 +893,14 @@
         </is>
       </c>
       <c r="G7" s="3" t="n">
-        <v>50.8</v>
+        <v>43.8</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>61</v>
+        <v>176</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -909,21 +909,21 @@
         </is>
       </c>
       <c r="K7" s="3" t="n">
-        <v>60</v>
+        <v>43.9</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N7" s="3" t="n">
-        <v>55</v>
+        <v>45.5</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>20</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8">
@@ -934,7 +934,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -943,48 +943,48 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>55.6</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G8" s="3" t="n">
-        <v>55.6</v>
+        <v>53.5</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-U</t>
+          <t>U-U-D-D</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K8" s="3" t="n">
-        <v>60</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N8" s="3" t="n">
-        <v>50</v>
+        <v>47.4</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1126,25 +1126,25 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>58.8</v>
+        <v>60.6</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G11" s="3" t="n">
-        <v>43.1</v>
+        <v>38</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-N</t>
+          <t>N-N-D-U</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1153,21 +1153,21 @@
         </is>
       </c>
       <c r="K11" s="3" t="n">
-        <v>66.7</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N11" s="3" t="n">
-        <v>58.3</v>
+        <v>52.6</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1187,10 +1187,10 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>64.7</v>
+        <v>76.5</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>68</v>
+        <v>17</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1198,14 +1198,14 @@
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>45.6</v>
+        <v>58.8</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>68</v>
+        <v>17</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-D</t>
+          <t>D-U-U-N</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1214,10 +1214,10 @@
         </is>
       </c>
       <c r="K12" s="3" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="N12" s="3" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1248,48 +1248,48 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>66.7</v>
+        <v>51.2</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G13" s="3" t="n">
-        <v>44.4</v>
+        <v>55.8</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="K13" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N13" s="3" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1492,25 +1492,25 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>75.40000000000001</v>
+        <v>62.9</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G17" s="3" t="n">
-        <v>38.5</v>
+        <v>40</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-N</t>
+          <t>U-D-N-D</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1519,21 +1519,21 @@
         </is>
       </c>
       <c r="K17" s="3" t="n">
-        <v>82.8</v>
+        <v>72</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N17" s="3" t="n">
-        <v>44.8</v>
+        <v>36</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1553,10 +1553,10 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>69.7</v>
+        <v>62.4</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1564,14 +1564,14 @@
         </is>
       </c>
       <c r="G18" s="3" t="n">
-        <v>35.5</v>
+        <v>42.1</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1580,10 +1580,10 @@
         </is>
       </c>
       <c r="K18" s="3" t="n">
-        <v>72.40000000000001</v>
+        <v>59.6</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="N18" s="3" t="n">
-        <v>41.4</v>
+        <v>45.6</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>29</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1614,48 +1614,48 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>62.9</v>
+        <v>60</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>42.9</v>
+        <v>40</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-U</t>
+          <t>D-N-U-N</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="K19" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="N19" s="3" t="n">
-        <v>44.4</v>
+        <v>50</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1736,25 +1736,25 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>72.09999999999999</v>
+        <v>57</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>68</v>
+        <v>158</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G21" s="3" t="n">
-        <v>47.1</v>
+        <v>45.6</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>68</v>
+        <v>158</v>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1763,21 +1763,21 @@
         </is>
       </c>
       <c r="K21" s="3" t="n">
-        <v>63.3</v>
+        <v>63</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N21" s="3" t="n">
-        <v>56.7</v>
+        <v>52.2</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22">
@@ -1788,34 +1788,34 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>60</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G22" s="3" t="n">
-        <v>60</v>
+        <v>58.8</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-N</t>
+          <t>U-D-N-U</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -1824,10 +1824,10 @@
         </is>
       </c>
       <c r="K22" s="3" t="n">
-        <v>66.7</v>
+        <v>75</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="N22" s="3" t="n">
-        <v>66.7</v>
+        <v>62.5</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1858,10 +1858,10 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>74.3</v>
+        <v>68.3</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1869,14 +1869,14 @@
         </is>
       </c>
       <c r="G23" s="3" t="n">
-        <v>51.4</v>
+        <v>46</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-U</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1885,10 +1885,10 @@
         </is>
       </c>
       <c r="K23" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>58.3</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
@@ -1896,10 +1896,10 @@
         </is>
       </c>
       <c r="N23" s="3" t="n">
-        <v>47.1</v>
+        <v>45.8</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2041,25 +2041,25 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>62.3</v>
+        <v>56.1</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>39.3</v>
+        <v>37.8</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>N-U-N-N</t>
+          <t>N-U-N-D</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="K26" s="3" t="n">
-        <v>63.2</v>
+        <v>86.7</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
@@ -2079,10 +2079,10 @@
         </is>
       </c>
       <c r="N26" s="3" t="n">
-        <v>42.1</v>
+        <v>46.7</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27">
@@ -2093,57 +2093,57 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>50</v>
+        <v>51.7</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>26</v>
+        <v>89</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>57.7</v>
+        <v>68.5</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>26</v>
+        <v>89</v>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-D</t>
+          <t>N-U-U-U</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K27" s="3" t="n">
-        <v>66.7</v>
+        <v>55.6</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N27" s="3" t="n">
-        <v>66.7</v>
+        <v>55.6</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2163,25 +2163,25 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>63.6</v>
+        <v>72.3</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G28" s="3" t="n">
-        <v>43.2</v>
+        <v>52.3</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-N-U-D</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -2190,21 +2190,21 @@
         </is>
       </c>
       <c r="K28" s="3" t="n">
-        <v>64.7</v>
+        <v>70</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N28" s="3" t="n">
-        <v>41.2</v>
+        <v>55</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2407,25 +2407,25 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>79.2</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G32" s="3" t="n">
-        <v>41.2</v>
+        <v>47.2</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-N</t>
+          <t>D-U-N-D</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -2434,21 +2434,21 @@
         </is>
       </c>
       <c r="K32" s="3" t="n">
-        <v>82.40000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N32" s="3" t="n">
-        <v>41.2</v>
+        <v>40.9</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="33">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-U</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2590,37 +2590,37 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>U-N-N-N</t>
+          <t>U-N-N-U</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K35" s="3" t="n">
         <v>100</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>100</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2712,25 +2712,25 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>50.9</v>
+        <v>74</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="G37" s="3" t="n">
-        <v>43.9</v>
+        <v>38</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-U</t>
+          <t>U-N-D-N</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -2739,10 +2739,10 @@
         </is>
       </c>
       <c r="K37" s="3" t="n">
-        <v>50</v>
+        <v>68.8</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         <v>50</v>
       </c>
       <c r="O37" s="4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="38">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2895,10 +2895,10 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>70.8</v>
+        <v>79.3</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2906,26 +2906,26 @@
         </is>
       </c>
       <c r="G40" s="3" t="n">
-        <v>58.3</v>
+        <v>48.3</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-N</t>
+          <t>U-N-D-U</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K40" s="3" t="n">
-        <v>50</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
@@ -2933,10 +2933,10 @@
         </is>
       </c>
       <c r="N40" s="3" t="n">
-        <v>100</v>
+        <v>53.8</v>
       </c>
       <c r="O40" s="4" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="41">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3078,10 +3078,10 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>81.5</v>
+        <v>74</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -3089,14 +3089,14 @@
         </is>
       </c>
       <c r="G43" s="3" t="n">
-        <v>44.4</v>
+        <v>44.2</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-N</t>
+          <t>N-D-U-D</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -3105,10 +3105,10 @@
         </is>
       </c>
       <c r="K43" s="3" t="n">
-        <v>83.3</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
@@ -3116,10 +3116,10 @@
         </is>
       </c>
       <c r="N43" s="3" t="n">
-        <v>66.7</v>
+        <v>53.8</v>
       </c>
       <c r="O43" s="4" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="44">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -3505,25 +3505,25 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>57.9</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>133</v>
+        <v>61</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G50" s="3" t="n">
-        <v>45.9</v>
+        <v>42.6</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>133</v>
+        <v>61</v>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -3532,21 +3532,21 @@
         </is>
       </c>
       <c r="K50" s="3" t="n">
-        <v>62.5</v>
+        <v>56.5</v>
       </c>
       <c r="L50" s="4" t="n">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N50" s="3" t="n">
-        <v>50</v>
+        <v>47.8</v>
       </c>
       <c r="O50" s="4" t="n">
-        <v>48</v>
+        <v>23</v>
       </c>
     </row>
     <row r="51">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3627,10 +3627,10 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>63.3</v>
+        <v>64.3</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>79</v>
+        <v>140</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3638,14 +3638,14 @@
         </is>
       </c>
       <c r="G52" s="3" t="n">
-        <v>46.8</v>
+        <v>45.7</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>79</v>
+        <v>140</v>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-N</t>
+          <t>U-U-D-D</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -3654,10 +3654,10 @@
         </is>
       </c>
       <c r="K52" s="3" t="n">
-        <v>63.2</v>
+        <v>69.2</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
@@ -3665,10 +3665,10 @@
         </is>
       </c>
       <c r="N52" s="3" t="n">
-        <v>52.6</v>
+        <v>44.2</v>
       </c>
       <c r="O52" s="4" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
     </row>
     <row r="53">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3688,10 +3688,10 @@
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>60.5</v>
+        <v>56.2</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3699,14 +3699,14 @@
         </is>
       </c>
       <c r="G53" s="3" t="n">
-        <v>44.7</v>
+        <v>56.2</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-D</t>
+          <t>N-D-U-N</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -3715,10 +3715,10 @@
         </is>
       </c>
       <c r="K53" s="3" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="L53" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
@@ -3726,10 +3726,10 @@
         </is>
       </c>
       <c r="N53" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="O53" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3810,10 +3810,10 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>56.7</v>
+        <v>59.5</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3821,14 +3821,14 @@
         </is>
       </c>
       <c r="G55" s="3" t="n">
-        <v>50</v>
+        <v>42.9</v>
       </c>
       <c r="H55" s="4" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-U</t>
+          <t>D-N-N-D</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -3837,10 +3837,10 @@
         </is>
       </c>
       <c r="K55" s="3" t="n">
-        <v>60</v>
+        <v>53.3</v>
       </c>
       <c r="L55" s="4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
@@ -3848,10 +3848,10 @@
         </is>
       </c>
       <c r="N55" s="3" t="n">
-        <v>60</v>
+        <v>46.7</v>
       </c>
       <c r="O55" s="4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="56">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3993,10 +3993,10 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>68.8</v>
+        <v>45.8</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -4004,37 +4004,37 @@
         </is>
       </c>
       <c r="G58" s="3" t="n">
-        <v>43.8</v>
+        <v>50</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>N-D-N-N</t>
+          <t>N-D-N-D</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K58" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N58" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="O58" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-U</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4054,25 +4054,25 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>69.8</v>
+        <v>67.5</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>43</v>
+        <v>77</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G59" s="3" t="n">
-        <v>37.2</v>
+        <v>46.8</v>
       </c>
       <c r="H59" s="4" t="n">
-        <v>43</v>
+        <v>77</v>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-N</t>
+          <t>D-U-N-U</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -4081,21 +4081,21 @@
         </is>
       </c>
       <c r="K59" s="3" t="n">
-        <v>66.7</v>
+        <v>75</v>
       </c>
       <c r="L59" s="4" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N59" s="3" t="n">
-        <v>38.9</v>
+        <v>50</v>
       </c>
       <c r="O59" s="4" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
     </row>
     <row r="60">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4115,10 +4115,10 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>70.2</v>
+        <v>63.9</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>94</v>
+        <v>144</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -4126,14 +4126,14 @@
         </is>
       </c>
       <c r="G60" s="3" t="n">
-        <v>42.6</v>
+        <v>41.7</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>94</v>
+        <v>144</v>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -4142,10 +4142,10 @@
         </is>
       </c>
       <c r="K60" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>64.5</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
@@ -4153,10 +4153,10 @@
         </is>
       </c>
       <c r="N60" s="3" t="n">
-        <v>42.9</v>
+        <v>41.9</v>
       </c>
       <c r="O60" s="4" t="n">
-        <v>28</v>
+        <v>62</v>
       </c>
     </row>
     <row r="61">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4176,10 +4176,10 @@
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>56.9</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>102</v>
+        <v>28</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -4187,14 +4187,14 @@
         </is>
       </c>
       <c r="G61" s="3" t="n">
-        <v>51</v>
+        <v>57.1</v>
       </c>
       <c r="H61" s="4" t="n">
-        <v>102</v>
+        <v>28</v>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -4203,21 +4203,21 @@
         </is>
       </c>
       <c r="K61" s="3" t="n">
+        <v>78.59999999999999</v>
+      </c>
+      <c r="L61" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="L61" s="4" t="n">
-        <v>52</v>
-      </c>
-      <c r="M61" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="N61" s="3" t="n">
-        <v>48.1</v>
-      </c>
       <c r="O61" s="4" t="n">
-        <v>52</v>
+        <v>14</v>
       </c>
     </row>
     <row r="62">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -4298,10 +4298,10 @@
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>48.8</v>
+        <v>63</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -4309,14 +4309,14 @@
         </is>
       </c>
       <c r="G63" s="3" t="n">
-        <v>51.2</v>
+        <v>43.5</v>
       </c>
       <c r="H63" s="4" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-U</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -4325,10 +4325,10 @@
         </is>
       </c>
       <c r="K63" s="3" t="n">
-        <v>55.6</v>
+        <v>46.7</v>
       </c>
       <c r="L63" s="4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
@@ -4336,10 +4336,10 @@
         </is>
       </c>
       <c r="N63" s="3" t="n">
-        <v>61.1</v>
+        <v>40</v>
       </c>
       <c r="O63" s="4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="64">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -4359,25 +4359,25 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>52.2</v>
+        <v>45.7</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G64" s="3" t="n">
-        <v>39.1</v>
+        <v>42.9</v>
       </c>
       <c r="H64" s="4" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-N</t>
+          <t>D-N-N-D</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -4386,21 +4386,21 @@
         </is>
       </c>
       <c r="K64" s="3" t="n">
-        <v>57.1</v>
+        <v>58.3</v>
       </c>
       <c r="L64" s="4" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N64" s="3" t="n">
-        <v>42.9</v>
+        <v>41.7</v>
       </c>
       <c r="O64" s="4" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="65">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -4420,25 +4420,25 @@
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>80.3</v>
+        <v>66.5</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>76</v>
+        <v>158</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G65" s="3" t="n">
-        <v>39.5</v>
+        <v>44.3</v>
       </c>
       <c r="H65" s="4" t="n">
-        <v>76</v>
+        <v>158</v>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-U</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -4447,21 +4447,21 @@
         </is>
       </c>
       <c r="K65" s="3" t="n">
-        <v>89.7</v>
+        <v>61.5</v>
       </c>
       <c r="L65" s="4" t="n">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N65" s="3" t="n">
-        <v>44.8</v>
+        <v>44.2</v>
       </c>
       <c r="O65" s="4" t="n">
-        <v>29</v>
+        <v>52</v>
       </c>
     </row>
     <row r="66">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>N-U-D</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -4664,25 +4664,25 @@
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>55.6</v>
+        <v>50</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G69" s="3" t="n">
-        <v>55.6</v>
+        <v>50</v>
       </c>
       <c r="H69" s="4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-D</t>
+          <t>U-N-U-U</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -4691,10 +4691,10 @@
         </is>
       </c>
       <c r="K69" s="3" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="L69" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
@@ -4702,10 +4702,10 @@
         </is>
       </c>
       <c r="N69" s="3" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="O69" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="70">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -4725,10 +4725,10 @@
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>69.8</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4736,14 +4736,14 @@
         </is>
       </c>
       <c r="G70" s="3" t="n">
-        <v>44.4</v>
+        <v>46.4</v>
       </c>
       <c r="H70" s="4" t="n">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-N</t>
+          <t>U-N-U-D</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -4752,10 +4752,10 @@
         </is>
       </c>
       <c r="K70" s="3" t="n">
-        <v>75</v>
+        <v>62.5</v>
       </c>
       <c r="L70" s="4" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
@@ -4763,10 +4763,10 @@
         </is>
       </c>
       <c r="N70" s="3" t="n">
-        <v>41.7</v>
+        <v>43.8</v>
       </c>
       <c r="O70" s="4" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="71">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -4908,25 +4908,25 @@
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>72.7</v>
+        <v>56.3</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G73" s="3" t="n">
-        <v>52.3</v>
+        <v>46</v>
       </c>
       <c r="H73" s="4" t="n">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-U</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -4935,10 +4935,10 @@
         </is>
       </c>
       <c r="K73" s="3" t="n">
-        <v>66.7</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L73" s="4" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
@@ -4946,10 +4946,10 @@
         </is>
       </c>
       <c r="N73" s="3" t="n">
-        <v>47.6</v>
+        <v>46.2</v>
       </c>
       <c r="O73" s="4" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="74">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -4969,37 +4969,37 @@
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>51.2</v>
+        <v>55.2</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>160</v>
+        <v>58</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G74" s="3" t="n">
-        <v>43.8</v>
+        <v>53.4</v>
       </c>
       <c r="H74" s="4" t="n">
-        <v>160</v>
+        <v>58</v>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-U</t>
+          <t>N-D-D-N</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K74" s="3" t="n">
-        <v>61.8</v>
+        <v>50</v>
       </c>
       <c r="L74" s="4" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
@@ -5007,10 +5007,10 @@
         </is>
       </c>
       <c r="N74" s="3" t="n">
-        <v>47.1</v>
+        <v>62.5</v>
       </c>
       <c r="O74" s="4" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
     </row>
     <row r="75">
@@ -5021,7 +5021,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-N-N</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5030,10 +5030,10 @@
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>66.7</v>
+        <v>80</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -5041,14 +5041,14 @@
         </is>
       </c>
       <c r="G75" s="3" t="n">
-        <v>58.3</v>
+        <v>60</v>
       </c>
       <c r="H75" s="4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-U</t>
+          <t>D-N-N-N</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
@@ -5057,21 +5057,21 @@
         </is>
       </c>
       <c r="K75" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="L75" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="N75" s="3" t="n">
-        <v>85.7</v>
+        <v>33.3</v>
       </c>
       <c r="O75" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -5091,10 +5091,10 @@
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>66.3</v>
+        <v>57.5</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>83</v>
+        <v>167</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -5102,14 +5102,14 @@
         </is>
       </c>
       <c r="G76" s="3" t="n">
-        <v>47</v>
+        <v>41.9</v>
       </c>
       <c r="H76" s="4" t="n">
-        <v>83</v>
+        <v>167</v>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-N</t>
+          <t>N-U-U-D</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -5118,21 +5118,21 @@
         </is>
       </c>
       <c r="K76" s="3" t="n">
-        <v>56</v>
+        <v>59.5</v>
       </c>
       <c r="L76" s="4" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N76" s="3" t="n">
-        <v>52</v>
+        <v>40.5</v>
       </c>
       <c r="O76" s="4" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
     </row>
     <row r="77">
@@ -5143,7 +5143,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -5152,10 +5152,10 @@
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>62.2</v>
+        <v>66</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>90</v>
+        <v>47</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -5163,14 +5163,14 @@
         </is>
       </c>
       <c r="G77" s="3" t="n">
-        <v>38.9</v>
+        <v>48.9</v>
       </c>
       <c r="H77" s="4" t="n">
-        <v>90</v>
+        <v>47</v>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-U</t>
+          <t>D-N-U-N</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -5179,10 +5179,10 @@
         </is>
       </c>
       <c r="K77" s="3" t="n">
-        <v>63.3</v>
+        <v>72.2</v>
       </c>
       <c r="L77" s="4" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
@@ -5190,10 +5190,10 @@
         </is>
       </c>
       <c r="N77" s="3" t="n">
-        <v>40</v>
+        <v>61.1</v>
       </c>
       <c r="O77" s="4" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
     </row>
     <row r="78">
@@ -5204,7 +5204,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -5213,25 +5213,25 @@
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>75</v>
+        <v>65.2</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G78" s="3" t="n">
-        <v>38.9</v>
+        <v>42.4</v>
       </c>
       <c r="H78" s="4" t="n">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>N-U-N-N</t>
+          <t>N-U-N-D</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -5240,21 +5240,21 @@
         </is>
       </c>
       <c r="K78" s="3" t="n">
-        <v>75</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="L78" s="4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N78" s="3" t="n">
-        <v>37.5</v>
+        <v>35.7</v>
       </c>
       <c r="O78" s="4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="79">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>N-U-D</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -5335,10 +5335,10 @@
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>45.1</v>
+        <v>61.9</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -5346,14 +5346,14 @@
         </is>
       </c>
       <c r="G80" s="3" t="n">
-        <v>36.6</v>
+        <v>40.5</v>
       </c>
       <c r="H80" s="4" t="n">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>N-N-U-D</t>
+          <t>N-N-U-N</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -5362,18 +5362,18 @@
         </is>
       </c>
       <c r="K80" s="3" t="n">
-        <v>69.2</v>
+        <v>61.5</v>
       </c>
       <c r="L80" s="4" t="n">
         <v>13</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N80" s="3" t="n">
-        <v>53.8</v>
+        <v>46.2</v>
       </c>
       <c r="O80" s="4" t="n">
         <v>13</v>
@@ -5631,7 +5631,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-U</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -5640,25 +5640,25 @@
         </is>
       </c>
       <c r="D85" s="3" t="n">
-        <v>66.7</v>
+        <v>70</v>
       </c>
       <c r="E85" s="4" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G85" s="3" t="n">
-        <v>38.1</v>
+        <v>47.5</v>
       </c>
       <c r="H85" s="4" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>N-N-N-N</t>
+          <t>N-N-N-U</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
@@ -5667,21 +5667,21 @@
         </is>
       </c>
       <c r="K85" s="3" t="n">
-        <v>60</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="L85" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N85" s="3" t="n">
-        <v>40</v>
+        <v>38.5</v>
       </c>
       <c r="O85" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="86">
@@ -5692,7 +5692,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -5701,25 +5701,25 @@
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>54.9</v>
+        <v>60.8</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>182</v>
+        <v>166</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G86" s="3" t="n">
-        <v>40.7</v>
+        <v>44</v>
       </c>
       <c r="H86" s="4" t="n">
-        <v>182</v>
+        <v>166</v>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -5728,10 +5728,10 @@
         </is>
       </c>
       <c r="K86" s="3" t="n">
-        <v>54.5</v>
+        <v>55.7</v>
       </c>
       <c r="L86" s="4" t="n">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
@@ -5739,10 +5739,10 @@
         </is>
       </c>
       <c r="N86" s="3" t="n">
-        <v>40.3</v>
+        <v>41</v>
       </c>
       <c r="O86" s="4" t="n">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="87">
@@ -5753,7 +5753,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -5762,25 +5762,25 @@
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>68.2</v>
+        <v>60.4</v>
       </c>
       <c r="E87" s="4" t="n">
-        <v>88</v>
+        <v>154</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G87" s="3" t="n">
-        <v>37.5</v>
+        <v>41.6</v>
       </c>
       <c r="H87" s="4" t="n">
-        <v>88</v>
+        <v>154</v>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-N</t>
+          <t>N-U-D-D</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
@@ -5789,21 +5789,21 @@
         </is>
       </c>
       <c r="K87" s="3" t="n">
-        <v>72.2</v>
+        <v>65.7</v>
       </c>
       <c r="L87" s="4" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N87" s="3" t="n">
-        <v>44.4</v>
+        <v>45.7</v>
       </c>
       <c r="O87" s="4" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
     </row>
     <row r="88">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -5884,10 +5884,10 @@
         </is>
       </c>
       <c r="D89" s="3" t="n">
-        <v>67.2</v>
+        <v>57.2</v>
       </c>
       <c r="E89" s="4" t="n">
-        <v>67</v>
+        <v>187</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5895,14 +5895,14 @@
         </is>
       </c>
       <c r="G89" s="3" t="n">
-        <v>49.3</v>
+        <v>46</v>
       </c>
       <c r="H89" s="4" t="n">
-        <v>67</v>
+        <v>187</v>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
@@ -5911,10 +5911,10 @@
         </is>
       </c>
       <c r="K89" s="3" t="n">
-        <v>58.3</v>
+        <v>61.3</v>
       </c>
       <c r="L89" s="4" t="n">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
@@ -5922,10 +5922,10 @@
         </is>
       </c>
       <c r="N89" s="3" t="n">
-        <v>52.8</v>
+        <v>48</v>
       </c>
       <c r="O89" s="4" t="n">
-        <v>36</v>
+        <v>75</v>
       </c>
     </row>
     <row r="90">
@@ -5936,7 +5936,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -5945,10 +5945,10 @@
         </is>
       </c>
       <c r="D90" s="3" t="n">
-        <v>63</v>
+        <v>56.7</v>
       </c>
       <c r="E90" s="4" t="n">
-        <v>73</v>
+        <v>187</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5956,14 +5956,14 @@
         </is>
       </c>
       <c r="G90" s="3" t="n">
-        <v>57.5</v>
+        <v>49.2</v>
       </c>
       <c r="H90" s="4" t="n">
-        <v>73</v>
+        <v>187</v>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -5972,10 +5972,10 @@
         </is>
       </c>
       <c r="K90" s="3" t="n">
-        <v>57.1</v>
+        <v>51.2</v>
       </c>
       <c r="L90" s="4" t="n">
-        <v>35</v>
+        <v>86</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
@@ -5983,10 +5983,10 @@
         </is>
       </c>
       <c r="N90" s="3" t="n">
-        <v>57.1</v>
+        <v>46.5</v>
       </c>
       <c r="O90" s="4" t="n">
-        <v>35</v>
+        <v>86</v>
       </c>
     </row>
     <row r="91">
@@ -5997,7 +5997,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -6006,25 +6006,25 @@
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>62</v>
+        <v>44.7</v>
       </c>
       <c r="E91" s="4" t="n">
-        <v>79</v>
+        <v>150</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G91" s="3" t="n">
-        <v>40.5</v>
+        <v>42</v>
       </c>
       <c r="H91" s="4" t="n">
-        <v>79</v>
+        <v>150</v>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
@@ -6033,10 +6033,10 @@
         </is>
       </c>
       <c r="K91" s="3" t="n">
-        <v>66.7</v>
+        <v>47.5</v>
       </c>
       <c r="L91" s="4" t="n">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
@@ -6044,10 +6044,10 @@
         </is>
       </c>
       <c r="N91" s="3" t="n">
-        <v>43.3</v>
+        <v>39.3</v>
       </c>
       <c r="O91" s="4" t="n">
-        <v>30</v>
+        <v>61</v>
       </c>
     </row>
     <row r="92">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -6189,25 +6189,25 @@
         </is>
       </c>
       <c r="D94" s="3" t="n">
-        <v>77.2</v>
+        <v>66</v>
       </c>
       <c r="E94" s="4" t="n">
-        <v>79</v>
+        <v>144</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G94" s="3" t="n">
-        <v>38</v>
+        <v>47.2</v>
       </c>
       <c r="H94" s="4" t="n">
-        <v>79</v>
+        <v>144</v>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-N</t>
+          <t>N-U-D-D</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
@@ -6216,21 +6216,21 @@
         </is>
       </c>
       <c r="K94" s="3" t="n">
-        <v>94.09999999999999</v>
+        <v>69.2</v>
       </c>
       <c r="L94" s="4" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N94" s="3" t="n">
-        <v>41.2</v>
+        <v>42.3</v>
       </c>
       <c r="O94" s="4" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="95">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -6250,10 +6250,10 @@
         </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>90.3</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="E95" s="4" t="n">
-        <v>31</v>
+        <v>73</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -6261,14 +6261,14 @@
         </is>
       </c>
       <c r="G95" s="3" t="n">
-        <v>54.8</v>
+        <v>42.5</v>
       </c>
       <c r="H95" s="4" t="n">
-        <v>31</v>
+        <v>73</v>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
@@ -6277,10 +6277,10 @@
         </is>
       </c>
       <c r="K95" s="3" t="n">
-        <v>94.09999999999999</v>
+        <v>75.8</v>
       </c>
       <c r="L95" s="4" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
@@ -6288,10 +6288,10 @@
         </is>
       </c>
       <c r="N95" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>42.4</v>
       </c>
       <c r="O95" s="4" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
     </row>
     <row r="96">
@@ -6363,7 +6363,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -6372,25 +6372,25 @@
         </is>
       </c>
       <c r="D97" s="3" t="n">
-        <v>73</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="E97" s="4" t="n">
-        <v>74</v>
+        <v>152</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G97" s="3" t="n">
-        <v>36.5</v>
+        <v>44.1</v>
       </c>
       <c r="H97" s="4" t="n">
-        <v>74</v>
+        <v>152</v>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
@@ -6399,21 +6399,21 @@
         </is>
       </c>
       <c r="K97" s="3" t="n">
-        <v>63</v>
+        <v>65.5</v>
       </c>
       <c r="L97" s="4" t="n">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N97" s="3" t="n">
-        <v>48.1</v>
+        <v>44.8</v>
       </c>
       <c r="O97" s="4" t="n">
-        <v>27</v>
+        <v>58</v>
       </c>
     </row>
     <row r="98">
@@ -6424,7 +6424,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -6433,25 +6433,25 @@
         </is>
       </c>
       <c r="D98" s="3" t="n">
-        <v>62.2</v>
+        <v>46.5</v>
       </c>
       <c r="E98" s="4" t="n">
-        <v>82</v>
+        <v>170</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G98" s="3" t="n">
-        <v>42.7</v>
+        <v>42.9</v>
       </c>
       <c r="H98" s="4" t="n">
-        <v>82</v>
+        <v>170</v>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
@@ -6460,21 +6460,21 @@
         </is>
       </c>
       <c r="K98" s="3" t="n">
-        <v>64.7</v>
+        <v>44.8</v>
       </c>
       <c r="L98" s="4" t="n">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N98" s="3" t="n">
-        <v>47.1</v>
+        <v>43.3</v>
       </c>
       <c r="O98" s="4" t="n">
-        <v>34</v>
+        <v>67</v>
       </c>
     </row>
     <row r="99">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -6677,25 +6677,25 @@
         </is>
       </c>
       <c r="D102" s="3" t="n">
-        <v>85.59999999999999</v>
+        <v>73</v>
       </c>
       <c r="E102" s="4" t="n">
-        <v>118</v>
+        <v>74</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G102" s="3" t="n">
-        <v>39.8</v>
+        <v>40.5</v>
       </c>
       <c r="H102" s="4" t="n">
-        <v>118</v>
+        <v>74</v>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>N-U-N-N</t>
+          <t>N-U-N-D</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
@@ -6704,21 +6704,21 @@
         </is>
       </c>
       <c r="K102" s="3" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="L102" s="4" t="n">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N102" s="3" t="n">
-        <v>41.3</v>
+        <v>36</v>
       </c>
       <c r="O102" s="4" t="n">
-        <v>46</v>
+        <v>25</v>
       </c>
     </row>
     <row r="103">
@@ -7026,7 +7026,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -7035,10 +7035,10 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>55.6</v>
+        <v>81.8</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -7046,14 +7046,14 @@
         </is>
       </c>
       <c r="I2" s="3" t="n">
-        <v>55.6</v>
+        <v>45.5</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-U</t>
+          <t>D-N-D-N</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="M2" s="3" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
@@ -7073,10 +7073,10 @@
         </is>
       </c>
       <c r="P2" s="3" t="n">
-        <v>70</v>
+        <v>66.7</v>
       </c>
       <c r="Q2" s="4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -7097,7 +7097,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -7106,25 +7106,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>50</v>
+        <v>62.9</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I3" s="3" t="n">
-        <v>42.9</v>
+        <v>45.7</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-N</t>
+          <t>N-U-D-D</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -7133,21 +7133,21 @@
         </is>
       </c>
       <c r="M3" s="3" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="P3" s="3" t="n">
-        <v>66.7</v>
+        <v>40</v>
       </c>
       <c r="Q3" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -7239,7 +7239,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -7248,10 +7248,10 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>70</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -7259,37 +7259,37 @@
         </is>
       </c>
       <c r="I5" s="3" t="n">
-        <v>90</v>
+        <v>46.4</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-N</t>
+          <t>N-D-U-D</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M5" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="P5" s="3" t="n">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -7381,57 +7381,57 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>41.7</v>
+        <v>73</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I7" s="3" t="n">
-        <v>58.3</v>
+        <v>43.2</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M7" s="3" t="n">
-        <v>50</v>
+        <v>72.7</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P7" s="3" t="n">
-        <v>75</v>
+        <v>36.4</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -7452,7 +7452,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -7461,44 +7461,48 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>U-U-D-D</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="G8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="J8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>U-U-D-U</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr"/>
       <c r="N8" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="inlineStr"/>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>66.7</v>
+      </c>
       <c r="Q8" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -7661,7 +7665,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -7670,25 +7674,25 @@
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>77.8</v>
+        <v>64.7</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I11" s="3" t="n">
-        <v>44.4</v>
+        <v>41.2</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-N</t>
+          <t>N-N-D-U</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -7697,21 +7701,21 @@
         </is>
       </c>
       <c r="M11" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P11" s="3" t="n">
         <v>50</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -7732,7 +7736,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -7741,10 +7745,10 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>62.5</v>
+        <v>60</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -7752,37 +7756,37 @@
         </is>
       </c>
       <c r="I12" s="3" t="n">
-        <v>45.8</v>
+        <v>60</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-D</t>
+          <t>D-U-U-N</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M12" s="3" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P12" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -7803,49 +7807,57 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>62.5</v>
+      </c>
       <c r="G13" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr"/>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>75</v>
+      </c>
       <c r="J13" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M13" s="3" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="n">
+        <v>66.7</v>
+      </c>
       <c r="N13" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P13" s="3" t="inlineStr"/>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="Q13" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -8079,7 +8091,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -8088,10 +8100,10 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>75</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -8099,37 +8111,37 @@
         </is>
       </c>
       <c r="I17" s="3" t="n">
-        <v>57.1</v>
+        <v>41.7</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-N</t>
+          <t>U-D-N-D</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M17" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P17" s="3" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -8150,7 +8162,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -8159,48 +8171,48 @@
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>70</v>
+        <v>57.7</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I18" s="3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M18" s="3" t="n">
-        <v>50</v>
+        <v>41.7</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P18" s="3" t="n">
         <v>50</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19">
@@ -8221,7 +8233,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -8237,41 +8249,37 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="I19" s="3" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>5</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-U</t>
+          <t>D-N-U-N</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="M19" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr"/>
       <c r="N19" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P19" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr"/>
       <c r="Q19" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -8363,7 +8371,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -8372,25 +8380,25 @@
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>62.5</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I21" s="3" t="n">
-        <v>64.3</v>
+        <v>37.5</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -8399,10 +8407,10 @@
         </is>
       </c>
       <c r="M21" s="3" t="n">
-        <v>62.5</v>
+        <v>66.7</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -8410,10 +8418,10 @@
         </is>
       </c>
       <c r="P21" s="3" t="n">
-        <v>62.5</v>
+        <v>55.6</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22">
@@ -8434,49 +8442,57 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="G22" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr"/>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>75</v>
+      </c>
       <c r="J22" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-N</t>
+          <t>U-D-N-U</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="N22" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P22" s="3" t="inlineStr"/>
+          <t>D/U</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>50</v>
+      </c>
       <c r="Q22" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -8497,7 +8513,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -8506,10 +8522,10 @@
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>80</v>
+        <v>64.3</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -8517,14 +8533,14 @@
         </is>
       </c>
       <c r="I23" s="3" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-U</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -8533,7 +8549,7 @@
         </is>
       </c>
       <c r="M23" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>57.1</v>
       </c>
       <c r="N23" s="4" t="n">
         <v>7</v>
@@ -8710,7 +8726,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -8719,10 +8735,10 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>50</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -8730,26 +8746,26 @@
         </is>
       </c>
       <c r="I26" s="3" t="n">
-        <v>50</v>
+        <v>61.5</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>N-U-N-N</t>
+          <t>N-U-N-D</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M26" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -8757,10 +8773,10 @@
         </is>
       </c>
       <c r="P26" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -8781,34 +8797,34 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>50</v>
+        <v>55.6</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I27" s="3" t="n">
-        <v>50</v>
+        <v>72.2</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-D</t>
+          <t>N-U-U-U</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -8848,7 +8864,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -8857,48 +8873,48 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>72.7</v>
+        <v>66.7</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I28" s="3" t="n">
-        <v>36.4</v>
+        <v>55.6</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-N-U-D</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M28" s="3" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P28" s="3" t="n">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
@@ -9128,7 +9144,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -9137,48 +9153,48 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I32" s="3" t="n">
-        <v>85.7</v>
+        <v>54.5</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-N</t>
+          <t>D-U-N-D</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M32" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="P32" s="3" t="n">
         <v>50</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
@@ -9341,57 +9357,49 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-U</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr"/>
       <c r="G35" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I35" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr"/>
       <c r="J35" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>U-N-N-N</t>
+          <t>U-N-N-U</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M35" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr"/>
       <c r="N35" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P35" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr"/>
       <c r="Q35" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -9483,7 +9491,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -9492,25 +9500,25 @@
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>77.8</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I37" s="3" t="n">
         <v>50</v>
       </c>
       <c r="J37" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-U</t>
+          <t>U-N-D-N</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -9526,7 +9534,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P37" s="3" t="n">
@@ -9696,12 +9704,12 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F40" s="3" t="n">
@@ -9712,7 +9720,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="I40" s="3" t="n">
@@ -9723,30 +9731,30 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-N</t>
+          <t>U-N-D-U</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M40" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="P40" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q40" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41">
@@ -9909,7 +9917,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9918,44 +9926,48 @@
         </is>
       </c>
       <c r="F43" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="J43" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>N-D-U-D</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="G43" s="4" t="n">
+      <c r="N43" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="n">
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="J43" s="4" t="n">
+      <c r="Q43" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>N-D-U-N</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M43" s="3" t="inlineStr"/>
-      <c r="N43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P43" s="3" t="inlineStr"/>
-      <c r="Q43" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -10402,7 +10414,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -10411,10 +10423,10 @@
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>66.7</v>
+        <v>54.5</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -10422,37 +10434,37 @@
         </is>
       </c>
       <c r="I50" s="3" t="n">
-        <v>44.4</v>
+        <v>54.5</v>
       </c>
       <c r="J50" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
+          <t>N/U</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="N50" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
           <t>D/N</t>
         </is>
       </c>
-      <c r="M50" s="3" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="N50" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="O50" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
       <c r="P50" s="3" t="n">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="Q50" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -10544,7 +10556,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -10553,10 +10565,10 @@
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -10564,14 +10576,14 @@
         </is>
       </c>
       <c r="I52" s="3" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="J52" s="4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-N</t>
+          <t>U-U-D-D</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
@@ -10580,21 +10592,21 @@
         </is>
       </c>
       <c r="M52" s="3" t="n">
-        <v>77.8</v>
+        <v>75</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P52" s="3" t="n">
-        <v>44.4</v>
+        <v>50</v>
       </c>
       <c r="Q52" s="4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="53">
@@ -10615,7 +10627,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -10624,10 +10636,10 @@
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>62.5</v>
+        <v>100</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -10635,14 +10647,14 @@
         </is>
       </c>
       <c r="I53" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J53" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-D</t>
+          <t>N-D-U-N</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
@@ -10654,7 +10666,7 @@
         <v>100</v>
       </c>
       <c r="N53" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
@@ -10662,10 +10674,10 @@
         </is>
       </c>
       <c r="P53" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="Q53" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -10757,57 +10769,57 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>60</v>
+        <v>57.1</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I55" s="3" t="n">
-        <v>80</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="J55" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-U</t>
+          <t>D-N-N-D</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M55" s="3" t="n">
         <v>100</v>
       </c>
       <c r="N55" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P55" s="3" t="n">
         <v>100</v>
       </c>
       <c r="Q55" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -10970,7 +10982,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -10979,25 +10991,25 @@
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>66.7</v>
+        <v>80</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I58" s="3" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
       <c r="J58" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>N-D-N-N</t>
+          <t>N-D-N-D</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
@@ -11037,7 +11049,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-U</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -11046,14 +11058,14 @@
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>66.7</v>
+        <v>55.6</v>
       </c>
       <c r="G59" s="4" t="n">
         <v>9</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I59" s="3" t="n">
@@ -11064,19 +11076,19 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-N</t>
+          <t>D-U-N-U</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M59" s="3" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="N59" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
@@ -11084,10 +11096,10 @@
         </is>
       </c>
       <c r="P59" s="3" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="Q59" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -11108,7 +11120,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -11117,10 +11129,10 @@
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>75</v>
+        <v>48.4</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -11128,37 +11140,37 @@
         </is>
       </c>
       <c r="I60" s="3" t="n">
-        <v>40</v>
+        <v>45.2</v>
       </c>
       <c r="J60" s="4" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M60" s="3" t="n">
-        <v>100</v>
+        <v>44.4</v>
       </c>
       <c r="N60" s="4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P60" s="3" t="n">
-        <v>40</v>
+        <v>44.4</v>
       </c>
       <c r="Q60" s="4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="61">
@@ -11179,7 +11191,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -11188,10 +11200,10 @@
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>54.2</v>
+        <v>66.7</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -11199,14 +11211,14 @@
         </is>
       </c>
       <c r="I61" s="3" t="n">
-        <v>58.3</v>
+        <v>66.7</v>
       </c>
       <c r="J61" s="4" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
@@ -11215,10 +11227,10 @@
         </is>
       </c>
       <c r="M61" s="3" t="n">
-        <v>55.6</v>
+        <v>100</v>
       </c>
       <c r="N61" s="4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
@@ -11226,10 +11238,10 @@
         </is>
       </c>
       <c r="P61" s="3" t="n">
-        <v>44.4</v>
+        <v>66.7</v>
       </c>
       <c r="Q61" s="4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62">
@@ -11317,7 +11329,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -11326,10 +11338,10 @@
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>44.4</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -11337,37 +11349,37 @@
         </is>
       </c>
       <c r="I63" s="3" t="n">
-        <v>66.7</v>
+        <v>57.1</v>
       </c>
       <c r="J63" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-U</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M63" s="3" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="N63" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P63" s="3" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="Q63" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -11388,57 +11400,57 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>50</v>
+        <v>62.5</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I64" s="3" t="n">
-        <v>50</v>
+        <v>62.5</v>
       </c>
       <c r="J64" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-N</t>
+          <t>D-N-N-D</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M64" s="3" t="n">
         <v>100</v>
       </c>
       <c r="N64" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="P64" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q64" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -11459,7 +11471,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -11468,48 +11480,48 @@
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>72.7</v>
+        <v>56.2</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I65" s="3" t="n">
-        <v>36.4</v>
+        <v>43.8</v>
       </c>
       <c r="J65" s="4" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-U</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M65" s="3" t="n">
-        <v>66.7</v>
+        <v>57.1</v>
       </c>
       <c r="N65" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P65" s="3" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
       <c r="Q65" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66">
@@ -11743,19 +11755,19 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>N-U-D</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F69" s="3" t="n">
         <v>100</v>
       </c>
       <c r="G69" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -11766,16 +11778,16 @@
         <v>100</v>
       </c>
       <c r="J69" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-D</t>
+          <t>U-N-U-U</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M69" s="3" t="n">
@@ -11814,7 +11826,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -11823,10 +11835,10 @@
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>81</v>
+        <v>72.7</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -11834,14 +11846,14 @@
         </is>
       </c>
       <c r="I70" s="3" t="n">
-        <v>57.1</v>
+        <v>45.5</v>
       </c>
       <c r="J70" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-N</t>
+          <t>U-N-U-D</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
@@ -11850,10 +11862,10 @@
         </is>
       </c>
       <c r="M70" s="3" t="n">
-        <v>85.7</v>
+        <v>77.8</v>
       </c>
       <c r="N70" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
@@ -11861,10 +11873,10 @@
         </is>
       </c>
       <c r="P70" s="3" t="n">
-        <v>57.1</v>
+        <v>44.4</v>
       </c>
       <c r="Q70" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="71">
@@ -12023,7 +12035,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -12032,25 +12044,25 @@
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>80</v>
       </c>
       <c r="G73" s="4" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I73" s="3" t="n">
-        <v>33.3</v>
+        <v>53.3</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-U</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
@@ -12059,21 +12071,21 @@
         </is>
       </c>
       <c r="M73" s="3" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="N73" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P73" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="Q73" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74">
@@ -12094,7 +12106,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -12103,48 +12115,48 @@
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>50</v>
+        <v>58.3</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I74" s="3" t="n">
-        <v>50</v>
+        <v>58.3</v>
       </c>
       <c r="J74" s="4" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-U</t>
+          <t>N-D-D-N</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M74" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="N74" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P74" s="3" t="n">
         <v>66.7</v>
       </c>
       <c r="Q74" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75">
@@ -12165,7 +12177,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-N-N</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -12174,48 +12186,44 @@
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="G75" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I75" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="J75" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-U</t>
+          <t>D-N-N-N</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="M75" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M75" s="3" t="inlineStr"/>
       <c r="N75" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P75" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P75" s="3" t="inlineStr"/>
       <c r="Q75" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -12236,7 +12244,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -12245,25 +12253,25 @@
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>77.8</v>
+        <v>70</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I76" s="3" t="n">
-        <v>55.6</v>
+        <v>50</v>
       </c>
       <c r="J76" s="4" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-N</t>
+          <t>N-U-U-D</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
@@ -12272,10 +12280,10 @@
         </is>
       </c>
       <c r="M76" s="3" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="N76" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
@@ -12283,10 +12291,10 @@
         </is>
       </c>
       <c r="P76" s="3" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="Q76" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="77">
@@ -12307,7 +12315,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -12316,25 +12324,25 @@
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>72.2</v>
+        <v>75</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I77" s="3" t="n">
-        <v>38.9</v>
+        <v>58.3</v>
       </c>
       <c r="J77" s="4" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-U</t>
+          <t>D-N-U-N</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
@@ -12343,10 +12351,10 @@
         </is>
       </c>
       <c r="M77" s="3" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="N77" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
@@ -12354,10 +12362,10 @@
         </is>
       </c>
       <c r="P77" s="3" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="Q77" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78">
@@ -12378,7 +12386,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -12387,25 +12395,25 @@
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>83.3</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="G78" s="4" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I78" s="3" t="n">
-        <v>50</v>
+        <v>47.1</v>
       </c>
       <c r="J78" s="4" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>N-U-N-N</t>
+          <t>N-U-N-D</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
@@ -12421,7 +12429,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P78" s="3" t="n">
@@ -12520,7 +12528,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>N-U-D</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -12529,41 +12537,41 @@
         </is>
       </c>
       <c r="F80" s="3" t="n">
-        <v>63.6</v>
+        <v>66.7</v>
       </c>
       <c r="G80" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I80" s="3" t="n">
-        <v>45.5</v>
+        <v>44.4</v>
       </c>
       <c r="J80" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>N-N-U-D</t>
+          <t>N-N-U-N</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M80" s="3" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="N80" s="4" t="n">
         <v>4</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="P80" s="3" t="n">
@@ -12875,7 +12883,7 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-U</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -12884,25 +12892,25 @@
         </is>
       </c>
       <c r="F85" s="3" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G85" s="4" t="n">
         <v>5</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I85" s="3" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>5</v>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>N-N-N-N</t>
+          <t>N-N-N-U</t>
         </is>
       </c>
       <c r="L85" s="2" t="inlineStr">
@@ -12914,18 +12922,18 @@
         <v>100</v>
       </c>
       <c r="N85" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P85" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="Q85" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86">
@@ -12946,7 +12954,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -12955,10 +12963,10 @@
         </is>
       </c>
       <c r="F86" s="3" t="n">
-        <v>56.4</v>
+        <v>68.8</v>
       </c>
       <c r="G86" s="4" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -12966,14 +12974,14 @@
         </is>
       </c>
       <c r="I86" s="3" t="n">
-        <v>43.6</v>
+        <v>50</v>
       </c>
       <c r="J86" s="4" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
@@ -12982,21 +12990,21 @@
         </is>
       </c>
       <c r="M86" s="3" t="n">
-        <v>59.1</v>
+        <v>66.7</v>
       </c>
       <c r="N86" s="4" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P86" s="3" t="n">
-        <v>40.9</v>
+        <v>44.4</v>
       </c>
       <c r="Q86" s="4" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
     </row>
     <row r="87">
@@ -13017,7 +13025,7 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -13026,48 +13034,48 @@
         </is>
       </c>
       <c r="F87" s="3" t="n">
-        <v>72.2</v>
+        <v>66.7</v>
       </c>
       <c r="G87" s="4" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I87" s="3" t="n">
         <v>44.4</v>
       </c>
       <c r="J87" s="4" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-N</t>
+          <t>N-U-D-D</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M87" s="3" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
       <c r="N87" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P87" s="3" t="n">
-        <v>100</v>
+        <v>42.9</v>
       </c>
       <c r="Q87" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="88">
@@ -13159,7 +13167,7 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -13168,25 +13176,25 @@
         </is>
       </c>
       <c r="F89" s="3" t="n">
-        <v>73.90000000000001</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="G89" s="4" t="n">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I89" s="3" t="n">
-        <v>43.5</v>
+        <v>48.8</v>
       </c>
       <c r="J89" s="4" t="n">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="L89" s="2" t="inlineStr">
@@ -13195,21 +13203,21 @@
         </is>
       </c>
       <c r="M89" s="3" t="n">
-        <v>76.90000000000001</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="N89" s="4" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P89" s="3" t="n">
-        <v>38.5</v>
+        <v>48.1</v>
       </c>
       <c r="Q89" s="4" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
     </row>
     <row r="90">
@@ -13230,7 +13238,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -13239,25 +13247,25 @@
         </is>
       </c>
       <c r="F90" s="3" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G90" s="4" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I90" s="3" t="n">
-        <v>60</v>
+        <v>42.5</v>
       </c>
       <c r="J90" s="4" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
@@ -13266,21 +13274,21 @@
         </is>
       </c>
       <c r="M90" s="3" t="n">
-        <v>50</v>
+        <v>56.5</v>
       </c>
       <c r="N90" s="4" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P90" s="3" t="n">
-        <v>50</v>
+        <v>52.2</v>
       </c>
       <c r="Q90" s="4" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="91">
@@ -13301,7 +13309,7 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -13310,25 +13318,25 @@
         </is>
       </c>
       <c r="F91" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>48.7</v>
       </c>
       <c r="G91" s="4" t="n">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I91" s="3" t="n">
-        <v>35.3</v>
+        <v>48.7</v>
       </c>
       <c r="J91" s="4" t="n">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="L91" s="2" t="inlineStr">
@@ -13337,10 +13345,10 @@
         </is>
       </c>
       <c r="M91" s="3" t="n">
-        <v>80</v>
+        <v>56.2</v>
       </c>
       <c r="N91" s="4" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
@@ -13348,10 +13356,10 @@
         </is>
       </c>
       <c r="P91" s="3" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="Q91" s="4" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="92">
@@ -13514,7 +13522,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -13523,48 +13531,48 @@
         </is>
       </c>
       <c r="F94" s="3" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="G94" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I94" s="3" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="J94" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>N-U-D-D</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M94" s="3" t="n">
         <v>66.7</v>
       </c>
-      <c r="G94" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I94" s="3" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="J94" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="K94" s="2" t="inlineStr">
-        <is>
-          <t>N-U-D-N</t>
-        </is>
-      </c>
-      <c r="L94" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M94" s="3" t="n">
-        <v>100</v>
-      </c>
       <c r="N94" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="P94" s="3" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="Q94" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="95">
@@ -13585,57 +13593,57 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F95" s="3" t="n">
-        <v>50</v>
+        <v>72.7</v>
       </c>
       <c r="G95" s="4" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="I95" s="3" t="n">
-        <v>100</v>
+        <v>40.9</v>
       </c>
       <c r="J95" s="4" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M95" s="3" t="n">
-        <v>50</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="N95" s="4" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P95" s="3" t="n">
-        <v>100</v>
+        <v>53.8</v>
       </c>
       <c r="Q95" s="4" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="96">
@@ -13723,7 +13731,7 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -13732,10 +13740,10 @@
         </is>
       </c>
       <c r="F97" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>73.5</v>
       </c>
       <c r="G97" s="4" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
@@ -13743,26 +13751,26 @@
         </is>
       </c>
       <c r="I97" s="3" t="n">
-        <v>57.1</v>
+        <v>41.2</v>
       </c>
       <c r="J97" s="4" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="M97" s="3" t="n">
-        <v>75</v>
+        <v>44.4</v>
       </c>
       <c r="N97" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
@@ -13770,10 +13778,10 @@
         </is>
       </c>
       <c r="P97" s="3" t="n">
-        <v>75</v>
+        <v>55.6</v>
       </c>
       <c r="Q97" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="98">
@@ -13794,7 +13802,7 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -13803,25 +13811,25 @@
         </is>
       </c>
       <c r="F98" s="3" t="n">
-        <v>47.4</v>
+        <v>55.6</v>
       </c>
       <c r="G98" s="4" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I98" s="3" t="n">
-        <v>42.1</v>
+        <v>38.9</v>
       </c>
       <c r="J98" s="4" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
@@ -13830,10 +13838,10 @@
         </is>
       </c>
       <c r="M98" s="3" t="n">
-        <v>57.1</v>
+        <v>47.1</v>
       </c>
       <c r="N98" s="4" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
@@ -13841,10 +13849,10 @@
         </is>
       </c>
       <c r="P98" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>47.1</v>
       </c>
       <c r="Q98" s="4" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="99">
@@ -14078,7 +14086,7 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -14087,10 +14095,10 @@
         </is>
       </c>
       <c r="F102" s="3" t="n">
-        <v>84.2</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="G102" s="4" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
@@ -14098,14 +14106,14 @@
         </is>
       </c>
       <c r="I102" s="3" t="n">
-        <v>42.1</v>
+        <v>55.6</v>
       </c>
       <c r="J102" s="4" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>N-U-N-N</t>
+          <t>N-U-N-D</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
@@ -14114,21 +14122,21 @@
         </is>
       </c>
       <c r="M102" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N102" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P102" s="3" t="n">
         <v>75</v>
       </c>
-      <c r="N102" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="O102" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P102" s="3" t="n">
-        <v>50</v>
-      </c>
       <c r="Q102" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="103">

--- a/BIS_tr.xlsx
+++ b/BIS_tr.xlsx
@@ -568,7 +568,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -577,10 +577,10 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>68.09999999999999</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>47</v>
+        <v>85</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -588,14 +588,14 @@
         </is>
       </c>
       <c r="G2" s="3" t="n">
-        <v>42.6</v>
+        <v>47.1</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>47</v>
+        <v>85</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>D-N-D-D</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="K2" s="3" t="n">
-        <v>78.59999999999999</v>
+        <v>57.1</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
@@ -615,10 +615,10 @@
         </is>
       </c>
       <c r="N2" s="3" t="n">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="O2" s="4" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
@@ -995,7 +995,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1004,25 +1004,25 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>72.2</v>
+        <v>63.5</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>97</v>
+        <v>63</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G9" s="3" t="n">
-        <v>47.4</v>
+        <v>39.7</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>97</v>
+        <v>63</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-N</t>
+          <t>N-N-D-D</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1031,21 +1031,21 @@
         </is>
       </c>
       <c r="K9" s="3" t="n">
-        <v>76.09999999999999</v>
+        <v>59.3</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N9" s="3" t="n">
-        <v>47.8</v>
+        <v>40.7</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>46</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1065,25 +1065,25 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>77.90000000000001</v>
+        <v>67.3</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G10" s="3" t="n">
-        <v>39.7</v>
+        <v>44.9</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>N-N-N-N</t>
+          <t>N-N-N-D</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1092,21 +1092,21 @@
         </is>
       </c>
       <c r="K10" s="3" t="n">
-        <v>84.59999999999999</v>
+        <v>66.7</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N10" s="3" t="n">
         <v>50</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1309,25 +1309,25 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>63.7</v>
+        <v>67.2</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>102</v>
+        <v>134</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G14" s="3" t="n">
-        <v>42.2</v>
+        <v>41</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>102</v>
+        <v>134</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1336,21 +1336,21 @@
         </is>
       </c>
       <c r="K14" s="3" t="n">
-        <v>68.59999999999999</v>
+        <v>78.7</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N14" s="3" t="n">
-        <v>40</v>
+        <v>42.6</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1614,48 +1614,48 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>60</v>
+        <v>69.2</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>40</v>
+        <v>48.7</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-N-U-D</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K19" s="3" t="n">
-        <v>50</v>
+        <v>61.1</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N19" s="3" t="n">
-        <v>50</v>
+        <v>44.4</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20">
@@ -1788,34 +1788,34 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>60</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G22" s="3" t="n">
-        <v>58.8</v>
+        <v>60</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-U</t>
+          <t>U-D-N-N</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -1824,10 +1824,10 @@
         </is>
       </c>
       <c r="K22" s="3" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="N22" s="3" t="n">
-        <v>62.5</v>
+        <v>66.7</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -1971,7 +1971,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1980,25 +1980,25 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>68.90000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G25" s="3" t="n">
-        <v>40</v>
+        <v>41.2</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-N</t>
+          <t>U-N-D-D</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -2007,21 +2007,21 @@
         </is>
       </c>
       <c r="K25" s="3" t="n">
-        <v>66.7</v>
+        <v>73.7</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N25" s="3" t="n">
-        <v>40</v>
+        <v>42.1</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-U</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2468,25 +2468,25 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>78.8</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G33" s="3" t="n">
-        <v>37.9</v>
+        <v>41.2</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>N-N-N-N</t>
+          <t>N-N-N-U</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -2495,10 +2495,10 @@
         </is>
       </c>
       <c r="K33" s="3" t="n">
-        <v>79.2</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
@@ -2506,10 +2506,10 @@
         </is>
       </c>
       <c r="N33" s="3" t="n">
-        <v>37.5</v>
+        <v>57.9</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2651,25 +2651,25 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>48.3</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>46</v>
+        <v>36.8</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-U</t>
+          <t>U-U-U-N</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -2678,21 +2678,21 @@
         </is>
       </c>
       <c r="K36" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="L36" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="L36" s="4" t="n">
-        <v>36</v>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="N36" s="3" t="n">
-        <v>47.2</v>
-      </c>
       <c r="O36" s="4" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2712,37 +2712,37 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>74</v>
+        <v>50.9</v>
       </c>
       <c r="E37" s="4" t="n">
+        <v>57</v>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="H37" s="4" t="n">
+        <v>57</v>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>U-N-D-U</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>N/U</t>
-        </is>
-      </c>
-      <c r="G37" s="3" t="n">
-        <v>38</v>
-      </c>
-      <c r="H37" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>U-N-D-N</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K37" s="3" t="n">
-        <v>68.8</v>
-      </c>
       <c r="L37" s="4" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         <v>50</v>
       </c>
       <c r="O37" s="4" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="38">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2895,10 +2895,10 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>79.3</v>
+        <v>70.8</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2906,26 +2906,26 @@
         </is>
       </c>
       <c r="G40" s="3" t="n">
-        <v>48.3</v>
+        <v>58.3</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-U</t>
+          <t>U-N-D-N</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="K40" s="3" t="n">
-        <v>76.90000000000001</v>
+        <v>50</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
@@ -2933,10 +2933,10 @@
         </is>
       </c>
       <c r="N40" s="3" t="n">
-        <v>53.8</v>
+        <v>100</v>
       </c>
       <c r="O40" s="4" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3017,48 +3017,48 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>52.4</v>
+        <v>60</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G42" s="3" t="n">
-        <v>42.9</v>
+        <v>40</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="K42" s="3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="N42" s="3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="O42" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3078,10 +3078,10 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>74</v>
+        <v>81.5</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -3089,14 +3089,14 @@
         </is>
       </c>
       <c r="G43" s="3" t="n">
-        <v>44.2</v>
+        <v>44.4</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-D</t>
+          <t>N-D-U-N</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -3105,10 +3105,10 @@
         </is>
       </c>
       <c r="K43" s="3" t="n">
-        <v>84.59999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
@@ -3116,10 +3116,10 @@
         </is>
       </c>
       <c r="N43" s="3" t="n">
-        <v>53.8</v>
+        <v>66.7</v>
       </c>
       <c r="O43" s="4" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3322,25 +3322,25 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>43.5</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G47" s="3" t="n">
-        <v>52.2</v>
+        <v>37.8</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-U</t>
+          <t>D-N-U-N</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -3349,21 +3349,21 @@
         </is>
       </c>
       <c r="K47" s="3" t="n">
-        <v>40</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="L47" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N47" s="3" t="n">
-        <v>45</v>
+        <v>42.1</v>
       </c>
       <c r="O47" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="48">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -3444,25 +3444,25 @@
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>59</v>
+        <v>58.7</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>39</v>
+        <v>75</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G49" s="3" t="n">
-        <v>41</v>
+        <v>38.7</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>39</v>
+        <v>75</v>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-N-U-D</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -3471,10 +3471,10 @@
         </is>
       </c>
       <c r="K49" s="3" t="n">
-        <v>46.7</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="L49" s="4" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
@@ -3482,10 +3482,10 @@
         </is>
       </c>
       <c r="N49" s="3" t="n">
-        <v>60</v>
+        <v>46.4</v>
       </c>
       <c r="O49" s="4" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="50">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -3505,25 +3505,25 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>65.59999999999999</v>
+        <v>70.5</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>61</v>
+        <v>149</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G50" s="3" t="n">
-        <v>42.6</v>
+        <v>41.6</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>61</v>
+        <v>149</v>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -3532,21 +3532,21 @@
         </is>
       </c>
       <c r="K50" s="3" t="n">
-        <v>56.5</v>
+        <v>69.2</v>
       </c>
       <c r="L50" s="4" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N50" s="3" t="n">
-        <v>47.8</v>
+        <v>46.2</v>
       </c>
       <c r="O50" s="4" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
     </row>
     <row r="51">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3688,10 +3688,10 @@
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>56.2</v>
+        <v>60.5</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3699,14 +3699,14 @@
         </is>
       </c>
       <c r="G53" s="3" t="n">
-        <v>56.2</v>
+        <v>44.7</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-N</t>
+          <t>N-D-U-D</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -3715,10 +3715,10 @@
         </is>
       </c>
       <c r="K53" s="3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="L53" s="4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
@@ -3726,10 +3726,10 @@
         </is>
       </c>
       <c r="N53" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="O53" s="4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="54">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3871,10 +3871,10 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>57.1</v>
+        <v>56.5</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3882,26 +3882,26 @@
         </is>
       </c>
       <c r="G56" s="3" t="n">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="H56" s="4" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-D</t>
+          <t>U-U-D-U</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="K56" s="3" t="n">
-        <v>57.9</v>
+        <v>44</v>
       </c>
       <c r="L56" s="4" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
@@ -3909,10 +3909,10 @@
         </is>
       </c>
       <c r="N56" s="3" t="n">
-        <v>57.9</v>
+        <v>60</v>
       </c>
       <c r="O56" s="4" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="57">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>73</v>
+        <v>49.4</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>74</v>
+        <v>156</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3943,14 +3943,14 @@
         </is>
       </c>
       <c r="G57" s="3" t="n">
-        <v>40.5</v>
+        <v>41.7</v>
       </c>
       <c r="H57" s="4" t="n">
-        <v>74</v>
+        <v>156</v>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -3959,10 +3959,10 @@
         </is>
       </c>
       <c r="K57" s="3" t="n">
-        <v>69.2</v>
+        <v>55.9</v>
       </c>
       <c r="L57" s="4" t="n">
-        <v>26</v>
+        <v>68</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
@@ -3970,10 +3970,10 @@
         </is>
       </c>
       <c r="N57" s="3" t="n">
-        <v>38.5</v>
+        <v>36.8</v>
       </c>
       <c r="O57" s="4" t="n">
-        <v>26</v>
+        <v>68</v>
       </c>
     </row>
     <row r="58">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -4298,10 +4298,10 @@
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>63</v>
+        <v>48.8</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -4309,14 +4309,14 @@
         </is>
       </c>
       <c r="G63" s="3" t="n">
-        <v>43.5</v>
+        <v>51.2</v>
       </c>
       <c r="H63" s="4" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-D</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -4325,10 +4325,10 @@
         </is>
       </c>
       <c r="K63" s="3" t="n">
-        <v>46.7</v>
+        <v>55.6</v>
       </c>
       <c r="L63" s="4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
@@ -4336,10 +4336,10 @@
         </is>
       </c>
       <c r="N63" s="3" t="n">
-        <v>40</v>
+        <v>61.1</v>
       </c>
       <c r="O63" s="4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="64">
@@ -4533,57 +4533,53 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>U-N-N</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="G67" s="3" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H67" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-U</t>
+          <t>D-U-N-N</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K67" s="3" t="n">
-        <v>80</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr"/>
       <c r="L67" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
-        </is>
-      </c>
-      <c r="N67" s="3" t="n">
-        <v>40</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr"/>
       <c r="O67" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4960,7 +4956,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -4969,37 +4965,37 @@
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>55.2</v>
+        <v>51.2</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>58</v>
+        <v>160</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G74" s="3" t="n">
-        <v>53.4</v>
+        <v>43.8</v>
       </c>
       <c r="H74" s="4" t="n">
-        <v>58</v>
+        <v>160</v>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-N</t>
+          <t>N-D-D-U</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K74" s="3" t="n">
-        <v>50</v>
+        <v>61.8</v>
       </c>
       <c r="L74" s="4" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
@@ -5007,10 +5003,10 @@
         </is>
       </c>
       <c r="N74" s="3" t="n">
-        <v>62.5</v>
+        <v>47.1</v>
       </c>
       <c r="O74" s="4" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="75">
@@ -5021,7 +5017,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5030,10 +5026,10 @@
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>80</v>
+        <v>66.7</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -5041,37 +5037,33 @@
         </is>
       </c>
       <c r="G75" s="3" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="H75" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-N</t>
+          <t>D-N-N-D</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K75" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="K75" s="3" t="inlineStr"/>
       <c r="L75" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
-        </is>
-      </c>
-      <c r="N75" s="3" t="n">
-        <v>33.3</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr"/>
       <c r="O75" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -5143,7 +5135,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -5152,25 +5144,25 @@
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>66</v>
+        <v>66.7</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G77" s="3" t="n">
-        <v>48.9</v>
+        <v>38.3</v>
       </c>
       <c r="H77" s="4" t="n">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-N-U-D</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -5179,21 +5171,21 @@
         </is>
       </c>
       <c r="K77" s="3" t="n">
-        <v>72.2</v>
+        <v>62.1</v>
       </c>
       <c r="L77" s="4" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N77" s="3" t="n">
-        <v>61.1</v>
+        <v>37.9</v>
       </c>
       <c r="O77" s="4" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
     </row>
     <row r="78">
@@ -5204,7 +5196,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>U-N-D</t>
+          <t>U-N-N</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -5213,25 +5205,25 @@
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>65.2</v>
+        <v>75</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>66</v>
+        <v>36</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G78" s="3" t="n">
-        <v>42.4</v>
+        <v>38.9</v>
       </c>
       <c r="H78" s="4" t="n">
-        <v>66</v>
+        <v>36</v>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>N-U-N-D</t>
+          <t>N-U-N-N</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -5240,21 +5232,21 @@
         </is>
       </c>
       <c r="K78" s="3" t="n">
-        <v>78.59999999999999</v>
+        <v>75</v>
       </c>
       <c r="L78" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="N78" s="3" t="n">
-        <v>35.7</v>
+        <v>37.5</v>
       </c>
       <c r="O78" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="79">
@@ -5265,7 +5257,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -5274,48 +5266,48 @@
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>66</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="E79" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="H79" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>U-N-N-D</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K79" s="3" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="L79" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G79" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="H79" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="I79" s="2" t="inlineStr">
-        <is>
-          <t>U-N-N-N</t>
-        </is>
-      </c>
-      <c r="J79" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K79" s="3" t="n">
-        <v>73.3</v>
-      </c>
-      <c r="L79" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="M79" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="N79" s="3" t="n">
-        <v>40</v>
-      </c>
       <c r="O79" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="80">
@@ -5326,7 +5318,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -5335,10 +5327,10 @@
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>61.9</v>
+        <v>45.1</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -5346,14 +5338,14 @@
         </is>
       </c>
       <c r="G80" s="3" t="n">
-        <v>40.5</v>
+        <v>36.6</v>
       </c>
       <c r="H80" s="4" t="n">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>N-N-U-N</t>
+          <t>N-N-U-D</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -5362,18 +5354,18 @@
         </is>
       </c>
       <c r="K80" s="3" t="n">
-        <v>61.5</v>
+        <v>69.2</v>
       </c>
       <c r="L80" s="4" t="n">
         <v>13</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N80" s="3" t="n">
-        <v>46.2</v>
+        <v>53.8</v>
       </c>
       <c r="O80" s="4" t="n">
         <v>13</v>
@@ -5448,7 +5440,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -5457,25 +5449,25 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>68.59999999999999</v>
+        <v>69.2</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G82" s="3" t="n">
-        <v>40</v>
+        <v>46.2</v>
       </c>
       <c r="H82" s="4" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -5484,10 +5476,10 @@
         </is>
       </c>
       <c r="K82" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="L82" s="4" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
@@ -5495,10 +5487,10 @@
         </is>
       </c>
       <c r="N82" s="3" t="n">
-        <v>42.9</v>
+        <v>44.4</v>
       </c>
       <c r="O82" s="4" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="83">
@@ -5692,7 +5684,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -5701,25 +5693,25 @@
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>60.8</v>
+        <v>60.7</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>166</v>
+        <v>61</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G86" s="3" t="n">
-        <v>44</v>
+        <v>47.5</v>
       </c>
       <c r="H86" s="4" t="n">
-        <v>166</v>
+        <v>61</v>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-D</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -5728,10 +5720,10 @@
         </is>
       </c>
       <c r="K86" s="3" t="n">
-        <v>55.7</v>
+        <v>60</v>
       </c>
       <c r="L86" s="4" t="n">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
@@ -5739,10 +5731,10 @@
         </is>
       </c>
       <c r="N86" s="3" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="O86" s="4" t="n">
-        <v>61</v>
+        <v>25</v>
       </c>
     </row>
     <row r="87">
@@ -6119,7 +6111,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -6128,25 +6120,25 @@
         </is>
       </c>
       <c r="D93" s="3" t="n">
-        <v>57.1</v>
+        <v>73.5</v>
       </c>
       <c r="E93" s="4" t="n">
-        <v>28</v>
+        <v>68</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="G93" s="3" t="n">
-        <v>42.9</v>
+        <v>33.8</v>
       </c>
       <c r="H93" s="4" t="n">
-        <v>28</v>
+        <v>68</v>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-N</t>
+          <t>U-N-U-D</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
@@ -6155,21 +6147,21 @@
         </is>
       </c>
       <c r="K93" s="3" t="n">
-        <v>50</v>
+        <v>79.2</v>
       </c>
       <c r="L93" s="4" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N93" s="3" t="n">
-        <v>62.5</v>
+        <v>37.5</v>
       </c>
       <c r="O93" s="4" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
     </row>
     <row r="94">
@@ -6302,7 +6294,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>N-D-D</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -6311,10 +6303,10 @@
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>50.7</v>
+        <v>60</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -6322,26 +6314,26 @@
         </is>
       </c>
       <c r="G96" s="3" t="n">
-        <v>41.8</v>
+        <v>45</v>
       </c>
       <c r="H96" s="4" t="n">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-D</t>
+          <t>N-N-D-N</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K96" s="3" t="n">
-        <v>61.5</v>
+        <v>64.3</v>
       </c>
       <c r="L96" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
@@ -6349,10 +6341,10 @@
         </is>
       </c>
       <c r="N96" s="3" t="n">
-        <v>53.8</v>
+        <v>57.1</v>
       </c>
       <c r="O96" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="97">
@@ -6424,7 +6416,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -6433,25 +6425,25 @@
         </is>
       </c>
       <c r="D98" s="3" t="n">
-        <v>46.5</v>
+        <v>62.2</v>
       </c>
       <c r="E98" s="4" t="n">
-        <v>170</v>
+        <v>82</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G98" s="3" t="n">
-        <v>42.9</v>
+        <v>42.7</v>
       </c>
       <c r="H98" s="4" t="n">
-        <v>170</v>
+        <v>82</v>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-U</t>
+          <t>D-U-U-N</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
@@ -6460,21 +6452,21 @@
         </is>
       </c>
       <c r="K98" s="3" t="n">
-        <v>44.8</v>
+        <v>64.7</v>
       </c>
       <c r="L98" s="4" t="n">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N98" s="3" t="n">
-        <v>43.3</v>
+        <v>47.1</v>
       </c>
       <c r="O98" s="4" t="n">
-        <v>67</v>
+        <v>34</v>
       </c>
     </row>
     <row r="99">
@@ -6485,7 +6477,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -6494,10 +6486,10 @@
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>68.09999999999999</v>
+        <v>61.8</v>
       </c>
       <c r="E99" s="4" t="n">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -6505,14 +6497,14 @@
         </is>
       </c>
       <c r="G99" s="3" t="n">
-        <v>40.4</v>
+        <v>40.8</v>
       </c>
       <c r="H99" s="4" t="n">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-N</t>
+          <t>U-D-N-D</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
@@ -6521,10 +6513,10 @@
         </is>
       </c>
       <c r="K99" s="3" t="n">
-        <v>84.59999999999999</v>
+        <v>62.5</v>
       </c>
       <c r="L99" s="4" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
@@ -6532,10 +6524,10 @@
         </is>
       </c>
       <c r="N99" s="3" t="n">
-        <v>53.8</v>
+        <v>54.2</v>
       </c>
       <c r="O99" s="4" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="100">
@@ -6790,7 +6782,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-U</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -6799,25 +6791,25 @@
         </is>
       </c>
       <c r="D104" s="3" t="n">
-        <v>64.40000000000001</v>
+        <v>66.7</v>
       </c>
       <c r="E104" s="4" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G104" s="3" t="n">
-        <v>40</v>
+        <v>38.5</v>
       </c>
       <c r="H104" s="4" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>N-N-N-N</t>
+          <t>N-N-N-U</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
@@ -6826,10 +6818,10 @@
         </is>
       </c>
       <c r="K104" s="3" t="n">
-        <v>64.7</v>
+        <v>69.2</v>
       </c>
       <c r="L104" s="4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
@@ -6837,10 +6829,10 @@
         </is>
       </c>
       <c r="N104" s="3" t="n">
-        <v>58.8</v>
+        <v>46.2</v>
       </c>
       <c r="O104" s="4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -7026,7 +7018,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -7035,10 +7027,10 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>81.8</v>
+        <v>72.2</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -7046,19 +7038,19 @@
         </is>
       </c>
       <c r="I2" s="3" t="n">
-        <v>45.5</v>
+        <v>50</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>D-N-D-D</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M2" s="3" t="n">
@@ -7523,7 +7515,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -7532,25 +7524,25 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>72.2</v>
+        <v>87.5</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I9" s="3" t="n">
-        <v>61.1</v>
+        <v>50</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-N</t>
+          <t>N-N-D-D</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -7559,21 +7551,21 @@
         </is>
       </c>
       <c r="M9" s="3" t="n">
-        <v>77.8</v>
+        <v>100</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="P9" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -7594,7 +7586,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -7603,25 +7595,25 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>90.90000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I10" s="3" t="n">
-        <v>45.5</v>
+        <v>50</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>N-N-N-N</t>
+          <t>N-N-N-D</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -7637,11 +7629,11 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P10" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="Q10" s="4" t="n">
         <v>6</v>
@@ -7878,7 +7870,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -7887,48 +7879,48 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>58.8</v>
+        <v>81</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I14" s="3" t="n">
-        <v>41.2</v>
+        <v>38.1</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M14" s="3" t="n">
-        <v>60</v>
+        <v>85.7</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P14" s="3" t="n">
-        <v>60</v>
+        <v>42.9</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
@@ -8233,7 +8225,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -8242,44 +8234,48 @@
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>60</v>
+        <v>61.5</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I19" s="3" t="n">
-        <v>40</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-N-U-D</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M19" s="3" t="inlineStr"/>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="n">
+        <v>66.7</v>
+      </c>
       <c r="N19" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P19" s="3" t="inlineStr"/>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="Q19" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -8442,57 +8438,49 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr"/>
       <c r="G22" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="n">
-        <v>75</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr"/>
       <c r="J22" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-U</t>
+          <t>U-D-N-N</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr"/>
       <c r="N22" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
-        </is>
-      </c>
-      <c r="P22" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr"/>
       <c r="Q22" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -8655,7 +8643,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -8664,10 +8652,10 @@
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>90.90000000000001</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -8675,14 +8663,14 @@
         </is>
       </c>
       <c r="I25" s="3" t="n">
-        <v>45.5</v>
+        <v>47.4</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-N</t>
+          <t>U-N-D-D</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -8691,21 +8679,21 @@
         </is>
       </c>
       <c r="M25" s="3" t="n">
-        <v>66.7</v>
+        <v>80</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P25" s="3" t="n">
-        <v>33.3</v>
+        <v>60</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
@@ -9215,7 +9203,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-U</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -9224,25 +9212,25 @@
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>90.90000000000001</v>
+        <v>60</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I33" s="3" t="n">
-        <v>36.4</v>
+        <v>40</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>N-N-N-N</t>
+          <t>N-N-N-U</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -9251,21 +9239,21 @@
         </is>
       </c>
       <c r="M33" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P33" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34">
@@ -9420,7 +9408,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -9429,10 +9417,10 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -9440,14 +9428,14 @@
         </is>
       </c>
       <c r="I36" s="3" t="n">
-        <v>57.1</v>
+        <v>75</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-U</t>
+          <t>U-U-U-N</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -9456,10 +9444,10 @@
         </is>
       </c>
       <c r="M36" s="3" t="n">
-        <v>57.1</v>
+        <v>100</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
@@ -9467,10 +9455,10 @@
         </is>
       </c>
       <c r="P36" s="3" t="n">
-        <v>57.1</v>
+        <v>100</v>
       </c>
       <c r="Q36" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -9491,7 +9479,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -9500,25 +9488,25 @@
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>78.59999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I37" s="3" t="n">
         <v>50</v>
       </c>
       <c r="J37" s="4" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-N</t>
+          <t>U-N-D-U</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -9534,7 +9522,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P37" s="3" t="n">
@@ -9704,12 +9692,12 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F40" s="3" t="n">
@@ -9720,7 +9708,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I40" s="3" t="n">
@@ -9731,30 +9719,30 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-U</t>
+          <t>U-N-D-N</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M40" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P40" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q40" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -9846,23 +9834,23 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G42" s="4" t="n">
         <v>2</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I42" s="3" t="n">
@@ -9873,30 +9861,26 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M42" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr"/>
       <c r="N42" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P42" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr"/>
       <c r="Q42" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -9917,7 +9901,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9926,48 +9910,44 @@
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I43" s="3" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="J43" s="4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-D</t>
+          <t>N-D-U-N</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M43" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr"/>
       <c r="N43" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P43" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr"/>
       <c r="Q43" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -10201,7 +10181,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -10210,48 +10190,48 @@
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>47.6</v>
+        <v>54.5</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I47" s="3" t="n">
-        <v>57.1</v>
+        <v>45.5</v>
       </c>
       <c r="J47" s="4" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-U</t>
+          <t>D-N-U-N</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="M47" s="3" t="n">
-        <v>42.9</v>
+        <v>33.3</v>
       </c>
       <c r="N47" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="P47" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>33.3</v>
       </c>
       <c r="Q47" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -10343,7 +10323,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -10352,25 +10332,25 @@
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>72.7</v>
+        <v>69.2</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I49" s="3" t="n">
-        <v>54.5</v>
+        <v>46.2</v>
       </c>
       <c r="J49" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-N-U-D</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
@@ -10379,21 +10359,21 @@
         </is>
       </c>
       <c r="M49" s="3" t="n">
-        <v>66.7</v>
+        <v>75</v>
       </c>
       <c r="N49" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P49" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="Q49" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50">
@@ -10414,7 +10394,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -10423,10 +10403,10 @@
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>54.5</v>
+        <v>66.7</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -10434,37 +10414,37 @@
         </is>
       </c>
       <c r="I50" s="3" t="n">
-        <v>54.5</v>
+        <v>46.7</v>
       </c>
       <c r="J50" s="4" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M50" s="3" t="n">
-        <v>50</v>
+        <v>58.3</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P50" s="3" t="n">
         <v>50</v>
       </c>
       <c r="Q50" s="4" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="51">
@@ -10627,7 +10607,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -10636,10 +10616,10 @@
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>100</v>
+        <v>62.5</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -10647,14 +10627,14 @@
         </is>
       </c>
       <c r="I53" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J53" s="4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-N</t>
+          <t>N-D-U-D</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
@@ -10666,7 +10646,7 @@
         <v>100</v>
       </c>
       <c r="N53" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
@@ -10674,10 +10654,10 @@
         </is>
       </c>
       <c r="P53" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="Q53" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -10840,57 +10820,57 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I56" s="3" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J56" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-D</t>
+          <t>U-U-D-U</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M56" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N56" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P56" s="3" t="n">
         <v>100</v>
       </c>
       <c r="Q56" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -10911,7 +10891,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -10920,48 +10900,48 @@
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>54.5</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="I57" s="3" t="n">
-        <v>54.5</v>
+        <v>35.7</v>
       </c>
       <c r="J57" s="4" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M57" s="3" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="N57" s="4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="P57" s="3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="Q57" s="4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="58">
@@ -11329,7 +11309,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -11338,10 +11318,10 @@
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>44.4</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -11349,37 +11329,37 @@
         </is>
       </c>
       <c r="I63" s="3" t="n">
-        <v>57.1</v>
+        <v>66.7</v>
       </c>
       <c r="J63" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-D</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M63" s="3" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="N63" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P63" s="3" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="Q63" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64">
@@ -11613,57 +11593,49 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>U-N-N</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="F67" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr"/>
       <c r="G67" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I67" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="inlineStr"/>
       <c r="J67" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-U</t>
+          <t>D-U-N-N</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="M67" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M67" s="3" t="inlineStr"/>
       <c r="N67" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P67" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P67" s="3" t="inlineStr"/>
       <c r="Q67" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -12106,7 +12078,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -12115,48 +12087,48 @@
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>58.3</v>
+        <v>50</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I74" s="3" t="n">
-        <v>58.3</v>
+        <v>50</v>
       </c>
       <c r="J74" s="4" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-N</t>
+          <t>N-D-D-U</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M74" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="N74" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P74" s="3" t="n">
         <v>66.7</v>
       </c>
       <c r="Q74" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="75">
@@ -12177,12 +12149,12 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F75" s="3" t="n">
@@ -12193,7 +12165,7 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I75" s="3" t="n">
@@ -12204,7 +12176,7 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-N</t>
+          <t>D-N-N-D</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
@@ -12315,7 +12287,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -12324,48 +12296,48 @@
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="G77" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>D/U</t>
+        </is>
+      </c>
+      <c r="I77" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="J77" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>D-N-U-D</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M77" s="3" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="N77" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I77" s="3" t="n">
-        <v>58.3</v>
-      </c>
-      <c r="J77" s="4" t="n">
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P77" s="3" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="Q77" s="4" t="n">
         <v>12</v>
-      </c>
-      <c r="K77" s="2" t="inlineStr">
-        <is>
-          <t>D-N-U-N</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M77" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="N77" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="O77" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P77" s="3" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="Q77" s="4" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="78">
@@ -12386,7 +12358,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>U-N-D</t>
+          <t>U-N-N</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -12395,25 +12367,25 @@
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="G78" s="4" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I78" s="3" t="n">
-        <v>47.1</v>
+        <v>50</v>
       </c>
       <c r="J78" s="4" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>N-U-N-D</t>
+          <t>N-U-N-N</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
@@ -12429,7 +12401,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P78" s="3" t="n">
@@ -12457,7 +12429,7 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -12466,48 +12438,48 @@
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>60</v>
+        <v>58.3</v>
       </c>
       <c r="G79" s="4" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I79" s="3" t="n">
-        <v>40</v>
+        <v>66.7</v>
       </c>
       <c r="J79" s="4" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>U-N-N-N</t>
+          <t>U-N-N-D</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M79" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N79" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P79" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q79" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80">
@@ -12528,7 +12500,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -12537,41 +12509,41 @@
         </is>
       </c>
       <c r="F80" s="3" t="n">
-        <v>66.7</v>
+        <v>63.6</v>
       </c>
       <c r="G80" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I80" s="3" t="n">
-        <v>44.4</v>
+        <v>45.5</v>
       </c>
       <c r="J80" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>N-N-U-N</t>
+          <t>N-N-U-D</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M80" s="3" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="N80" s="4" t="n">
         <v>4</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P80" s="3" t="n">
@@ -12670,7 +12642,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -12679,25 +12651,25 @@
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>81.8</v>
+        <v>72.7</v>
       </c>
       <c r="G82" s="4" t="n">
         <v>11</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I82" s="3" t="n">
-        <v>36.4</v>
+        <v>54.5</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
@@ -12709,18 +12681,18 @@
         <v>50</v>
       </c>
       <c r="N82" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P82" s="3" t="n">
         <v>50</v>
       </c>
       <c r="Q82" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83">
@@ -12954,7 +12926,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -12963,48 +12935,48 @@
         </is>
       </c>
       <c r="F86" s="3" t="n">
-        <v>68.8</v>
+        <v>42.9</v>
       </c>
       <c r="G86" s="4" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I86" s="3" t="n">
         <v>50</v>
       </c>
       <c r="J86" s="4" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-D</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M86" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="N86" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P86" s="3" t="n">
-        <v>44.4</v>
+        <v>75</v>
       </c>
       <c r="Q86" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="87">
@@ -13451,7 +13423,7 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -13460,25 +13432,25 @@
         </is>
       </c>
       <c r="F93" s="3" t="n">
-        <v>66.7</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="G93" s="4" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I93" s="3" t="n">
-        <v>66.7</v>
+        <v>38.1</v>
       </c>
       <c r="J93" s="4" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-N</t>
+          <t>U-N-U-D</t>
         </is>
       </c>
       <c r="L93" s="2" t="inlineStr">
@@ -13490,18 +13462,18 @@
         <v>100</v>
       </c>
       <c r="N93" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="P93" s="3" t="n">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="Q93" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="94">
@@ -13664,7 +13636,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>N-D-D</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -13680,37 +13652,41 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I96" s="3" t="n">
-        <v>44.4</v>
+        <v>55.6</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-D</t>
+          <t>N-N-D-N</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M96" s="3" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M96" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="N96" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P96" s="3" t="inlineStr"/>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P96" s="3" t="n">
+        <v>66.7</v>
+      </c>
       <c r="Q96" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="97">
@@ -13802,7 +13778,7 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -13811,25 +13787,25 @@
         </is>
       </c>
       <c r="F98" s="3" t="n">
-        <v>55.6</v>
+        <v>47.4</v>
       </c>
       <c r="G98" s="4" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I98" s="3" t="n">
-        <v>38.9</v>
+        <v>42.1</v>
       </c>
       <c r="J98" s="4" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-U</t>
+          <t>D-U-U-N</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
@@ -13838,10 +13814,10 @@
         </is>
       </c>
       <c r="M98" s="3" t="n">
-        <v>47.1</v>
+        <v>57.1</v>
       </c>
       <c r="N98" s="4" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
@@ -13849,10 +13825,10 @@
         </is>
       </c>
       <c r="P98" s="3" t="n">
-        <v>47.1</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="Q98" s="4" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="99">
@@ -13873,7 +13849,7 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -13882,25 +13858,25 @@
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>87.5</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="G99" s="4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I99" s="3" t="n">
         <v>50</v>
       </c>
       <c r="J99" s="4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-N</t>
+          <t>U-D-N-D</t>
         </is>
       </c>
       <c r="L99" s="2" t="inlineStr">
@@ -13909,21 +13885,21 @@
         </is>
       </c>
       <c r="M99" s="3" t="n">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="N99" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P99" s="3" t="n">
-        <v>33.3</v>
+        <v>66.7</v>
       </c>
       <c r="Q99" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="100">
@@ -14228,7 +14204,7 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-U</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -14240,45 +14216,45 @@
         <v>50</v>
       </c>
       <c r="G104" s="4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I104" s="3" t="n">
-        <v>50</v>
+        <v>37.5</v>
       </c>
       <c r="J104" s="4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>N-N-N-N</t>
+          <t>N-N-N-U</t>
         </is>
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M104" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N104" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P104" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q104" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/BIS_tr.xlsx
+++ b/BIS_tr.xlsx
@@ -568,7 +568,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>N-D-D</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -577,10 +577,10 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>67.09999999999999</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>85</v>
+        <v>47</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -588,14 +588,14 @@
         </is>
       </c>
       <c r="G2" s="3" t="n">
-        <v>47.1</v>
+        <v>42.6</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>85</v>
+        <v>47</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-D</t>
+          <t>D-N-D-N</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="K2" s="3" t="n">
-        <v>57.1</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
@@ -615,10 +615,10 @@
         </is>
       </c>
       <c r="N2" s="3" t="n">
-        <v>50</v>
+        <v>42.9</v>
       </c>
       <c r="O2" s="4" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1187,10 +1187,10 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>76.5</v>
+        <v>64.7</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1198,14 +1198,14 @@
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>58.8</v>
+        <v>45.6</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1214,10 +1214,10 @@
         </is>
       </c>
       <c r="K12" s="3" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="N12" s="3" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1736,25 +1736,25 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>57</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>158</v>
+        <v>68</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G21" s="3" t="n">
-        <v>45.6</v>
+        <v>47.1</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>158</v>
+        <v>68</v>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-U</t>
+          <t>D-U-U-N</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1763,21 +1763,21 @@
         </is>
       </c>
       <c r="K21" s="3" t="n">
-        <v>63</v>
+        <v>63.3</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N21" s="3" t="n">
-        <v>52.2</v>
+        <v>56.7</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1919,25 +1919,25 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>58.1</v>
+        <v>66.2</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G24" s="3" t="n">
-        <v>41.9</v>
+        <v>38</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-N</t>
+          <t>N-U-D-D</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -1946,21 +1946,21 @@
         </is>
       </c>
       <c r="K24" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N24" s="3" t="n">
-        <v>55.6</v>
+        <v>54.5</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3078,10 +3078,10 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>81.5</v>
+        <v>74</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -3089,14 +3089,14 @@
         </is>
       </c>
       <c r="G43" s="3" t="n">
-        <v>44.4</v>
+        <v>44.2</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-N</t>
+          <t>N-D-U-D</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -3105,10 +3105,10 @@
         </is>
       </c>
       <c r="K43" s="3" t="n">
-        <v>83.3</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
@@ -3116,10 +3116,10 @@
         </is>
       </c>
       <c r="N43" s="3" t="n">
-        <v>66.7</v>
+        <v>53.8</v>
       </c>
       <c r="O43" s="4" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="44">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3139,37 +3139,37 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>66.7</v>
+        <v>56.9</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G44" s="3" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="H44" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>U-D-U-U</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="n">
         <v>55.6</v>
       </c>
-      <c r="H44" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>U-D-U-N</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K44" s="3" t="n">
-        <v>50</v>
-      </c>
       <c r="L44" s="4" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
@@ -3177,10 +3177,10 @@
         </is>
       </c>
       <c r="N44" s="3" t="n">
-        <v>50</v>
+        <v>44.4</v>
       </c>
       <c r="O44" s="4" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="45">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-N-N</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3200,25 +3200,25 @@
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>45.1</v>
+        <v>76.5</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G45" s="3" t="n">
-        <v>49</v>
+        <v>41.2</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>U-N-N-U</t>
+          <t>U-N-N-N</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -3227,21 +3227,21 @@
         </is>
       </c>
       <c r="K45" s="3" t="n">
-        <v>64.3</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N45" s="3" t="n">
-        <v>50</v>
+        <v>55.6</v>
       </c>
       <c r="O45" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="46">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -4660,48 +4660,48 @@
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G69" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="H69" s="4" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-U</t>
+          <t>U-N-U-N</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K69" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L69" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N69" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="O69" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4895,7 +4895,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -4904,25 +4904,25 @@
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>56.3</v>
+        <v>72.7</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>87</v>
+        <v>44</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G73" s="3" t="n">
-        <v>46</v>
+        <v>52.3</v>
       </c>
       <c r="H73" s="4" t="n">
-        <v>87</v>
+        <v>44</v>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-U</t>
+          <t>U-D-D-N</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -4931,10 +4931,10 @@
         </is>
       </c>
       <c r="K73" s="3" t="n">
-        <v>65.40000000000001</v>
+        <v>66.7</v>
       </c>
       <c r="L73" s="4" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
@@ -4942,10 +4942,10 @@
         </is>
       </c>
       <c r="N73" s="3" t="n">
-        <v>46.2</v>
+        <v>47.6</v>
       </c>
       <c r="O73" s="4" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="74">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -4965,7 +4965,7 @@
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>51.2</v>
+        <v>43.8</v>
       </c>
       <c r="E74" s="4" t="n">
         <v>160</v>
@@ -4976,14 +4976,14 @@
         </is>
       </c>
       <c r="G74" s="3" t="n">
-        <v>43.8</v>
+        <v>49.4</v>
       </c>
       <c r="H74" s="4" t="n">
         <v>160</v>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-U</t>
+          <t>N-D-D-D</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -4992,10 +4992,10 @@
         </is>
       </c>
       <c r="K74" s="3" t="n">
-        <v>61.8</v>
+        <v>56.5</v>
       </c>
       <c r="L74" s="4" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
@@ -5003,10 +5003,10 @@
         </is>
       </c>
       <c r="N74" s="3" t="n">
-        <v>47.1</v>
+        <v>47.8</v>
       </c>
       <c r="O74" s="4" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
     </row>
     <row r="75">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -5205,25 +5205,25 @@
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>75</v>
+        <v>65.2</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G78" s="3" t="n">
-        <v>38.9</v>
+        <v>42.4</v>
       </c>
       <c r="H78" s="4" t="n">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>N-U-N-N</t>
+          <t>N-U-N-D</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -5232,21 +5232,21 @@
         </is>
       </c>
       <c r="K78" s="3" t="n">
-        <v>75</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="L78" s="4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N78" s="3" t="n">
-        <v>37.5</v>
+        <v>35.7</v>
       </c>
       <c r="O78" s="4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="79">
@@ -5257,7 +5257,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>N-N-D</t>
+          <t>N-N-N</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -5266,10 +5266,10 @@
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>69.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -5277,14 +5277,14 @@
         </is>
       </c>
       <c r="G79" s="3" t="n">
-        <v>47.8</v>
+        <v>40</v>
       </c>
       <c r="H79" s="4" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>U-N-N-D</t>
+          <t>U-N-N-N</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -5293,21 +5293,21 @@
         </is>
       </c>
       <c r="K79" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="L79" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N79" s="3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="O79" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="80">
@@ -6294,7 +6294,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -6303,10 +6303,10 @@
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>60</v>
+        <v>50.7</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -6314,26 +6314,26 @@
         </is>
       </c>
       <c r="G96" s="3" t="n">
-        <v>45</v>
+        <v>41.8</v>
       </c>
       <c r="H96" s="4" t="n">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-N</t>
+          <t>N-N-D-D</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K96" s="3" t="n">
-        <v>64.3</v>
+        <v>61.5</v>
       </c>
       <c r="L96" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
@@ -6341,10 +6341,10 @@
         </is>
       </c>
       <c r="N96" s="3" t="n">
-        <v>57.1</v>
+        <v>53.8</v>
       </c>
       <c r="O96" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="97">
@@ -7018,7 +7018,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>N-D-D</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -7027,10 +7027,10 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>72.2</v>
+        <v>81.8</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -7038,19 +7038,19 @@
         </is>
       </c>
       <c r="I2" s="3" t="n">
-        <v>50</v>
+        <v>45.5</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-D</t>
+          <t>D-N-D-N</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M2" s="3" t="n">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -7737,10 +7737,10 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -7748,37 +7748,37 @@
         </is>
       </c>
       <c r="I12" s="3" t="n">
-        <v>60</v>
+        <v>45.8</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="M12" s="3" t="n">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P12" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -8367,7 +8367,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -8376,37 +8376,37 @@
         </is>
       </c>
       <c r="F21" s="3" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="J21" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>D-U-U-N</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="n">
         <v>62.5</v>
       </c>
-      <c r="G21" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>D/U</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="J21" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>D-U-U-U</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M21" s="3" t="n">
-        <v>66.7</v>
-      </c>
       <c r="N21" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -8414,10 +8414,10 @@
         </is>
       </c>
       <c r="P21" s="3" t="n">
-        <v>55.6</v>
+        <v>62.5</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22">
@@ -8572,34 +8572,34 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>50</v>
+        <v>81.2</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="I24" s="3" t="n">
-        <v>70</v>
+        <v>43.8</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-N</t>
+          <t>N-U-D-D</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -8611,18 +8611,18 @@
         <v>100</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P24" s="3" t="n">
         <v>100</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -9901,7 +9901,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9910,44 +9910,48 @@
         </is>
       </c>
       <c r="F43" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="J43" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>N-D-U-D</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="G43" s="4" t="n">
+      <c r="N43" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="n">
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="J43" s="4" t="n">
+      <c r="Q43" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>N-D-U-N</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M43" s="3" t="inlineStr"/>
-      <c r="N43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P43" s="3" t="inlineStr"/>
-      <c r="Q43" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -9968,7 +9972,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -9977,10 +9981,10 @@
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>66.7</v>
+        <v>62.5</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -9988,26 +9992,26 @@
         </is>
       </c>
       <c r="I44" s="3" t="n">
-        <v>66.7</v>
+        <v>62.5</v>
       </c>
       <c r="J44" s="4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-U</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M44" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="N44" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
@@ -10015,10 +10019,10 @@
         </is>
       </c>
       <c r="P44" s="3" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Q44" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45">
@@ -10039,7 +10043,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-N-N</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -10048,10 +10052,10 @@
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>42.9</v>
+        <v>100</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -10059,14 +10063,14 @@
         </is>
       </c>
       <c r="I45" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="J45" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>U-N-N-U</t>
+          <t>U-N-N-N</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
@@ -10075,10 +10079,10 @@
         </is>
       </c>
       <c r="M45" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="N45" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
@@ -10089,7 +10093,7 @@
         <v>100</v>
       </c>
       <c r="Q45" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -11727,57 +11731,49 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F69" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr"/>
       <c r="G69" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I69" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="inlineStr"/>
       <c r="J69" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-U</t>
+          <t>U-N-U-N</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M69" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M69" s="3" t="inlineStr"/>
       <c r="N69" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P69" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P69" s="3" t="inlineStr"/>
       <c r="Q69" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -12007,7 +12003,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -12016,25 +12012,25 @@
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>80</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="G73" s="4" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="I73" s="3" t="n">
-        <v>53.3</v>
+        <v>33.3</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-U</t>
+          <t>U-D-D-N</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
@@ -12043,21 +12039,21 @@
         </is>
       </c>
       <c r="M73" s="3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="N73" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P73" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="Q73" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">
@@ -12078,7 +12074,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -12087,48 +12083,48 @@
         </is>
       </c>
       <c r="F74" s="3" t="n">
+        <v>51.6</v>
+      </c>
+      <c r="G74" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I74" s="3" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="J74" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>N-D-D-D</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M74" s="3" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="N74" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>D/U</t>
+        </is>
+      </c>
+      <c r="P74" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="G74" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I74" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="J74" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="K74" s="2" t="inlineStr">
-        <is>
-          <t>N-D-D-U</t>
-        </is>
-      </c>
-      <c r="L74" s="2" t="inlineStr">
-        <is>
-          <t>N/U</t>
-        </is>
-      </c>
-      <c r="M74" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="N74" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="O74" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P74" s="3" t="n">
-        <v>66.7</v>
-      </c>
       <c r="Q74" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="75">
@@ -12358,7 +12354,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -12367,25 +12363,25 @@
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>83.3</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="G78" s="4" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I78" s="3" t="n">
-        <v>50</v>
+        <v>47.1</v>
       </c>
       <c r="J78" s="4" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>N-U-N-N</t>
+          <t>N-U-N-D</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
@@ -12401,7 +12397,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P78" s="3" t="n">
@@ -12429,7 +12425,7 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>N-N-D</t>
+          <t>N-N-N</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -12438,48 +12434,48 @@
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>58.3</v>
+        <v>60</v>
       </c>
       <c r="G79" s="4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="I79" s="3" t="n">
-        <v>66.7</v>
+        <v>40</v>
       </c>
       <c r="J79" s="4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>U-N-N-D</t>
+          <t>U-N-N-N</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M79" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N79" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P79" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q79" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -13636,7 +13632,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -13652,41 +13648,37 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="I96" s="3" t="n">
-        <v>55.6</v>
+        <v>44.4</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-N</t>
+          <t>N-N-D-D</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M96" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M96" s="3" t="inlineStr"/>
       <c r="N96" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P96" s="3" t="n">
-        <v>66.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P96" s="3" t="inlineStr"/>
       <c r="Q96" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">

--- a/BIS_tr.xlsx
+++ b/BIS_tr.xlsx
@@ -568,7 +568,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -577,25 +577,25 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>82.7</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G2" s="3" t="n">
-        <v>40.4</v>
+        <v>40.7</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>N-D-N-N</t>
+          <t>N-D-N-U</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -604,21 +604,21 @@
         </is>
       </c>
       <c r="K2" s="3" t="n">
-        <v>93.8</v>
+        <v>65</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N2" s="3" t="n">
-        <v>37.5</v>
+        <v>40</v>
       </c>
       <c r="O2" s="4" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -629,7 +629,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -638,25 +638,25 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>67.59999999999999</v>
+        <v>53.6</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>71</v>
+        <v>168</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G3" s="3" t="n">
-        <v>42.3</v>
+        <v>41.7</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>71</v>
+        <v>168</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-U</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -665,21 +665,21 @@
         </is>
       </c>
       <c r="K3" s="3" t="n">
-        <v>76</v>
+        <v>51.5</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N3" s="3" t="n">
-        <v>40</v>
+        <v>42.6</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>25</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4">
@@ -751,7 +751,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -760,25 +760,25 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>74.7</v>
+        <v>63.3</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>87</v>
+        <v>166</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G5" s="3" t="n">
-        <v>40.2</v>
+        <v>41.6</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>87</v>
+        <v>166</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="K5" s="3" t="n">
-        <v>64.7</v>
+        <v>63.9</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N5" s="3" t="n">
-        <v>38.2</v>
+        <v>43.1</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>34</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6">
@@ -812,7 +812,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>72.7</v>
+        <v>53.4</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>33</v>
+        <v>73</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -832,14 +832,14 @@
         </is>
       </c>
       <c r="G6" s="3" t="n">
-        <v>39.4</v>
+        <v>43.8</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>33</v>
+        <v>73</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-N</t>
+          <t>U-D-N-U</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -848,21 +848,21 @@
         </is>
       </c>
       <c r="K6" s="3" t="n">
-        <v>53.8</v>
+        <v>48.6</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N6" s="3" t="n">
-        <v>46.2</v>
+        <v>43.2</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>13</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7">
@@ -873,7 +873,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -882,10 +882,10 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>61.3</v>
+        <v>54.4</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>75</v>
+        <v>180</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -893,14 +893,14 @@
         </is>
       </c>
       <c r="G7" s="3" t="n">
-        <v>48</v>
+        <v>41.7</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>75</v>
+        <v>180</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-U</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="K7" s="3" t="n">
-        <v>61.3</v>
+        <v>48.1</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>31</v>
+        <v>77</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="N7" s="3" t="n">
-        <v>51.6</v>
+        <v>39</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>31</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1065,10 +1065,10 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>66.7</v>
+        <v>59.2</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -1076,14 +1076,14 @@
         </is>
       </c>
       <c r="G10" s="3" t="n">
-        <v>38.9</v>
+        <v>42.1</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-N</t>
+          <t>N-N-D-U</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1092,21 +1092,21 @@
         </is>
       </c>
       <c r="K10" s="3" t="n">
-        <v>64.3</v>
+        <v>61.5</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N10" s="3" t="n">
-        <v>50</v>
+        <v>38.5</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1126,48 +1126,48 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>56</v>
+        <v>66.7</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>182</v>
+        <v>90</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G11" s="3" t="n">
-        <v>45.6</v>
+        <v>40</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>182</v>
+        <v>90</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-D</t>
+          <t>N-D-U-N</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K11" s="3" t="n">
-        <v>59.3</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N11" s="3" t="n">
-        <v>63</v>
+        <v>47.8</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1309,25 +1309,25 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>65.09999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G14" s="3" t="n">
-        <v>37.2</v>
+        <v>40.7</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-D</t>
+          <t>U-D-U-U</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="K14" s="3" t="n">
-        <v>72.7</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="N14" s="3" t="n">
-        <v>38.2</v>
+        <v>50</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1553,10 +1553,10 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>67.5</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1564,14 +1564,14 @@
         </is>
       </c>
       <c r="G18" s="3" t="n">
-        <v>43.8</v>
+        <v>43.5</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1580,21 +1580,21 @@
         </is>
       </c>
       <c r="K18" s="3" t="n">
-        <v>73.3</v>
+        <v>64.3</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N18" s="3" t="n">
-        <v>40</v>
+        <v>42.9</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1675,10 +1675,10 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>75</v>
+        <v>63.4</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>76</v>
+        <v>142</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1686,14 +1686,14 @@
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>46.1</v>
+        <v>45.1</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>76</v>
+        <v>142</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-U</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1702,10 +1702,10 @@
         </is>
       </c>
       <c r="K20" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>67.7</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="N20" s="3" t="n">
-        <v>46.4</v>
+        <v>45.2</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>28</v>
+        <v>62</v>
       </c>
     </row>
     <row r="21">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2041,25 +2041,25 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>65.8</v>
+        <v>59.8</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>38</v>
+        <v>82</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>44.7</v>
+        <v>42.7</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>38</v>
+        <v>82</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-N</t>
+          <t>U-N-D-U</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -2068,21 +2068,21 @@
         </is>
       </c>
       <c r="K26" s="3" t="n">
-        <v>66.7</v>
+        <v>51.6</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N26" s="3" t="n">
-        <v>42.9</v>
+        <v>38.7</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2163,25 +2163,25 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>51.8</v>
+        <v>72.2</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>168</v>
+        <v>79</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G28" s="3" t="n">
-        <v>45.8</v>
+        <v>45.6</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>168</v>
+        <v>79</v>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-U</t>
+          <t>N-U-D-N</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -2190,21 +2190,21 @@
         </is>
       </c>
       <c r="K28" s="3" t="n">
-        <v>62.5</v>
+        <v>86.7</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N28" s="3" t="n">
-        <v>50</v>
+        <v>46.7</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2712,25 +2712,25 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>58.1</v>
+        <v>45.5</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>62</v>
+        <v>154</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G37" s="3" t="n">
-        <v>38.7</v>
+        <v>46.8</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>62</v>
+        <v>154</v>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-N</t>
+          <t>N-D-U-U</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -2739,21 +2739,21 @@
         </is>
       </c>
       <c r="K37" s="3" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N37" s="3" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="O37" s="4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="38">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2773,25 +2773,25 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>63.6</v>
+        <v>67.5</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>33</v>
+        <v>77</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G38" s="3" t="n">
-        <v>51.5</v>
+        <v>49.4</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>33</v>
+        <v>77</v>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-N</t>
+          <t>U-N-D-U</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -2800,21 +2800,21 @@
         </is>
       </c>
       <c r="K38" s="3" t="n">
-        <v>66.7</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N38" s="3" t="n">
-        <v>44.4</v>
+        <v>40.6</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
     </row>
     <row r="39">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3017,10 +3017,10 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -3031,11 +3031,11 @@
         <v>50</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-N</t>
+          <t>U-D-N-U</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -3047,18 +3047,18 @@
         <v>100</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N42" s="3" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="O42" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3139,10 +3139,10 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>89.5</v>
+        <v>60.8</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -3150,14 +3150,14 @@
         </is>
       </c>
       <c r="G44" s="3" t="n">
-        <v>52.6</v>
+        <v>45.1</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -3166,10 +3166,10 @@
         </is>
       </c>
       <c r="K44" s="3" t="n">
-        <v>83.3</v>
+        <v>60</v>
       </c>
       <c r="L44" s="4" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
@@ -3177,10 +3177,10 @@
         </is>
       </c>
       <c r="N44" s="3" t="n">
-        <v>58.3</v>
+        <v>45</v>
       </c>
       <c r="O44" s="4" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3261,10 +3261,10 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>62.6</v>
+        <v>56.3</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>91</v>
+        <v>142</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -3272,14 +3272,14 @@
         </is>
       </c>
       <c r="G46" s="3" t="n">
-        <v>42.9</v>
+        <v>43.7</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>91</v>
+        <v>142</v>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-N</t>
+          <t>U-U-D-U</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -3288,21 +3288,21 @@
         </is>
       </c>
       <c r="K46" s="3" t="n">
-        <v>80</v>
+        <v>63.8</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>30</v>
+        <v>69</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N46" s="3" t="n">
-        <v>46.7</v>
+        <v>42</v>
       </c>
       <c r="O46" s="4" t="n">
-        <v>30</v>
+        <v>69</v>
       </c>
     </row>
     <row r="47">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3810,10 +3810,10 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>47.2</v>
+        <v>46.4</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3821,14 +3821,14 @@
         </is>
       </c>
       <c r="G55" s="3" t="n">
-        <v>47.2</v>
+        <v>40.6</v>
       </c>
       <c r="H55" s="4" t="n">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-N</t>
+          <t>N-N-D-U</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -3837,21 +3837,21 @@
         </is>
       </c>
       <c r="K55" s="3" t="n">
-        <v>81.8</v>
+        <v>50</v>
       </c>
       <c r="L55" s="4" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N55" s="3" t="n">
-        <v>54.5</v>
+        <v>55.6</v>
       </c>
       <c r="O55" s="4" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="56">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3871,48 +3871,48 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>45.9</v>
+        <v>62.5</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G56" s="3" t="n">
-        <v>43.2</v>
+        <v>50</v>
       </c>
       <c r="H56" s="4" t="n">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-D</t>
+          <t>U-D-U-N</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K56" s="3" t="n">
-        <v>43.8</v>
+        <v>57.1</v>
       </c>
       <c r="L56" s="4" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N56" s="3" t="n">
-        <v>56.2</v>
+        <v>57.1</v>
       </c>
       <c r="O56" s="4" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="57">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>61.5</v>
+        <v>59.1</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3943,14 +3943,14 @@
         </is>
       </c>
       <c r="G57" s="3" t="n">
-        <v>51.3</v>
+        <v>43.4</v>
       </c>
       <c r="H57" s="4" t="n">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -3959,21 +3959,21 @@
         </is>
       </c>
       <c r="K57" s="3" t="n">
-        <v>69.2</v>
+        <v>55.4</v>
       </c>
       <c r="L57" s="4" t="n">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N57" s="3" t="n">
-        <v>48.7</v>
+        <v>44.6</v>
       </c>
       <c r="O57" s="4" t="n">
-        <v>39</v>
+        <v>65</v>
       </c>
     </row>
     <row r="58">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3993,48 +3993,48 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>81.8</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="E58" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="H58" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>D-N-D-D</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="L58" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="G58" s="3" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="H58" s="4" t="n">
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="O58" s="4" t="n">
         <v>11</v>
-      </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>D-N-D-N</t>
-        </is>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K58" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="L58" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M58" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N58" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="O58" s="4" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4115,25 +4115,25 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>65.2</v>
+        <v>58.7</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>69</v>
+        <v>138</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G60" s="3" t="n">
-        <v>49.3</v>
+        <v>39.1</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>69</v>
+        <v>138</v>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-U</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -4142,10 +4142,10 @@
         </is>
       </c>
       <c r="K60" s="3" t="n">
-        <v>66.7</v>
+        <v>58.3</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
@@ -4153,10 +4153,10 @@
         </is>
       </c>
       <c r="N60" s="3" t="n">
-        <v>48.5</v>
+        <v>45</v>
       </c>
       <c r="O60" s="4" t="n">
-        <v>33</v>
+        <v>60</v>
       </c>
     </row>
     <row r="61">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -4298,48 +4298,48 @@
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>93.8</v>
+        <v>50</v>
       </c>
       <c r="E63" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="H63" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>U-U-U-U</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="L63" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G63" s="3" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="H63" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>U-U-U-N</t>
-        </is>
-      </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K63" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="L63" s="4" t="n">
-        <v>4</v>
-      </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N63" s="3" t="n">
         <v>50</v>
       </c>
       <c r="O63" s="4" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="64">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -4359,25 +4359,25 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>64.5</v>
+        <v>50</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G64" s="3" t="n">
-        <v>45.2</v>
+        <v>51.8</v>
       </c>
       <c r="H64" s="4" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-N</t>
+          <t>N-N-D-U</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -4386,10 +4386,10 @@
         </is>
       </c>
       <c r="K64" s="3" t="n">
-        <v>60</v>
+        <v>46.7</v>
       </c>
       <c r="L64" s="4" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>60</v>
       </c>
       <c r="O64" s="4" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="65">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-U</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D67" s="3" t="n">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>U-N-N-N</t>
+          <t>U-N-N-U</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K67" s="3" t="n">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -4603,37 +4603,37 @@
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>76.5</v>
+        <v>59.6</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G68" s="3" t="n">
-        <v>47.1</v>
+        <v>46.8</v>
       </c>
       <c r="H68" s="4" t="n">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-N</t>
+          <t>N-U-U-D</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="K68" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="L68" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
@@ -4641,10 +4641,10 @@
         </is>
       </c>
       <c r="N68" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="O68" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="69">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>U-N-D</t>
+          <t>U-N-N</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -4664,48 +4664,44 @@
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G69" s="3" t="n">
-        <v>55.6</v>
+        <v>100</v>
       </c>
       <c r="H69" s="4" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>N-U-N-D</t>
+          <t>N-U-N-N</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
-        </is>
-      </c>
-      <c r="K69" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr"/>
       <c r="L69" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
-        </is>
-      </c>
-      <c r="N69" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr"/>
       <c r="O69" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -4716,7 +4712,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -4725,10 +4721,10 @@
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>61.3</v>
+        <v>63</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4739,11 +4735,11 @@
         <v>39.4</v>
       </c>
       <c r="H70" s="4" t="n">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-D</t>
+          <t>N-U-D-U</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -4752,21 +4748,21 @@
         </is>
       </c>
       <c r="K70" s="3" t="n">
-        <v>58.6</v>
+        <v>56.4</v>
       </c>
       <c r="L70" s="4" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N70" s="3" t="n">
-        <v>34.5</v>
+        <v>43.6</v>
       </c>
       <c r="O70" s="4" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
     </row>
     <row r="71">
@@ -4899,7 +4895,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -4908,10 +4904,10 @@
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>62.5</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4919,14 +4915,14 @@
         </is>
       </c>
       <c r="G73" s="3" t="n">
-        <v>40.6</v>
+        <v>47.6</v>
       </c>
       <c r="H73" s="4" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-U</t>
+          <t>D-D-N-N</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -4935,21 +4931,21 @@
         </is>
       </c>
       <c r="K73" s="3" t="n">
-        <v>64.3</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="L73" s="4" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N73" s="3" t="n">
-        <v>42.9</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="O73" s="4" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="74">
@@ -5021,7 +5017,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5030,48 +5026,48 @@
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G75" s="3" t="n">
-        <v>66.7</v>
+        <v>41.2</v>
       </c>
       <c r="H75" s="4" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-N</t>
+          <t>N-N-D-U</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="K75" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="L75" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="N75" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="O75" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
@@ -5143,7 +5139,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -5152,25 +5148,25 @@
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>75.3</v>
+        <v>57.9</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>97</v>
+        <v>152</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G77" s="3" t="n">
-        <v>34</v>
+        <v>39.5</v>
       </c>
       <c r="H77" s="4" t="n">
-        <v>97</v>
+        <v>152</v>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-N</t>
+          <t>N-U-D-U</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -5179,21 +5175,21 @@
         </is>
       </c>
       <c r="K77" s="3" t="n">
-        <v>71</v>
+        <v>64.3</v>
       </c>
       <c r="L77" s="4" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N77" s="3" t="n">
-        <v>41.9</v>
+        <v>46.4</v>
       </c>
       <c r="O77" s="4" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="78">
@@ -5387,7 +5383,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -5396,48 +5392,48 @@
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>85.7</v>
+        <v>55.2</v>
       </c>
       <c r="E81" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="H81" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>U-N-D-U</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K81" s="3" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="L81" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>D/U</t>
-        </is>
-      </c>
-      <c r="G81" s="3" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="H81" s="4" t="n">
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="N81" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="O81" s="4" t="n">
         <v>28</v>
-      </c>
-      <c r="I81" s="2" t="inlineStr">
-        <is>
-          <t>U-N-D-N</t>
-        </is>
-      </c>
-      <c r="J81" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K81" s="3" t="n">
-        <v>84.59999999999999</v>
-      </c>
-      <c r="L81" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="M81" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="N81" s="3" t="n">
-        <v>46.2</v>
-      </c>
-      <c r="O81" s="4" t="n">
-        <v>13</v>
       </c>
     </row>
     <row r="82">
@@ -5509,7 +5505,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -5518,10 +5514,10 @@
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>56.8</v>
+        <v>61.4</v>
       </c>
       <c r="E83" s="4" t="n">
-        <v>162</v>
+        <v>70</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -5529,14 +5525,14 @@
         </is>
       </c>
       <c r="G83" s="3" t="n">
-        <v>50.6</v>
+        <v>38.6</v>
       </c>
       <c r="H83" s="4" t="n">
-        <v>162</v>
+        <v>70</v>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-U</t>
+          <t>U-D-U-N</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
@@ -5545,10 +5541,10 @@
         </is>
       </c>
       <c r="K83" s="3" t="n">
-        <v>57.4</v>
+        <v>59.4</v>
       </c>
       <c r="L83" s="4" t="n">
-        <v>68</v>
+        <v>32</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
@@ -5556,10 +5552,10 @@
         </is>
       </c>
       <c r="N83" s="3" t="n">
-        <v>50</v>
+        <v>40.6</v>
       </c>
       <c r="O83" s="4" t="n">
-        <v>68</v>
+        <v>32</v>
       </c>
     </row>
     <row r="84">
@@ -5570,7 +5566,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -5579,25 +5575,25 @@
         </is>
       </c>
       <c r="D84" s="3" t="n">
-        <v>65.59999999999999</v>
+        <v>61.7</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G84" s="3" t="n">
-        <v>34.4</v>
+        <v>43.2</v>
       </c>
       <c r="H84" s="4" t="n">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-N</t>
+          <t>U-D-N-U</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -5606,21 +5602,21 @@
         </is>
       </c>
       <c r="K84" s="3" t="n">
-        <v>64.3</v>
+        <v>62.9</v>
       </c>
       <c r="L84" s="4" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N84" s="3" t="n">
-        <v>39.3</v>
+        <v>45.7</v>
       </c>
       <c r="O84" s="4" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
     </row>
     <row r="85">
@@ -5692,7 +5688,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-U</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -5701,25 +5697,25 @@
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G86" s="3" t="n">
-        <v>40</v>
+        <v>48.2</v>
       </c>
       <c r="H86" s="4" t="n">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-N</t>
+          <t>D-U-N-U</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -5728,21 +5724,21 @@
         </is>
       </c>
       <c r="K86" s="3" t="n">
-        <v>75</v>
+        <v>58.6</v>
       </c>
       <c r="L86" s="4" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N86" s="3" t="n">
-        <v>41.7</v>
+        <v>41.4</v>
       </c>
       <c r="O86" s="4" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
     </row>
     <row r="87">
@@ -5753,7 +5749,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -5762,10 +5758,10 @@
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>69.2</v>
+        <v>53.2</v>
       </c>
       <c r="E87" s="4" t="n">
-        <v>65</v>
+        <v>156</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5773,14 +5769,14 @@
         </is>
       </c>
       <c r="G87" s="3" t="n">
-        <v>44.6</v>
+        <v>42.3</v>
       </c>
       <c r="H87" s="4" t="n">
-        <v>65</v>
+        <v>156</v>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-U</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
@@ -5789,21 +5785,21 @@
         </is>
       </c>
       <c r="K87" s="3" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="L87" s="4" t="n">
         <v>63</v>
       </c>
-      <c r="L87" s="4" t="n">
-        <v>27</v>
-      </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N87" s="3" t="n">
-        <v>55.6</v>
+        <v>47.6</v>
       </c>
       <c r="O87" s="4" t="n">
-        <v>27</v>
+        <v>63</v>
       </c>
     </row>
     <row r="88">
@@ -6058,7 +6054,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -6067,25 +6063,25 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>73.2</v>
+        <v>60.7</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>41</v>
+        <v>84</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G92" s="3" t="n">
-        <v>36.6</v>
+        <v>41.7</v>
       </c>
       <c r="H92" s="4" t="n">
-        <v>41</v>
+        <v>84</v>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-N</t>
+          <t>U-D-N-U</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
@@ -6094,21 +6090,21 @@
         </is>
       </c>
       <c r="K92" s="3" t="n">
-        <v>70</v>
+        <v>63.2</v>
       </c>
       <c r="L92" s="4" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N92" s="3" t="n">
-        <v>45</v>
+        <v>55.3</v>
       </c>
       <c r="O92" s="4" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
     </row>
     <row r="93">
@@ -6119,7 +6115,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -6128,25 +6124,25 @@
         </is>
       </c>
       <c r="D93" s="3" t="n">
-        <v>66.7</v>
+        <v>52.6</v>
       </c>
       <c r="E93" s="4" t="n">
-        <v>81</v>
+        <v>137</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G93" s="3" t="n">
-        <v>44.4</v>
+        <v>40.9</v>
       </c>
       <c r="H93" s="4" t="n">
-        <v>81</v>
+        <v>137</v>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-N</t>
+          <t>N-U-D-U</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
@@ -6155,21 +6151,21 @@
         </is>
       </c>
       <c r="K93" s="3" t="n">
-        <v>91.3</v>
+        <v>59.1</v>
       </c>
       <c r="L93" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N93" s="3" t="n">
-        <v>43.5</v>
+        <v>54.5</v>
       </c>
       <c r="O93" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="94">
@@ -6180,7 +6176,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -6189,10 +6185,10 @@
         </is>
       </c>
       <c r="D94" s="3" t="n">
-        <v>66.09999999999999</v>
+        <v>59.8</v>
       </c>
       <c r="E94" s="4" t="n">
-        <v>59</v>
+        <v>169</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -6200,14 +6196,14 @@
         </is>
       </c>
       <c r="G94" s="3" t="n">
-        <v>45.8</v>
+        <v>40.8</v>
       </c>
       <c r="H94" s="4" t="n">
-        <v>59</v>
+        <v>169</v>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-U</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
@@ -6216,10 +6212,10 @@
         </is>
       </c>
       <c r="K94" s="3" t="n">
-        <v>74.09999999999999</v>
+        <v>64.7</v>
       </c>
       <c r="L94" s="4" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
@@ -6227,10 +6223,10 @@
         </is>
       </c>
       <c r="N94" s="3" t="n">
-        <v>59.3</v>
+        <v>42.6</v>
       </c>
       <c r="O94" s="4" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
     </row>
     <row r="95">
@@ -6363,7 +6359,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -6372,10 +6368,10 @@
         </is>
       </c>
       <c r="D97" s="3" t="n">
-        <v>67.5</v>
+        <v>57.3</v>
       </c>
       <c r="E97" s="4" t="n">
-        <v>77</v>
+        <v>157</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -6383,14 +6379,14 @@
         </is>
       </c>
       <c r="G97" s="3" t="n">
-        <v>42.9</v>
+        <v>43.3</v>
       </c>
       <c r="H97" s="4" t="n">
-        <v>77</v>
+        <v>157</v>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-U</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
@@ -6399,10 +6395,10 @@
         </is>
       </c>
       <c r="K97" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>61.2</v>
       </c>
       <c r="L97" s="4" t="n">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
@@ -6410,10 +6406,10 @@
         </is>
       </c>
       <c r="N97" s="3" t="n">
-        <v>42.9</v>
+        <v>44.8</v>
       </c>
       <c r="O97" s="4" t="n">
-        <v>28</v>
+        <v>67</v>
       </c>
     </row>
     <row r="98">
@@ -6485,7 +6481,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -6494,10 +6490,10 @@
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>70</v>
+        <v>51.5</v>
       </c>
       <c r="E99" s="4" t="n">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -6505,14 +6501,14 @@
         </is>
       </c>
       <c r="G99" s="3" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="H99" s="4" t="n">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>D-N-D-U</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
@@ -6521,21 +6517,21 @@
         </is>
       </c>
       <c r="K99" s="3" t="n">
-        <v>88.2</v>
+        <v>57.1</v>
       </c>
       <c r="L99" s="4" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N99" s="3" t="n">
-        <v>52.9</v>
+        <v>39.3</v>
       </c>
       <c r="O99" s="4" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="100">
@@ -6607,7 +6603,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-U</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -6616,25 +6612,25 @@
         </is>
       </c>
       <c r="D101" s="3" t="n">
-        <v>78.40000000000001</v>
+        <v>76.7</v>
       </c>
       <c r="E101" s="4" t="n">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G101" s="3" t="n">
-        <v>37.8</v>
+        <v>38.4</v>
       </c>
       <c r="H101" s="4" t="n">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>U-N-N-N</t>
+          <t>U-N-N-U</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
@@ -6643,18 +6639,18 @@
         </is>
       </c>
       <c r="K101" s="3" t="n">
-        <v>81.8</v>
+        <v>72.7</v>
       </c>
       <c r="L101" s="4" t="n">
         <v>33</v>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N101" s="3" t="n">
-        <v>36.4</v>
+        <v>39.4</v>
       </c>
       <c r="O101" s="4" t="n">
         <v>33</v>
@@ -6668,7 +6664,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -6677,25 +6673,25 @@
         </is>
       </c>
       <c r="D102" s="3" t="n">
-        <v>75.40000000000001</v>
+        <v>75</v>
       </c>
       <c r="E102" s="4" t="n">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G102" s="3" t="n">
-        <v>38.5</v>
+        <v>35.7</v>
       </c>
       <c r="H102" s="4" t="n">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-N</t>
+          <t>U-N-D-U</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
@@ -6704,21 +6700,21 @@
         </is>
       </c>
       <c r="K102" s="3" t="n">
-        <v>86.40000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="L102" s="4" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N102" s="3" t="n">
-        <v>45.5</v>
+        <v>36.7</v>
       </c>
       <c r="O102" s="4" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
     <row r="103">
@@ -7026,7 +7022,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -7035,10 +7031,10 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -7046,37 +7042,37 @@
         </is>
       </c>
       <c r="I2" s="3" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="J2" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>N-D-N-U</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>N/U</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="N2" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P2" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="J2" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>N-D-N-N</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="N2" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P2" s="3" t="n">
-        <v>50</v>
-      </c>
       <c r="Q2" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -7097,7 +7093,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -7106,10 +7102,10 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -7117,14 +7113,14 @@
         </is>
       </c>
       <c r="I3" s="3" t="n">
-        <v>50</v>
+        <v>52.9</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-U</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -7133,21 +7129,21 @@
         </is>
       </c>
       <c r="M3" s="3" t="n">
-        <v>75</v>
+        <v>57.1</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P3" s="3" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
       <c r="Q3" s="4" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
@@ -7239,7 +7235,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -7248,25 +7244,25 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>90.5</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I5" s="3" t="n">
-        <v>33.3</v>
+        <v>45.9</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -7275,21 +7271,21 @@
         </is>
       </c>
       <c r="M5" s="3" t="n">
-        <v>83.3</v>
+        <v>66.7</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P5" s="3" t="n">
-        <v>50</v>
+        <v>55.6</v>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -7310,57 +7306,57 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>62.5</v>
+        <v>41.7</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I6" s="3" t="n">
         <v>50</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-N</t>
+          <t>U-D-N-U</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M6" s="3" t="n">
         <v>50</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P6" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -7381,19 +7377,19 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>42.9</v>
+        <v>51.5</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -7401,26 +7397,26 @@
         </is>
       </c>
       <c r="I7" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>45.5</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-U</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M7" s="3" t="n">
-        <v>40</v>
+        <v>56.2</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
@@ -7428,10 +7424,10 @@
         </is>
       </c>
       <c r="P7" s="3" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
@@ -7594,7 +7590,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -7603,25 +7599,25 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>50</v>
+        <v>64.3</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I10" s="3" t="n">
         <v>50</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-N</t>
+          <t>N-N-D-U</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -7630,21 +7626,21 @@
         </is>
       </c>
       <c r="M10" s="3" t="n">
-        <v>57.1</v>
+        <v>100</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P10" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>66.7</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -7665,7 +7661,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -7674,25 +7670,25 @@
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>68.59999999999999</v>
+        <v>42.9</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I11" s="3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-D</t>
+          <t>N-D-U-N</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -7701,21 +7697,21 @@
         </is>
       </c>
       <c r="M11" s="3" t="n">
-        <v>57.1</v>
+        <v>66.7</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P11" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -7878,7 +7874,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -7887,25 +7883,25 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>60</v>
+        <v>76.2</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I14" s="3" t="n">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-D</t>
+          <t>U-D-U-U</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -7914,21 +7910,21 @@
         </is>
       </c>
       <c r="M14" s="3" t="n">
-        <v>55.6</v>
+        <v>85.7</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P14" s="3" t="n">
-        <v>55.6</v>
+        <v>42.9</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
@@ -8162,7 +8158,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -8171,25 +8167,25 @@
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>57.1</v>
+        <v>73.3</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I18" s="3" t="n">
-        <v>42.9</v>
+        <v>60</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -8198,21 +8194,21 @@
         </is>
       </c>
       <c r="M18" s="3" t="n">
-        <v>75</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P18" s="3" t="n">
-        <v>50</v>
+        <v>53.8</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19">
@@ -8304,7 +8300,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -8313,10 +8309,10 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>76.5</v>
+        <v>57.7</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -8324,14 +8320,14 @@
         </is>
       </c>
       <c r="I20" s="3" t="n">
-        <v>52.9</v>
+        <v>53.8</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-U</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -8351,7 +8347,7 @@
         </is>
       </c>
       <c r="P20" s="3" t="n">
-        <v>44.4</v>
+        <v>77.8</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>9</v>
@@ -8722,7 +8718,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -8731,37 +8727,37 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="J26" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>U-N-D-U</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="n">
         <v>66.7</v>
       </c>
-      <c r="G26" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>D/U</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="J26" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>U-N-D-N</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>D/N</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="n">
-        <v>50</v>
-      </c>
       <c r="N26" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -8769,10 +8765,10 @@
         </is>
       </c>
       <c r="P26" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -8864,7 +8860,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -8873,48 +8869,48 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>57.6</v>
+        <v>73.7</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I28" s="3" t="n">
-        <v>42.4</v>
+        <v>42.1</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-U</t>
+          <t>N-U-D-N</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M28" s="3" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P28" s="3" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -9491,7 +9487,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -9500,48 +9496,48 @@
         </is>
       </c>
       <c r="F37" s="3" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="J37" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>N-D-U-U</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="n">
         <v>66.7</v>
       </c>
-      <c r="G37" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I37" s="3" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="J37" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>N-D-U-N</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M37" s="3" t="n">
-        <v>75</v>
-      </c>
       <c r="N37" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P37" s="3" t="n">
-        <v>50</v>
+        <v>44.4</v>
       </c>
       <c r="Q37" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38">
@@ -9562,7 +9558,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -9571,37 +9567,37 @@
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>42.9</v>
+        <v>53.3</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I38" s="3" t="n">
-        <v>42.9</v>
+        <v>46.7</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-N</t>
+          <t>U-N-D-U</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M38" s="3" t="n">
-        <v>33.3</v>
+        <v>55.6</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -9609,10 +9605,10 @@
         </is>
       </c>
       <c r="P38" s="3" t="n">
-        <v>66.7</v>
+        <v>44.4</v>
       </c>
       <c r="Q38" s="4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39">
@@ -9846,34 +9842,34 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F42" s="3" t="n">
         <v>100</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="I42" s="3" t="n">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-N</t>
+          <t>U-D-N-U</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -9984,7 +9980,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -9993,48 +9989,48 @@
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>100</v>
+        <v>64.3</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I44" s="3" t="n">
-        <v>100</v>
+        <v>42.9</v>
       </c>
       <c r="J44" s="4" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M44" s="3" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="N44" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P44" s="3" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="Q44" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45">
@@ -10122,19 +10118,19 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>69.2</v>
+        <v>42.4</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -10142,26 +10138,26 @@
         </is>
       </c>
       <c r="I46" s="3" t="n">
-        <v>42.3</v>
+        <v>42.4</v>
       </c>
       <c r="J46" s="4" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-N</t>
+          <t>U-U-D-U</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M46" s="3" t="n">
-        <v>80</v>
+        <v>46.7</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
@@ -10169,10 +10165,10 @@
         </is>
       </c>
       <c r="P46" s="3" t="n">
-        <v>50</v>
+        <v>46.7</v>
       </c>
       <c r="Q46" s="4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="47">
@@ -10757,49 +10753,57 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="F55" s="3" t="inlineStr"/>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>56.2</v>
+      </c>
       <c r="G55" s="4" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="I55" s="3" t="inlineStr"/>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="n">
+        <v>50</v>
+      </c>
       <c r="J55" s="4" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-N</t>
+          <t>N-N-D-U</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M55" s="3" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="n">
+        <v>60</v>
+      </c>
       <c r="N55" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P55" s="3" t="inlineStr"/>
+          <t>N/U</t>
+        </is>
+      </c>
+      <c r="P55" s="3" t="n">
+        <v>40</v>
+      </c>
       <c r="Q55" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56">
@@ -10820,57 +10824,49 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F56" s="3" t="n">
-        <v>71.40000000000001</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr"/>
       <c r="G56" s="4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I56" s="3" t="n">
-        <v>42.9</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr"/>
       <c r="J56" s="4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-D</t>
+          <t>U-D-U-N</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
-        </is>
-      </c>
-      <c r="M56" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr"/>
       <c r="N56" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
-        </is>
-      </c>
-      <c r="P56" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P56" s="3" t="inlineStr"/>
       <c r="Q56" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -10891,7 +10887,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -10900,10 +10896,10 @@
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>81.2</v>
+        <v>57.7</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -10911,14 +10907,14 @@
         </is>
       </c>
       <c r="I57" s="3" t="n">
-        <v>43.8</v>
+        <v>42.3</v>
       </c>
       <c r="J57" s="4" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
@@ -10927,10 +10923,10 @@
         </is>
       </c>
       <c r="M57" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>62.5</v>
       </c>
       <c r="N57" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
@@ -10938,10 +10934,10 @@
         </is>
       </c>
       <c r="P57" s="3" t="n">
-        <v>44.4</v>
+        <v>50</v>
       </c>
       <c r="Q57" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="58">
@@ -10962,7 +10958,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -10971,44 +10967,48 @@
         </is>
       </c>
       <c r="F58" s="3" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="G58" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="J58" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>D-N-D-D</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="G58" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>N/U</t>
-        </is>
-      </c>
-      <c r="I58" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="J58" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K58" s="2" t="inlineStr">
-        <is>
-          <t>D-N-D-N</t>
-        </is>
-      </c>
-      <c r="L58" s="2" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M58" s="3" t="inlineStr"/>
       <c r="N58" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P58" s="3" t="inlineStr"/>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P58" s="3" t="n">
+        <v>66.7</v>
+      </c>
       <c r="Q58" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -11100,7 +11100,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -11109,37 +11109,37 @@
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>64.7</v>
+        <v>51.6</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I60" s="3" t="n">
-        <v>52.9</v>
+        <v>45.2</v>
       </c>
       <c r="J60" s="4" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-U</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M60" s="3" t="n">
-        <v>75</v>
+        <v>56.2</v>
       </c>
       <c r="N60" s="4" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
@@ -11147,10 +11147,10 @@
         </is>
       </c>
       <c r="P60" s="3" t="n">
-        <v>50</v>
+        <v>43.8</v>
       </c>
       <c r="Q60" s="4" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="61">
@@ -11313,57 +11313,57 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I63" s="3" t="n">
         <v>66.7</v>
       </c>
       <c r="J63" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-U</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M63" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N63" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P63" s="3" t="n">
         <v>100</v>
       </c>
       <c r="Q63" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -11384,57 +11384,57 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F64" s="3" t="n">
         <v>66.7</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="I64" s="3" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="J64" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>N-N-D-U</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>N/U</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="J64" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="K64" s="2" t="inlineStr">
-        <is>
-          <t>N-N-D-N</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M64" s="3" t="n">
-        <v>100</v>
-      </c>
       <c r="N64" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="P64" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q64" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -11597,7 +11597,7 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-U</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -11620,7 +11620,7 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>U-N-N-N</t>
+          <t>U-N-N-U</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
@@ -11660,7 +11660,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -11669,30 +11669,30 @@
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>75</v>
+        <v>62.5</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I68" s="3" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="J68" s="4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-N</t>
+          <t>N-U-U-D</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M68" s="3" t="n">
@@ -11703,7 +11703,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P68" s="3" t="n">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>U-N-D</t>
+          <t>U-N-N</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -11754,7 +11754,7 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>N-U-N-D</t>
+          <t>N-U-N-N</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
@@ -11794,7 +11794,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -11803,10 +11803,10 @@
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>59.1</v>
+        <v>46.9</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -11814,14 +11814,14 @@
         </is>
       </c>
       <c r="I70" s="3" t="n">
-        <v>45.5</v>
+        <v>46.9</v>
       </c>
       <c r="J70" s="4" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-D</t>
+          <t>N-U-D-U</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
@@ -11830,21 +11830,21 @@
         </is>
       </c>
       <c r="M70" s="3" t="n">
-        <v>60</v>
+        <v>42.9</v>
       </c>
       <c r="N70" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P70" s="3" t="n">
-        <v>60</v>
+        <v>42.9</v>
       </c>
       <c r="Q70" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="71">
@@ -12007,7 +12007,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -12016,25 +12016,25 @@
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>85.7</v>
+        <v>80</v>
       </c>
       <c r="G73" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I73" s="3" t="n">
-        <v>42.9</v>
+        <v>60</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-U</t>
+          <t>D-D-N-N</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
@@ -12050,11 +12050,11 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="P73" s="3" t="n">
-        <v>66.7</v>
+        <v>33.3</v>
       </c>
       <c r="Q73" s="4" t="n">
         <v>3</v>
@@ -12149,7 +12149,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -12158,48 +12158,44 @@
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="G75" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I75" s="3" t="n">
         <v>100</v>
       </c>
       <c r="J75" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-N</t>
+          <t>N-N-D-U</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M75" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M75" s="3" t="inlineStr"/>
       <c r="N75" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P75" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P75" s="3" t="inlineStr"/>
       <c r="Q75" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -12291,7 +12287,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -12300,25 +12296,25 @@
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>87.5</v>
+        <v>60.5</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I77" s="3" t="n">
-        <v>41.7</v>
+        <v>39.5</v>
       </c>
       <c r="J77" s="4" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-N</t>
+          <t>N-U-D-U</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
@@ -12327,21 +12323,21 @@
         </is>
       </c>
       <c r="M77" s="3" t="n">
-        <v>85.7</v>
+        <v>75</v>
       </c>
       <c r="N77" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P77" s="3" t="n">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="Q77" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="78">
@@ -12575,7 +12571,7 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -12584,10 +12580,10 @@
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>66.7</v>
+        <v>70</v>
       </c>
       <c r="G81" s="4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
@@ -12595,26 +12591,26 @@
         </is>
       </c>
       <c r="I81" s="3" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-N</t>
+          <t>U-N-D-U</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M81" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N81" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
@@ -12622,10 +12618,10 @@
         </is>
       </c>
       <c r="P81" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q81" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="82">
@@ -12717,34 +12713,34 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F83" s="3" t="n">
-        <v>65.59999999999999</v>
+        <v>47.1</v>
       </c>
       <c r="G83" s="4" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I83" s="3" t="n">
-        <v>43.8</v>
+        <v>41.2</v>
       </c>
       <c r="J83" s="4" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-U</t>
+          <t>U-D-U-N</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr">
@@ -12753,21 +12749,21 @@
         </is>
       </c>
       <c r="M83" s="3" t="n">
-        <v>60</v>
+        <v>57.1</v>
       </c>
       <c r="N83" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P83" s="3" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
       <c r="Q83" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="84">
@@ -12788,7 +12784,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -12797,10 +12793,10 @@
         </is>
       </c>
       <c r="F84" s="3" t="n">
-        <v>55.6</v>
+        <v>61.9</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -12808,26 +12804,26 @@
         </is>
       </c>
       <c r="I84" s="3" t="n">
-        <v>44.4</v>
+        <v>52.4</v>
       </c>
       <c r="J84" s="4" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-N</t>
+          <t>U-D-N-U</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M84" s="3" t="n">
-        <v>100</v>
+        <v>57.1</v>
       </c>
       <c r="N84" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
@@ -12835,10 +12831,10 @@
         </is>
       </c>
       <c r="P84" s="3" t="n">
-        <v>100</v>
+        <v>57.1</v>
       </c>
       <c r="Q84" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="85">
@@ -12930,46 +12926,46 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-U</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="F86" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="G86" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I86" s="3" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="J86" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>D-U-N-U</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
           <t>N/U</t>
         </is>
       </c>
-      <c r="F86" s="3" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="G86" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I86" s="3" t="n">
+      <c r="M86" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="J86" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="K86" s="2" t="inlineStr">
-        <is>
-          <t>D-U-N-N</t>
-        </is>
-      </c>
-      <c r="L86" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="M86" s="3" t="n">
-        <v>66.7</v>
-      </c>
       <c r="N86" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
@@ -12977,10 +12973,10 @@
         </is>
       </c>
       <c r="P86" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="Q86" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="87">
@@ -13001,7 +12997,7 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -13010,48 +13006,48 @@
         </is>
       </c>
       <c r="F87" s="3" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="G87" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I87" s="3" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="J87" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>U-D-D-U</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="M87" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="N87" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P87" s="3" t="n">
         <v>66.7</v>
       </c>
-      <c r="G87" s="4" t="n">
+      <c r="Q87" s="4" t="n">
         <v>12</v>
-      </c>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I87" s="3" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="J87" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="K87" s="2" t="inlineStr">
-        <is>
-          <t>U-D-D-N</t>
-        </is>
-      </c>
-      <c r="L87" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M87" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="N87" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="O87" s="2" t="inlineStr">
-        <is>
-          <t>D/U</t>
-        </is>
-      </c>
-      <c r="P87" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="Q87" s="4" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="88">
@@ -13356,7 +13352,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -13365,48 +13361,48 @@
         </is>
       </c>
       <c r="F92" s="3" t="n">
-        <v>66.7</v>
+        <v>47.4</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I92" s="3" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="J92" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>U-D-N-U</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M92" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="J92" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="K92" s="2" t="inlineStr">
-        <is>
-          <t>U-D-N-N</t>
-        </is>
-      </c>
-      <c r="L92" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M92" s="3" t="n">
-        <v>66.7</v>
-      </c>
       <c r="N92" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P92" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="Q92" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="93">
@@ -13427,7 +13423,7 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -13436,25 +13432,25 @@
         </is>
       </c>
       <c r="F93" s="3" t="n">
-        <v>78.3</v>
+        <v>48.3</v>
       </c>
       <c r="G93" s="4" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I93" s="3" t="n">
-        <v>52.2</v>
+        <v>51.7</v>
       </c>
       <c r="J93" s="4" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-N</t>
+          <t>N-U-D-U</t>
         </is>
       </c>
       <c r="L93" s="2" t="inlineStr">
@@ -13463,21 +13459,21 @@
         </is>
       </c>
       <c r="M93" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="N93" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="P93" s="3" t="n">
-        <v>42.9</v>
+        <v>33.3</v>
       </c>
       <c r="Q93" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="94">
@@ -13498,19 +13494,19 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F94" s="3" t="n">
-        <v>46.2</v>
+        <v>52.9</v>
       </c>
       <c r="G94" s="4" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -13518,26 +13514,26 @@
         </is>
       </c>
       <c r="I94" s="3" t="n">
-        <v>61.5</v>
+        <v>50</v>
       </c>
       <c r="J94" s="4" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-U</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M94" s="3" t="n">
-        <v>42.9</v>
+        <v>60</v>
       </c>
       <c r="N94" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
@@ -13545,10 +13541,10 @@
         </is>
       </c>
       <c r="P94" s="3" t="n">
-        <v>57.1</v>
+        <v>60</v>
       </c>
       <c r="Q94" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="95">
@@ -13711,7 +13707,7 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -13720,25 +13716,25 @@
         </is>
       </c>
       <c r="F97" s="3" t="n">
-        <v>75</v>
+        <v>60.7</v>
       </c>
       <c r="G97" s="4" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I97" s="3" t="n">
-        <v>37.5</v>
+        <v>53.6</v>
       </c>
       <c r="J97" s="4" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-U</t>
         </is>
       </c>
       <c r="L97" s="2" t="inlineStr">
@@ -13747,21 +13743,21 @@
         </is>
       </c>
       <c r="M97" s="3" t="n">
-        <v>85.7</v>
+        <v>69.2</v>
       </c>
       <c r="N97" s="4" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P97" s="3" t="n">
-        <v>42.9</v>
+        <v>46.2</v>
       </c>
       <c r="Q97" s="4" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="98">
@@ -13853,7 +13849,7 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -13862,10 +13858,10 @@
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>55.6</v>
+        <v>50</v>
       </c>
       <c r="G99" s="4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
@@ -13873,14 +13869,14 @@
         </is>
       </c>
       <c r="I99" s="3" t="n">
-        <v>55.6</v>
+        <v>41.7</v>
       </c>
       <c r="J99" s="4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>D-N-D-U</t>
         </is>
       </c>
       <c r="L99" s="2" t="inlineStr">
@@ -13889,21 +13885,21 @@
         </is>
       </c>
       <c r="M99" s="3" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="N99" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="P99" s="3" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="Q99" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="100">
@@ -13995,7 +13991,7 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-U</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -14011,18 +14007,18 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I101" s="3" t="n">
-        <v>55.6</v>
+        <v>44.4</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>U-N-N-N</t>
+          <t>U-N-N-U</t>
         </is>
       </c>
       <c r="L101" s="2" t="inlineStr">
@@ -14031,21 +14027,21 @@
         </is>
       </c>
       <c r="M101" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="N101" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P101" s="3" t="n">
         <v>100</v>
       </c>
       <c r="Q101" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102">
@@ -14066,7 +14062,7 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -14075,48 +14071,48 @@
         </is>
       </c>
       <c r="F102" s="3" t="n">
-        <v>58.3</v>
+        <v>60</v>
       </c>
       <c r="G102" s="4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I102" s="3" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="J102" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>U-N-D-U</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M102" s="3" t="n">
         <v>66.7</v>
       </c>
-      <c r="J102" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="K102" s="2" t="inlineStr">
-        <is>
-          <t>U-N-D-N</t>
-        </is>
-      </c>
-      <c r="L102" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M102" s="3" t="n">
-        <v>100</v>
-      </c>
       <c r="N102" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P102" s="3" t="n">
         <v>100</v>
       </c>
       <c r="Q102" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="103">

--- a/BIS_tr.xlsx
+++ b/BIS_tr.xlsx
@@ -995,7 +995,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1004,25 +1004,25 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>60.2</v>
+        <v>73.7</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>93</v>
+        <v>57</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G9" s="3" t="n">
-        <v>37.6</v>
+        <v>42.1</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>93</v>
+        <v>57</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-U</t>
+          <t>N-D-D-N</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1031,21 +1031,21 @@
         </is>
       </c>
       <c r="K9" s="3" t="n">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N9" s="3" t="n">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1126,48 +1126,48 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>66.7</v>
+        <v>56</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>90</v>
+        <v>182</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G11" s="3" t="n">
-        <v>40</v>
+        <v>45.6</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>90</v>
+        <v>182</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-N</t>
+          <t>N-D-U-D</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K11" s="3" t="n">
-        <v>73.90000000000001</v>
+        <v>59.3</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N11" s="3" t="n">
-        <v>47.8</v>
+        <v>63</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1248,48 +1248,48 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>66.7</v>
+        <v>52.3</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G13" s="3" t="n">
-        <v>44.4</v>
+        <v>56.8</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K13" s="3" t="n">
         <v>50</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N13" s="3" t="n">
-        <v>50</v>
+        <v>58.3</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1431,25 +1431,25 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>64.90000000000001</v>
+        <v>57.8</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>74</v>
+        <v>180</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>36.5</v>
+        <v>40</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>74</v>
+        <v>180</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-N</t>
+          <t>N-U-D-D</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1458,21 +1458,21 @@
         </is>
       </c>
       <c r="K16" s="3" t="n">
-        <v>73.3</v>
+        <v>61</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N16" s="3" t="n">
-        <v>46.7</v>
+        <v>36.6</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>15</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1492,25 +1492,25 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>71.7</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G17" s="3" t="n">
-        <v>41.3</v>
+        <v>44.1</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>D-N-D-D</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="K17" s="3" t="n">
-        <v>60</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
@@ -1530,10 +1530,10 @@
         </is>
       </c>
       <c r="N17" s="3" t="n">
-        <v>46.7</v>
+        <v>42.9</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1553,10 +1553,10 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>67.40000000000001</v>
+        <v>67.5</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>138</v>
+        <v>80</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1564,14 +1564,14 @@
         </is>
       </c>
       <c r="G18" s="3" t="n">
-        <v>43.5</v>
+        <v>43.8</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>138</v>
+        <v>80</v>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1580,21 +1580,21 @@
         </is>
       </c>
       <c r="K18" s="3" t="n">
-        <v>64.3</v>
+        <v>73.3</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N18" s="3" t="n">
-        <v>42.9</v>
+        <v>40</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>56</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19">
@@ -1788,57 +1788,57 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>N/U</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>D-N-N-D</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>D/N/U</t>
         </is>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="K22" s="3" t="n">
         <v>33.3</v>
       </c>
-      <c r="E22" s="4" t="n">
+      <c r="L22" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="H22" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>D-N-N-N</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="L22" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N22" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -3557,19 +3557,19 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-U</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>87.5</v>
+        <v>43.8</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3577,37 +3577,37 @@
         </is>
       </c>
       <c r="G51" s="3" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="H51" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>D-N-N-U</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="L51" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="H51" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>D-N-N-N</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K51" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="L51" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M51" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="N51" s="3" t="n">
-        <v>66.7</v>
-      </c>
       <c r="O51" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3627,25 +3627,25 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>65.2</v>
+        <v>53.8</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>69</v>
+        <v>106</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G52" s="3" t="n">
-        <v>47.8</v>
+        <v>45.3</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>69</v>
+        <v>106</v>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -3654,21 +3654,21 @@
         </is>
       </c>
       <c r="K52" s="3" t="n">
-        <v>62.9</v>
+        <v>51.2</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N52" s="3" t="n">
-        <v>51.4</v>
+        <v>58.5</v>
       </c>
       <c r="O52" s="4" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="53">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3688,10 +3688,10 @@
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>60.9</v>
+        <v>60</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3699,14 +3699,14 @@
         </is>
       </c>
       <c r="G53" s="3" t="n">
-        <v>47.8</v>
+        <v>50</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-D</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -3715,10 +3715,10 @@
         </is>
       </c>
       <c r="K53" s="3" t="n">
-        <v>64.7</v>
+        <v>66.7</v>
       </c>
       <c r="L53" s="4" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
@@ -3726,10 +3726,10 @@
         </is>
       </c>
       <c r="N53" s="3" t="n">
-        <v>41.2</v>
+        <v>50</v>
       </c>
       <c r="O53" s="4" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3871,25 +3871,25 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>62.5</v>
+        <v>59.2</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G56" s="3" t="n">
-        <v>50</v>
+        <v>46.9</v>
       </c>
       <c r="H56" s="4" t="n">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-U</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -3898,21 +3898,21 @@
         </is>
       </c>
       <c r="K56" s="3" t="n">
-        <v>57.1</v>
+        <v>56.5</v>
       </c>
       <c r="L56" s="4" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N56" s="3" t="n">
-        <v>57.1</v>
+        <v>52.2</v>
       </c>
       <c r="O56" s="4" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
     </row>
     <row r="57">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>N-D-D</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3993,10 +3993,10 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>78.59999999999999</v>
+        <v>81.8</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -4004,14 +4004,14 @@
         </is>
       </c>
       <c r="G58" s="3" t="n">
-        <v>57.1</v>
+        <v>45.5</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-D</t>
+          <t>D-N-D-N</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -4020,21 +4020,21 @@
         </is>
       </c>
       <c r="K58" s="3" t="n">
-        <v>72.7</v>
+        <v>100</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N58" s="3" t="n">
-        <v>63.6</v>
+        <v>100</v>
       </c>
       <c r="O58" s="4" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -4298,10 +4298,10 @@
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -4309,26 +4309,26 @@
         </is>
       </c>
       <c r="G63" s="3" t="n">
-        <v>50</v>
+        <v>43.5</v>
       </c>
       <c r="H63" s="4" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-U</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K63" s="3" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
       <c r="L63" s="4" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
@@ -4336,10 +4336,10 @@
         </is>
       </c>
       <c r="N63" s="3" t="n">
-        <v>50</v>
+        <v>52.4</v>
       </c>
       <c r="O63" s="4" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="64">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -4603,37 +4603,37 @@
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>59.6</v>
+        <v>76.5</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G68" s="3" t="n">
-        <v>46.8</v>
+        <v>47.1</v>
       </c>
       <c r="H68" s="4" t="n">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-D</t>
+          <t>N-U-U-N</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K68" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="L68" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
@@ -4641,10 +4641,10 @@
         </is>
       </c>
       <c r="N68" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="O68" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -4664,44 +4664,48 @@
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G69" s="3" t="n">
-        <v>100</v>
+        <v>55.6</v>
       </c>
       <c r="H69" s="4" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>N-U-N-N</t>
+          <t>N-U-N-D</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="K69" s="3" t="inlineStr"/>
+          <t>N/U</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="n">
+        <v>50</v>
+      </c>
       <c r="L69" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N69" s="3" t="inlineStr"/>
+          <t>D/U</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="n">
+        <v>50</v>
+      </c>
       <c r="O69" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -4895,7 +4899,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -4904,10 +4908,10 @@
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>62.5</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4915,14 +4919,14 @@
         </is>
       </c>
       <c r="G73" s="3" t="n">
-        <v>47.6</v>
+        <v>40.6</v>
       </c>
       <c r="H73" s="4" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-N</t>
+          <t>D-D-N-U</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -4931,21 +4935,21 @@
         </is>
       </c>
       <c r="K73" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="L73" s="4" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N73" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>42.9</v>
       </c>
       <c r="O73" s="4" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="74">
@@ -4956,7 +4960,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -4965,25 +4969,25 @@
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>55.2</v>
+        <v>51.2</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>58</v>
+        <v>160</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G74" s="3" t="n">
-        <v>53.4</v>
+        <v>43.8</v>
       </c>
       <c r="H74" s="4" t="n">
-        <v>58</v>
+        <v>160</v>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -4992,21 +4996,21 @@
         </is>
       </c>
       <c r="K74" s="3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="L74" s="4" t="n">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N74" s="3" t="n">
-        <v>46.7</v>
+        <v>51.5</v>
       </c>
       <c r="O74" s="4" t="n">
-        <v>15</v>
+        <v>66</v>
       </c>
     </row>
     <row r="75">
@@ -5383,7 +5387,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -5392,25 +5396,25 @@
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>55.2</v>
+        <v>85.7</v>
       </c>
       <c r="E81" s="4" t="n">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G81" s="3" t="n">
-        <v>50.7</v>
+        <v>35.7</v>
       </c>
       <c r="H81" s="4" t="n">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-U</t>
+          <t>U-N-D-N</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -5419,21 +5423,21 @@
         </is>
       </c>
       <c r="K81" s="3" t="n">
-        <v>46.4</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="L81" s="4" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N81" s="3" t="n">
-        <v>50</v>
+        <v>46.2</v>
       </c>
       <c r="O81" s="4" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="82">
@@ -5444,7 +5448,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -5453,10 +5457,10 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>80.40000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -5464,14 +5468,14 @@
         </is>
       </c>
       <c r="G82" s="3" t="n">
-        <v>43.5</v>
+        <v>43.9</v>
       </c>
       <c r="H82" s="4" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-U</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -5480,10 +5484,10 @@
         </is>
       </c>
       <c r="K82" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>75</v>
       </c>
       <c r="L82" s="4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
@@ -5491,10 +5495,10 @@
         </is>
       </c>
       <c r="N82" s="3" t="n">
-        <v>50</v>
+        <v>43.8</v>
       </c>
       <c r="O82" s="4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="83">
@@ -5749,7 +5753,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -5758,10 +5762,10 @@
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>53.2</v>
+        <v>69.2</v>
       </c>
       <c r="E87" s="4" t="n">
-        <v>156</v>
+        <v>65</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5769,14 +5773,14 @@
         </is>
       </c>
       <c r="G87" s="3" t="n">
-        <v>42.3</v>
+        <v>44.6</v>
       </c>
       <c r="H87" s="4" t="n">
-        <v>156</v>
+        <v>65</v>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-U</t>
+          <t>U-D-D-N</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
@@ -5785,21 +5789,21 @@
         </is>
       </c>
       <c r="K87" s="3" t="n">
-        <v>61.9</v>
+        <v>63</v>
       </c>
       <c r="L87" s="4" t="n">
-        <v>63</v>
+        <v>27</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N87" s="3" t="n">
-        <v>47.6</v>
+        <v>55.6</v>
       </c>
       <c r="O87" s="4" t="n">
-        <v>63</v>
+        <v>27</v>
       </c>
     </row>
     <row r="88">
@@ -6237,7 +6241,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -6246,10 +6250,10 @@
         </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>70.90000000000001</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="E95" s="4" t="n">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -6257,14 +6261,14 @@
         </is>
       </c>
       <c r="G95" s="3" t="n">
-        <v>53.2</v>
+        <v>41.3</v>
       </c>
       <c r="H95" s="4" t="n">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
@@ -6273,21 +6277,21 @@
         </is>
       </c>
       <c r="K95" s="3" t="n">
-        <v>53.6</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="L95" s="4" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N95" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>42.9</v>
       </c>
       <c r="O95" s="4" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
     </row>
     <row r="96">
@@ -7519,7 +7523,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -7528,25 +7532,25 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>61.1</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="I9" s="3" t="n">
-        <v>44.4</v>
+        <v>45.5</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-U</t>
+          <t>N-D-D-N</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -7555,21 +7559,21 @@
         </is>
       </c>
       <c r="M9" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P9" s="3" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -7661,7 +7665,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -7670,25 +7674,25 @@
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>42.9</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I11" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-N</t>
+          <t>N-D-U-D</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -7697,21 +7701,21 @@
         </is>
       </c>
       <c r="M11" s="3" t="n">
-        <v>66.7</v>
+        <v>57.1</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P11" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -7803,7 +7807,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -7812,48 +7816,48 @@
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I13" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M13" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P13" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
@@ -8016,7 +8020,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -8025,37 +8029,37 @@
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>50</v>
+        <v>61.7</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I16" s="3" t="n">
-        <v>40.9</v>
+        <v>42.6</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-N</t>
+          <t>N-U-D-D</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M16" s="3" t="n">
-        <v>50</v>
+        <v>64.3</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -8063,10 +8067,10 @@
         </is>
       </c>
       <c r="P16" s="3" t="n">
-        <v>50</v>
+        <v>42.9</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17">
@@ -8087,7 +8091,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -8096,41 +8100,41 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I17" s="3" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>D-N-D-D</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M17" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N17" s="4" t="n">
         <v>4</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P17" s="3" t="n">
@@ -8158,7 +8162,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -8167,25 +8171,25 @@
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>73.3</v>
+        <v>57.1</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="I18" s="3" t="n">
-        <v>60</v>
+        <v>42.9</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -8194,21 +8198,21 @@
         </is>
       </c>
       <c r="M18" s="3" t="n">
-        <v>76.90000000000001</v>
+        <v>75</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="P18" s="3" t="n">
-        <v>53.8</v>
+        <v>50</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -8442,30 +8446,34 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="G22" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr"/>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="J22" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-N</t>
+          <t>D-N-N-D</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -10473,19 +10481,19 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-U</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -10496,30 +10504,34 @@
         <v>100</v>
       </c>
       <c r="J51" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>D-N-N-U</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N51" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>D-N-N-N</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M51" s="3" t="inlineStr"/>
-      <c r="N51" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P51" s="3" t="inlineStr"/>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P51" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="Q51" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -10540,34 +10552,34 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>60</v>
+        <v>44.4</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I52" s="3" t="n">
-        <v>40</v>
+        <v>61.1</v>
       </c>
       <c r="J52" s="4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
@@ -10576,21 +10588,21 @@
         </is>
       </c>
       <c r="M52" s="3" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P52" s="3" t="n">
-        <v>37.5</v>
+        <v>66.7</v>
       </c>
       <c r="Q52" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53">
@@ -10611,34 +10623,34 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>77.8</v>
+        <v>50</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I53" s="3" t="n">
-        <v>44.4</v>
+        <v>50</v>
       </c>
       <c r="J53" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-D</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
@@ -10647,21 +10659,21 @@
         </is>
       </c>
       <c r="M53" s="3" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="N53" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P53" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q53" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -10824,49 +10836,57 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="F56" s="3" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>83.3</v>
+      </c>
       <c r="G56" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="I56" s="3" t="inlineStr"/>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="n">
+        <v>50</v>
+      </c>
       <c r="J56" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-U</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M56" s="3" t="inlineStr"/>
+          <t>N/U</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="n">
+        <v>50</v>
+      </c>
       <c r="N56" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P56" s="3" t="inlineStr"/>
+          <t>D/U</t>
+        </is>
+      </c>
+      <c r="P56" s="3" t="n">
+        <v>50</v>
+      </c>
       <c r="Q56" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -10958,7 +10978,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>N-D-D</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -10967,48 +10987,44 @@
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>62.5</v>
+        <v>100</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="I58" s="3" t="n">
-        <v>62.5</v>
+        <v>50</v>
       </c>
       <c r="J58" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-D</t>
+          <t>D-N-D-N</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M58" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr"/>
       <c r="N58" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P58" s="3" t="n">
-        <v>66.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P58" s="3" t="inlineStr"/>
       <c r="Q58" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -11313,7 +11329,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -11322,48 +11338,48 @@
         </is>
       </c>
       <c r="F63" s="3" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="G63" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="J63" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>U-U-U-D</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="M63" s="3" t="n">
         <v>66.7</v>
       </c>
-      <c r="G63" s="4" t="n">
+      <c r="N63" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I63" s="3" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="J63" s="4" t="n">
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>D/N</t>
+        </is>
+      </c>
+      <c r="P63" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q63" s="4" t="n">
         <v>6</v>
-      </c>
-      <c r="K63" s="2" t="inlineStr">
-        <is>
-          <t>U-U-U-U</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="inlineStr">
-        <is>
-          <t>N/U</t>
-        </is>
-      </c>
-      <c r="M63" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="N63" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="O63" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P63" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q63" s="4" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -11660,7 +11676,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -11669,30 +11685,30 @@
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>62.5</v>
+        <v>75</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I68" s="3" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="J68" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-D</t>
+          <t>N-U-U-N</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M68" s="3" t="n">
@@ -11703,7 +11719,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P68" s="3" t="n">
@@ -11731,7 +11747,7 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -11754,7 +11770,7 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>N-U-N-N</t>
+          <t>N-U-N-D</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
@@ -12007,7 +12023,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -12016,25 +12032,25 @@
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>80</v>
+        <v>85.7</v>
       </c>
       <c r="G73" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I73" s="3" t="n">
-        <v>60</v>
+        <v>42.9</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-N</t>
+          <t>D-D-N-U</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
@@ -12050,11 +12066,11 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P73" s="3" t="n">
-        <v>33.3</v>
+        <v>66.7</v>
       </c>
       <c r="Q73" s="4" t="n">
         <v>3</v>
@@ -12078,7 +12094,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -12087,10 +12103,10 @@
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>56.2</v>
+        <v>53.8</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -12098,37 +12114,37 @@
         </is>
       </c>
       <c r="I74" s="3" t="n">
-        <v>43.8</v>
+        <v>42.3</v>
       </c>
       <c r="J74" s="4" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M74" s="3" t="n">
-        <v>50</v>
+        <v>38.5</v>
       </c>
       <c r="N74" s="4" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P74" s="3" t="n">
-        <v>50</v>
+        <v>46.2</v>
       </c>
       <c r="Q74" s="4" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="75">
@@ -12571,7 +12587,7 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -12580,10 +12596,10 @@
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>70</v>
+        <v>66.7</v>
       </c>
       <c r="G81" s="4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
@@ -12591,26 +12607,26 @@
         </is>
       </c>
       <c r="I81" s="3" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-U</t>
+          <t>U-N-D-N</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M81" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N81" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
@@ -12618,10 +12634,10 @@
         </is>
       </c>
       <c r="P81" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q81" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -12642,57 +12658,57 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>88.2</v>
+        <v>57.1</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I82" s="3" t="n">
-        <v>47.1</v>
+        <v>42.9</v>
       </c>
       <c r="J82" s="4" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-U</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M82" s="3" t="n">
-        <v>83.3</v>
+        <v>66.7</v>
       </c>
       <c r="N82" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="P82" s="3" t="n">
-        <v>66.7</v>
+        <v>33.3</v>
       </c>
       <c r="Q82" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -12997,7 +13013,7 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -13006,48 +13022,48 @@
         </is>
       </c>
       <c r="F87" s="3" t="n">
-        <v>43.3</v>
+        <v>66.7</v>
       </c>
       <c r="G87" s="4" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I87" s="3" t="n">
-        <v>53.3</v>
+        <v>66.7</v>
       </c>
       <c r="J87" s="4" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-U</t>
+          <t>U-D-D-N</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M87" s="3" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="N87" s="4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P87" s="3" t="n">
-        <v>66.7</v>
+        <v>40</v>
       </c>
       <c r="Q87" s="4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="88">
@@ -13565,7 +13581,7 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -13574,48 +13590,48 @@
         </is>
       </c>
       <c r="F95" s="3" t="n">
-        <v>80</v>
+        <v>84.2</v>
       </c>
       <c r="G95" s="4" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I95" s="3" t="n">
-        <v>40</v>
+        <v>42.1</v>
       </c>
       <c r="J95" s="4" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M95" s="3" t="n">
-        <v>50</v>
+        <v>87.5</v>
       </c>
       <c r="N95" s="4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P95" s="3" t="n">
-        <v>50</v>
+        <v>62.5</v>
       </c>
       <c r="Q95" s="4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="96">

--- a/BIS_tr.xlsx
+++ b/BIS_tr.xlsx
@@ -568,7 +568,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -577,25 +577,25 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>65.40000000000001</v>
+        <v>82.7</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G2" s="3" t="n">
-        <v>40.7</v>
+        <v>40.4</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>N-D-N-U</t>
+          <t>N-D-N-N</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -604,21 +604,21 @@
         </is>
       </c>
       <c r="K2" s="3" t="n">
-        <v>65</v>
+        <v>93.8</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N2" s="3" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="O2" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -629,7 +629,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -638,25 +638,25 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>53.6</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>168</v>
+        <v>71</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G3" s="3" t="n">
-        <v>41.7</v>
+        <v>42.3</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>168</v>
+        <v>71</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-U</t>
+          <t>U-D-D-N</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -665,21 +665,21 @@
         </is>
       </c>
       <c r="K3" s="3" t="n">
-        <v>51.5</v>
+        <v>76</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N3" s="3" t="n">
-        <v>42.6</v>
+        <v>40</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>68</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1187,10 +1187,10 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>58.5</v>
+        <v>60.9</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1198,14 +1198,14 @@
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>44.6</v>
+        <v>56.5</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-U</t>
+          <t>U-U-D-N</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1214,10 +1214,10 @@
         </is>
       </c>
       <c r="K12" s="3" t="n">
-        <v>55.6</v>
+        <v>90</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="N12" s="3" t="n">
-        <v>48.1</v>
+        <v>60</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1309,25 +1309,25 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>64.3</v>
+        <v>66.3</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>140</v>
+        <v>86</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G14" s="3" t="n">
-        <v>40.7</v>
+        <v>36</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>140</v>
+        <v>86</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-U</t>
+          <t>U-D-U-N</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1336,21 +1336,21 @@
         </is>
       </c>
       <c r="K14" s="3" t="n">
-        <v>65.90000000000001</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N14" s="3" t="n">
-        <v>50</v>
+        <v>34.3</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1614,25 +1614,25 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>48.9</v>
+        <v>55</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>92</v>
+        <v>40</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>46.7</v>
+        <v>45</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>92</v>
+        <v>40</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-U</t>
+          <t>N-U-D-N</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1641,21 +1641,21 @@
         </is>
       </c>
       <c r="K19" s="3" t="n">
-        <v>64.3</v>
+        <v>66.7</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="N19" s="3" t="n">
-        <v>57.1</v>
+        <v>33.3</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1919,25 +1919,25 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>62.5</v>
+        <v>56.7</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G24" s="3" t="n">
-        <v>43.8</v>
+        <v>51.7</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -1946,21 +1946,21 @@
         </is>
       </c>
       <c r="K24" s="3" t="n">
-        <v>78.90000000000001</v>
+        <v>60</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N24" s="3" t="n">
-        <v>42.1</v>
+        <v>60</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25">
@@ -1971,7 +1971,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1980,25 +1980,25 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>55.4</v>
+        <v>73.3</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>148</v>
+        <v>90</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G25" s="3" t="n">
-        <v>42.6</v>
+        <v>37.8</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>148</v>
+        <v>90</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-U</t>
+          <t>N-D-D-N</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -2007,21 +2007,21 @@
         </is>
       </c>
       <c r="K25" s="3" t="n">
-        <v>48.5</v>
+        <v>80</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N25" s="3" t="n">
-        <v>48.5</v>
+        <v>40</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2651,10 +2651,10 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>70.40000000000001</v>
+        <v>52.9</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2662,23 +2662,23 @@
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>48.1</v>
+        <v>41.2</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>U-U-N-U</t>
+          <t>U-U-N-D</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="K36" s="3" t="n">
-        <v>57.1</v>
+        <v>42.9</v>
       </c>
       <c r="L36" s="4" t="n">
         <v>7</v>
@@ -2689,7 +2689,7 @@
         </is>
       </c>
       <c r="N36" s="3" t="n">
-        <v>57.1</v>
+        <v>42.9</v>
       </c>
       <c r="O36" s="4" t="n">
         <v>7</v>
@@ -3557,19 +3557,19 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-N-N</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>43.8</v>
+        <v>87.5</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3577,14 +3577,14 @@
         </is>
       </c>
       <c r="G51" s="3" t="n">
-        <v>43.8</v>
+        <v>50</v>
       </c>
       <c r="H51" s="4" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-U</t>
+          <t>D-N-N-N</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -3593,21 +3593,21 @@
         </is>
       </c>
       <c r="K51" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="L51" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="n">
         <v>66.7</v>
       </c>
-      <c r="L51" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="M51" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N51" s="3" t="n">
-        <v>50</v>
-      </c>
       <c r="O51" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3688,10 +3688,10 @@
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>60</v>
+        <v>60.9</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3699,14 +3699,14 @@
         </is>
       </c>
       <c r="G53" s="3" t="n">
-        <v>50</v>
+        <v>47.8</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -3715,10 +3715,10 @@
         </is>
       </c>
       <c r="K53" s="3" t="n">
-        <v>66.7</v>
+        <v>64.7</v>
       </c>
       <c r="L53" s="4" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
@@ -3726,10 +3726,10 @@
         </is>
       </c>
       <c r="N53" s="3" t="n">
-        <v>50</v>
+        <v>41.2</v>
       </c>
       <c r="O53" s="4" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="54">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>59.1</v>
+        <v>61.5</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3943,14 +3943,14 @@
         </is>
       </c>
       <c r="G57" s="3" t="n">
-        <v>43.4</v>
+        <v>51.3</v>
       </c>
       <c r="H57" s="4" t="n">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -3959,21 +3959,21 @@
         </is>
       </c>
       <c r="K57" s="3" t="n">
-        <v>55.4</v>
+        <v>69.2</v>
       </c>
       <c r="L57" s="4" t="n">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N57" s="3" t="n">
-        <v>44.6</v>
+        <v>48.7</v>
       </c>
       <c r="O57" s="4" t="n">
-        <v>65</v>
+        <v>39</v>
       </c>
     </row>
     <row r="58">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3993,10 +3993,10 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>81.8</v>
+        <v>50</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -4004,37 +4004,37 @@
         </is>
       </c>
       <c r="G58" s="3" t="n">
-        <v>45.5</v>
+        <v>61.5</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>D-N-D-U</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K58" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N58" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="O58" s="4" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="59">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4054,10 +4054,10 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>74.40000000000001</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -4065,14 +4065,14 @@
         </is>
       </c>
       <c r="G59" s="3" t="n">
-        <v>43.6</v>
+        <v>40.4</v>
       </c>
       <c r="H59" s="4" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-N</t>
+          <t>U-N-U-D</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -4081,21 +4081,21 @@
         </is>
       </c>
       <c r="K59" s="3" t="n">
-        <v>62.5</v>
+        <v>68</v>
       </c>
       <c r="L59" s="4" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N59" s="3" t="n">
-        <v>43.8</v>
+        <v>40</v>
       </c>
       <c r="O59" s="4" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="60">
@@ -4228,7 +4228,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4237,25 +4237,25 @@
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>75</v>
+        <v>66.2</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G62" s="3" t="n">
-        <v>33.3</v>
+        <v>46.2</v>
       </c>
       <c r="H62" s="4" t="n">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-N</t>
+          <t>N-N-D-D</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -4264,10 +4264,10 @@
         </is>
       </c>
       <c r="K62" s="3" t="n">
-        <v>75</v>
+        <v>64.7</v>
       </c>
       <c r="L62" s="4" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
@@ -4275,10 +4275,10 @@
         </is>
       </c>
       <c r="N62" s="3" t="n">
-        <v>41.7</v>
+        <v>41.2</v>
       </c>
       <c r="O62" s="4" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="63">
@@ -4472,7 +4472,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -4481,10 +4481,10 @@
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>62.7</v>
+        <v>53.7</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>67</v>
+        <v>149</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -4492,14 +4492,14 @@
         </is>
       </c>
       <c r="G66" s="3" t="n">
-        <v>43.3</v>
+        <v>47.7</v>
       </c>
       <c r="H66" s="4" t="n">
-        <v>67</v>
+        <v>149</v>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-N</t>
+          <t>N-U-U-U</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -4508,21 +4508,21 @@
         </is>
       </c>
       <c r="K66" s="3" t="n">
-        <v>76.90000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="L66" s="4" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N66" s="3" t="n">
-        <v>38.5</v>
+        <v>48.1</v>
       </c>
       <c r="O66" s="4" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
     </row>
     <row r="67">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -4603,48 +4603,48 @@
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>76.5</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="H68" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>N-U-U-U</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="L68" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
           <t>D/U</t>
         </is>
       </c>
-      <c r="G68" s="3" t="n">
-        <v>47.1</v>
-      </c>
-      <c r="H68" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t>N-U-U-N</t>
-        </is>
-      </c>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="K68" s="3" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="L68" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M68" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
       <c r="N68" s="3" t="n">
-        <v>66.7</v>
+        <v>44.4</v>
       </c>
       <c r="O68" s="4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="69">
@@ -4838,7 +4838,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -4847,25 +4847,25 @@
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>62.5</v>
+        <v>62.9</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>32</v>
+        <v>89</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G72" s="3" t="n">
-        <v>50</v>
+        <v>48.3</v>
       </c>
       <c r="H72" s="4" t="n">
-        <v>32</v>
+        <v>89</v>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-N</t>
+          <t>N-U-D-D</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -4874,21 +4874,21 @@
         </is>
       </c>
       <c r="K72" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>66.7</v>
       </c>
       <c r="L72" s="4" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N72" s="3" t="n">
-        <v>42.9</v>
+        <v>66.7</v>
       </c>
       <c r="O72" s="4" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="73">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -4908,10 +4908,10 @@
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>62.5</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4919,14 +4919,14 @@
         </is>
       </c>
       <c r="G73" s="3" t="n">
-        <v>40.6</v>
+        <v>47.6</v>
       </c>
       <c r="H73" s="4" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-U</t>
+          <t>D-D-N-N</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -4935,21 +4935,21 @@
         </is>
       </c>
       <c r="K73" s="3" t="n">
-        <v>64.3</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="L73" s="4" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N73" s="3" t="n">
-        <v>42.9</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="O73" s="4" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="74">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -4969,25 +4969,25 @@
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>51.2</v>
+        <v>55.2</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>160</v>
+        <v>58</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G74" s="3" t="n">
-        <v>43.8</v>
+        <v>53.4</v>
       </c>
       <c r="H74" s="4" t="n">
-        <v>160</v>
+        <v>58</v>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -4996,21 +4996,21 @@
         </is>
       </c>
       <c r="K74" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="L74" s="4" t="n">
-        <v>66</v>
+        <v>15</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N74" s="3" t="n">
-        <v>51.5</v>
+        <v>46.7</v>
       </c>
       <c r="O74" s="4" t="n">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="75">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -5091,48 +5091,48 @@
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>47.8</v>
+        <v>64.8</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>159</v>
+        <v>88</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G76" s="3" t="n">
-        <v>37.7</v>
+        <v>40.9</v>
       </c>
       <c r="H76" s="4" t="n">
-        <v>159</v>
+        <v>88</v>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-U</t>
+          <t>U-U-D-N</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K76" s="3" t="n">
-        <v>45.7</v>
+        <v>61</v>
       </c>
       <c r="L76" s="4" t="n">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N76" s="3" t="n">
-        <v>38.6</v>
+        <v>43.9</v>
       </c>
       <c r="O76" s="4" t="n">
-        <v>70</v>
+        <v>41</v>
       </c>
     </row>
     <row r="77">
@@ -5387,7 +5387,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -5396,25 +5396,25 @@
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>85.7</v>
+        <v>61.8</v>
       </c>
       <c r="E81" s="4" t="n">
-        <v>28</v>
+        <v>68</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G81" s="3" t="n">
-        <v>35.7</v>
+        <v>45.6</v>
       </c>
       <c r="H81" s="4" t="n">
-        <v>28</v>
+        <v>68</v>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-N</t>
+          <t>U-N-D-D</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -5423,10 +5423,10 @@
         </is>
       </c>
       <c r="K81" s="3" t="n">
-        <v>84.59999999999999</v>
+        <v>52</v>
       </c>
       <c r="L81" s="4" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
@@ -5434,10 +5434,10 @@
         </is>
       </c>
       <c r="N81" s="3" t="n">
-        <v>46.2</v>
+        <v>40</v>
       </c>
       <c r="O81" s="4" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
     <row r="82">
@@ -7026,7 +7026,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -7035,10 +7035,10 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -7046,26 +7046,26 @@
         </is>
       </c>
       <c r="I2" s="3" t="n">
-        <v>37.5</v>
+        <v>60</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>N-D-N-U</t>
+          <t>N-D-N-N</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M2" s="3" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
@@ -7073,10 +7073,10 @@
         </is>
       </c>
       <c r="P2" s="3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="Q2" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -7097,7 +7097,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -7106,25 +7106,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="G3" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="n">
-        <v>52.9</v>
-      </c>
       <c r="J3" s="4" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-U</t>
+          <t>U-D-D-N</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -7133,21 +7133,21 @@
         </is>
       </c>
       <c r="M3" s="3" t="n">
-        <v>57.1</v>
+        <v>75</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="P3" s="3" t="n">
-        <v>57.1</v>
+        <v>50</v>
       </c>
       <c r="Q3" s="4" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -7745,25 +7745,25 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>52.9</v>
+        <v>66.7</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I12" s="3" t="n">
-        <v>35.3</v>
+        <v>83.3</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-U</t>
+          <t>U-U-D-N</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -7772,10 +7772,10 @@
         </is>
       </c>
       <c r="M12" s="3" t="n">
-        <v>55.6</v>
+        <v>66.7</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -7783,10 +7783,10 @@
         </is>
       </c>
       <c r="P12" s="3" t="n">
-        <v>44.4</v>
+        <v>66.7</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -7878,7 +7878,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -7887,48 +7887,48 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>76.2</v>
+        <v>42.9</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I14" s="3" t="n">
-        <v>38.1</v>
+        <v>50</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-U</t>
+          <t>U-D-U-N</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="M14" s="3" t="n">
-        <v>85.7</v>
+        <v>33.3</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P14" s="3" t="n">
-        <v>42.9</v>
+        <v>66.7</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
@@ -8233,46 +8233,46 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>53.8</v>
+        <v>62.5</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="I19" s="3" t="n">
-        <v>46.2</v>
+        <v>50</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-U</t>
+          <t>N-U-D-N</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M19" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         <v>100</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -8584,7 +8584,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -8593,48 +8593,48 @@
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>75</v>
+        <v>42.9</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I24" s="3" t="n">
         <v>50</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M24" s="3" t="n">
-        <v>85.7</v>
+        <v>100</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P24" s="3" t="n">
-        <v>42.9</v>
+        <v>100</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -8655,7 +8655,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -8664,48 +8664,48 @@
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I25" s="3" t="n">
-        <v>51.9</v>
+        <v>40</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-U</t>
+          <t>N-D-D-N</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M25" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P25" s="3" t="n">
-        <v>62.5</v>
+        <v>66.7</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -9428,53 +9428,57 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I36" s="3" t="n">
         <v>50</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>U-U-N-U</t>
+          <t>U-U-N-D</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M36" s="3" t="inlineStr"/>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="n">
+        <v>66.7</v>
+      </c>
       <c r="N36" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P36" s="3" t="inlineStr"/>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="n">
+        <v>66.7</v>
+      </c>
       <c r="Q36" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -10481,19 +10485,19 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-N-N</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -10504,34 +10508,30 @@
         <v>100</v>
       </c>
       <c r="J51" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-U</t>
+          <t>D-N-N-N</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="M51" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr"/>
       <c r="N51" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P51" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P51" s="3" t="inlineStr"/>
       <c r="Q51" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -10623,57 +10623,57 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F53" s="3" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="G53" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="J53" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>D-U-D-D</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="N53" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P53" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="G53" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>D/U</t>
-        </is>
-      </c>
-      <c r="I53" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="J53" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>D-U-D-N</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M53" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="N53" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O53" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P53" s="3" t="n">
-        <v>100</v>
-      </c>
       <c r="Q53" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54">
@@ -10907,7 +10907,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -10916,10 +10916,10 @@
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>57.7</v>
+        <v>81.2</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -10927,14 +10927,14 @@
         </is>
       </c>
       <c r="I57" s="3" t="n">
-        <v>42.3</v>
+        <v>43.8</v>
       </c>
       <c r="J57" s="4" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
@@ -10943,10 +10943,10 @@
         </is>
       </c>
       <c r="M57" s="3" t="n">
-        <v>62.5</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="N57" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
@@ -10954,10 +10954,10 @@
         </is>
       </c>
       <c r="P57" s="3" t="n">
-        <v>50</v>
+        <v>44.4</v>
       </c>
       <c r="Q57" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="58">
@@ -10978,53 +10978,57 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F58" s="3" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="G58" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="J58" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>D-N-D-U</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="G58" s="4" t="n">
+      <c r="N58" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>N/U</t>
-        </is>
-      </c>
-      <c r="I58" s="3" t="n">
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>D/U</t>
+        </is>
+      </c>
+      <c r="P58" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="J58" s="4" t="n">
+      <c r="Q58" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="K58" s="2" t="inlineStr">
-        <is>
-          <t>D-N-D-N</t>
-        </is>
-      </c>
-      <c r="L58" s="2" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M58" s="3" t="inlineStr"/>
-      <c r="N58" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" s="2" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P58" s="3" t="inlineStr"/>
-      <c r="Q58" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -11045,7 +11049,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -11054,48 +11058,48 @@
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>100</v>
+        <v>54.5</v>
       </c>
       <c r="G59" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="J59" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>U-N-U-D</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>N/U</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="N59" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I59" s="3" t="n">
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P59" s="3" t="n">
         <v>75</v>
       </c>
-      <c r="J59" s="4" t="n">
+      <c r="Q59" s="4" t="n">
         <v>4</v>
-      </c>
-      <c r="K59" s="2" t="inlineStr">
-        <is>
-          <t>U-N-U-N</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M59" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="N59" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="O59" s="2" t="inlineStr">
-        <is>
-          <t>D/U</t>
-        </is>
-      </c>
-      <c r="P59" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q59" s="4" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -11258,7 +11262,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -11270,22 +11274,22 @@
         <v>57.1</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I62" s="3" t="n">
         <v>57.1</v>
       </c>
       <c r="J62" s="4" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-N</t>
+          <t>N-N-D-D</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
@@ -11294,21 +11298,21 @@
         </is>
       </c>
       <c r="M62" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N62" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P62" s="3" t="n">
         <v>100</v>
       </c>
       <c r="Q62" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="63">
@@ -11542,19 +11546,19 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>54.5</v>
+        <v>55.6</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -11562,14 +11566,14 @@
         </is>
       </c>
       <c r="I66" s="3" t="n">
-        <v>45.5</v>
+        <v>51.9</v>
       </c>
       <c r="J66" s="4" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-N</t>
+          <t>N-U-U-U</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
@@ -11581,18 +11585,18 @@
         <v>100</v>
       </c>
       <c r="N66" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P66" s="3" t="n">
         <v>100</v>
       </c>
       <c r="Q66" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -11676,7 +11680,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -11685,30 +11689,30 @@
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>75</v>
+        <v>63.6</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I68" s="3" t="n">
-        <v>75</v>
+        <v>63.6</v>
       </c>
       <c r="J68" s="4" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-N</t>
+          <t>N-U-U-U</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M68" s="3" t="n">
@@ -11719,7 +11723,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P68" s="3" t="n">
@@ -11952,34 +11956,34 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F72" s="3" t="n">
-        <v>55.6</v>
+        <v>56</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I72" s="3" t="n">
-        <v>44.4</v>
+        <v>44</v>
       </c>
       <c r="J72" s="4" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-N</t>
+          <t>N-U-D-D</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
@@ -11991,18 +11995,18 @@
         <v>100</v>
       </c>
       <c r="N72" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P72" s="3" t="n">
         <v>100</v>
       </c>
       <c r="Q72" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -12023,7 +12027,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -12032,25 +12036,25 @@
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>85.7</v>
+        <v>80</v>
       </c>
       <c r="G73" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I73" s="3" t="n">
-        <v>42.9</v>
+        <v>60</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-U</t>
+          <t>D-D-N-N</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
@@ -12066,11 +12070,11 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="P73" s="3" t="n">
-        <v>66.7</v>
+        <v>33.3</v>
       </c>
       <c r="Q73" s="4" t="n">
         <v>3</v>
@@ -12094,7 +12098,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -12103,10 +12107,10 @@
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>53.8</v>
+        <v>56.2</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -12114,37 +12118,37 @@
         </is>
       </c>
       <c r="I74" s="3" t="n">
-        <v>42.3</v>
+        <v>43.8</v>
       </c>
       <c r="J74" s="4" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="M74" s="3" t="n">
-        <v>38.5</v>
+        <v>50</v>
       </c>
       <c r="N74" s="4" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P74" s="3" t="n">
-        <v>46.2</v>
+        <v>50</v>
       </c>
       <c r="Q74" s="4" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
@@ -12232,34 +12236,34 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>53.5</v>
+        <v>58.3</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I76" s="3" t="n">
-        <v>39.5</v>
+        <v>41.7</v>
       </c>
       <c r="J76" s="4" t="n">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-U</t>
+          <t>U-U-D-N</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
@@ -12268,21 +12272,21 @@
         </is>
       </c>
       <c r="M76" s="3" t="n">
-        <v>52.4</v>
+        <v>50</v>
       </c>
       <c r="N76" s="4" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P76" s="3" t="n">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="Q76" s="4" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
     </row>
     <row r="77">
@@ -12587,7 +12591,7 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -12596,25 +12600,25 @@
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>66.7</v>
+        <v>58.3</v>
       </c>
       <c r="G81" s="4" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I81" s="3" t="n">
         <v>66.7</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-N</t>
+          <t>U-N-D-D</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
@@ -12623,21 +12627,21 @@
         </is>
       </c>
       <c r="M81" s="3" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="N81" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P81" s="3" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="Q81" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82">

--- a/BIS_tr.xlsx
+++ b/BIS_tr.xlsx
@@ -568,7 +568,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -577,25 +577,25 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>88.7</v>
+        <v>66</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G2" s="3" t="n">
-        <v>50</v>
+        <v>38.3</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-N</t>
+          <t>D-N-N-D</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -604,21 +604,21 @@
         </is>
       </c>
       <c r="K2" s="3" t="n">
-        <v>89.5</v>
+        <v>66.7</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N2" s="3" t="n">
-        <v>47.4</v>
+        <v>41.7</v>
       </c>
       <c r="O2" s="4" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -690,7 +690,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -699,10 +699,10 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>51.2</v>
+        <v>53.5</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -710,37 +710,37 @@
         </is>
       </c>
       <c r="G4" s="3" t="n">
-        <v>38.8</v>
+        <v>46.5</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-U</t>
+          <t>U-N-U-N</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K4" s="3" t="n">
-        <v>63</v>
+        <v>57.1</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N4" s="3" t="n">
-        <v>40.7</v>
+        <v>50</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
@@ -751,7 +751,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -760,25 +760,25 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>65.09999999999999</v>
+        <v>57.3</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>63</v>
+        <v>164</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G5" s="3" t="n">
-        <v>46</v>
+        <v>44.5</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>63</v>
+        <v>164</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="K5" s="3" t="n">
-        <v>64.3</v>
+        <v>53.6</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N5" s="3" t="n">
-        <v>42.9</v>
+        <v>44.9</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>28</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6">
@@ -995,7 +995,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1004,10 +1004,10 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>81.7</v>
+        <v>71</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>93</v>
+        <v>62</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -1015,14 +1015,14 @@
         </is>
       </c>
       <c r="G9" s="3" t="n">
-        <v>41.9</v>
+        <v>46.8</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>93</v>
+        <v>62</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-N</t>
+          <t>D-D-N-D</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1031,21 +1031,21 @@
         </is>
       </c>
       <c r="K9" s="3" t="n">
-        <v>85.7</v>
+        <v>58.3</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N9" s="3" t="n">
-        <v>38.1</v>
+        <v>41.7</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1126,10 +1126,10 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>70.90000000000001</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>79</v>
+        <v>195</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1137,14 +1137,14 @@
         </is>
       </c>
       <c r="G11" s="3" t="n">
-        <v>39.2</v>
+        <v>42.1</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>79</v>
+        <v>195</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="K11" s="3" t="n">
-        <v>76.3</v>
+        <v>62.7</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>38</v>
+        <v>83</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
@@ -1164,10 +1164,10 @@
         </is>
       </c>
       <c r="N11" s="3" t="n">
-        <v>42.1</v>
+        <v>54.2</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>38</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1248,48 +1248,48 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>66.7</v>
+        <v>53.3</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G13" s="3" t="n">
-        <v>44.4</v>
+        <v>57.8</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K13" s="3" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N13" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1309,10 +1309,10 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>71.2</v>
+        <v>67</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1320,14 +1320,14 @@
         </is>
       </c>
       <c r="G14" s="3" t="n">
-        <v>36.4</v>
+        <v>45.1</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-N</t>
+          <t>D-U-N-D</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="K14" s="3" t="n">
-        <v>66.7</v>
+        <v>64.5</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="N14" s="3" t="n">
-        <v>37.5</v>
+        <v>51.6</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1553,25 +1553,25 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>78.8</v>
+        <v>61.5</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G18" s="3" t="n">
-        <v>34.8</v>
+        <v>47.7</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-N</t>
+          <t>U-D-N-D</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1580,10 +1580,10 @@
         </is>
       </c>
       <c r="K18" s="3" t="n">
-        <v>70.8</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="N18" s="3" t="n">
-        <v>41.7</v>
+        <v>52.4</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1675,25 +1675,25 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>70.5</v>
+        <v>60</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>38.9</v>
+        <v>42.9</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1702,21 +1702,21 @@
         </is>
       </c>
       <c r="K20" s="3" t="n">
-        <v>61.1</v>
+        <v>57.1</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N20" s="3" t="n">
-        <v>41.7</v>
+        <v>45.2</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1736,48 +1736,48 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>57.6</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>U-N-U-D</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>N/U</t>
         </is>
       </c>
-      <c r="G21" s="3" t="n">
-        <v>35.3</v>
-      </c>
-      <c r="H21" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>U-N-U-N</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="K21" s="3" t="n">
-        <v>85.7</v>
+        <v>45</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N21" s="3" t="n">
-        <v>42.9</v>
+        <v>55</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22">
@@ -1788,34 +1788,34 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>57.9</v>
+        <v>84.2</v>
       </c>
       <c r="E22" s="4" t="n">
         <v>19</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G22" s="3" t="n">
-        <v>52.6</v>
+        <v>73.7</v>
       </c>
       <c r="H22" s="4" t="n">
         <v>19</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-U</t>
+          <t>N-N-D-D</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -1824,10 +1824,10 @@
         </is>
       </c>
       <c r="K22" s="3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="N22" s="3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1858,10 +1858,10 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>58.8</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1869,26 +1869,26 @@
         </is>
       </c>
       <c r="G23" s="3" t="n">
-        <v>52.9</v>
+        <v>38.2</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K23" s="3" t="n">
-        <v>60</v>
+        <v>73.5</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
@@ -1896,10 +1896,10 @@
         </is>
       </c>
       <c r="N23" s="3" t="n">
-        <v>80</v>
+        <v>38.2</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2041,25 +2041,25 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>50.6</v>
+        <v>47.3</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>79</v>
+        <v>167</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>38</v>
+        <v>44.3</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>79</v>
+        <v>167</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-N</t>
+          <t>N-D-U-D</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -2068,21 +2068,21 @@
         </is>
       </c>
       <c r="K26" s="3" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="L26" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="L26" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="N26" s="3" t="n">
-        <v>37.5</v>
-      </c>
       <c r="O26" s="4" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27">
@@ -2093,57 +2093,57 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>78.90000000000001</v>
+        <v>50</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>68.40000000000001</v>
+        <v>57.7</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K27" s="3" t="n">
-        <v>81.8</v>
+        <v>41.2</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N27" s="3" t="n">
-        <v>63.6</v>
+        <v>52.9</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>77.09999999999999</v>
+        <v>64</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -2174,14 +2174,14 @@
         </is>
       </c>
       <c r="G28" s="3" t="n">
-        <v>45.7</v>
+        <v>49.3</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-N</t>
+          <t>U-D-N-D</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -2190,10 +2190,10 @@
         </is>
       </c>
       <c r="K28" s="3" t="n">
-        <v>76.90000000000001</v>
+        <v>75</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
@@ -2201,10 +2201,10 @@
         </is>
       </c>
       <c r="N28" s="3" t="n">
-        <v>53.8</v>
+        <v>44.4</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>13</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2224,37 +2224,37 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>53.3</v>
+        <v>45.2</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>53.3</v>
+        <v>58.1</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K29" s="3" t="n">
-        <v>58.3</v>
+        <v>41.2</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="N29" s="3" t="n">
-        <v>66.7</v>
+        <v>52.9</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2346,25 +2346,25 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>74.09999999999999</v>
+        <v>66.2</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>40.7</v>
+        <v>49.3</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-U</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -2373,21 +2373,21 @@
         </is>
       </c>
       <c r="K31" s="3" t="n">
-        <v>81.8</v>
+        <v>64.7</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N31" s="3" t="n">
-        <v>36.4</v>
+        <v>52.9</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
     </row>
     <row r="32">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2407,10 +2407,10 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>69.40000000000001</v>
+        <v>58.3</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>62</v>
+        <v>144</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2418,14 +2418,14 @@
         </is>
       </c>
       <c r="G32" s="3" t="n">
-        <v>37.1</v>
+        <v>43.1</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>62</v>
+        <v>144</v>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-N</t>
+          <t>N-D-U-U</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -2434,21 +2434,21 @@
         </is>
       </c>
       <c r="K32" s="3" t="n">
-        <v>54.5</v>
+        <v>56</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N32" s="3" t="n">
-        <v>45.5</v>
+        <v>44</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="33">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>63.1</v>
+        <v>58.9</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>84</v>
+        <v>56</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2540,14 +2540,14 @@
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>44</v>
+        <v>39.3</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>84</v>
+        <v>56</v>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>N-N-U-U</t>
+          <t>N-N-U-N</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="K34" s="3" t="n">
-        <v>60.9</v>
+        <v>63.6</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="N34" s="3" t="n">
-        <v>56.5</v>
+        <v>63.6</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="35">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2773,25 +2773,25 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>64.8</v>
+        <v>63.4</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>88</v>
+        <v>153</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G38" s="3" t="n">
-        <v>43.2</v>
+        <v>45.8</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>88</v>
+        <v>153</v>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-N</t>
+          <t>N-D-U-D</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -2800,21 +2800,21 @@
         </is>
       </c>
       <c r="K38" s="3" t="n">
-        <v>76.5</v>
+        <v>60.5</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N38" s="3" t="n">
-        <v>47.1</v>
+        <v>44.7</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>17</v>
+        <v>38</v>
       </c>
     </row>
     <row r="39">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2895,25 +2895,25 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>63.6</v>
+        <v>77.5</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G40" s="3" t="n">
-        <v>45.5</v>
+        <v>55</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-N-U-U</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -2922,10 +2922,10 @@
         </is>
       </c>
       <c r="K40" s="3" t="n">
-        <v>58.3</v>
+        <v>80</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
@@ -2933,10 +2933,10 @@
         </is>
       </c>
       <c r="N40" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="O40" s="4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3139,25 +3139,25 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>89.5</v>
+        <v>70.8</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G44" s="3" t="n">
-        <v>52.6</v>
+        <v>45.8</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -3166,21 +3166,21 @@
         </is>
       </c>
       <c r="K44" s="3" t="n">
-        <v>100</v>
+        <v>61.9</v>
       </c>
       <c r="L44" s="4" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N44" s="3" t="n">
         <v>42.9</v>
       </c>
       <c r="O44" s="4" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="45">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3261,25 +3261,25 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>51.6</v>
+        <v>60</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>153</v>
+        <v>65</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G46" s="3" t="n">
-        <v>41.8</v>
+        <v>47.7</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>153</v>
+        <v>65</v>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-U</t>
+          <t>U-D-U-N</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -3288,21 +3288,21 @@
         </is>
       </c>
       <c r="K46" s="3" t="n">
-        <v>53.2</v>
+        <v>63</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N46" s="3" t="n">
-        <v>37.1</v>
+        <v>51.9</v>
       </c>
       <c r="O46" s="4" t="n">
-        <v>62</v>
+        <v>27</v>
       </c>
     </row>
     <row r="47">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3383,25 +3383,25 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>76.5</v>
+        <v>50</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>35.3</v>
+        <v>50</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-N</t>
+          <t>U-D-N-U</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -3410,10 +3410,10 @@
         </is>
       </c>
       <c r="K48" s="3" t="n">
-        <v>74.09999999999999</v>
+        <v>54.2</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
@@ -3421,10 +3421,10 @@
         </is>
       </c>
       <c r="N48" s="3" t="n">
-        <v>44.4</v>
+        <v>58.3</v>
       </c>
       <c r="O48" s="4" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="49">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -3505,25 +3505,25 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>65.40000000000001</v>
+        <v>72</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>133</v>
+        <v>82</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G50" s="3" t="n">
-        <v>42.9</v>
+        <v>48.8</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>133</v>
+        <v>82</v>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -3532,10 +3532,10 @@
         </is>
       </c>
       <c r="K50" s="3" t="n">
-        <v>67.40000000000001</v>
+        <v>69.7</v>
       </c>
       <c r="L50" s="4" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
@@ -3543,10 +3543,10 @@
         </is>
       </c>
       <c r="N50" s="3" t="n">
-        <v>46.5</v>
+        <v>51.5</v>
       </c>
       <c r="O50" s="4" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
     <row r="51">
@@ -3557,7 +3557,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -3566,14 +3566,14 @@
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="E51" s="4" t="n">
         <v>9</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G51" s="3" t="n">
@@ -3584,30 +3584,30 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>N-N-N-N</t>
+          <t>N-N-N-D</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K51" s="3" t="n">
         <v>100</v>
       </c>
       <c r="L51" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N51" s="3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="O51" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52">
@@ -3679,57 +3679,57 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>45.5</v>
+        <v>55</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G53" s="3" t="n">
-        <v>45.5</v>
+        <v>50</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-U</t>
+          <t>U-D-D-N</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K53" s="3" t="n">
-        <v>60</v>
+        <v>55.6</v>
       </c>
       <c r="L53" s="4" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N53" s="3" t="n">
-        <v>60</v>
+        <v>55.6</v>
       </c>
       <c r="O53" s="4" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="54">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3871,48 +3871,48 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>63.5</v>
+        <v>55.6</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G56" s="3" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="H56" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>D-U-U-N</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="L56" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>D/U</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="H56" s="4" t="n">
-        <v>52</v>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>D-U-U-D</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K56" s="3" t="n">
-        <v>65.2</v>
-      </c>
-      <c r="L56" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="M56" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="N56" s="3" t="n">
-        <v>56.5</v>
-      </c>
       <c r="O56" s="4" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4054,10 +4054,10 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>69.59999999999999</v>
+        <v>71.2</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>138</v>
+        <v>66</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -4065,14 +4065,14 @@
         </is>
       </c>
       <c r="G59" s="3" t="n">
-        <v>42</v>
+        <v>42.4</v>
       </c>
       <c r="H59" s="4" t="n">
-        <v>138</v>
+        <v>66</v>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-U</t>
+          <t>N-U-D-N</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -4081,21 +4081,21 @@
         </is>
       </c>
       <c r="K59" s="3" t="n">
-        <v>72.7</v>
+        <v>91.7</v>
       </c>
       <c r="L59" s="4" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N59" s="3" t="n">
         <v>50</v>
       </c>
       <c r="O59" s="4" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="60">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4115,10 +4115,10 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>59.2</v>
+        <v>64.8</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>147</v>
+        <v>71</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -4126,14 +4126,14 @@
         </is>
       </c>
       <c r="G60" s="3" t="n">
-        <v>40.1</v>
+        <v>52.1</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>147</v>
+        <v>71</v>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -4142,21 +4142,21 @@
         </is>
       </c>
       <c r="K60" s="3" t="n">
-        <v>62.3</v>
+        <v>67.7</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N60" s="3" t="n">
-        <v>43.4</v>
+        <v>45.2</v>
       </c>
       <c r="O60" s="4" t="n">
-        <v>53</v>
+        <v>31</v>
       </c>
     </row>
     <row r="61">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -4298,25 +4298,25 @@
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>76.5</v>
+        <v>66.7</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G63" s="3" t="n">
-        <v>41.2</v>
+        <v>37.5</v>
       </c>
       <c r="H63" s="4" t="n">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-N</t>
+          <t>U-U-D-D</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -4325,10 +4325,10 @@
         </is>
       </c>
       <c r="K63" s="3" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="L63" s="4" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
@@ -4336,10 +4336,10 @@
         </is>
       </c>
       <c r="N63" s="3" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="O63" s="4" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="64">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -4359,10 +4359,10 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>46.6</v>
+        <v>59.7</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>178</v>
+        <v>67</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -4370,14 +4370,14 @@
         </is>
       </c>
       <c r="G64" s="3" t="n">
-        <v>48.3</v>
+        <v>40.3</v>
       </c>
       <c r="H64" s="4" t="n">
-        <v>178</v>
+        <v>67</v>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-U</t>
+          <t>N-D-U-N</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -4386,10 +4386,10 @@
         </is>
       </c>
       <c r="K64" s="3" t="n">
-        <v>63.2</v>
+        <v>87.5</v>
       </c>
       <c r="L64" s="4" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
@@ -4397,10 +4397,10 @@
         </is>
       </c>
       <c r="N64" s="3" t="n">
-        <v>42.1</v>
+        <v>75</v>
       </c>
       <c r="O64" s="4" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="65">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -4420,10 +4420,10 @@
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>79.5</v>
+        <v>64.2</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>78</v>
+        <v>173</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -4431,14 +4431,14 @@
         </is>
       </c>
       <c r="G65" s="3" t="n">
-        <v>41</v>
+        <v>41.6</v>
       </c>
       <c r="H65" s="4" t="n">
-        <v>78</v>
+        <v>173</v>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -4447,10 +4447,10 @@
         </is>
       </c>
       <c r="K65" s="3" t="n">
-        <v>83.3</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="L65" s="4" t="n">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
@@ -4458,10 +4458,10 @@
         </is>
       </c>
       <c r="N65" s="3" t="n">
-        <v>47.2</v>
+        <v>45.6</v>
       </c>
       <c r="O65" s="4" t="n">
-        <v>36</v>
+        <v>68</v>
       </c>
     </row>
     <row r="66">
@@ -4472,7 +4472,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -4481,25 +4481,25 @@
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>62.7</v>
+        <v>53.8</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>67</v>
+        <v>130</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G66" s="3" t="n">
-        <v>43.3</v>
+        <v>40.8</v>
       </c>
       <c r="H66" s="4" t="n">
-        <v>67</v>
+        <v>130</v>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -4508,21 +4508,21 @@
         </is>
       </c>
       <c r="K66" s="3" t="n">
-        <v>62.1</v>
+        <v>53.1</v>
       </c>
       <c r="L66" s="4" t="n">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N66" s="3" t="n">
-        <v>41.4</v>
+        <v>46.9</v>
       </c>
       <c r="O66" s="4" t="n">
-        <v>29</v>
+        <v>49</v>
       </c>
     </row>
     <row r="67">
@@ -4590,7 +4590,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -4599,25 +4599,25 @@
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>76.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G68" s="3" t="n">
-        <v>47.1</v>
+        <v>51.5</v>
       </c>
       <c r="H68" s="4" t="n">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-U</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -4626,10 +4626,10 @@
         </is>
       </c>
       <c r="K68" s="3" t="n">
-        <v>100</v>
+        <v>61.8</v>
       </c>
       <c r="L68" s="4" t="n">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
@@ -4637,10 +4637,10 @@
         </is>
       </c>
       <c r="N68" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="O68" s="4" t="n">
-        <v>9</v>
+        <v>34</v>
       </c>
     </row>
     <row r="69">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -4721,10 +4721,10 @@
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>53.8</v>
+        <v>64.3</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>80</v>
+        <v>143</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4732,14 +4732,14 @@
         </is>
       </c>
       <c r="G70" s="3" t="n">
-        <v>42.5</v>
+        <v>39.9</v>
       </c>
       <c r="H70" s="4" t="n">
-        <v>80</v>
+        <v>143</v>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -4748,10 +4748,10 @@
         </is>
       </c>
       <c r="K70" s="3" t="n">
-        <v>50</v>
+        <v>70.8</v>
       </c>
       <c r="L70" s="4" t="n">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
@@ -4759,10 +4759,10 @@
         </is>
       </c>
       <c r="N70" s="3" t="n">
-        <v>44.4</v>
+        <v>44.6</v>
       </c>
       <c r="O70" s="4" t="n">
-        <v>36</v>
+        <v>65</v>
       </c>
     </row>
     <row r="71">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -4782,25 +4782,25 @@
         </is>
       </c>
       <c r="D71" s="3" t="n">
-        <v>63.6</v>
+        <v>63</v>
       </c>
       <c r="E71" s="4" t="n">
-        <v>33</v>
+        <v>73</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G71" s="3" t="n">
-        <v>45.5</v>
+        <v>39.7</v>
       </c>
       <c r="H71" s="4" t="n">
-        <v>33</v>
+        <v>73</v>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>N-N-U-N</t>
+          <t>N-N-U-D</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -4809,21 +4809,21 @@
         </is>
       </c>
       <c r="K71" s="3" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="L71" s="4" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N71" s="3" t="n">
-        <v>40</v>
+        <v>43.8</v>
       </c>
       <c r="O71" s="4" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="72">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -4965,25 +4965,25 @@
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>46.4</v>
+        <v>64.3</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G74" s="3" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="H74" s="4" t="n">
         <v>42</v>
       </c>
-      <c r="H74" s="4" t="n">
-        <v>69</v>
-      </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-U</t>
+          <t>D-D-N-N</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -4992,10 +4992,10 @@
         </is>
       </c>
       <c r="K74" s="3" t="n">
-        <v>54.8</v>
+        <v>72.7</v>
       </c>
       <c r="L74" s="4" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
@@ -5003,10 +5003,10 @@
         </is>
       </c>
       <c r="N74" s="3" t="n">
-        <v>45.2</v>
+        <v>63.6</v>
       </c>
       <c r="O74" s="4" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
     </row>
     <row r="75">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -5148,10 +5148,10 @@
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>67.90000000000001</v>
+        <v>62.2</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>78</v>
+        <v>148</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -5159,14 +5159,14 @@
         </is>
       </c>
       <c r="G77" s="3" t="n">
-        <v>38.5</v>
+        <v>41.2</v>
       </c>
       <c r="H77" s="4" t="n">
-        <v>78</v>
+        <v>148</v>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -5175,10 +5175,10 @@
         </is>
       </c>
       <c r="K77" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>56.7</v>
       </c>
       <c r="L77" s="4" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
@@ -5186,10 +5186,10 @@
         </is>
       </c>
       <c r="N77" s="3" t="n">
-        <v>44.1</v>
+        <v>43.3</v>
       </c>
       <c r="O77" s="4" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
     </row>
     <row r="78">
@@ -5200,7 +5200,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -5209,48 +5209,48 @@
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>63.6</v>
+        <v>49.1</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>66</v>
+        <v>171</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G78" s="3" t="n">
-        <v>39.4</v>
+        <v>42.1</v>
       </c>
       <c r="H78" s="4" t="n">
-        <v>66</v>
+        <v>171</v>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-N</t>
+          <t>N-D-U-U</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K78" s="3" t="n">
-        <v>75</v>
+        <v>51.7</v>
       </c>
       <c r="L78" s="4" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N78" s="3" t="n">
-        <v>50</v>
+        <v>55.2</v>
       </c>
       <c r="O78" s="4" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
     </row>
     <row r="79">
@@ -5444,7 +5444,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -5453,25 +5453,25 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>80.40000000000001</v>
+        <v>75</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G82" s="3" t="n">
-        <v>43.5</v>
+        <v>43.8</v>
       </c>
       <c r="H82" s="4" t="n">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -5480,10 +5480,10 @@
         </is>
       </c>
       <c r="K82" s="3" t="n">
-        <v>72.2</v>
+        <v>57.1</v>
       </c>
       <c r="L82" s="4" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
@@ -5491,10 +5491,10 @@
         </is>
       </c>
       <c r="N82" s="3" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
       <c r="O82" s="4" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
     <row r="83">
@@ -5505,7 +5505,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -5514,10 +5514,10 @@
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>60.5</v>
+        <v>54.7</v>
       </c>
       <c r="E83" s="4" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -5525,14 +5525,14 @@
         </is>
       </c>
       <c r="G83" s="3" t="n">
-        <v>47.4</v>
+        <v>45.3</v>
       </c>
       <c r="H83" s="4" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-N</t>
+          <t>D-U-N-D</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
@@ -5541,21 +5541,21 @@
         </is>
       </c>
       <c r="K83" s="3" t="n">
-        <v>50</v>
+        <v>60.9</v>
       </c>
       <c r="L83" s="4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N83" s="3" t="n">
-        <v>40</v>
+        <v>56.5</v>
       </c>
       <c r="O83" s="4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="84">
@@ -5566,7 +5566,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -5575,25 +5575,25 @@
         </is>
       </c>
       <c r="D84" s="3" t="n">
-        <v>62</v>
+        <v>66.7</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G84" s="3" t="n">
-        <v>38</v>
+        <v>39.5</v>
       </c>
       <c r="H84" s="4" t="n">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-U</t>
+          <t>D-N-U-D</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -5602,21 +5602,21 @@
         </is>
       </c>
       <c r="K84" s="3" t="n">
-        <v>60</v>
+        <v>63.6</v>
       </c>
       <c r="L84" s="4" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N84" s="3" t="n">
-        <v>37.1</v>
+        <v>39.4</v>
       </c>
       <c r="O84" s="4" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="85">
@@ -5627,7 +5627,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -5636,25 +5636,25 @@
         </is>
       </c>
       <c r="D85" s="3" t="n">
-        <v>65.40000000000001</v>
+        <v>59.2</v>
       </c>
       <c r="E85" s="4" t="n">
-        <v>78</v>
+        <v>147</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G85" s="3" t="n">
-        <v>43.6</v>
+        <v>44.9</v>
       </c>
       <c r="H85" s="4" t="n">
-        <v>78</v>
+        <v>147</v>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-N</t>
+          <t>N-U-U-D</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
@@ -5663,21 +5663,21 @@
         </is>
       </c>
       <c r="K85" s="3" t="n">
-        <v>78.59999999999999</v>
+        <v>70.8</v>
       </c>
       <c r="L85" s="4" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N85" s="3" t="n">
-        <v>64.3</v>
+        <v>54.2</v>
       </c>
       <c r="O85" s="4" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="86">
@@ -5688,7 +5688,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -5697,37 +5697,37 @@
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>52.4</v>
+        <v>70.3</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>82</v>
+        <v>37</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G86" s="3" t="n">
-        <v>47.6</v>
+        <v>43.2</v>
       </c>
       <c r="H86" s="4" t="n">
-        <v>82</v>
+        <v>37</v>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-U</t>
+          <t>U-N-U-N</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K86" s="3" t="n">
-        <v>47.5</v>
+        <v>64.7</v>
       </c>
       <c r="L86" s="4" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
@@ -5735,10 +5735,10 @@
         </is>
       </c>
       <c r="N86" s="3" t="n">
-        <v>37.5</v>
+        <v>41.2</v>
       </c>
       <c r="O86" s="4" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
     </row>
     <row r="87">
@@ -5810,7 +5810,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -5819,10 +5819,10 @@
         </is>
       </c>
       <c r="D88" s="3" t="n">
-        <v>48.3</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="E88" s="4" t="n">
-        <v>174</v>
+        <v>87</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5830,14 +5830,14 @@
         </is>
       </c>
       <c r="G88" s="3" t="n">
-        <v>50.6</v>
+        <v>42.5</v>
       </c>
       <c r="H88" s="4" t="n">
-        <v>174</v>
+        <v>87</v>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-U</t>
+          <t>U-D-U-N</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
@@ -5846,10 +5846,10 @@
         </is>
       </c>
       <c r="K88" s="3" t="n">
-        <v>48.8</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="L88" s="4" t="n">
-        <v>84</v>
+        <v>35</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
@@ -5857,10 +5857,10 @@
         </is>
       </c>
       <c r="N88" s="3" t="n">
-        <v>51.2</v>
+        <v>42.9</v>
       </c>
       <c r="O88" s="4" t="n">
-        <v>84</v>
+        <v>35</v>
       </c>
     </row>
     <row r="89">
@@ -5871,7 +5871,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -5880,10 +5880,10 @@
         </is>
       </c>
       <c r="D89" s="3" t="n">
-        <v>48.5</v>
+        <v>56.1</v>
       </c>
       <c r="E89" s="4" t="n">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5891,14 +5891,14 @@
         </is>
       </c>
       <c r="G89" s="3" t="n">
-        <v>51.5</v>
+        <v>41.7</v>
       </c>
       <c r="H89" s="4" t="n">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-U</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
@@ -5907,10 +5907,10 @@
         </is>
       </c>
       <c r="K89" s="3" t="n">
-        <v>44.3</v>
+        <v>51.9</v>
       </c>
       <c r="L89" s="4" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
@@ -5918,10 +5918,10 @@
         </is>
       </c>
       <c r="N89" s="3" t="n">
-        <v>48.1</v>
+        <v>45.7</v>
       </c>
       <c r="O89" s="4" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="90">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -6063,10 +6063,10 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>64.09999999999999</v>
+        <v>64.7</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>39</v>
+        <v>85</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -6074,14 +6074,14 @@
         </is>
       </c>
       <c r="G92" s="3" t="n">
-        <v>46.2</v>
+        <v>43.5</v>
       </c>
       <c r="H92" s="4" t="n">
-        <v>39</v>
+        <v>85</v>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-N-U-D</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
@@ -6090,21 +6090,21 @@
         </is>
       </c>
       <c r="K92" s="3" t="n">
-        <v>66.7</v>
+        <v>54.3</v>
       </c>
       <c r="L92" s="4" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N92" s="3" t="n">
-        <v>46.7</v>
+        <v>51.4</v>
       </c>
       <c r="O92" s="4" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
     </row>
     <row r="93">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -6490,48 +6490,48 @@
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>64.8</v>
+        <v>45</v>
       </c>
       <c r="E99" s="4" t="n">
-        <v>71</v>
+        <v>149</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G99" s="3" t="n">
-        <v>45.1</v>
+        <v>46.3</v>
       </c>
       <c r="H99" s="4" t="n">
-        <v>71</v>
+        <v>149</v>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-N</t>
+          <t>N-D-U-U</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K99" s="3" t="n">
-        <v>53.8</v>
+        <v>50</v>
       </c>
       <c r="L99" s="4" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N99" s="3" t="n">
-        <v>46.2</v>
+        <v>50</v>
       </c>
       <c r="O99" s="4" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="100">
@@ -7022,7 +7022,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -7031,25 +7031,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>92.90000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I2" s="3" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-N</t>
+          <t>D-N-N-D</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -7061,18 +7061,18 @@
         <v>100</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P2" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="Q2" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -7164,7 +7164,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -7173,10 +7173,10 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>47.4</v>
+        <v>66.7</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -7184,14 +7184,14 @@
         </is>
       </c>
       <c r="I4" s="3" t="n">
-        <v>42.1</v>
+        <v>100</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-U</t>
+          <t>U-N-U-N</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -7200,21 +7200,21 @@
         </is>
       </c>
       <c r="M4" s="3" t="n">
-        <v>55.6</v>
+        <v>100</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P4" s="3" t="n">
-        <v>44.4</v>
+        <v>100</v>
       </c>
       <c r="Q4" s="4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -7235,7 +7235,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -7255,37 +7255,37 @@
         </is>
       </c>
       <c r="I5" s="3" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>U-D-U-D</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="N5" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="J5" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>U-D-U-N</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="N5" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="n">
-        <v>60</v>
-      </c>
       <c r="Q5" s="4" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
@@ -7519,7 +7519,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -7528,10 +7528,10 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>85</v>
+        <v>77.8</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -7539,37 +7539,37 @@
         </is>
       </c>
       <c r="I9" s="3" t="n">
-        <v>40</v>
+        <v>44.4</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-N</t>
+          <t>D-D-N-D</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M9" s="3" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P9" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -7661,7 +7661,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -7670,10 +7670,10 @@
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>61.9</v>
+        <v>76.8</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>21</v>
+        <v>56</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -7681,14 +7681,14 @@
         </is>
       </c>
       <c r="I11" s="3" t="n">
-        <v>38.1</v>
+        <v>37.5</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>21</v>
+        <v>56</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -7697,10 +7697,10 @@
         </is>
       </c>
       <c r="M11" s="3" t="n">
-        <v>60</v>
+        <v>81.8</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -7708,10 +7708,10 @@
         </is>
       </c>
       <c r="P11" s="3" t="n">
-        <v>50</v>
+        <v>59.1</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -7812,10 +7812,10 @@
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -7823,33 +7823,37 @@
         </is>
       </c>
       <c r="I13" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M13" s="3" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="n">
+        <v>83.3</v>
+      </c>
       <c r="N13" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P13" s="3" t="inlineStr"/>
+          <t>D/U</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="n">
+        <v>50</v>
+      </c>
       <c r="Q13" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
@@ -7870,7 +7874,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -7879,48 +7883,48 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>75</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I14" s="3" t="n">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-N</t>
+          <t>D-U-N-D</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M14" s="3" t="n">
-        <v>33.3</v>
+        <v>83.3</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P14" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
@@ -8154,7 +8158,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -8163,25 +8167,25 @@
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>86.7</v>
+        <v>77.8</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I18" s="3" t="n">
-        <v>46.7</v>
+        <v>44.4</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-N</t>
+          <t>U-D-N-D</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -8190,21 +8194,21 @@
         </is>
       </c>
       <c r="M18" s="3" t="n">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="P18" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -8296,7 +8300,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -8305,48 +8309,48 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>68.40000000000001</v>
+        <v>50</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I20" s="3" t="n">
-        <v>52.6</v>
+        <v>50</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M20" s="3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="P20" s="3" t="n">
-        <v>66.7</v>
+        <v>40</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -8367,7 +8371,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -8376,10 +8380,10 @@
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>57.1</v>
+        <v>60</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -8387,26 +8391,26 @@
         </is>
       </c>
       <c r="I21" s="3" t="n">
-        <v>42.9</v>
+        <v>40</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-N</t>
+          <t>U-N-U-D</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M21" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -8414,10 +8418,10 @@
         </is>
       </c>
       <c r="P21" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -8438,7 +8442,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -8447,10 +8451,10 @@
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -8458,37 +8462,33 @@
         </is>
       </c>
       <c r="I22" s="3" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-U</t>
+          <t>N-N-D-D</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr"/>
       <c r="N22" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P22" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr"/>
       <c r="Q22" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -8518,10 +8518,10 @@
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>66.7</v>
+        <v>46.2</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -8529,14 +8529,14 @@
         </is>
       </c>
       <c r="I23" s="3" t="n">
-        <v>66.7</v>
+        <v>53.8</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -8545,21 +8545,21 @@
         </is>
       </c>
       <c r="M23" s="3" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P23" s="3" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -8722,7 +8722,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -8731,25 +8731,25 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>75</v>
+        <v>54.5</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I26" s="3" t="n">
-        <v>100</v>
+        <v>39.4</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-N</t>
+          <t>N-D-U-D</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -8758,21 +8758,21 @@
         </is>
       </c>
       <c r="M26" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P26" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27">
@@ -8793,57 +8793,57 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>80</v>
+        <v>42.9</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I27" s="3" t="n">
-        <v>60</v>
+        <v>57.1</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M27" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="N27" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="N27" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>D/N/U</t>
-        </is>
-      </c>
-      <c r="P27" s="3" t="n">
-        <v>33.3</v>
-      </c>
       <c r="Q27" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -8864,7 +8864,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -8873,10 +8873,10 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>83.3</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -8884,14 +8884,14 @@
         </is>
       </c>
       <c r="I28" s="3" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-N</t>
+          <t>U-D-N-D</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -8900,10 +8900,10 @@
         </is>
       </c>
       <c r="M28" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -8911,10 +8911,10 @@
         </is>
       </c>
       <c r="P28" s="3" t="n">
-        <v>66.7</v>
+        <v>57.1</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -8944,48 +8944,48 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I29" s="3" t="n">
         <v>66.7</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M29" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P29" s="3" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -9077,7 +9077,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -9089,7 +9089,7 @@
         <v>66.7</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -9097,26 +9097,26 @@
         </is>
       </c>
       <c r="I31" s="3" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="J31" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>U-U-U-U</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="n">
         <v>66.7</v>
       </c>
-      <c r="J31" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>U-U-U-N</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M31" s="3" t="n">
-        <v>100</v>
-      </c>
       <c r="N31" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -9124,10 +9124,10 @@
         </is>
       </c>
       <c r="P31" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32">
@@ -9148,7 +9148,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -9157,10 +9157,10 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>83.3</v>
+        <v>84</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -9168,14 +9168,14 @@
         </is>
       </c>
       <c r="I32" s="3" t="n">
-        <v>41.7</v>
+        <v>48</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-N</t>
+          <t>N-D-U-U</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -9184,10 +9184,10 @@
         </is>
       </c>
       <c r="M32" s="3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -9198,7 +9198,7 @@
         <v>50</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
@@ -9290,7 +9290,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -9299,10 +9299,10 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>91.7</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -9310,37 +9310,37 @@
         </is>
       </c>
       <c r="I34" s="3" t="n">
-        <v>58.3</v>
+        <v>55.6</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>N-N-U-U</t>
+          <t>N-N-U-N</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M34" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P34" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -9570,7 +9570,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -9579,25 +9579,25 @@
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>68.2</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I38" s="3" t="n">
-        <v>52.9</v>
+        <v>36.4</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-N</t>
+          <t>N-D-U-D</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -9606,21 +9606,21 @@
         </is>
       </c>
       <c r="M38" s="3" t="n">
-        <v>50</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P38" s="3" t="n">
-        <v>50</v>
+        <v>42.9</v>
       </c>
       <c r="Q38" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39">
@@ -9712,7 +9712,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -9739,30 +9739,26 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-N-U-U</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M40" s="3" t="n">
-        <v>75</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr"/>
       <c r="N40" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P40" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr"/>
       <c r="Q40" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -9984,7 +9980,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -9993,25 +9989,25 @@
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>87.5</v>
+        <v>63.6</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I44" s="3" t="n">
-        <v>87.5</v>
+        <v>81.8</v>
       </c>
       <c r="J44" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
@@ -10020,21 +10016,21 @@
         </is>
       </c>
       <c r="M44" s="3" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="N44" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P44" s="3" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="Q44" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45">
@@ -10122,7 +10118,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -10131,25 +10127,25 @@
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>50</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I46" s="3" t="n">
-        <v>50</v>
+        <v>53.8</v>
       </c>
       <c r="J46" s="4" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-U</t>
+          <t>U-D-U-N</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -10158,21 +10154,21 @@
         </is>
       </c>
       <c r="M46" s="3" t="n">
-        <v>57.1</v>
+        <v>75</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P46" s="3" t="n">
-        <v>35.7</v>
+        <v>62.5</v>
       </c>
       <c r="Q46" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="47">
@@ -10264,34 +10260,34 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>87.5</v>
+        <v>53.8</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I48" s="3" t="n">
-        <v>62.5</v>
+        <v>61.5</v>
       </c>
       <c r="J48" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-N</t>
+          <t>U-D-N-U</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
@@ -10300,18 +10296,18 @@
         </is>
       </c>
       <c r="M48" s="3" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="N48" s="4" t="n">
         <v>5</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P48" s="3" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="Q48" s="4" t="n">
         <v>5</v>
@@ -10406,7 +10402,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -10415,25 +10411,25 @@
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>69</v>
+        <v>77.8</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I50" s="3" t="n">
-        <v>37.9</v>
+        <v>50</v>
       </c>
       <c r="J50" s="4" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
@@ -10442,14 +10438,14 @@
         </is>
       </c>
       <c r="M50" s="3" t="n">
-        <v>85.7</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="N50" s="4" t="n">
         <v>7</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P50" s="3" t="n">
@@ -10477,7 +10473,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -10489,41 +10485,45 @@
         <v>100</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I51" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J51" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>N-N-N-N</t>
+          <t>N-N-N-D</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M51" s="3" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="N51" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P51" s="3" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P51" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="Q51" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -10615,7 +10615,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -10624,48 +10624,48 @@
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>55.6</v>
+        <v>50</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I53" s="3" t="n">
-        <v>44.4</v>
+        <v>50</v>
       </c>
       <c r="J53" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-U</t>
+          <t>U-D-D-N</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="M53" s="3" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="N53" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="P53" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="Q53" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -10828,34 +10828,34 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="F56" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="G56" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="G56" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I56" s="3" t="n">
-        <v>55.6</v>
-      </c>
       <c r="J56" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-D</t>
+          <t>D-U-U-N</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
@@ -10867,18 +10867,18 @@
         <v>100</v>
       </c>
       <c r="N56" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P56" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q56" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -11050,25 +11050,25 @@
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>73.8</v>
+        <v>62.5</v>
       </c>
       <c r="G59" s="4" t="n">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I59" s="3" t="n">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="J59" s="4" t="n">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-U</t>
+          <t>N-U-D-N</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
@@ -11077,21 +11077,21 @@
         </is>
       </c>
       <c r="M59" s="3" t="n">
-        <v>57.1</v>
+        <v>100</v>
       </c>
       <c r="N59" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P59" s="3" t="n">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="Q59" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -11112,7 +11112,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -11124,7 +11124,7 @@
         <v>53.3</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -11132,14 +11132,14 @@
         </is>
       </c>
       <c r="I60" s="3" t="n">
-        <v>56.7</v>
+        <v>40</v>
       </c>
       <c r="J60" s="4" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
@@ -11148,21 +11148,21 @@
         </is>
       </c>
       <c r="M60" s="3" t="n">
-        <v>55.6</v>
+        <v>42.9</v>
       </c>
       <c r="N60" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P60" s="3" t="n">
-        <v>44.4</v>
+        <v>42.9</v>
       </c>
       <c r="Q60" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61">
@@ -11325,7 +11325,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -11334,10 +11334,10 @@
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>50</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -11345,26 +11345,26 @@
         </is>
       </c>
       <c r="I63" s="3" t="n">
-        <v>50</v>
+        <v>44.4</v>
       </c>
       <c r="J63" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-N</t>
+          <t>U-U-D-D</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M63" s="3" t="n">
-        <v>33.3</v>
+        <v>80</v>
       </c>
       <c r="N63" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
@@ -11372,10 +11372,10 @@
         </is>
       </c>
       <c r="P63" s="3" t="n">
-        <v>66.7</v>
+        <v>80</v>
       </c>
       <c r="Q63" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64">
@@ -11396,43 +11396,43 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>41.9</v>
+        <v>90</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I64" s="3" t="n">
-        <v>58.1</v>
+        <v>60</v>
       </c>
       <c r="J64" s="4" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-U</t>
+          <t>N-D-U-N</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M64" s="3" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="N64" s="4" t="n">
         <v>3</v>
@@ -11443,7 +11443,7 @@
         </is>
       </c>
       <c r="P64" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="Q64" s="4" t="n">
         <v>3</v>
@@ -11467,7 +11467,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -11476,25 +11476,25 @@
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>77.8</v>
+        <v>72.7</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I65" s="3" t="n">
-        <v>44.4</v>
+        <v>45.5</v>
       </c>
       <c r="J65" s="4" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
@@ -11503,21 +11503,21 @@
         </is>
       </c>
       <c r="M65" s="3" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="N65" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P65" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="Q65" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66">
@@ -11538,7 +11538,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -11547,25 +11547,25 @@
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>91.7</v>
+        <v>41.2</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I66" s="3" t="n">
-        <v>41.7</v>
+        <v>47.1</v>
       </c>
       <c r="J66" s="4" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
@@ -11574,7 +11574,7 @@
         </is>
       </c>
       <c r="M66" s="3" t="n">
-        <v>85.7</v>
+        <v>57.1</v>
       </c>
       <c r="N66" s="4" t="n">
         <v>7</v>
@@ -11585,7 +11585,7 @@
         </is>
       </c>
       <c r="P66" s="3" t="n">
-        <v>57.1</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="Q66" s="4" t="n">
         <v>7</v>
@@ -11676,7 +11676,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -11685,25 +11685,25 @@
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>100</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I68" s="3" t="n">
-        <v>100</v>
+        <v>57.1</v>
       </c>
       <c r="J68" s="4" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-U</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
@@ -11712,21 +11712,21 @@
         </is>
       </c>
       <c r="M68" s="3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="N68" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P68" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q68" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="69">
@@ -11814,7 +11814,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -11823,25 +11823,25 @@
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>61.5</v>
+        <v>73.7</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I70" s="3" t="n">
-        <v>46.2</v>
+        <v>42.1</v>
       </c>
       <c r="J70" s="4" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
@@ -11850,21 +11850,21 @@
         </is>
       </c>
       <c r="M70" s="3" t="n">
-        <v>66.7</v>
+        <v>80</v>
       </c>
       <c r="N70" s="4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P70" s="3" t="n">
         <v>50</v>
       </c>
       <c r="Q70" s="4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="71">
@@ -11885,7 +11885,7 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -11894,10 +11894,10 @@
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="G71" s="4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
@@ -11908,23 +11908,23 @@
         <v>50</v>
       </c>
       <c r="J71" s="4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>N-N-U-N</t>
+          <t>N-N-U-D</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="M71" s="3" t="n">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="N71" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
@@ -11932,10 +11932,10 @@
         </is>
       </c>
       <c r="P71" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="Q71" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
@@ -12098,7 +12098,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -12107,25 +12107,25 @@
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>46.2</v>
+        <v>77.8</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I74" s="3" t="n">
-        <v>38.5</v>
+        <v>66.7</v>
       </c>
       <c r="J74" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-U</t>
+          <t>D-D-N-N</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
@@ -12134,21 +12134,21 @@
         </is>
       </c>
       <c r="M74" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="N74" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P74" s="3" t="n">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="Q74" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75">
@@ -12303,7 +12303,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -12312,25 +12312,25 @@
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>79.2</v>
+        <v>66.7</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I77" s="3" t="n">
-        <v>45.8</v>
+        <v>48.1</v>
       </c>
       <c r="J77" s="4" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
@@ -12339,21 +12339,21 @@
         </is>
       </c>
       <c r="M77" s="3" t="n">
-        <v>72.7</v>
+        <v>50</v>
       </c>
       <c r="N77" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="P77" s="3" t="n">
-        <v>54.5</v>
+        <v>41.7</v>
       </c>
       <c r="Q77" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="78">
@@ -12374,7 +12374,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -12383,25 +12383,25 @@
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>77.8</v>
+        <v>42.4</v>
       </c>
       <c r="G78" s="4" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I78" s="3" t="n">
-        <v>44.4</v>
+        <v>45.5</v>
       </c>
       <c r="J78" s="4" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-N</t>
+          <t>N-D-U-U</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
@@ -12410,21 +12410,21 @@
         </is>
       </c>
       <c r="M78" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N78" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P78" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q78" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="79">
@@ -12658,7 +12658,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -12670,34 +12670,34 @@
         <v>75</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I82" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J82" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>D-D-D-N</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
           <t>N/U</t>
         </is>
       </c>
-      <c r="I82" s="3" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="J82" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="K82" s="2" t="inlineStr">
-        <is>
-          <t>D-D-D-U</t>
-        </is>
-      </c>
-      <c r="L82" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="M82" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="N82" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
@@ -12705,10 +12705,10 @@
         </is>
       </c>
       <c r="P82" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="Q82" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -12729,19 +12729,19 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F83" s="3" t="n">
-        <v>70</v>
+        <v>69.2</v>
       </c>
       <c r="G83" s="4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
@@ -12749,37 +12749,37 @@
         </is>
       </c>
       <c r="I83" s="3" t="n">
-        <v>60</v>
+        <v>46.2</v>
       </c>
       <c r="J83" s="4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-N</t>
+          <t>D-U-N-D</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M83" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>75</v>
       </c>
       <c r="N83" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P83" s="3" t="n">
-        <v>57.1</v>
+        <v>75</v>
       </c>
       <c r="Q83" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="84">
@@ -12800,7 +12800,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -12809,10 +12809,10 @@
         </is>
       </c>
       <c r="F84" s="3" t="n">
-        <v>68.2</v>
+        <v>86.7</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -12820,37 +12820,37 @@
         </is>
       </c>
       <c r="I84" s="3" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="J84" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>D-N-U-D</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M84" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="N84" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P84" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="J84" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="K84" s="2" t="inlineStr">
-        <is>
-          <t>D-N-U-U</t>
-        </is>
-      </c>
-      <c r="L84" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M84" s="3" t="n">
-        <v>54.5</v>
-      </c>
-      <c r="N84" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="O84" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P84" s="3" t="n">
-        <v>45.5</v>
-      </c>
       <c r="Q84" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="85">
@@ -12871,7 +12871,7 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -12880,44 +12880,48 @@
         </is>
       </c>
       <c r="F85" s="3" t="n">
-        <v>50</v>
+        <v>61.9</v>
       </c>
       <c r="G85" s="4" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I85" s="3" t="n">
-        <v>37.5</v>
+        <v>52.4</v>
       </c>
       <c r="J85" s="4" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-N</t>
+          <t>N-U-U-D</t>
         </is>
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M85" s="3" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M85" s="3" t="n">
+        <v>66.7</v>
+      </c>
       <c r="N85" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P85" s="3" t="inlineStr"/>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P85" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="Q85" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86">
@@ -12938,7 +12942,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -12947,37 +12951,37 @@
         </is>
       </c>
       <c r="F86" s="3" t="n">
-        <v>47.6</v>
+        <v>100</v>
       </c>
       <c r="G86" s="4" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I86" s="3" t="n">
-        <v>42.9</v>
+        <v>100</v>
       </c>
       <c r="J86" s="4" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-U</t>
+          <t>U-N-U-N</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M86" s="3" t="n">
-        <v>62.5</v>
+        <v>100</v>
       </c>
       <c r="N86" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
@@ -12985,10 +12989,10 @@
         </is>
       </c>
       <c r="P86" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q86" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
@@ -13080,7 +13084,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -13089,25 +13093,25 @@
         </is>
       </c>
       <c r="F88" s="3" t="n">
-        <v>61</v>
+        <v>87.5</v>
       </c>
       <c r="G88" s="4" t="n">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I88" s="3" t="n">
-        <v>48.8</v>
+        <v>50</v>
       </c>
       <c r="J88" s="4" t="n">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-U</t>
+          <t>U-D-U-N</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
@@ -13116,21 +13120,21 @@
         </is>
       </c>
       <c r="M88" s="3" t="n">
-        <v>58.3</v>
+        <v>90</v>
       </c>
       <c r="N88" s="4" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="P88" s="3" t="n">
-        <v>45.8</v>
+        <v>40</v>
       </c>
       <c r="Q88" s="4" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
     </row>
     <row r="89">
@@ -13151,57 +13155,57 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F89" s="3" t="n">
-        <v>52.6</v>
+        <v>64</v>
       </c>
       <c r="G89" s="4" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I89" s="3" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="J89" s="4" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-U</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M89" s="3" t="n">
-        <v>55</v>
+        <v>58.3</v>
       </c>
       <c r="N89" s="4" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="P89" s="3" t="n">
-        <v>60</v>
+        <v>41.7</v>
       </c>
       <c r="Q89" s="4" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="90">
@@ -13364,57 +13368,57 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F92" s="3" t="n">
-        <v>37.5</v>
+        <v>63.6</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I92" s="3" t="n">
-        <v>50</v>
+        <v>36.4</v>
       </c>
       <c r="J92" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-N-U-D</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M92" s="3" t="n">
         <v>50</v>
       </c>
       <c r="N92" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P92" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q92" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="93">
@@ -13861,7 +13865,7 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -13870,48 +13874,48 @@
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>76.2</v>
+        <v>46.4</v>
       </c>
       <c r="G99" s="4" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I99" s="3" t="n">
-        <v>52.4</v>
+        <v>42.9</v>
       </c>
       <c r="J99" s="4" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-N</t>
+          <t>N-D-U-U</t>
         </is>
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="M99" s="3" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="N99" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P99" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="Q99" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="100">

--- a/BIS_tr.xlsx
+++ b/BIS_tr.xlsx
@@ -629,7 +629,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>68.09999999999999</v>
+        <v>53.7</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -649,14 +649,14 @@
         </is>
       </c>
       <c r="G3" s="3" t="n">
-        <v>38.3</v>
+        <v>43.3</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-N</t>
+          <t>D-D-N-D</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -665,10 +665,10 @@
         </is>
       </c>
       <c r="K3" s="3" t="n">
-        <v>65</v>
+        <v>47.6</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="N3" s="3" t="n">
-        <v>45</v>
+        <v>42.9</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
@@ -690,7 +690,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -699,37 +699,37 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>53.5</v>
+        <v>52.7</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G4" s="3" t="n">
-        <v>46.5</v>
+        <v>39.2</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-N</t>
+          <t>U-N-U-D</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K4" s="3" t="n">
-        <v>57.1</v>
+        <v>59.4</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
@@ -737,10 +737,10 @@
         </is>
       </c>
       <c r="N4" s="3" t="n">
-        <v>50</v>
+        <v>40.6</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1248,25 +1248,25 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="n">
         <v>53.3</v>
       </c>
-      <c r="E13" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="n">
-        <v>57.8</v>
-      </c>
       <c r="H13" s="4" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-D</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1275,21 +1275,21 @@
         </is>
       </c>
       <c r="K13" s="3" t="n">
-        <v>52</v>
+        <v>76.5</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N13" s="3" t="n">
-        <v>60</v>
+        <v>64.7</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1858,25 +1858,25 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>72.09999999999999</v>
+        <v>49.2</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G23" s="3" t="n">
-        <v>38.2</v>
+        <v>45.8</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-D</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1885,21 +1885,21 @@
         </is>
       </c>
       <c r="K23" s="3" t="n">
-        <v>73.5</v>
+        <v>56.5</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N23" s="3" t="n">
-        <v>38.2</v>
+        <v>47.8</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1919,10 +1919,10 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>62.5</v>
+        <v>61.1</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>32</v>
+        <v>72</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1930,26 +1930,26 @@
         </is>
       </c>
       <c r="G24" s="3" t="n">
-        <v>43.8</v>
+        <v>45.8</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>32</v>
+        <v>72</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K24" s="3" t="n">
-        <v>50</v>
+        <v>51.6</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
@@ -1957,10 +1957,10 @@
         </is>
       </c>
       <c r="N24" s="3" t="n">
-        <v>50</v>
+        <v>45.2</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2041,7 +2041,7 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>47.3</v>
+        <v>59.9</v>
       </c>
       <c r="E26" s="4" t="n">
         <v>167</v>
@@ -2052,14 +2052,14 @@
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>44.3</v>
+        <v>45.5</v>
       </c>
       <c r="H26" s="4" t="n">
         <v>167</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-D</t>
+          <t>N-D-U-U</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -2068,21 +2068,21 @@
         </is>
       </c>
       <c r="K26" s="3" t="n">
-        <v>47.1</v>
+        <v>58.1</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N26" s="3" t="n">
-        <v>50</v>
+        <v>45.2</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>41.8</v>
+        <v>50.6</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>67</v>
+        <v>166</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2296,37 +2296,37 @@
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>44.8</v>
+        <v>42.8</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>67</v>
+        <v>166</v>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K30" s="3" t="n">
-        <v>50</v>
+        <v>53.3</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N30" s="3" t="n">
-        <v>46.7</v>
+        <v>40</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2407,25 +2407,25 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>58.3</v>
+        <v>65.5</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>144</v>
+        <v>119</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G32" s="3" t="n">
-        <v>43.1</v>
+        <v>46.2</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>144</v>
+        <v>119</v>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-U</t>
+          <t>N-D-U-D</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -2434,21 +2434,21 @@
         </is>
       </c>
       <c r="K32" s="3" t="n">
-        <v>56</v>
+        <v>62.9</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N32" s="3" t="n">
-        <v>44</v>
+        <v>42.9</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
     </row>
     <row r="33">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2468,25 +2468,25 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>76.09999999999999</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>71</v>
+        <v>159</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G33" s="3" t="n">
-        <v>38</v>
+        <v>47.2</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>71</v>
+        <v>159</v>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-N</t>
+          <t>N-U-U-D</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -2495,21 +2495,21 @@
         </is>
       </c>
       <c r="K33" s="3" t="n">
-        <v>87.5</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N33" s="3" t="n">
-        <v>54.2</v>
+        <v>43.2</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
     </row>
     <row r="34">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2651,25 +2651,25 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>47.6</v>
+        <v>83.3</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>42.9</v>
+        <v>41.7</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-U</t>
+          <t>U-N-D-N</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -2678,10 +2678,10 @@
         </is>
       </c>
       <c r="K36" s="3" t="n">
-        <v>42.9</v>
+        <v>75</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="N36" s="3" t="n">
-        <v>57.1</v>
+        <v>75</v>
       </c>
       <c r="O36" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2834,10 +2834,10 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>58</v>
+        <v>63.5</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2845,14 +2845,14 @@
         </is>
       </c>
       <c r="G39" s="3" t="n">
-        <v>44.1</v>
+        <v>43.4</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-U</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -2861,21 +2861,21 @@
         </is>
       </c>
       <c r="K39" s="3" t="n">
-        <v>60.3</v>
+        <v>58.7</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N39" s="3" t="n">
-        <v>43.1</v>
+        <v>46</v>
       </c>
       <c r="O39" s="4" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="40">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2895,25 +2895,25 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>77.5</v>
+        <v>64.7</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G40" s="3" t="n">
-        <v>55</v>
+        <v>41.2</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-U</t>
+          <t>D-N-U-D</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -2922,21 +2922,21 @@
         </is>
       </c>
       <c r="K40" s="3" t="n">
-        <v>80</v>
+        <v>52.9</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N40" s="3" t="n">
-        <v>60</v>
+        <v>47.1</v>
       </c>
       <c r="O40" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="41">
@@ -3008,19 +3008,19 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>37.5</v>
+        <v>63.6</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -3028,37 +3028,37 @@
         </is>
       </c>
       <c r="G42" s="3" t="n">
-        <v>62.5</v>
+        <v>45.5</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-N-U-D</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K42" s="3" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="L42" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="L42" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="N42" s="3" t="n">
-        <v>75</v>
-      </c>
       <c r="O42" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3078,25 +3078,25 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>64.7</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G43" s="3" t="n">
-        <v>41.2</v>
+        <v>54.8</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-N</t>
+          <t>U-D-N-D</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -3105,21 +3105,21 @@
         </is>
       </c>
       <c r="K43" s="3" t="n">
-        <v>55.6</v>
+        <v>73.3</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N43" s="3" t="n">
-        <v>55.6</v>
+        <v>60</v>
       </c>
       <c r="O43" s="4" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="44">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3200,10 +3200,10 @@
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>60.6</v>
+        <v>49.4</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>33</v>
+        <v>77</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -3211,14 +3211,14 @@
         </is>
       </c>
       <c r="G45" s="3" t="n">
-        <v>45.5</v>
+        <v>48.1</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>33</v>
+        <v>77</v>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>N-N-U-N</t>
+          <t>N-N-U-D</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -3227,21 +3227,21 @@
         </is>
       </c>
       <c r="K45" s="3" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N45" s="3" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="O45" s="4" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="46">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3261,25 +3261,25 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>60</v>
+        <v>51.6</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>65</v>
+        <v>153</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G46" s="3" t="n">
-        <v>47.7</v>
+        <v>41.8</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>65</v>
+        <v>153</v>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-U</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -3288,21 +3288,21 @@
         </is>
       </c>
       <c r="K46" s="3" t="n">
-        <v>63</v>
+        <v>53.2</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N46" s="3" t="n">
-        <v>51.9</v>
+        <v>37.1</v>
       </c>
       <c r="O46" s="4" t="n">
-        <v>27</v>
+        <v>62</v>
       </c>
     </row>
     <row r="47">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -3444,25 +3444,25 @@
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>57.1</v>
+        <v>51</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G49" s="3" t="n">
-        <v>36.4</v>
+        <v>45.8</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -3471,21 +3471,21 @@
         </is>
       </c>
       <c r="K49" s="3" t="n">
-        <v>65.59999999999999</v>
+        <v>54.4</v>
       </c>
       <c r="L49" s="4" t="n">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N49" s="3" t="n">
-        <v>37.5</v>
+        <v>52.9</v>
       </c>
       <c r="O49" s="4" t="n">
-        <v>32</v>
+        <v>68</v>
       </c>
     </row>
     <row r="50">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -3505,10 +3505,10 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>72</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>82</v>
+        <v>137</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3516,14 +3516,14 @@
         </is>
       </c>
       <c r="G50" s="3" t="n">
-        <v>48.8</v>
+        <v>48.2</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>82</v>
+        <v>137</v>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -3532,10 +3532,10 @@
         </is>
       </c>
       <c r="K50" s="3" t="n">
-        <v>69.7</v>
+        <v>70.3</v>
       </c>
       <c r="L50" s="4" t="n">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
@@ -3543,10 +3543,10 @@
         </is>
       </c>
       <c r="N50" s="3" t="n">
-        <v>51.5</v>
+        <v>46.9</v>
       </c>
       <c r="O50" s="4" t="n">
-        <v>33</v>
+        <v>64</v>
       </c>
     </row>
     <row r="51">
@@ -3557,7 +3557,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>N-N-D</t>
+          <t>N-N-N</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -3566,14 +3566,14 @@
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>100</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="E51" s="4" t="n">
         <v>9</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G51" s="3" t="n">
@@ -3584,30 +3584,30 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>N-N-N-D</t>
+          <t>N-N-N-N</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K51" s="3" t="n">
         <v>100</v>
       </c>
       <c r="L51" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N51" s="3" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="O51" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3688,10 +3688,10 @@
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>55</v>
+        <v>50.9</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3699,14 +3699,14 @@
         </is>
       </c>
       <c r="G53" s="3" t="n">
-        <v>50</v>
+        <v>49.1</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -3715,21 +3715,21 @@
         </is>
       </c>
       <c r="K53" s="3" t="n">
-        <v>55.6</v>
+        <v>72.7</v>
       </c>
       <c r="L53" s="4" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N53" s="3" t="n">
-        <v>55.6</v>
+        <v>59.1</v>
       </c>
       <c r="O53" s="4" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
     </row>
     <row r="54">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3871,25 +3871,25 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>55.6</v>
+        <v>47.4</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G56" s="3" t="n">
-        <v>38.9</v>
+        <v>47.4</v>
       </c>
       <c r="H56" s="4" t="n">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -3898,21 +3898,21 @@
         </is>
       </c>
       <c r="K56" s="3" t="n">
-        <v>75</v>
+        <v>54.5</v>
       </c>
       <c r="L56" s="4" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N56" s="3" t="n">
         <v>50</v>
       </c>
       <c r="O56" s="4" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="57">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3932,25 +3932,25 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>74.5</v>
+        <v>60.9</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>47</v>
+        <v>92</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G57" s="3" t="n">
-        <v>46.8</v>
+        <v>41.3</v>
       </c>
       <c r="H57" s="4" t="n">
-        <v>47</v>
+        <v>92</v>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-N</t>
+          <t>U-D-N-D</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -3959,21 +3959,21 @@
         </is>
       </c>
       <c r="K57" s="3" t="n">
-        <v>81.2</v>
+        <v>67.5</v>
       </c>
       <c r="L57" s="4" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N57" s="3" t="n">
-        <v>50</v>
+        <v>42.5</v>
       </c>
       <c r="O57" s="4" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="58">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3993,37 +3993,37 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>57.4</v>
+        <v>61.8</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>94</v>
+        <v>68</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G58" s="3" t="n">
-        <v>50</v>
+        <v>44.1</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>94</v>
+        <v>68</v>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-U</t>
+          <t>N-D-U-D</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="K58" s="3" t="n">
-        <v>87.5</v>
+        <v>44.4</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
@@ -4031,10 +4031,10 @@
         </is>
       </c>
       <c r="N58" s="3" t="n">
-        <v>56.2</v>
+        <v>44.4</v>
       </c>
       <c r="O58" s="4" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="59">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4054,10 +4054,10 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>71.2</v>
+        <v>75.2</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>66</v>
+        <v>129</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -4065,14 +4065,14 @@
         </is>
       </c>
       <c r="G59" s="3" t="n">
-        <v>42.4</v>
+        <v>42.6</v>
       </c>
       <c r="H59" s="4" t="n">
-        <v>66</v>
+        <v>129</v>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-N</t>
+          <t>N-U-D-D</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -4081,21 +4081,21 @@
         </is>
       </c>
       <c r="K59" s="3" t="n">
-        <v>91.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="L59" s="4" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N59" s="3" t="n">
-        <v>50</v>
+        <v>47.8</v>
       </c>
       <c r="O59" s="4" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="60">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4115,10 +4115,10 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>64.8</v>
+        <v>59.2</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>71</v>
+        <v>147</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -4126,14 +4126,14 @@
         </is>
       </c>
       <c r="G60" s="3" t="n">
-        <v>52.1</v>
+        <v>40.1</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>71</v>
+        <v>147</v>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-U</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -4142,21 +4142,21 @@
         </is>
       </c>
       <c r="K60" s="3" t="n">
-        <v>67.7</v>
+        <v>62.3</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N60" s="3" t="n">
-        <v>45.2</v>
+        <v>43.4</v>
       </c>
       <c r="O60" s="4" t="n">
-        <v>31</v>
+        <v>53</v>
       </c>
     </row>
     <row r="61">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4176,48 +4176,48 @@
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>57.1</v>
+        <v>62.5</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G61" s="3" t="n">
-        <v>57.1</v>
+        <v>50</v>
       </c>
       <c r="H61" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-N</t>
+          <t>D-N-N-D</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K61" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="L61" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="L61" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M61" s="2" t="inlineStr">
-        <is>
-          <t>D/U</t>
-        </is>
-      </c>
-      <c r="N61" s="3" t="n">
-        <v>50</v>
-      </c>
       <c r="O61" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="62">
@@ -4228,7 +4228,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4237,25 +4237,25 @@
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>60.8</v>
+        <v>58.9</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>51</v>
+        <v>124</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G62" s="3" t="n">
-        <v>43.1</v>
+        <v>44.4</v>
       </c>
       <c r="H62" s="4" t="n">
-        <v>51</v>
+        <v>124</v>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-N</t>
+          <t>N-D-D-D</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -4264,21 +4264,21 @@
         </is>
       </c>
       <c r="K62" s="3" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="L62" s="4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N62" s="3" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="O62" s="4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="63">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -4359,25 +4359,25 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>59.7</v>
+        <v>44.9</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>67</v>
+        <v>185</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G64" s="3" t="n">
-        <v>40.3</v>
+        <v>49.2</v>
       </c>
       <c r="H64" s="4" t="n">
-        <v>67</v>
+        <v>185</v>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-N</t>
+          <t>N-D-U-D</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -4386,21 +4386,21 @@
         </is>
       </c>
       <c r="K64" s="3" t="n">
-        <v>87.5</v>
+        <v>58.6</v>
       </c>
       <c r="L64" s="4" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N64" s="3" t="n">
-        <v>75</v>
+        <v>58.6</v>
       </c>
       <c r="O64" s="4" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
     </row>
     <row r="65">
@@ -4472,7 +4472,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -4481,25 +4481,25 @@
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>53.8</v>
+        <v>62.7</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>130</v>
+        <v>67</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G66" s="3" t="n">
-        <v>40.8</v>
+        <v>43.3</v>
       </c>
       <c r="H66" s="4" t="n">
-        <v>130</v>
+        <v>67</v>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-D</t>
+          <t>U-U-U-N</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -4508,21 +4508,21 @@
         </is>
       </c>
       <c r="K66" s="3" t="n">
-        <v>53.1</v>
+        <v>62.1</v>
       </c>
       <c r="L66" s="4" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N66" s="3" t="n">
-        <v>46.9</v>
+        <v>41.4</v>
       </c>
       <c r="O66" s="4" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="67">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -4965,10 +4965,10 @@
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>64.3</v>
+        <v>60</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4976,14 +4976,14 @@
         </is>
       </c>
       <c r="G74" s="3" t="n">
-        <v>54.8</v>
+        <v>49.1</v>
       </c>
       <c r="H74" s="4" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-N</t>
+          <t>D-D-N-D</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -4992,21 +4992,21 @@
         </is>
       </c>
       <c r="K74" s="3" t="n">
-        <v>72.7</v>
+        <v>56.2</v>
       </c>
       <c r="L74" s="4" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N74" s="3" t="n">
-        <v>63.6</v>
+        <v>37.5</v>
       </c>
       <c r="O74" s="4" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="75">
@@ -5017,7 +5017,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5026,25 +5026,25 @@
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>80</v>
+        <v>72.5</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G75" s="3" t="n">
-        <v>50</v>
+        <v>52.9</v>
       </c>
       <c r="H75" s="4" t="n">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-N</t>
+          <t>N-D-U-D</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
@@ -5053,21 +5053,21 @@
         </is>
       </c>
       <c r="K75" s="3" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="L75" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="N75" s="3" t="n">
-        <v>75</v>
+        <v>33.3</v>
       </c>
       <c r="O75" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76">
@@ -5261,7 +5261,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -5270,10 +5270,10 @@
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>73.7</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -5281,14 +5281,14 @@
         </is>
       </c>
       <c r="G79" s="3" t="n">
-        <v>38.6</v>
+        <v>42.5</v>
       </c>
       <c r="H79" s="4" t="n">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>N-N-U-N</t>
+          <t>N-N-U-D</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -5297,10 +5297,10 @@
         </is>
       </c>
       <c r="K79" s="3" t="n">
-        <v>61.1</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="L79" s="4" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
@@ -5308,10 +5308,10 @@
         </is>
       </c>
       <c r="N79" s="3" t="n">
-        <v>44.4</v>
+        <v>43.5</v>
       </c>
       <c r="O79" s="4" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="80">
@@ -5322,19 +5322,19 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>45.5</v>
+        <v>53.8</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>156</v>
+        <v>80</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -5342,26 +5342,26 @@
         </is>
       </c>
       <c r="G80" s="3" t="n">
-        <v>46.8</v>
+        <v>42.5</v>
       </c>
       <c r="H80" s="4" t="n">
-        <v>156</v>
+        <v>80</v>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-U</t>
+          <t>U-D-U-N</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K80" s="3" t="n">
-        <v>48.4</v>
+        <v>55.6</v>
       </c>
       <c r="L80" s="4" t="n">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
@@ -5369,10 +5369,10 @@
         </is>
       </c>
       <c r="N80" s="3" t="n">
-        <v>45.3</v>
+        <v>44.4</v>
       </c>
       <c r="O80" s="4" t="n">
-        <v>64</v>
+        <v>27</v>
       </c>
     </row>
     <row r="81">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -5392,10 +5392,10 @@
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>51.7</v>
+        <v>52.5</v>
       </c>
       <c r="E81" s="4" t="n">
-        <v>60</v>
+        <v>122</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -5403,14 +5403,14 @@
         </is>
       </c>
       <c r="G81" s="3" t="n">
-        <v>41.7</v>
+        <v>41.8</v>
       </c>
       <c r="H81" s="4" t="n">
-        <v>60</v>
+        <v>122</v>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-N</t>
+          <t>N-D-D-D</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -5419,21 +5419,21 @@
         </is>
       </c>
       <c r="K81" s="3" t="n">
-        <v>60</v>
+        <v>54.8</v>
       </c>
       <c r="L81" s="4" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N81" s="3" t="n">
-        <v>53.3</v>
+        <v>54.8</v>
       </c>
       <c r="O81" s="4" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
     </row>
     <row r="82">
@@ -5688,7 +5688,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -5697,25 +5697,25 @@
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>70.3</v>
+        <v>62.7</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G86" s="3" t="n">
-        <v>43.2</v>
+        <v>40.3</v>
       </c>
       <c r="H86" s="4" t="n">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-N</t>
+          <t>U-N-U-D</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="K86" s="3" t="n">
-        <v>64.7</v>
+        <v>57.7</v>
       </c>
       <c r="L86" s="4" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
@@ -5735,10 +5735,10 @@
         </is>
       </c>
       <c r="N86" s="3" t="n">
-        <v>41.2</v>
+        <v>38.5</v>
       </c>
       <c r="O86" s="4" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="87">
@@ -5810,7 +5810,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -5819,10 +5819,10 @@
         </is>
       </c>
       <c r="D88" s="3" t="n">
-        <v>70.09999999999999</v>
+        <v>61</v>
       </c>
       <c r="E88" s="4" t="n">
-        <v>87</v>
+        <v>182</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5830,14 +5830,14 @@
         </is>
       </c>
       <c r="G88" s="3" t="n">
-        <v>42.5</v>
+        <v>44.5</v>
       </c>
       <c r="H88" s="4" t="n">
-        <v>87</v>
+        <v>182</v>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
@@ -5846,10 +5846,10 @@
         </is>
       </c>
       <c r="K88" s="3" t="n">
-        <v>82.90000000000001</v>
+        <v>66.7</v>
       </c>
       <c r="L88" s="4" t="n">
-        <v>35</v>
+        <v>84</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
@@ -5857,10 +5857,10 @@
         </is>
       </c>
       <c r="N88" s="3" t="n">
-        <v>42.9</v>
+        <v>45.2</v>
       </c>
       <c r="O88" s="4" t="n">
-        <v>35</v>
+        <v>84</v>
       </c>
     </row>
     <row r="89">
@@ -5932,7 +5932,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -5941,10 +5941,10 @@
         </is>
       </c>
       <c r="D90" s="3" t="n">
-        <v>53.1</v>
+        <v>56.2</v>
       </c>
       <c r="E90" s="4" t="n">
-        <v>179</v>
+        <v>73</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5952,14 +5952,14 @@
         </is>
       </c>
       <c r="G90" s="3" t="n">
-        <v>47.5</v>
+        <v>46.6</v>
       </c>
       <c r="H90" s="4" t="n">
-        <v>179</v>
+        <v>73</v>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-U</t>
+          <t>U-D-U-N</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -5968,10 +5968,10 @@
         </is>
       </c>
       <c r="K90" s="3" t="n">
-        <v>56.2</v>
+        <v>52.9</v>
       </c>
       <c r="L90" s="4" t="n">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
@@ -5979,10 +5979,10 @@
         </is>
       </c>
       <c r="N90" s="3" t="n">
-        <v>52.5</v>
+        <v>50</v>
       </c>
       <c r="O90" s="4" t="n">
-        <v>80</v>
+        <v>34</v>
       </c>
     </row>
     <row r="91">
@@ -5993,7 +5993,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -6002,25 +6002,25 @@
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>67.40000000000001</v>
+        <v>47.1</v>
       </c>
       <c r="E91" s="4" t="n">
-        <v>86</v>
+        <v>172</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G91" s="3" t="n">
-        <v>43</v>
+        <v>43.6</v>
       </c>
       <c r="H91" s="4" t="n">
-        <v>86</v>
+        <v>172</v>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
@@ -6029,21 +6029,21 @@
         </is>
       </c>
       <c r="K91" s="3" t="n">
-        <v>69.7</v>
+        <v>54.5</v>
       </c>
       <c r="L91" s="4" t="n">
-        <v>33</v>
+        <v>77</v>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N91" s="3" t="n">
-        <v>42.4</v>
+        <v>41.6</v>
       </c>
       <c r="O91" s="4" t="n">
-        <v>33</v>
+        <v>77</v>
       </c>
     </row>
     <row r="92">
@@ -6237,7 +6237,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -6246,25 +6246,25 @@
         </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>73.90000000000001</v>
+        <v>69</v>
       </c>
       <c r="E95" s="4" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G95" s="3" t="n">
-        <v>43.5</v>
+        <v>42.9</v>
       </c>
       <c r="H95" s="4" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-N</t>
+          <t>U-D-N-D</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
@@ -6273,21 +6273,21 @@
         </is>
       </c>
       <c r="K95" s="3" t="n">
-        <v>75</v>
+        <v>73.3</v>
       </c>
       <c r="L95" s="4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N95" s="3" t="n">
-        <v>50</v>
+        <v>46.7</v>
       </c>
       <c r="O95" s="4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="96">
@@ -6359,7 +6359,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -6368,10 +6368,10 @@
         </is>
       </c>
       <c r="D97" s="3" t="n">
-        <v>54.9</v>
+        <v>53.2</v>
       </c>
       <c r="E97" s="4" t="n">
-        <v>71</v>
+        <v>156</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -6379,14 +6379,14 @@
         </is>
       </c>
       <c r="G97" s="3" t="n">
-        <v>49.3</v>
+        <v>46.8</v>
       </c>
       <c r="H97" s="4" t="n">
-        <v>71</v>
+        <v>156</v>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-U</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
@@ -6395,10 +6395,10 @@
         </is>
       </c>
       <c r="K97" s="3" t="n">
-        <v>51.7</v>
+        <v>50</v>
       </c>
       <c r="L97" s="4" t="n">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
@@ -6406,10 +6406,10 @@
         </is>
       </c>
       <c r="N97" s="3" t="n">
-        <v>51.7</v>
+        <v>42.6</v>
       </c>
       <c r="O97" s="4" t="n">
-        <v>29</v>
+        <v>68</v>
       </c>
     </row>
     <row r="98">
@@ -6420,7 +6420,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -6429,10 +6429,10 @@
         </is>
       </c>
       <c r="D98" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E98" s="4" t="n">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -6440,14 +6440,14 @@
         </is>
       </c>
       <c r="G98" s="3" t="n">
-        <v>43.6</v>
+        <v>45</v>
       </c>
       <c r="H98" s="4" t="n">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-U</t>
+          <t>U-N-U-N</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
@@ -6456,21 +6456,21 @@
         </is>
       </c>
       <c r="K98" s="3" t="n">
-        <v>54.8</v>
+        <v>66.7</v>
       </c>
       <c r="L98" s="4" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N98" s="3" t="n">
-        <v>41.9</v>
+        <v>40</v>
       </c>
       <c r="O98" s="4" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="99">
@@ -6542,7 +6542,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -6551,25 +6551,25 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>64.90000000000001</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>94</v>
+        <v>55</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G100" s="3" t="n">
-        <v>35.1</v>
+        <v>41.8</v>
       </c>
       <c r="H100" s="4" t="n">
-        <v>94</v>
+        <v>55</v>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-U</t>
+          <t>U-N-U-N</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
@@ -6578,21 +6578,21 @@
         </is>
       </c>
       <c r="K100" s="3" t="n">
-        <v>66.7</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L100" s="4" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N100" s="3" t="n">
-        <v>38.9</v>
+        <v>42.3</v>
       </c>
       <c r="O100" s="4" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="101">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -6612,25 +6612,25 @@
         </is>
       </c>
       <c r="D101" s="3" t="n">
-        <v>80.5</v>
+        <v>58.4</v>
       </c>
       <c r="E101" s="4" t="n">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G101" s="3" t="n">
-        <v>40.2</v>
+        <v>37.7</v>
       </c>
       <c r="H101" s="4" t="n">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>N-N-U-N</t>
+          <t>N-N-U-D</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
@@ -6639,10 +6639,10 @@
         </is>
       </c>
       <c r="K101" s="3" t="n">
-        <v>88.5</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L101" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
@@ -6650,10 +6650,10 @@
         </is>
       </c>
       <c r="N101" s="3" t="n">
-        <v>38.5</v>
+        <v>40.7</v>
       </c>
       <c r="O101" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="102">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -6734,25 +6734,25 @@
         </is>
       </c>
       <c r="D103" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>54.8</v>
       </c>
       <c r="E103" s="4" t="n">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G103" s="3" t="n">
-        <v>38.8</v>
+        <v>34.2</v>
       </c>
       <c r="H103" s="4" t="n">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-N</t>
+          <t>U-N-U-D</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
@@ -6761,10 +6761,10 @@
         </is>
       </c>
       <c r="K103" s="3" t="n">
-        <v>70</v>
+        <v>70.8</v>
       </c>
       <c r="L103" s="4" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
@@ -6772,10 +6772,10 @@
         </is>
       </c>
       <c r="N103" s="3" t="n">
-        <v>40</v>
+        <v>41.7</v>
       </c>
       <c r="O103" s="4" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="104">
@@ -7093,7 +7093,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -7102,25 +7102,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>85.7</v>
+        <v>52.9</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I3" s="3" t="n">
-        <v>57.1</v>
+        <v>47.1</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-N</t>
+          <t>D-D-N-D</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -7129,21 +7129,21 @@
         </is>
       </c>
       <c r="M3" s="3" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P3" s="3" t="n">
-        <v>66.7</v>
+        <v>40</v>
       </c>
       <c r="Q3" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -7164,7 +7164,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -7173,25 +7173,25 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>66.7</v>
+        <v>52.9</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I4" s="3" t="n">
-        <v>100</v>
+        <v>58.8</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-N</t>
+          <t>U-N-U-D</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -7200,21 +7200,21 @@
         </is>
       </c>
       <c r="M4" s="3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P4" s="3" t="n">
-        <v>100</v>
+        <v>62.5</v>
       </c>
       <c r="Q4" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -7812,25 +7812,25 @@
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I13" s="3" t="n">
         <v>50</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-D</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -7839,21 +7839,21 @@
         </is>
       </c>
       <c r="M13" s="3" t="n">
-        <v>83.3</v>
+        <v>60</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P13" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -8518,10 +8518,10 @@
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>46.2</v>
+        <v>55</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -8529,14 +8529,14 @@
         </is>
       </c>
       <c r="I23" s="3" t="n">
-        <v>53.8</v>
+        <v>50</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-D</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -8545,21 +8545,21 @@
         </is>
       </c>
       <c r="M23" s="3" t="n">
-        <v>60</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P23" s="3" t="n">
-        <v>60</v>
+        <v>57.1</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -8580,57 +8580,57 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>40</v>
+        <v>81.2</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I24" s="3" t="n">
-        <v>70</v>
+        <v>43.8</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M24" s="3" t="n">
-        <v>33.3</v>
+        <v>66.7</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P24" s="3" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25">
@@ -8722,7 +8722,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -8731,10 +8731,10 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>54.5</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -8742,14 +8742,14 @@
         </is>
       </c>
       <c r="I26" s="3" t="n">
-        <v>39.4</v>
+        <v>44.1</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-D</t>
+          <t>N-D-U-U</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -8761,18 +8761,18 @@
         <v>66.7</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P26" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -9006,57 +9006,57 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I30" s="3" t="n">
-        <v>62.5</v>
+        <v>41.7</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M30" s="3" t="n">
-        <v>33.3</v>
+        <v>60</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P30" s="3" t="n">
-        <v>66.7</v>
+        <v>40</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31">
@@ -9148,7 +9148,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -9157,25 +9157,25 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="G32" s="4" t="n">
         <v>25</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I32" s="3" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-U</t>
+          <t>N-D-U-D</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -9184,21 +9184,21 @@
         </is>
       </c>
       <c r="M32" s="3" t="n">
-        <v>75</v>
+        <v>85.7</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P32" s="3" t="n">
-        <v>50</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33">
@@ -9219,7 +9219,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -9228,25 +9228,25 @@
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>68.8</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I33" s="3" t="n">
-        <v>56.2</v>
+        <v>51.9</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-N</t>
+          <t>N-U-U-D</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -9255,21 +9255,21 @@
         </is>
       </c>
       <c r="M33" s="3" t="n">
-        <v>66.7</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P33" s="3" t="n">
-        <v>66.7</v>
+        <v>55.6</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34">
@@ -9428,7 +9428,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -9437,48 +9437,48 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I36" s="3" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-U</t>
+          <t>U-N-D-N</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M36" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P36" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q36" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -9641,7 +9641,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -9650,25 +9650,25 @@
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>66.7</v>
+        <v>56.2</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I39" s="3" t="n">
-        <v>44.4</v>
+        <v>53.1</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-U</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
@@ -9677,21 +9677,21 @@
         </is>
       </c>
       <c r="M39" s="3" t="n">
-        <v>66.7</v>
+        <v>64.3</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P39" s="3" t="n">
-        <v>53.3</v>
+        <v>64.3</v>
       </c>
       <c r="Q39" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="40">
@@ -9712,53 +9712,57 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="G40" s="4" t="n">
         <v>5</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I40" s="3" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>5</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-U</t>
+          <t>D-N-U-D</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M40" s="3" t="inlineStr"/>
+          <t>D/U</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="n">
+        <v>50</v>
+      </c>
       <c r="N40" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P40" s="3" t="inlineStr"/>
+          <t>D/U</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="n">
+        <v>50</v>
+      </c>
       <c r="Q40" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -9850,49 +9854,57 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="F42" s="3" t="inlineStr"/>
+          <t>N/U</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>50</v>
+      </c>
       <c r="G42" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="I42" s="3" t="inlineStr"/>
+          <t>D/N</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="n">
+        <v>50</v>
+      </c>
       <c r="J42" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-N-U-D</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M42" s="3" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="N42" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P42" s="3" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="Q42" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -9913,7 +9925,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9922,44 +9934,48 @@
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="G43" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="J43" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>U-D-N-D</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="N43" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>D/N/U</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="J43" s="4" t="n">
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="Q43" s="4" t="n">
         <v>3</v>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>U-D-N-N</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M43" s="3" t="inlineStr"/>
-      <c r="N43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P43" s="3" t="inlineStr"/>
-      <c r="Q43" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -10051,53 +10067,57 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I45" s="3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J45" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>N-N-U-N</t>
+          <t>N-N-U-D</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M45" s="3" t="inlineStr"/>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="N45" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P45" s="3" t="inlineStr"/>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="Q45" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -10118,7 +10138,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -10127,25 +10147,25 @@
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>76.90000000000001</v>
+        <v>50</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I46" s="3" t="n">
-        <v>53.8</v>
+        <v>50</v>
       </c>
       <c r="J46" s="4" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-U</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -10154,21 +10174,21 @@
         </is>
       </c>
       <c r="M46" s="3" t="n">
-        <v>75</v>
+        <v>57.1</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P46" s="3" t="n">
-        <v>62.5</v>
+        <v>35.7</v>
       </c>
       <c r="Q46" s="4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="47">
@@ -10331,7 +10351,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -10340,10 +10360,10 @@
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>52.4</v>
+        <v>50</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -10351,14 +10371,14 @@
         </is>
       </c>
       <c r="I49" s="3" t="n">
-        <v>38.1</v>
+        <v>35.7</v>
       </c>
       <c r="J49" s="4" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
@@ -10367,10 +10387,10 @@
         </is>
       </c>
       <c r="M49" s="3" t="n">
-        <v>66.7</v>
+        <v>57.1</v>
       </c>
       <c r="N49" s="4" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
@@ -10378,10 +10398,10 @@
         </is>
       </c>
       <c r="P49" s="3" t="n">
-        <v>44.4</v>
+        <v>50</v>
       </c>
       <c r="Q49" s="4" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="50">
@@ -10402,7 +10422,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -10411,10 +10431,10 @@
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>77.8</v>
+        <v>62.5</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -10422,14 +10442,14 @@
         </is>
       </c>
       <c r="I50" s="3" t="n">
-        <v>50</v>
+        <v>45.8</v>
       </c>
       <c r="J50" s="4" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
@@ -10438,21 +10458,21 @@
         </is>
       </c>
       <c r="M50" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>75</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="P50" s="3" t="n">
-        <v>57.1</v>
+        <v>33.3</v>
       </c>
       <c r="Q50" s="4" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="51">
@@ -10473,7 +10493,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>N-N-D</t>
+          <t>N-N-N</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -10485,45 +10505,41 @@
         <v>100</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I51" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J51" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>N-N-N-D</t>
+          <t>N-N-N-N</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M51" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr"/>
       <c r="N51" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P51" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P51" s="3" t="inlineStr"/>
       <c r="Q51" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -10615,7 +10631,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -10624,10 +10640,10 @@
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -10635,37 +10651,37 @@
         </is>
       </c>
       <c r="I53" s="3" t="n">
-        <v>50</v>
+        <v>55.6</v>
       </c>
       <c r="J53" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M53" s="3" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="N53" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P53" s="3" t="n">
         <v>50</v>
       </c>
       <c r="Q53" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54">
@@ -10828,19 +10844,19 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>50</v>
+        <v>55.6</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -10848,26 +10864,26 @@
         </is>
       </c>
       <c r="I56" s="3" t="n">
-        <v>100</v>
+        <v>44.4</v>
       </c>
       <c r="J56" s="4" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="M56" s="3" t="n">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="N56" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
@@ -10875,10 +10891,10 @@
         </is>
       </c>
       <c r="P56" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="Q56" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -10899,34 +10915,34 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I57" s="3" t="n">
-        <v>62.5</v>
+        <v>46.7</v>
       </c>
       <c r="J57" s="4" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-N</t>
+          <t>U-D-N-D</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
@@ -10935,21 +10951,21 @@
         </is>
       </c>
       <c r="M57" s="3" t="n">
-        <v>66.7</v>
+        <v>57.1</v>
       </c>
       <c r="N57" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="P57" s="3" t="n">
-        <v>66.7</v>
+        <v>42.9</v>
       </c>
       <c r="Q57" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="58">
@@ -10970,7 +10986,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -10979,48 +10995,48 @@
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>57.9</v>
+        <v>57.1</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I58" s="3" t="n">
-        <v>57.9</v>
+        <v>42.9</v>
       </c>
       <c r="J58" s="4" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-U</t>
+          <t>N-D-U-D</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M58" s="3" t="n">
         <v>100</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="P58" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q58" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -11041,7 +11057,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -11050,34 +11066,34 @@
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>62.5</v>
+        <v>78.3</v>
       </c>
       <c r="G59" s="4" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I59" s="3" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="J59" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>N-U-D-D</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>N/U</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="n">
         <v>50</v>
-      </c>
-      <c r="J59" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="K59" s="2" t="inlineStr">
-        <is>
-          <t>N-U-D-N</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M59" s="3" t="n">
-        <v>100</v>
       </c>
       <c r="N59" s="4" t="n">
         <v>2</v>
@@ -11112,7 +11128,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -11124,7 +11140,7 @@
         <v>53.3</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -11132,14 +11148,14 @@
         </is>
       </c>
       <c r="I60" s="3" t="n">
-        <v>40</v>
+        <v>56.7</v>
       </c>
       <c r="J60" s="4" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-U</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
@@ -11148,21 +11164,21 @@
         </is>
       </c>
       <c r="M60" s="3" t="n">
-        <v>42.9</v>
+        <v>55.6</v>
       </c>
       <c r="N60" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P60" s="3" t="n">
-        <v>42.9</v>
+        <v>44.4</v>
       </c>
       <c r="Q60" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="61">
@@ -11183,39 +11199,39 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I61" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="J61" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-N</t>
+          <t>D-N-N-D</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M61" s="3" t="n">
@@ -11254,7 +11270,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -11266,7 +11282,7 @@
         <v>71.40000000000001</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -11274,14 +11290,14 @@
         </is>
       </c>
       <c r="I62" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>47.6</v>
       </c>
       <c r="J62" s="4" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-N</t>
+          <t>N-D-D-D</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
@@ -11290,21 +11306,21 @@
         </is>
       </c>
       <c r="M62" s="3" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="N62" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P62" s="3" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="Q62" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63">
@@ -11396,7 +11412,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -11405,10 +11421,10 @@
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>90</v>
+        <v>48.7</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -11416,14 +11432,14 @@
         </is>
       </c>
       <c r="I64" s="3" t="n">
-        <v>60</v>
+        <v>43.6</v>
       </c>
       <c r="J64" s="4" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-N</t>
+          <t>N-D-U-D</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
@@ -11432,7 +11448,7 @@
         </is>
       </c>
       <c r="M64" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="N64" s="4" t="n">
         <v>3</v>
@@ -11443,7 +11459,7 @@
         </is>
       </c>
       <c r="P64" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="Q64" s="4" t="n">
         <v>3</v>
@@ -11538,7 +11554,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -11547,25 +11563,25 @@
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>41.2</v>
+        <v>91.7</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I66" s="3" t="n">
-        <v>47.1</v>
+        <v>41.7</v>
       </c>
       <c r="J66" s="4" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-D</t>
+          <t>U-U-U-N</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
@@ -11574,7 +11590,7 @@
         </is>
       </c>
       <c r="M66" s="3" t="n">
-        <v>57.1</v>
+        <v>85.7</v>
       </c>
       <c r="N66" s="4" t="n">
         <v>7</v>
@@ -11585,7 +11601,7 @@
         </is>
       </c>
       <c r="P66" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>57.1</v>
       </c>
       <c r="Q66" s="4" t="n">
         <v>7</v>
@@ -12098,7 +12114,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -12107,25 +12123,25 @@
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>77.8</v>
+        <v>61.5</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I74" s="3" t="n">
-        <v>66.7</v>
+        <v>46.2</v>
       </c>
       <c r="J74" s="4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-N</t>
+          <t>D-D-N-D</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
@@ -12134,10 +12150,10 @@
         </is>
       </c>
       <c r="M74" s="3" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="N74" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
@@ -12145,10 +12161,10 @@
         </is>
       </c>
       <c r="P74" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="Q74" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75">
@@ -12169,30 +12185,34 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="F75" s="3" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>83.3</v>
+      </c>
       <c r="G75" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="I75" s="3" t="inlineStr"/>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I75" s="3" t="n">
+        <v>66.7</v>
+      </c>
       <c r="J75" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-N</t>
+          <t>N-D-U-D</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
@@ -12445,7 +12465,7 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -12454,48 +12474,48 @@
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>57.1</v>
+        <v>62.5</v>
       </c>
       <c r="G79" s="4" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I79" s="3" t="n">
-        <v>57.1</v>
+        <v>56.2</v>
       </c>
       <c r="J79" s="4" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>N-N-U-N</t>
+          <t>N-N-U-D</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M79" s="3" t="n">
         <v>50</v>
       </c>
       <c r="N79" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P79" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="Q79" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="80">
@@ -12516,7 +12536,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -12525,48 +12545,48 @@
         </is>
       </c>
       <c r="F80" s="3" t="n">
-        <v>45.2</v>
+        <v>53.8</v>
       </c>
       <c r="G80" s="4" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I80" s="3" t="n">
-        <v>54.8</v>
+        <v>53.8</v>
       </c>
       <c r="J80" s="4" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-U</t>
+          <t>U-D-U-N</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M80" s="3" t="n">
         <v>50</v>
       </c>
       <c r="N80" s="4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P80" s="3" t="n">
         <v>50</v>
       </c>
       <c r="Q80" s="4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="81">
@@ -12587,7 +12607,7 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -12596,48 +12616,48 @@
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>66.7</v>
+        <v>68</v>
       </c>
       <c r="G81" s="4" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I81" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="J81" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>N-D-D-D</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M81" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="N81" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
           <t>D/U</t>
         </is>
       </c>
-      <c r="I81" s="3" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="J81" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="K81" s="2" t="inlineStr">
-        <is>
-          <t>N-D-D-N</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="M81" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="N81" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O81" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
       <c r="P81" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q81" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="82">
@@ -12942,7 +12962,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -12951,25 +12971,25 @@
         </is>
       </c>
       <c r="F86" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="G86" s="4" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="I86" s="3" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="J86" s="4" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-N</t>
+          <t>U-N-U-D</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
@@ -12978,21 +12998,21 @@
         </is>
       </c>
       <c r="M86" s="3" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="N86" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P86" s="3" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Q86" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87">
@@ -13084,7 +13104,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -13093,25 +13113,25 @@
         </is>
       </c>
       <c r="F88" s="3" t="n">
-        <v>87.5</v>
+        <v>75</v>
       </c>
       <c r="G88" s="4" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I88" s="3" t="n">
-        <v>50</v>
+        <v>46.9</v>
       </c>
       <c r="J88" s="4" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
@@ -13120,21 +13140,21 @@
         </is>
       </c>
       <c r="M88" s="3" t="n">
-        <v>90</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="N88" s="4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P88" s="3" t="n">
-        <v>40</v>
+        <v>53.8</v>
       </c>
       <c r="Q88" s="4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="89">
@@ -13226,7 +13246,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -13235,37 +13255,37 @@
         </is>
       </c>
       <c r="F90" s="3" t="n">
-        <v>48.8</v>
+        <v>75</v>
       </c>
       <c r="G90" s="4" t="n">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I90" s="3" t="n">
-        <v>41.5</v>
+        <v>50</v>
       </c>
       <c r="J90" s="4" t="n">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-U</t>
+          <t>U-D-U-N</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M90" s="3" t="n">
-        <v>53.3</v>
+        <v>66.7</v>
       </c>
       <c r="N90" s="4" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
@@ -13273,10 +13293,10 @@
         </is>
       </c>
       <c r="P90" s="3" t="n">
-        <v>53.3</v>
+        <v>66.7</v>
       </c>
       <c r="Q90" s="4" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91">
@@ -13297,7 +13317,7 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -13306,25 +13326,25 @@
         </is>
       </c>
       <c r="F91" s="3" t="n">
-        <v>84.2</v>
+        <v>40.6</v>
       </c>
       <c r="G91" s="4" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I91" s="3" t="n">
-        <v>36.8</v>
+        <v>46.9</v>
       </c>
       <c r="J91" s="4" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="L91" s="2" t="inlineStr">
@@ -13333,21 +13353,21 @@
         </is>
       </c>
       <c r="M91" s="3" t="n">
-        <v>75</v>
+        <v>58.8</v>
       </c>
       <c r="N91" s="4" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P91" s="3" t="n">
-        <v>50</v>
+        <v>47.1</v>
       </c>
       <c r="Q91" s="4" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="92">
@@ -13581,7 +13601,7 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -13590,25 +13610,25 @@
         </is>
       </c>
       <c r="F95" s="3" t="n">
-        <v>80</v>
+        <v>86.7</v>
       </c>
       <c r="G95" s="4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I95" s="3" t="n">
-        <v>40</v>
+        <v>46.7</v>
       </c>
       <c r="J95" s="4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-N</t>
+          <t>U-D-N-D</t>
         </is>
       </c>
       <c r="L95" s="2" t="inlineStr">
@@ -13617,21 +13637,21 @@
         </is>
       </c>
       <c r="M95" s="3" t="n">
-        <v>83.3</v>
+        <v>87.5</v>
       </c>
       <c r="N95" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P95" s="3" t="n">
-        <v>50</v>
+        <v>37.5</v>
       </c>
       <c r="Q95" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="96">
@@ -13723,7 +13743,7 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -13732,10 +13752,10 @@
         </is>
       </c>
       <c r="F97" s="3" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="G97" s="4" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
@@ -13743,37 +13763,37 @@
         </is>
       </c>
       <c r="I97" s="3" t="n">
-        <v>50</v>
+        <v>42.9</v>
       </c>
       <c r="J97" s="4" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-U</t>
         </is>
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="M97" s="3" t="n">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="N97" s="4" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P97" s="3" t="n">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="Q97" s="4" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="98">
@@ -13794,34 +13814,34 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F98" s="3" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G98" s="4" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="I98" s="3" t="n">
         <v>50</v>
       </c>
       <c r="J98" s="4" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-U</t>
+          <t>U-N-U-N</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
@@ -13830,21 +13850,21 @@
         </is>
       </c>
       <c r="M98" s="3" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="N98" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P98" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q98" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
@@ -13936,7 +13956,7 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -13945,25 +13965,25 @@
         </is>
       </c>
       <c r="F100" s="3" t="n">
-        <v>60.9</v>
+        <v>72.7</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I100" s="3" t="n">
-        <v>39.1</v>
+        <v>45.5</v>
       </c>
       <c r="J100" s="4" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-U</t>
+          <t>U-N-U-N</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
@@ -13972,21 +13992,21 @@
         </is>
       </c>
       <c r="M100" s="3" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="N100" s="4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P100" s="3" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="Q100" s="4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="101">
@@ -14007,7 +14027,7 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -14016,25 +14036,25 @@
         </is>
       </c>
       <c r="F101" s="3" t="n">
-        <v>93.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G101" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I101" s="3" t="n">
-        <v>73.3</v>
+        <v>54.5</v>
       </c>
       <c r="J101" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>N-N-U-N</t>
+          <t>N-N-U-D</t>
         </is>
       </c>
       <c r="L101" s="2" t="inlineStr">
@@ -14046,7 +14066,7 @@
         <v>100</v>
       </c>
       <c r="N101" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
@@ -14054,10 +14074,10 @@
         </is>
       </c>
       <c r="P101" s="3" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="Q101" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="102">
@@ -14149,7 +14169,7 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -14158,25 +14178,25 @@
         </is>
       </c>
       <c r="F103" s="3" t="n">
-        <v>75</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="G103" s="4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="I103" s="3" t="n">
-        <v>75</v>
+        <v>42.9</v>
       </c>
       <c r="J103" s="4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-N</t>
+          <t>U-N-U-D</t>
         </is>
       </c>
       <c r="L103" s="2" t="inlineStr">
@@ -14185,21 +14205,21 @@
         </is>
       </c>
       <c r="M103" s="3" t="n">
-        <v>100</v>
+        <v>85.7</v>
       </c>
       <c r="N103" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P103" s="3" t="n">
-        <v>100</v>
+        <v>42.9</v>
       </c>
       <c r="Q103" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="104">

--- a/BIS_tr.xlsx
+++ b/BIS_tr.xlsx
@@ -690,7 +690,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>N-U-D</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -699,37 +699,37 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>52.7</v>
+        <v>53.5</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G4" s="3" t="n">
-        <v>39.2</v>
+        <v>46.5</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-D</t>
+          <t>U-N-U-N</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K4" s="3" t="n">
-        <v>59.4</v>
+        <v>57.1</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
@@ -737,10 +737,10 @@
         </is>
       </c>
       <c r="N4" s="3" t="n">
-        <v>40.6</v>
+        <v>50</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1065,10 +1065,10 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>66.7</v>
+        <v>57.8</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>81</v>
+        <v>128</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -1076,14 +1076,14 @@
         </is>
       </c>
       <c r="G10" s="3" t="n">
-        <v>35.8</v>
+        <v>41.4</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>81</v>
+        <v>128</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-N</t>
+          <t>N-D-U-U</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1092,21 +1092,21 @@
         </is>
       </c>
       <c r="K10" s="3" t="n">
-        <v>68.40000000000001</v>
+        <v>80</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N10" s="3" t="n">
-        <v>42.1</v>
+        <v>56</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1614,25 +1614,25 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>53.3</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>63.3</v>
+        <v>42.3</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-U</t>
+          <t>U-D-N-N</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1641,21 +1641,21 @@
         </is>
       </c>
       <c r="K19" s="3" t="n">
-        <v>58.3</v>
+        <v>72.2</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N19" s="3" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1919,10 +1919,10 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>61.1</v>
+        <v>62.5</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>72</v>
+        <v>32</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1930,26 +1930,26 @@
         </is>
       </c>
       <c r="G24" s="3" t="n">
-        <v>45.8</v>
+        <v>43.8</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>72</v>
+        <v>32</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K24" s="3" t="n">
-        <v>51.6</v>
+        <v>50</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
@@ -1957,10 +1957,10 @@
         </is>
       </c>
       <c r="N24" s="3" t="n">
-        <v>45.2</v>
+        <v>50</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2224,37 +2224,37 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>45.2</v>
+        <v>53.3</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>58.1</v>
+        <v>53.3</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-D</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K29" s="3" t="n">
-        <v>41.2</v>
+        <v>58.3</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="N29" s="3" t="n">
-        <v>52.9</v>
+        <v>66.7</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>50.6</v>
+        <v>41.8</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>166</v>
+        <v>67</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2296,37 +2296,37 @@
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>42.8</v>
+        <v>44.8</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>166</v>
+        <v>67</v>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-D</t>
+          <t>U-D-U-N</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K30" s="3" t="n">
-        <v>53.3</v>
+        <v>50</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N30" s="3" t="n">
-        <v>40</v>
+        <v>46.7</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2468,25 +2468,25 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>67.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>159</v>
+        <v>71</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G33" s="3" t="n">
-        <v>47.2</v>
+        <v>38</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>159</v>
+        <v>71</v>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-D</t>
+          <t>N-U-U-N</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -2495,21 +2495,21 @@
         </is>
       </c>
       <c r="K33" s="3" t="n">
-        <v>78.40000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N33" s="3" t="n">
-        <v>43.2</v>
+        <v>54.2</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>37</v>
+        <v>24</v>
       </c>
     </row>
     <row r="34">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2834,25 +2834,25 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>63.5</v>
+        <v>62.5</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>159</v>
+        <v>64</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G39" s="3" t="n">
-        <v>43.4</v>
+        <v>37.5</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>159</v>
+        <v>64</v>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-D</t>
+          <t>U-U-U-N</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -2861,21 +2861,21 @@
         </is>
       </c>
       <c r="K39" s="3" t="n">
-        <v>58.7</v>
+        <v>66.7</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>63</v>
+        <v>21</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N39" s="3" t="n">
-        <v>46</v>
+        <v>38.1</v>
       </c>
       <c r="O39" s="4" t="n">
-        <v>63</v>
+        <v>21</v>
       </c>
     </row>
     <row r="40">
@@ -3008,19 +3008,19 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>N-U-D</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>63.6</v>
+        <v>37.5</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -3028,37 +3028,37 @@
         </is>
       </c>
       <c r="G42" s="3" t="n">
-        <v>45.5</v>
+        <v>62.5</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-D</t>
+          <t>D-N-U-N</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="K42" s="3" t="n">
-        <v>83.3</v>
+        <v>50</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N42" s="3" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="O42" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3383,25 +3383,25 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>50</v>
+        <v>76.5</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>50</v>
+        <v>35.3</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-U</t>
+          <t>U-D-N-N</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -3410,10 +3410,10 @@
         </is>
       </c>
       <c r="K48" s="3" t="n">
-        <v>54.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
@@ -3421,10 +3421,10 @@
         </is>
       </c>
       <c r="N48" s="3" t="n">
-        <v>58.3</v>
+        <v>44.4</v>
       </c>
       <c r="O48" s="4" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="49">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>D-N-D</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3932,25 +3932,25 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>60.9</v>
+        <v>74.5</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>92</v>
+        <v>47</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G57" s="3" t="n">
-        <v>41.3</v>
+        <v>46.8</v>
       </c>
       <c r="H57" s="4" t="n">
-        <v>92</v>
+        <v>47</v>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-D</t>
+          <t>U-D-N-N</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -3959,21 +3959,21 @@
         </is>
       </c>
       <c r="K57" s="3" t="n">
-        <v>67.5</v>
+        <v>81.2</v>
       </c>
       <c r="L57" s="4" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N57" s="3" t="n">
-        <v>42.5</v>
+        <v>50</v>
       </c>
       <c r="O57" s="4" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
     </row>
     <row r="58">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3993,37 +3993,37 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>61.8</v>
+        <v>57.4</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G58" s="3" t="n">
-        <v>44.1</v>
+        <v>50</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-D</t>
+          <t>N-D-U-U</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K58" s="3" t="n">
-        <v>44.4</v>
+        <v>87.5</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
@@ -4031,10 +4031,10 @@
         </is>
       </c>
       <c r="N58" s="3" t="n">
-        <v>44.4</v>
+        <v>56.2</v>
       </c>
       <c r="O58" s="4" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="59">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>N-N-D</t>
+          <t>N-N-N</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4176,48 +4176,48 @@
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>62.5</v>
+        <v>57.1</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G61" s="3" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="H61" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>D-N-N-N</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="L61" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>D/U</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="H61" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>D-N-N-D</t>
-        </is>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K61" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="L61" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="M61" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="N61" s="3" t="n">
-        <v>100</v>
-      </c>
       <c r="O61" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -4843,10 +4843,10 @@
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>44.6</v>
+        <v>46.6</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>92</v>
+        <v>118</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4854,26 +4854,26 @@
         </is>
       </c>
       <c r="G72" s="3" t="n">
-        <v>50</v>
+        <v>46.6</v>
       </c>
       <c r="H72" s="4" t="n">
-        <v>92</v>
+        <v>118</v>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-U</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K72" s="3" t="n">
-        <v>43.3</v>
+        <v>44.2</v>
       </c>
       <c r="L72" s="4" t="n">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
@@ -4881,10 +4881,10 @@
         </is>
       </c>
       <c r="N72" s="3" t="n">
-        <v>53.3</v>
+        <v>51.2</v>
       </c>
       <c r="O72" s="4" t="n">
-        <v>30</v>
+        <v>43</v>
       </c>
     </row>
     <row r="73">
@@ -5017,7 +5017,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5026,25 +5026,25 @@
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>72.5</v>
+        <v>80</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G75" s="3" t="n">
-        <v>52.9</v>
+        <v>50</v>
       </c>
       <c r="H75" s="4" t="n">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-D</t>
+          <t>N-D-U-N</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
@@ -5053,21 +5053,21 @@
         </is>
       </c>
       <c r="K75" s="3" t="n">
-        <v>66.7</v>
+        <v>75</v>
       </c>
       <c r="L75" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N75" s="3" t="n">
-        <v>33.3</v>
+        <v>75</v>
       </c>
       <c r="O75" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76">
@@ -5261,7 +5261,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>N-U-D</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -5270,10 +5270,10 @@
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>69.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -5281,14 +5281,14 @@
         </is>
       </c>
       <c r="G79" s="3" t="n">
-        <v>42.5</v>
+        <v>38.6</v>
       </c>
       <c r="H79" s="4" t="n">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>N-N-U-D</t>
+          <t>N-N-U-N</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -5297,10 +5297,10 @@
         </is>
       </c>
       <c r="K79" s="3" t="n">
-        <v>73.90000000000001</v>
+        <v>61.1</v>
       </c>
       <c r="L79" s="4" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
@@ -5308,10 +5308,10 @@
         </is>
       </c>
       <c r="N79" s="3" t="n">
-        <v>43.5</v>
+        <v>44.4</v>
       </c>
       <c r="O79" s="4" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="80">
@@ -5444,7 +5444,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -5453,48 +5453,48 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>75</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="E82" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="H82" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>D-D-D-D</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K82" s="3" t="n">
+        <v>81.2</v>
+      </c>
+      <c r="L82" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>D/U</t>
-        </is>
-      </c>
-      <c r="G82" s="3" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="H82" s="4" t="n">
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="O82" s="4" t="n">
         <v>16</v>
-      </c>
-      <c r="I82" s="2" t="inlineStr">
-        <is>
-          <t>D-D-D-N</t>
-        </is>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K82" s="3" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="L82" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="M82" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="N82" s="3" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="O82" s="4" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="83">
@@ -5505,7 +5505,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>U-N-D</t>
+          <t>U-N-N</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -5514,10 +5514,10 @@
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>54.7</v>
+        <v>60.5</v>
       </c>
       <c r="E83" s="4" t="n">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -5525,14 +5525,14 @@
         </is>
       </c>
       <c r="G83" s="3" t="n">
-        <v>45.3</v>
+        <v>47.4</v>
       </c>
       <c r="H83" s="4" t="n">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-D</t>
+          <t>D-U-N-N</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
@@ -5541,21 +5541,21 @@
         </is>
       </c>
       <c r="K83" s="3" t="n">
-        <v>60.9</v>
+        <v>50</v>
       </c>
       <c r="L83" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N83" s="3" t="n">
-        <v>56.5</v>
+        <v>40</v>
       </c>
       <c r="O83" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="84">
@@ -5627,7 +5627,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -5636,25 +5636,25 @@
         </is>
       </c>
       <c r="D85" s="3" t="n">
-        <v>59.2</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="E85" s="4" t="n">
-        <v>147</v>
+        <v>78</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G85" s="3" t="n">
-        <v>44.9</v>
+        <v>43.6</v>
       </c>
       <c r="H85" s="4" t="n">
-        <v>147</v>
+        <v>78</v>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-D</t>
+          <t>N-U-U-N</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
@@ -5663,21 +5663,21 @@
         </is>
       </c>
       <c r="K85" s="3" t="n">
-        <v>70.8</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="L85" s="4" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N85" s="3" t="n">
-        <v>54.2</v>
+        <v>64.3</v>
       </c>
       <c r="O85" s="4" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="86">
@@ -5688,7 +5688,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>N-U-D</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -5697,25 +5697,25 @@
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>62.7</v>
+        <v>70.3</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G86" s="3" t="n">
-        <v>40.3</v>
+        <v>43.2</v>
       </c>
       <c r="H86" s="4" t="n">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-D</t>
+          <t>U-N-U-N</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="K86" s="3" t="n">
-        <v>57.7</v>
+        <v>64.7</v>
       </c>
       <c r="L86" s="4" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
@@ -5735,10 +5735,10 @@
         </is>
       </c>
       <c r="N86" s="3" t="n">
-        <v>38.5</v>
+        <v>41.2</v>
       </c>
       <c r="O86" s="4" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="87">
@@ -5810,7 +5810,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -5819,10 +5819,10 @@
         </is>
       </c>
       <c r="D88" s="3" t="n">
-        <v>61</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="E88" s="4" t="n">
-        <v>182</v>
+        <v>87</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5830,14 +5830,14 @@
         </is>
       </c>
       <c r="G88" s="3" t="n">
-        <v>44.5</v>
+        <v>42.5</v>
       </c>
       <c r="H88" s="4" t="n">
-        <v>182</v>
+        <v>87</v>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-D</t>
+          <t>U-D-U-N</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
@@ -5846,10 +5846,10 @@
         </is>
       </c>
       <c r="K88" s="3" t="n">
-        <v>66.7</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="L88" s="4" t="n">
-        <v>84</v>
+        <v>35</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
@@ -5857,10 +5857,10 @@
         </is>
       </c>
       <c r="N88" s="3" t="n">
-        <v>45.2</v>
+        <v>42.9</v>
       </c>
       <c r="O88" s="4" t="n">
-        <v>84</v>
+        <v>35</v>
       </c>
     </row>
     <row r="89">
@@ -5932,7 +5932,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -5941,37 +5941,37 @@
         </is>
       </c>
       <c r="D90" s="3" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="E90" s="4" t="n">
+        <v>179</v>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="H90" s="4" t="n">
+        <v>179</v>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>U-D-U-U</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K90" s="3" t="n">
         <v>56.2</v>
       </c>
-      <c r="E90" s="4" t="n">
-        <v>73</v>
-      </c>
-      <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="G90" s="3" t="n">
-        <v>46.6</v>
-      </c>
-      <c r="H90" s="4" t="n">
-        <v>73</v>
-      </c>
-      <c r="I90" s="2" t="inlineStr">
-        <is>
-          <t>U-D-U-N</t>
-        </is>
-      </c>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K90" s="3" t="n">
-        <v>52.9</v>
-      </c>
       <c r="L90" s="4" t="n">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
@@ -5979,10 +5979,10 @@
         </is>
       </c>
       <c r="N90" s="3" t="n">
-        <v>50</v>
+        <v>52.5</v>
       </c>
       <c r="O90" s="4" t="n">
-        <v>34</v>
+        <v>80</v>
       </c>
     </row>
     <row r="91">
@@ -6176,7 +6176,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -6185,10 +6185,10 @@
         </is>
       </c>
       <c r="D94" s="3" t="n">
-        <v>55.6</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="E94" s="4" t="n">
-        <v>153</v>
+        <v>74</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -6196,14 +6196,14 @@
         </is>
       </c>
       <c r="G94" s="3" t="n">
-        <v>41.2</v>
+        <v>35.1</v>
       </c>
       <c r="H94" s="4" t="n">
-        <v>153</v>
+        <v>74</v>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
@@ -6212,21 +6212,21 @@
         </is>
       </c>
       <c r="K94" s="3" t="n">
-        <v>49.3</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="L94" s="4" t="n">
-        <v>69</v>
+        <v>32</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N94" s="3" t="n">
-        <v>43.5</v>
+        <v>37.5</v>
       </c>
       <c r="O94" s="4" t="n">
-        <v>69</v>
+        <v>32</v>
       </c>
     </row>
     <row r="95">
@@ -6298,7 +6298,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -6307,48 +6307,48 @@
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>49.7</v>
+        <v>47.7</v>
       </c>
       <c r="E96" s="4" t="n">
         <v>153</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G96" s="3" t="n">
-        <v>41.8</v>
+        <v>45.1</v>
       </c>
       <c r="H96" s="4" t="n">
         <v>153</v>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-D</t>
+          <t>D-D-U-U</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K96" s="3" t="n">
-        <v>46.9</v>
+        <v>44.4</v>
       </c>
       <c r="L96" s="4" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N96" s="3" t="n">
-        <v>42.2</v>
+        <v>50.8</v>
       </c>
       <c r="O96" s="4" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="97">
@@ -6359,7 +6359,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -6368,10 +6368,10 @@
         </is>
       </c>
       <c r="D97" s="3" t="n">
-        <v>53.2</v>
+        <v>54.9</v>
       </c>
       <c r="E97" s="4" t="n">
-        <v>156</v>
+        <v>71</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -6379,14 +6379,14 @@
         </is>
       </c>
       <c r="G97" s="3" t="n">
-        <v>46.8</v>
+        <v>49.3</v>
       </c>
       <c r="H97" s="4" t="n">
-        <v>156</v>
+        <v>71</v>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
@@ -6395,10 +6395,10 @@
         </is>
       </c>
       <c r="K97" s="3" t="n">
-        <v>50</v>
+        <v>51.7</v>
       </c>
       <c r="L97" s="4" t="n">
-        <v>68</v>
+        <v>29</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
@@ -6406,10 +6406,10 @@
         </is>
       </c>
       <c r="N97" s="3" t="n">
-        <v>42.6</v>
+        <v>51.7</v>
       </c>
       <c r="O97" s="4" t="n">
-        <v>68</v>
+        <v>29</v>
       </c>
     </row>
     <row r="98">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -6673,10 +6673,10 @@
         </is>
       </c>
       <c r="D102" s="3" t="n">
-        <v>66.7</v>
+        <v>71.2</v>
       </c>
       <c r="E102" s="4" t="n">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -6684,14 +6684,14 @@
         </is>
       </c>
       <c r="G102" s="3" t="n">
-        <v>48.6</v>
+        <v>39.7</v>
       </c>
       <c r="H102" s="4" t="n">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-U</t>
+          <t>N-D-U-N</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
@@ -6707,11 +6707,11 @@
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N102" s="3" t="n">
-        <v>40.7</v>
+        <v>51.9</v>
       </c>
       <c r="O102" s="4" t="n">
         <v>27</v>
@@ -7164,7 +7164,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>N-U-D</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -7173,25 +7173,25 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>52.9</v>
+        <v>66.7</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I4" s="3" t="n">
-        <v>58.8</v>
+        <v>100</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-D</t>
+          <t>U-N-U-N</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -7200,21 +7200,21 @@
         </is>
       </c>
       <c r="M4" s="3" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P4" s="3" t="n">
-        <v>62.5</v>
+        <v>100</v>
       </c>
       <c r="Q4" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -7590,7 +7590,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -7599,25 +7599,25 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>72.2</v>
+        <v>60.6</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I10" s="3" t="n">
-        <v>50</v>
+        <v>36.4</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-N</t>
+          <t>N-D-U-U</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -7626,21 +7626,21 @@
         </is>
       </c>
       <c r="M10" s="3" t="n">
-        <v>80</v>
+        <v>62.5</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P10" s="3" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
@@ -8229,34 +8229,34 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>57.1</v>
+        <v>75</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I19" s="3" t="n">
-        <v>85.7</v>
+        <v>75</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-U</t>
+          <t>U-D-N-N</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -8265,18 +8265,18 @@
         </is>
       </c>
       <c r="M19" s="3" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="N19" s="4" t="n">
         <v>4</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P19" s="3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>4</v>
@@ -8580,57 +8580,57 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>81.2</v>
+        <v>40</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I24" s="3" t="n">
-        <v>43.8</v>
+        <v>70</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="M24" s="3" t="n">
-        <v>66.7</v>
+        <v>33.3</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="P24" s="3" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -8944,48 +8944,48 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I29" s="3" t="n">
         <v>66.7</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-D</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M29" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P29" s="3" t="n">
-        <v>66.7</v>
+        <v>75</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
@@ -9006,57 +9006,57 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F30" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="J30" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>U-D-U-N</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>D/N/U</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="N30" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="n">
         <v>66.7</v>
       </c>
-      <c r="G30" s="4" t="n">
-        <v>36</v>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I30" s="3" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="J30" s="4" t="n">
-        <v>36</v>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>U-D-U-D</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M30" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="N30" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P30" s="3" t="n">
-        <v>40</v>
-      </c>
       <c r="Q30" s="4" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -9219,7 +9219,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -9228,25 +9228,25 @@
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>74.09999999999999</v>
+        <v>68.8</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I33" s="3" t="n">
-        <v>51.9</v>
+        <v>56.2</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-D</t>
+          <t>N-U-U-N</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -9255,21 +9255,21 @@
         </is>
       </c>
       <c r="M33" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>66.7</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P33" s="3" t="n">
-        <v>55.6</v>
+        <v>66.7</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34">
@@ -9641,7 +9641,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -9650,10 +9650,10 @@
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>56.2</v>
+        <v>66.7</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -9661,14 +9661,14 @@
         </is>
       </c>
       <c r="I39" s="3" t="n">
-        <v>53.1</v>
+        <v>44.4</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-D</t>
+          <t>U-U-U-N</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
@@ -9677,21 +9677,21 @@
         </is>
       </c>
       <c r="M39" s="3" t="n">
-        <v>64.3</v>
+        <v>66.7</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P39" s="3" t="n">
-        <v>64.3</v>
+        <v>66.7</v>
       </c>
       <c r="Q39" s="4" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
@@ -9854,57 +9854,49 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>N-U-D</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
-        </is>
-      </c>
-      <c r="F42" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr"/>
       <c r="G42" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
-        </is>
-      </c>
-      <c r="I42" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr"/>
       <c r="J42" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-D</t>
+          <t>D-N-U-N</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M42" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr"/>
       <c r="N42" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P42" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr"/>
       <c r="Q42" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -10280,34 +10272,34 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>53.8</v>
+        <v>87.5</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I48" s="3" t="n">
-        <v>61.5</v>
+        <v>62.5</v>
       </c>
       <c r="J48" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-U</t>
+          <t>U-D-N-N</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
@@ -10316,18 +10308,18 @@
         </is>
       </c>
       <c r="M48" s="3" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="N48" s="4" t="n">
         <v>5</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P48" s="3" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="Q48" s="4" t="n">
         <v>5</v>
@@ -10915,34 +10907,34 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>D-N-D</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I57" s="3" t="n">
-        <v>46.7</v>
+        <v>62.5</v>
       </c>
       <c r="J57" s="4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-D</t>
+          <t>U-D-N-N</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
@@ -10951,21 +10943,21 @@
         </is>
       </c>
       <c r="M57" s="3" t="n">
-        <v>57.1</v>
+        <v>66.7</v>
       </c>
       <c r="N57" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P57" s="3" t="n">
-        <v>42.9</v>
+        <v>66.7</v>
       </c>
       <c r="Q57" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -10986,7 +10978,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -10995,48 +10987,48 @@
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>57.1</v>
+        <v>57.9</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I58" s="3" t="n">
-        <v>42.9</v>
+        <v>57.9</v>
       </c>
       <c r="J58" s="4" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-D</t>
+          <t>N-D-U-U</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M58" s="3" t="n">
         <v>100</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P58" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q58" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -11199,39 +11191,39 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>N-N-D</t>
+          <t>N-N-N</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I61" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="J61" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-D</t>
+          <t>D-N-N-N</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M61" s="3" t="n">
@@ -11972,7 +11964,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -11981,48 +11973,48 @@
         </is>
       </c>
       <c r="F72" s="3" t="n">
-        <v>55.2</v>
+        <v>42.3</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I72" s="3" t="n">
-        <v>58.6</v>
+        <v>46.2</v>
       </c>
       <c r="J72" s="4" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-U</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="M72" s="3" t="n">
-        <v>54.5</v>
+        <v>40</v>
       </c>
       <c r="N72" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P72" s="3" t="n">
-        <v>45.5</v>
+        <v>50</v>
       </c>
       <c r="Q72" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="73">
@@ -12185,34 +12177,30 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F75" s="3" t="n">
-        <v>83.3</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="inlineStr"/>
       <c r="G75" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I75" s="3" t="n">
-        <v>66.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I75" s="3" t="inlineStr"/>
       <c r="J75" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-D</t>
+          <t>N-D-U-N</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
@@ -12465,7 +12453,7 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>N-U-D</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -12474,48 +12462,48 @@
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>62.5</v>
+        <v>57.1</v>
       </c>
       <c r="G79" s="4" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I79" s="3" t="n">
-        <v>56.2</v>
+        <v>57.1</v>
       </c>
       <c r="J79" s="4" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>N-N-U-D</t>
+          <t>N-N-U-N</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="M79" s="3" t="n">
         <v>50</v>
       </c>
       <c r="N79" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P79" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="Q79" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
@@ -12678,7 +12666,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -12687,41 +12675,41 @@
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>75</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I82" s="3" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="J82" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>D-D-D-D</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M82" s="3" t="n">
         <v>100</v>
-      </c>
-      <c r="J82" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="K82" s="2" t="inlineStr">
-        <is>
-          <t>D-D-D-N</t>
-        </is>
-      </c>
-      <c r="L82" s="2" t="inlineStr">
-        <is>
-          <t>N/U</t>
-        </is>
-      </c>
-      <c r="M82" s="3" t="n">
-        <v>50</v>
       </c>
       <c r="N82" s="4" t="n">
         <v>2</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P82" s="3" t="n">
@@ -12749,19 +12737,19 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>U-N-D</t>
+          <t>U-N-N</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F83" s="3" t="n">
-        <v>69.2</v>
+        <v>70</v>
       </c>
       <c r="G83" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
@@ -12769,37 +12757,37 @@
         </is>
       </c>
       <c r="I83" s="3" t="n">
-        <v>46.2</v>
+        <v>60</v>
       </c>
       <c r="J83" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-D</t>
+          <t>D-U-N-N</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M83" s="3" t="n">
-        <v>75</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="N83" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P83" s="3" t="n">
-        <v>75</v>
+        <v>57.1</v>
       </c>
       <c r="Q83" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="84">
@@ -12891,7 +12879,7 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -12900,48 +12888,44 @@
         </is>
       </c>
       <c r="F85" s="3" t="n">
-        <v>61.9</v>
+        <v>50</v>
       </c>
       <c r="G85" s="4" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="I85" s="3" t="n">
-        <v>52.4</v>
+        <v>37.5</v>
       </c>
       <c r="J85" s="4" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-D</t>
+          <t>N-U-U-N</t>
         </is>
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M85" s="3" t="n">
-        <v>66.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M85" s="3" t="inlineStr"/>
       <c r="N85" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P85" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P85" s="3" t="inlineStr"/>
       <c r="Q85" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -12962,7 +12946,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>N-U-D</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -12971,25 +12955,25 @@
         </is>
       </c>
       <c r="F86" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="G86" s="4" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I86" s="3" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="J86" s="4" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-D</t>
+          <t>U-N-U-N</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
@@ -12998,21 +12982,21 @@
         </is>
       </c>
       <c r="M86" s="3" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="N86" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P86" s="3" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="Q86" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
@@ -13104,7 +13088,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -13113,25 +13097,25 @@
         </is>
       </c>
       <c r="F88" s="3" t="n">
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="G88" s="4" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I88" s="3" t="n">
-        <v>46.9</v>
+        <v>50</v>
       </c>
       <c r="J88" s="4" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-D</t>
+          <t>U-D-U-N</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
@@ -13140,21 +13124,21 @@
         </is>
       </c>
       <c r="M88" s="3" t="n">
-        <v>84.59999999999999</v>
+        <v>90</v>
       </c>
       <c r="N88" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="P88" s="3" t="n">
-        <v>53.8</v>
+        <v>40</v>
       </c>
       <c r="Q88" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="89">
@@ -13246,7 +13230,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -13255,37 +13239,37 @@
         </is>
       </c>
       <c r="F90" s="3" t="n">
-        <v>75</v>
+        <v>48.8</v>
       </c>
       <c r="G90" s="4" t="n">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I90" s="3" t="n">
-        <v>50</v>
+        <v>41.5</v>
       </c>
       <c r="J90" s="4" t="n">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-U</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M90" s="3" t="n">
-        <v>66.7</v>
+        <v>53.3</v>
       </c>
       <c r="N90" s="4" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
@@ -13293,10 +13277,10 @@
         </is>
       </c>
       <c r="P90" s="3" t="n">
-        <v>66.7</v>
+        <v>53.3</v>
       </c>
       <c r="Q90" s="4" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="91">
@@ -13530,7 +13514,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -13539,10 +13523,10 @@
         </is>
       </c>
       <c r="F94" s="3" t="n">
-        <v>54.3</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="G94" s="4" t="n">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -13550,26 +13534,26 @@
         </is>
       </c>
       <c r="I94" s="3" t="n">
-        <v>37.1</v>
+        <v>38.5</v>
       </c>
       <c r="J94" s="4" t="n">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M94" s="3" t="n">
-        <v>35.3</v>
+        <v>100</v>
       </c>
       <c r="N94" s="4" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
@@ -13577,10 +13561,10 @@
         </is>
       </c>
       <c r="P94" s="3" t="n">
-        <v>52.9</v>
+        <v>42.9</v>
       </c>
       <c r="Q94" s="4" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="95">
@@ -13672,7 +13656,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -13681,10 +13665,10 @@
         </is>
       </c>
       <c r="F96" s="3" t="n">
-        <v>50</v>
+        <v>56.2</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -13692,26 +13676,26 @@
         </is>
       </c>
       <c r="I96" s="3" t="n">
-        <v>60</v>
+        <v>43.8</v>
       </c>
       <c r="J96" s="4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-D</t>
+          <t>D-D-U-U</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M96" s="3" t="n">
-        <v>44.4</v>
+        <v>66.7</v>
       </c>
       <c r="N96" s="4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
@@ -13719,10 +13703,10 @@
         </is>
       </c>
       <c r="P96" s="3" t="n">
-        <v>55.6</v>
+        <v>41.7</v>
       </c>
       <c r="Q96" s="4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="97">
@@ -13743,7 +13727,7 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -13752,10 +13736,10 @@
         </is>
       </c>
       <c r="F97" s="3" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G97" s="4" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
@@ -13763,37 +13747,37 @@
         </is>
       </c>
       <c r="I97" s="3" t="n">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="J97" s="4" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M97" s="3" t="n">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="N97" s="4" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P97" s="3" t="n">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="Q97" s="4" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="98">
@@ -14098,7 +14082,7 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -14107,10 +14091,10 @@
         </is>
       </c>
       <c r="F102" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="G102" s="4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
@@ -14118,14 +14102,14 @@
         </is>
       </c>
       <c r="I102" s="3" t="n">
-        <v>58.8</v>
+        <v>53.8</v>
       </c>
       <c r="J102" s="4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-U</t>
+          <t>N-D-U-N</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
@@ -14137,18 +14121,18 @@
         <v>100</v>
       </c>
       <c r="N102" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P102" s="3" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="Q102" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="103">

--- a/BIS_tr.xlsx
+++ b/BIS_tr.xlsx
@@ -629,7 +629,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -638,48 +638,48 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>65.90000000000001</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>D-N-D-U</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="L3" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
           <t>D/U</t>
         </is>
       </c>
-      <c r="G3" s="3" t="n">
-        <v>36.6</v>
-      </c>
-      <c r="H3" s="4" t="n">
-        <v>41</v>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>D-N-D-N</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="n">
-        <v>61.5</v>
-      </c>
-      <c r="L3" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
       <c r="N3" s="3" t="n">
-        <v>53.8</v>
+        <v>36</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
@@ -812,7 +812,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -821,25 +821,25 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>68.5</v>
+        <v>58.9</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>89</v>
+        <v>175</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G6" s="3" t="n">
-        <v>43.8</v>
+        <v>39.4</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>89</v>
+        <v>175</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-N</t>
+          <t>N-U-U-U</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -848,10 +848,10 @@
         </is>
       </c>
       <c r="K6" s="3" t="n">
-        <v>68.2</v>
+        <v>53.3</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="N6" s="3" t="n">
-        <v>45.5</v>
+        <v>50</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7">
@@ -934,7 +934,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -943,48 +943,48 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>76.2</v>
+        <v>47.1</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>D-D-U-U</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>D/N</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="G8" s="3" t="n">
-        <v>47.6</v>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>D-D-U-N</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="n">
-        <v>88.90000000000001</v>
-      </c>
-      <c r="L8" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
       <c r="N8" s="3" t="n">
-        <v>44.4</v>
+        <v>62.5</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -995,7 +995,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1004,25 +1004,25 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>72.2</v>
+        <v>65.7</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>97</v>
+        <v>67</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G9" s="3" t="n">
-        <v>47.4</v>
+        <v>35.8</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>97</v>
+        <v>67</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>D-N-D-U</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1031,21 +1031,21 @@
         </is>
       </c>
       <c r="K9" s="3" t="n">
-        <v>72.40000000000001</v>
+        <v>50</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N9" s="3" t="n">
-        <v>51.7</v>
+        <v>43.8</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1065,25 +1065,25 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>64.09999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>78</v>
+        <v>146</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G10" s="3" t="n">
-        <v>35.9</v>
+        <v>38.4</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>78</v>
+        <v>146</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1092,21 +1092,21 @@
         </is>
       </c>
       <c r="K10" s="3" t="n">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N10" s="3" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1126,10 +1126,10 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>54.4</v>
+        <v>66.7</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>149</v>
+        <v>90</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1137,14 +1137,14 @@
         </is>
       </c>
       <c r="G11" s="3" t="n">
-        <v>43.6</v>
+        <v>40</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>149</v>
+        <v>90</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-U</t>
+          <t>U-D-U-N</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="K11" s="3" t="n">
-        <v>57.9</v>
+        <v>59.5</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>76</v>
+        <v>37</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
@@ -1164,10 +1164,10 @@
         </is>
       </c>
       <c r="N11" s="3" t="n">
-        <v>42.1</v>
+        <v>40.5</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>76</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1187,10 +1187,10 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>57.1</v>
+        <v>42.3</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1198,14 +1198,14 @@
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>57.1</v>
+        <v>57.7</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-N-U-D</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1214,21 +1214,21 @@
         </is>
       </c>
       <c r="K12" s="3" t="n">
-        <v>60</v>
+        <v>61.5</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N12" s="3" t="n">
-        <v>40</v>
+        <v>61.5</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1248,25 +1248,25 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>55.6</v>
+        <v>55.2</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G13" s="3" t="n">
-        <v>44.4</v>
+        <v>48.3</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1275,21 +1275,21 @@
         </is>
       </c>
       <c r="K13" s="3" t="n">
-        <v>100</v>
+        <v>53.8</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N13" s="3" t="n">
-        <v>100</v>
+        <v>53.8</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1309,25 +1309,25 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>64.2</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G14" s="3" t="n">
-        <v>45.3</v>
+        <v>35.4</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-U</t>
+          <t>U-N-D-N</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1336,21 +1336,21 @@
         </is>
       </c>
       <c r="K14" s="3" t="n">
-        <v>58.5</v>
+        <v>85.7</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N14" s="3" t="n">
-        <v>39</v>
+        <v>42.9</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1492,48 +1492,48 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>65.90000000000001</v>
+        <v>48.1</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>82</v>
+        <v>133</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>133</v>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>D-D-D-D</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>N/U</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="L17" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="G17" s="3" t="n">
-        <v>43.9</v>
-      </c>
-      <c r="H17" s="4" t="n">
-        <v>82</v>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>D-D-D-N</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="n">
-        <v>67.59999999999999</v>
-      </c>
-      <c r="L17" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
       <c r="N17" s="3" t="n">
-        <v>41.2</v>
+        <v>45.2</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1553,25 +1553,25 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>81.8</v>
+        <v>73.7</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G18" s="3" t="n">
-        <v>45.5</v>
+        <v>53.9</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>D-N-D-D</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1580,21 +1580,21 @@
         </is>
       </c>
       <c r="K18" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>64.5</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N18" s="3" t="n">
-        <v>57.1</v>
+        <v>58.1</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1675,10 +1675,10 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>68.2</v>
+        <v>75.3</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>129</v>
+        <v>81</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1686,14 +1686,14 @@
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>129</v>
+        <v>81</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1702,10 +1702,10 @@
         </is>
       </c>
       <c r="K20" s="3" t="n">
-        <v>71.09999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="N20" s="3" t="n">
-        <v>48.9</v>
+        <v>38.9</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>45</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21">
@@ -1788,53 +1788,57 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>55.6</v>
+        <v>47.8</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>18</v>
+        <v>69</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G22" s="3" t="n">
-        <v>50</v>
+        <v>43.5</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>18</v>
+        <v>69</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-N</t>
+          <t>N-D-D-U</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr"/>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="L22" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N22" s="3" t="inlineStr"/>
+          <t>D/N</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>40</v>
+      </c>
       <c r="O22" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
@@ -1845,7 +1849,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1854,10 +1858,10 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>57.1</v>
+        <v>64.3</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1865,14 +1869,14 @@
         </is>
       </c>
       <c r="G23" s="3" t="n">
-        <v>54</v>
+        <v>53.6</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-D</t>
+          <t>U-D-U-N</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1881,10 +1885,10 @@
         </is>
       </c>
       <c r="K23" s="3" t="n">
-        <v>60.9</v>
+        <v>55.6</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
@@ -1892,10 +1896,10 @@
         </is>
       </c>
       <c r="N23" s="3" t="n">
-        <v>60.9</v>
+        <v>66.7</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24">
@@ -2272,7 +2276,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2281,25 +2285,25 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>60</v>
+        <v>58.6</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>40</v>
+        <v>42.9</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-N</t>
+          <t>D-U-N-D</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -2308,21 +2312,21 @@
         </is>
       </c>
       <c r="K30" s="3" t="n">
-        <v>63.6</v>
+        <v>63.3</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N30" s="3" t="n">
-        <v>63.6</v>
+        <v>56.7</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31">
@@ -2394,7 +2398,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2403,10 +2407,10 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>73</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>74</v>
+        <v>141</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2414,14 +2418,14 @@
         </is>
       </c>
       <c r="G32" s="3" t="n">
-        <v>40.5</v>
+        <v>44.7</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>74</v>
+        <v>141</v>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -2430,21 +2434,21 @@
         </is>
       </c>
       <c r="K32" s="3" t="n">
-        <v>72.7</v>
+        <v>60</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N32" s="3" t="n">
-        <v>40.9</v>
+        <v>45.5</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>22</v>
+        <v>55</v>
       </c>
     </row>
     <row r="33">
@@ -2455,7 +2459,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-U</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2464,25 +2468,25 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>75.3</v>
+        <v>63.4</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G33" s="3" t="n">
-        <v>39.7</v>
+        <v>39.8</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>U-U-N-N</t>
+          <t>U-U-N-U</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -2491,21 +2495,21 @@
         </is>
       </c>
       <c r="K33" s="3" t="n">
-        <v>66.7</v>
+        <v>57.1</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N33" s="3" t="n">
-        <v>48.1</v>
+        <v>38.1</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="34">
@@ -2577,34 +2581,34 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>50.7</v>
+        <v>50</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>69</v>
+        <v>20</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v>44.9</v>
+        <v>55</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>69</v>
+        <v>20</v>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-U</t>
+          <t>U-U-U-N</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -2613,21 +2617,21 @@
         </is>
       </c>
       <c r="K35" s="3" t="n">
-        <v>53.3</v>
+        <v>70</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N35" s="3" t="n">
-        <v>46.7</v>
+        <v>50</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36">
@@ -2699,7 +2703,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2708,10 +2712,10 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>63.2</v>
+        <v>54.3</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>57</v>
+        <v>175</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2719,14 +2723,14 @@
         </is>
       </c>
       <c r="G37" s="3" t="n">
-        <v>45.6</v>
+        <v>43.4</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>57</v>
+        <v>175</v>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -2735,10 +2739,10 @@
         </is>
       </c>
       <c r="K37" s="3" t="n">
-        <v>63.2</v>
+        <v>53.9</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
@@ -2746,10 +2750,10 @@
         </is>
       </c>
       <c r="N37" s="3" t="n">
-        <v>47.4</v>
+        <v>50</v>
       </c>
       <c r="O37" s="4" t="n">
-        <v>19</v>
+        <v>76</v>
       </c>
     </row>
     <row r="38">
@@ -2821,7 +2825,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-U</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2830,10 +2834,10 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>59.6</v>
+        <v>60.6</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2841,14 +2845,14 @@
         </is>
       </c>
       <c r="G39" s="3" t="n">
-        <v>36.8</v>
+        <v>43.7</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>U-U-N-N</t>
+          <t>U-U-N-U</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -2857,10 +2861,10 @@
         </is>
       </c>
       <c r="K39" s="3" t="n">
-        <v>57.9</v>
+        <v>62.5</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
@@ -2868,10 +2872,10 @@
         </is>
       </c>
       <c r="N39" s="3" t="n">
-        <v>42.1</v>
+        <v>45.8</v>
       </c>
       <c r="O39" s="4" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="40">
@@ -2882,7 +2886,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2891,25 +2895,25 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>75.7</v>
+        <v>63.6</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G40" s="3" t="n">
-        <v>43.2</v>
+        <v>52.3</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-N</t>
+          <t>N-U-D-U</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -2918,7 +2922,7 @@
         </is>
       </c>
       <c r="K40" s="3" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="L40" s="4" t="n">
         <v>10</v>
@@ -2943,7 +2947,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2952,48 +2956,48 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>47.3</v>
+        <v>42.1</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>112</v>
+        <v>19</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G41" s="3" t="n">
-        <v>48.2</v>
+        <v>36.8</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>112</v>
+        <v>19</v>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-U</t>
+          <t>U-U-U-N</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="K41" s="3" t="n">
-        <v>52.8</v>
+        <v>40</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="N41" s="3" t="n">
-        <v>56.6</v>
+        <v>40</v>
       </c>
       <c r="O41" s="4" t="n">
-        <v>53</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42">
@@ -3126,7 +3130,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3135,10 +3139,10 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>88.2</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -3146,14 +3150,14 @@
         </is>
       </c>
       <c r="G44" s="3" t="n">
-        <v>52.9</v>
+        <v>48.7</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-N</t>
+          <t>U-U-D-U</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -3162,21 +3166,21 @@
         </is>
       </c>
       <c r="K44" s="3" t="n">
-        <v>100</v>
+        <v>52.6</v>
       </c>
       <c r="L44" s="4" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N44" s="3" t="n">
-        <v>57.1</v>
+        <v>42.1</v>
       </c>
       <c r="O44" s="4" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="45">
@@ -3187,7 +3191,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3196,10 +3200,10 @@
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>53.6</v>
+        <v>49.7</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>84</v>
+        <v>197</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -3207,14 +3211,14 @@
         </is>
       </c>
       <c r="G45" s="3" t="n">
-        <v>34.5</v>
+        <v>45.2</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>84</v>
+        <v>197</v>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-N</t>
+          <t>N-U-D-D</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -3223,21 +3227,21 @@
         </is>
       </c>
       <c r="K45" s="3" t="n">
-        <v>84.59999999999999</v>
+        <v>48.6</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N45" s="3" t="n">
-        <v>38.5</v>
+        <v>62.2</v>
       </c>
       <c r="O45" s="4" t="n">
-        <v>13</v>
+        <v>37</v>
       </c>
     </row>
     <row r="46">
@@ -3370,7 +3374,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-U</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3379,48 +3383,48 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>73.2</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="H48" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>D-N-N-U</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="L48" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="G48" s="3" t="n">
-        <v>39</v>
-      </c>
-      <c r="H48" s="4" t="n">
-        <v>41</v>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>D-N-N-N</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K48" s="3" t="n">
-        <v>58.8</v>
-      </c>
-      <c r="L48" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="M48" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="N48" s="3" t="n">
-        <v>41.2</v>
+        <v>43.8</v>
       </c>
       <c r="O48" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="49">
@@ -3492,7 +3496,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -3501,25 +3505,25 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>65.59999999999999</v>
+        <v>57.9</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>61</v>
+        <v>133</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G50" s="3" t="n">
-        <v>42.6</v>
+        <v>45.9</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>61</v>
+        <v>133</v>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -3528,21 +3532,21 @@
         </is>
       </c>
       <c r="K50" s="3" t="n">
-        <v>56.5</v>
+        <v>62.5</v>
       </c>
       <c r="L50" s="4" t="n">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N50" s="3" t="n">
-        <v>47.8</v>
+        <v>50</v>
       </c>
       <c r="O50" s="4" t="n">
-        <v>23</v>
+        <v>48</v>
       </c>
     </row>
     <row r="51">
@@ -3614,7 +3618,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3623,25 +3627,25 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>67.5</v>
+        <v>70.2</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G52" s="3" t="n">
-        <v>41.2</v>
+        <v>38.3</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-U</t>
+          <t>D-D-N-N</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -3650,10 +3654,10 @@
         </is>
       </c>
       <c r="K52" s="3" t="n">
-        <v>66.7</v>
+        <v>77.8</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
@@ -3661,10 +3665,10 @@
         </is>
       </c>
       <c r="N52" s="3" t="n">
-        <v>44.4</v>
+        <v>55.6</v>
       </c>
       <c r="O52" s="4" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
     </row>
     <row r="53">
@@ -3858,7 +3862,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3867,48 +3871,48 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>63.5</v>
+        <v>55.6</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G56" s="3" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="H56" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>U-U-U-N</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="L56" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="H56" s="4" t="n">
-        <v>52</v>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>U-U-U-D</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K56" s="3" t="n">
-        <v>70</v>
-      </c>
-      <c r="L56" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="M56" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="N56" s="3" t="n">
-        <v>55</v>
-      </c>
       <c r="O56" s="4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="57">
@@ -3919,7 +3923,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-N-N</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3928,10 +3932,10 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>64.3</v>
+        <v>76.8</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3939,14 +3943,14 @@
         </is>
       </c>
       <c r="G57" s="3" t="n">
-        <v>61.9</v>
+        <v>37.5</v>
       </c>
       <c r="H57" s="4" t="n">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-U</t>
+          <t>D-N-N-N</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -3955,21 +3959,21 @@
         </is>
       </c>
       <c r="K57" s="3" t="n">
-        <v>66.7</v>
+        <v>77.3</v>
       </c>
       <c r="L57" s="4" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="N57" s="3" t="n">
-        <v>50</v>
+        <v>36.4</v>
       </c>
       <c r="O57" s="4" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="58">
@@ -4102,7 +4106,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4111,25 +4115,25 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>61.5</v>
+        <v>63.2</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>156</v>
+        <v>87</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G60" s="3" t="n">
-        <v>39.1</v>
+        <v>37.9</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>156</v>
+        <v>87</v>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-U</t>
+          <t>D-U-U-N</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -4138,10 +4142,10 @@
         </is>
       </c>
       <c r="K60" s="3" t="n">
-        <v>59.3</v>
+        <v>75.8</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>59</v>
+        <v>33</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
@@ -4149,10 +4153,10 @@
         </is>
       </c>
       <c r="N60" s="3" t="n">
-        <v>44.1</v>
+        <v>36.4</v>
       </c>
       <c r="O60" s="4" t="n">
-        <v>59</v>
+        <v>33</v>
       </c>
     </row>
     <row r="61">
@@ -4163,19 +4167,19 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-N-N</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>62.5</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -4183,37 +4187,37 @@
         </is>
       </c>
       <c r="G61" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>50</v>
       </c>
       <c r="H61" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>N-N-N-U</t>
+          <t>N-N-N-N</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K61" s="3" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="L61" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="N61" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -4285,7 +4289,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -4294,25 +4298,25 @@
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>82.59999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G63" s="3" t="n">
-        <v>47.8</v>
+        <v>53.5</v>
       </c>
       <c r="H63" s="4" t="n">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-U</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -4321,21 +4325,21 @@
         </is>
       </c>
       <c r="K63" s="3" t="n">
-        <v>76.90000000000001</v>
+        <v>76.5</v>
       </c>
       <c r="L63" s="4" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N63" s="3" t="n">
-        <v>46.2</v>
+        <v>52.9</v>
       </c>
       <c r="O63" s="4" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="64">
@@ -4529,7 +4533,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -4538,48 +4542,44 @@
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>55.6</v>
+        <v>75</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="G67" s="3" t="n">
-        <v>55.6</v>
+        <v>50</v>
       </c>
       <c r="H67" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-U</t>
+          <t>N-U-U-N</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K67" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr"/>
       <c r="L67" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="N67" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr"/>
       <c r="O67" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -4782,10 +4782,10 @@
         </is>
       </c>
       <c r="D71" s="3" t="n">
-        <v>61.3</v>
+        <v>51.9</v>
       </c>
       <c r="E71" s="4" t="n">
-        <v>80</v>
+        <v>156</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4793,14 +4793,14 @@
         </is>
       </c>
       <c r="G71" s="3" t="n">
-        <v>43.8</v>
+        <v>44.9</v>
       </c>
       <c r="H71" s="4" t="n">
-        <v>80</v>
+        <v>156</v>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-N</t>
+          <t>N-U-D-D</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -4809,10 +4809,10 @@
         </is>
       </c>
       <c r="K71" s="3" t="n">
-        <v>53.3</v>
+        <v>55.2</v>
       </c>
       <c r="L71" s="4" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
@@ -4820,10 +4820,10 @@
         </is>
       </c>
       <c r="N71" s="3" t="n">
-        <v>46.7</v>
+        <v>44.8</v>
       </c>
       <c r="O71" s="4" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
     </row>
     <row r="72">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -4965,25 +4965,25 @@
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>67.40000000000001</v>
+        <v>50.8</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G74" s="3" t="n">
-        <v>37.2</v>
+        <v>44.4</v>
       </c>
       <c r="H74" s="4" t="n">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>D-N-D-U</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -4992,10 +4992,10 @@
         </is>
       </c>
       <c r="K74" s="3" t="n">
-        <v>54.5</v>
+        <v>58.8</v>
       </c>
       <c r="L74" s="4" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
@@ -5003,10 +5003,10 @@
         </is>
       </c>
       <c r="N74" s="3" t="n">
-        <v>45.5</v>
+        <v>47.1</v>
       </c>
       <c r="O74" s="4" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="75">
@@ -5017,53 +5017,57 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="E75" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="H75" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>D-U-N-D</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K75" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="L75" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>D/U</t>
-        </is>
-      </c>
-      <c r="G75" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="H75" s="4" t="n">
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="O75" s="4" t="n">
         <v>5</v>
-      </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>D-U-N-N</t>
-        </is>
-      </c>
-      <c r="J75" s="2" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="K75" s="3" t="inlineStr"/>
-      <c r="L75" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M75" s="2" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N75" s="3" t="inlineStr"/>
-      <c r="O75" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -5257,7 +5261,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-U</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -5266,25 +5270,25 @@
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>65.5</v>
+        <v>66.2</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="G79" s="3" t="n">
-        <v>45.5</v>
+        <v>33.8</v>
       </c>
       <c r="H79" s="4" t="n">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>N-U-N-N</t>
+          <t>N-U-N-U</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -5293,21 +5297,21 @@
         </is>
       </c>
       <c r="K79" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>63.6</v>
       </c>
       <c r="L79" s="4" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N79" s="3" t="n">
-        <v>57.1</v>
+        <v>40.9</v>
       </c>
       <c r="O79" s="4" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
     </row>
     <row r="80">
@@ -5379,7 +5383,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -5388,25 +5392,25 @@
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>51.7</v>
+        <v>57.7</v>
       </c>
       <c r="E81" s="4" t="n">
-        <v>60</v>
+        <v>123</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G81" s="3" t="n">
-        <v>41.7</v>
+        <v>42.3</v>
       </c>
       <c r="H81" s="4" t="n">
-        <v>60</v>
+        <v>123</v>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -5415,10 +5419,10 @@
         </is>
       </c>
       <c r="K81" s="3" t="n">
-        <v>50</v>
+        <v>58.8</v>
       </c>
       <c r="L81" s="4" t="n">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
@@ -5426,10 +5430,10 @@
         </is>
       </c>
       <c r="N81" s="3" t="n">
-        <v>38.5</v>
+        <v>43.1</v>
       </c>
       <c r="O81" s="4" t="n">
-        <v>26</v>
+        <v>51</v>
       </c>
     </row>
     <row r="82">
@@ -5562,7 +5566,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -5571,25 +5575,25 @@
         </is>
       </c>
       <c r="D84" s="3" t="n">
-        <v>62.3</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>130</v>
+        <v>91</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G84" s="3" t="n">
-        <v>40</v>
+        <v>39.6</v>
       </c>
       <c r="H84" s="4" t="n">
-        <v>130</v>
+        <v>91</v>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-U</t>
+          <t>N-U-D-N</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -5598,21 +5602,21 @@
         </is>
       </c>
       <c r="K84" s="3" t="n">
-        <v>78.3</v>
+        <v>69.2</v>
       </c>
       <c r="L84" s="4" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N84" s="3" t="n">
-        <v>43.5</v>
+        <v>50</v>
       </c>
       <c r="O84" s="4" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="85">
@@ -5684,7 +5688,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-U</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -5693,48 +5697,48 @@
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>75</v>
+        <v>53.6</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G86" s="3" t="n">
-        <v>40</v>
+        <v>47.6</v>
       </c>
       <c r="H86" s="4" t="n">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>N-U-N-N</t>
+          <t>N-U-N-U</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K86" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="L86" s="4" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N86" s="3" t="n">
-        <v>44.4</v>
+        <v>43.8</v>
       </c>
       <c r="O86" s="4" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="87">
@@ -5989,7 +5993,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -5998,10 +6002,10 @@
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>58</v>
+        <v>54.2</v>
       </c>
       <c r="E91" s="4" t="n">
-        <v>88</v>
+        <v>179</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -6009,14 +6013,14 @@
         </is>
       </c>
       <c r="G91" s="3" t="n">
-        <v>37.5</v>
+        <v>43.6</v>
       </c>
       <c r="H91" s="4" t="n">
-        <v>88</v>
+        <v>179</v>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
@@ -6025,10 +6029,10 @@
         </is>
       </c>
       <c r="K91" s="3" t="n">
-        <v>66.7</v>
+        <v>54.7</v>
       </c>
       <c r="L91" s="4" t="n">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
@@ -6036,10 +6040,10 @@
         </is>
       </c>
       <c r="N91" s="3" t="n">
-        <v>50</v>
+        <v>41.3</v>
       </c>
       <c r="O91" s="4" t="n">
-        <v>30</v>
+        <v>75</v>
       </c>
     </row>
     <row r="92">
@@ -6111,7 +6115,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>U-N-N</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -6120,25 +6124,25 @@
         </is>
       </c>
       <c r="D93" s="3" t="n">
-        <v>60</v>
+        <v>64.3</v>
       </c>
       <c r="E93" s="4" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G93" s="3" t="n">
-        <v>45</v>
+        <v>42.9</v>
       </c>
       <c r="H93" s="4" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-U</t>
+          <t>D-U-N-N</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
@@ -6147,10 +6151,10 @@
         </is>
       </c>
       <c r="K93" s="3" t="n">
-        <v>71</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="L93" s="4" t="n">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
@@ -6158,10 +6162,10 @@
         </is>
       </c>
       <c r="N93" s="3" t="n">
-        <v>48.4</v>
+        <v>64.3</v>
       </c>
       <c r="O93" s="4" t="n">
-        <v>31</v>
+        <v>14</v>
       </c>
     </row>
     <row r="94">
@@ -6294,7 +6298,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -6303,10 +6307,10 @@
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>54.4</v>
+        <v>51.6</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>169</v>
+        <v>64</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -6314,14 +6318,14 @@
         </is>
       </c>
       <c r="G96" s="3" t="n">
-        <v>48.5</v>
+        <v>42.2</v>
       </c>
       <c r="H96" s="4" t="n">
-        <v>169</v>
+        <v>64</v>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-U</t>
+          <t>D-U-U-N</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
@@ -6330,10 +6334,10 @@
         </is>
       </c>
       <c r="K96" s="3" t="n">
-        <v>52.2</v>
+        <v>50</v>
       </c>
       <c r="L96" s="4" t="n">
-        <v>69</v>
+        <v>32</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
@@ -6341,10 +6345,10 @@
         </is>
       </c>
       <c r="N96" s="3" t="n">
-        <v>53.6</v>
+        <v>43.8</v>
       </c>
       <c r="O96" s="4" t="n">
-        <v>69</v>
+        <v>32</v>
       </c>
     </row>
     <row r="97">
@@ -6355,7 +6359,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -6364,25 +6368,25 @@
         </is>
       </c>
       <c r="D97" s="3" t="n">
-        <v>70.90000000000001</v>
+        <v>71.2</v>
       </c>
       <c r="E97" s="4" t="n">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="G97" s="3" t="n">
-        <v>41.8</v>
+        <v>35.6</v>
       </c>
       <c r="H97" s="4" t="n">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-N</t>
+          <t>D-U-N-D</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
@@ -6391,21 +6395,21 @@
         </is>
       </c>
       <c r="K97" s="3" t="n">
-        <v>76.5</v>
+        <v>73.7</v>
       </c>
       <c r="L97" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N97" s="3" t="n">
-        <v>52.9</v>
+        <v>52.6</v>
       </c>
       <c r="O97" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="98">
@@ -6782,7 +6786,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-U</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -6791,25 +6795,25 @@
         </is>
       </c>
       <c r="D104" s="3" t="n">
-        <v>64.40000000000001</v>
+        <v>67.5</v>
       </c>
       <c r="E104" s="4" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G104" s="3" t="n">
-        <v>37.8</v>
+        <v>37.5</v>
       </c>
       <c r="H104" s="4" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>U-N-N-N</t>
+          <t>U-N-N-U</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
@@ -6818,21 +6822,21 @@
         </is>
       </c>
       <c r="K104" s="3" t="n">
-        <v>61.5</v>
+        <v>72.2</v>
       </c>
       <c r="L104" s="4" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="N104" s="3" t="n">
-        <v>38.5</v>
+        <v>33.3</v>
       </c>
       <c r="O104" s="4" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -7089,7 +7093,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -7098,25 +7102,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>75</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I3" s="3" t="n">
-        <v>75</v>
+        <v>41.2</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>D-N-D-U</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -7125,21 +7129,21 @@
         </is>
       </c>
       <c r="M3" s="3" t="n">
-        <v>66.7</v>
+        <v>62.5</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P3" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="Q3" s="4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -7298,7 +7302,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -7307,10 +7311,10 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>51.5</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -7318,26 +7322,26 @@
         </is>
       </c>
       <c r="I6" s="3" t="n">
-        <v>57.1</v>
+        <v>39.4</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-N</t>
+          <t>N-U-U-U</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M6" s="3" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -7345,10 +7349,10 @@
         </is>
       </c>
       <c r="P6" s="3" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -7440,39 +7444,39 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>57.1</v>
+        <v>50</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I8" s="3" t="n">
-        <v>42.9</v>
+        <v>62.5</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-U</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="M8" s="3" t="n">
@@ -7483,11 +7487,11 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P8" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q8" s="4" t="n">
         <v>2</v>
@@ -7511,7 +7515,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -7520,48 +7524,48 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I9" s="3" t="n">
-        <v>41.7</v>
+        <v>43.8</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>D-N-D-U</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M9" s="3" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P9" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -7582,57 +7586,57 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>46.2</v>
+        <v>67.7</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I10" s="3" t="n">
-        <v>46.2</v>
+        <v>41.9</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M10" s="3" t="n">
-        <v>37.5</v>
+        <v>58.3</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="P10" s="3" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
@@ -7653,7 +7657,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -7662,10 +7666,10 @@
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>47.4</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -7673,14 +7677,14 @@
         </is>
       </c>
       <c r="I11" s="3" t="n">
-        <v>47.4</v>
+        <v>38.5</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-U</t>
+          <t>U-D-U-N</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -7689,10 +7693,10 @@
         </is>
       </c>
       <c r="M11" s="3" t="n">
-        <v>57.1</v>
+        <v>66.7</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -7700,10 +7704,10 @@
         </is>
       </c>
       <c r="P11" s="3" t="n">
-        <v>47.6</v>
+        <v>40</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
@@ -7724,57 +7728,57 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>100</v>
+        <v>45.5</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I12" s="3" t="n">
-        <v>100</v>
+        <v>54.5</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-N-U-D</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="M12" s="3" t="n">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P12" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -7795,7 +7799,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -7804,44 +7808,48 @@
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>75</v>
+        <v>42.9</v>
       </c>
       <c r="G13" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>D-D-U-D</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="N13" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="n">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>D/U</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="J13" s="4" t="n">
+      <c r="Q13" s="4" t="n">
         <v>4</v>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>D-D-U-N</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M13" s="3" t="inlineStr"/>
-      <c r="N13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P13" s="3" t="inlineStr"/>
-      <c r="Q13" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -7862,7 +7870,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -7871,37 +7879,37 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>45.5</v>
+        <v>69.2</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I14" s="3" t="n">
-        <v>45.5</v>
+        <v>46.2</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-U</t>
+          <t>U-N-D-N</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M14" s="3" t="n">
-        <v>36.4</v>
+        <v>100</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -7909,10 +7917,10 @@
         </is>
       </c>
       <c r="P14" s="3" t="n">
-        <v>36.4</v>
+        <v>40</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -8075,7 +8083,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -8084,10 +8092,10 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>44.4</v>
+        <v>45.8</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -8095,14 +8103,14 @@
         </is>
       </c>
       <c r="I17" s="3" t="n">
-        <v>44.4</v>
+        <v>41.7</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -8111,21 +8119,21 @@
         </is>
       </c>
       <c r="M17" s="3" t="n">
-        <v>60</v>
+        <v>42.9</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P17" s="3" t="n">
-        <v>40</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
@@ -8146,7 +8154,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -8155,48 +8163,48 @@
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>80</v>
+        <v>72.7</v>
       </c>
       <c r="G18" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="J18" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>D-N-D-D</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="N18" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J18" s="4" t="n">
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>D/U</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q18" s="4" t="n">
         <v>5</v>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>D-N-D-N</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M18" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="N18" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P18" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q18" s="4" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -8288,7 +8296,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -8297,25 +8305,25 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>61.9</v>
+        <v>62.5</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I20" s="3" t="n">
-        <v>38.1</v>
+        <v>50</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -8324,21 +8332,21 @@
         </is>
       </c>
       <c r="M20" s="3" t="n">
-        <v>57.1</v>
+        <v>100</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P20" s="3" t="n">
-        <v>42.9</v>
+        <v>100</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -8430,53 +8438,57 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I22" s="3" t="n">
-        <v>50</v>
+        <v>44.4</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-N</t>
+          <t>N-D-D-U</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="inlineStr"/>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="N22" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P22" s="3" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="Q22" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -8497,7 +8509,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -8506,48 +8518,48 @@
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>47.4</v>
+        <v>60</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I23" s="3" t="n">
-        <v>68.40000000000001</v>
+        <v>50</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-D</t>
+          <t>U-D-U-N</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M23" s="3" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P23" s="3" t="n">
-        <v>80</v>
+        <v>66.7</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -8994,57 +9006,57 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F30" s="3" t="n">
         <v>50</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I30" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-N</t>
+          <t>D-U-N-D</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M30" s="3" t="n">
         <v>100</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="P30" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -9136,7 +9148,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -9145,10 +9157,10 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>75</v>
+        <v>60.7</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -9156,14 +9168,14 @@
         </is>
       </c>
       <c r="I32" s="3" t="n">
-        <v>58.3</v>
+        <v>50</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -9172,21 +9184,21 @@
         </is>
       </c>
       <c r="M32" s="3" t="n">
-        <v>80</v>
+        <v>66.7</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P32" s="3" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="33">
@@ -9207,7 +9219,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-U</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -9216,48 +9228,48 @@
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>47.1</v>
+        <v>58.3</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I33" s="3" t="n">
-        <v>41.2</v>
+        <v>41.7</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>U-U-N-N</t>
+          <t>U-U-N-U</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M33" s="3" t="n">
-        <v>44.4</v>
+        <v>100</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="P33" s="3" t="n">
-        <v>66.7</v>
+        <v>33.3</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -9349,54 +9361,54 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I35" s="3" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-U</t>
+          <t>U-U-U-N</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M35" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N35" s="4" t="n">
         <v>2</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P35" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q35" s="4" t="n">
         <v>2</v>
@@ -9487,7 +9499,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -9496,48 +9508,48 @@
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>44.4</v>
+        <v>48.1</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="J37" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>U-U-U-D</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="N37" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="I37" s="3" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="J37" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>U-U-U-N</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="M37" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="N37" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
       <c r="P37" s="3" t="n">
-        <v>60</v>
+        <v>58.3</v>
       </c>
       <c r="Q37" s="4" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38">
@@ -9629,19 +9641,19 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-U</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>50</v>
+        <v>55.6</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -9649,26 +9661,26 @@
         </is>
       </c>
       <c r="I39" s="3" t="n">
-        <v>60</v>
+        <v>44.4</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>U-U-N-N</t>
+          <t>U-U-N-U</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M39" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
@@ -9679,7 +9691,7 @@
         <v>100</v>
       </c>
       <c r="Q39" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
@@ -9700,7 +9712,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -9709,10 +9721,10 @@
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>80</v>
+        <v>62.5</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -9720,37 +9732,37 @@
         </is>
       </c>
       <c r="I40" s="3" t="n">
-        <v>80</v>
+        <v>56.2</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-N</t>
+          <t>N-U-D-U</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="M40" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="P40" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q40" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -9771,57 +9783,53 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>68.2</v>
+        <v>50</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I41" s="3" t="n">
-        <v>63.6</v>
+        <v>50</v>
       </c>
       <c r="J41" s="4" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-U</t>
+          <t>U-U-U-N</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="M41" s="3" t="n">
-        <v>85.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr"/>
       <c r="N41" s="4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P41" s="3" t="n">
-        <v>42.9</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr"/>
       <c r="Q41" s="4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -9972,53 +9980,57 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="G44" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="J44" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>U-U-D-U</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N44" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I44" s="3" t="n">
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P44" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="J44" s="4" t="n">
+      <c r="Q44" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>U-U-D-N</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M44" s="3" t="inlineStr"/>
-      <c r="N44" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P44" s="3" t="inlineStr"/>
-      <c r="Q44" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -10039,57 +10051,57 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F45" s="3" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="J45" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>N-U-D-D</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>N/U</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="G45" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I45" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J45" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>N-U-D-N</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="M45" s="3" t="n">
-        <v>100</v>
-      </c>
       <c r="N45" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P45" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q45" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -10252,7 +10264,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-U</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -10261,48 +10273,48 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I48" s="3" t="n">
-        <v>41.7</v>
+        <v>100</v>
       </c>
       <c r="J48" s="4" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-N</t>
+          <t>D-N-N-U</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M48" s="3" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P48" s="3" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="Q48" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -10394,7 +10406,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -10403,25 +10415,25 @@
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I50" s="3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J50" s="4" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
@@ -10430,21 +10442,21 @@
         </is>
       </c>
       <c r="M50" s="3" t="n">
-        <v>75</v>
+        <v>77.8</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P50" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="Q50" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="51">
@@ -10536,19 +10548,19 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>41.7</v>
+        <v>100</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -10556,34 +10568,34 @@
         </is>
       </c>
       <c r="I52" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="J52" s="4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-U</t>
+          <t>D-D-N-N</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M52" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="N52" s="4" t="n">
         <v>3</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P52" s="3" t="n">
-        <v>33.3</v>
+        <v>66.7</v>
       </c>
       <c r="Q52" s="4" t="n">
         <v>3</v>
@@ -10820,57 +10832,57 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="F56" s="3" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="G56" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="J56" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>U-U-U-N</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>N/U</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="G56" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I56" s="3" t="n">
-        <v>58.3</v>
-      </c>
-      <c r="J56" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>U-U-U-D</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M56" s="3" t="n">
-        <v>66.7</v>
-      </c>
       <c r="N56" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="P56" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="Q56" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -10891,7 +10903,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-N-N</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -10900,10 +10912,10 @@
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>42.9</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -10911,14 +10923,14 @@
         </is>
       </c>
       <c r="I57" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>46.2</v>
       </c>
       <c r="J57" s="4" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-U</t>
+          <t>D-N-N-N</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
@@ -10927,10 +10939,10 @@
         </is>
       </c>
       <c r="M57" s="3" t="n">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="N57" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
@@ -10938,10 +10950,10 @@
         </is>
       </c>
       <c r="P57" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q57" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58">
@@ -11104,7 +11116,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -11113,10 +11125,10 @@
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>52.9</v>
+        <v>53.8</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -11124,37 +11136,37 @@
         </is>
       </c>
       <c r="I60" s="3" t="n">
-        <v>44.1</v>
+        <v>46.2</v>
       </c>
       <c r="J60" s="4" t="n">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-U</t>
+          <t>D-U-U-N</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M60" s="3" t="n">
-        <v>52.9</v>
+        <v>50</v>
       </c>
       <c r="N60" s="4" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="P60" s="3" t="n">
-        <v>47.1</v>
+        <v>50</v>
       </c>
       <c r="Q60" s="4" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
     </row>
     <row r="61">
@@ -11175,7 +11187,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-N-N</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -11184,10 +11196,10 @@
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -11198,34 +11210,30 @@
         <v>100</v>
       </c>
       <c r="J61" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>N-N-N-U</t>
+          <t>N-N-N-N</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
-        </is>
-      </c>
-      <c r="M61" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M61" s="3" t="inlineStr"/>
       <c r="N61" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P61" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P61" s="3" t="inlineStr"/>
       <c r="Q61" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -11317,57 +11325,57 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I63" s="3" t="n">
-        <v>100</v>
+        <v>62.5</v>
       </c>
       <c r="J63" s="4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-U</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M63" s="3" t="n">
         <v>50</v>
       </c>
       <c r="N63" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P63" s="3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="Q63" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="64">
@@ -11601,34 +11609,30 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F67" s="3" t="n">
-        <v>66.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr"/>
       <c r="G67" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I67" s="3" t="n">
-        <v>66.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="inlineStr"/>
       <c r="J67" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-U</t>
+          <t>N-U-U-N</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
@@ -11877,19 +11881,19 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>37.5</v>
+        <v>45.8</v>
       </c>
       <c r="G71" s="4" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
@@ -11897,14 +11901,14 @@
         </is>
       </c>
       <c r="I71" s="3" t="n">
-        <v>56.2</v>
+        <v>41.7</v>
       </c>
       <c r="J71" s="4" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-N</t>
+          <t>N-U-D-D</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
@@ -11913,10 +11917,10 @@
         </is>
       </c>
       <c r="M71" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N71" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
@@ -11924,10 +11928,10 @@
         </is>
       </c>
       <c r="P71" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q71" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="72">
@@ -12090,7 +12094,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -12099,48 +12103,48 @@
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>55.6</v>
+        <v>58.3</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="I74" s="3" t="n">
-        <v>44.4</v>
+        <v>41.7</v>
       </c>
       <c r="J74" s="4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>D-N-D-U</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M74" s="3" t="n">
         <v>66.7</v>
       </c>
       <c r="N74" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P74" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="Q74" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="75">
@@ -12161,34 +12165,30 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="F75" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="inlineStr"/>
       <c r="G75" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I75" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I75" s="3" t="inlineStr"/>
       <c r="J75" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-N</t>
+          <t>D-U-N-D</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
@@ -12441,19 +12441,19 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-U</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="G79" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
@@ -12461,14 +12461,14 @@
         </is>
       </c>
       <c r="I79" s="3" t="n">
-        <v>50</v>
+        <v>55.6</v>
       </c>
       <c r="J79" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>N-U-N-N</t>
+          <t>N-U-N-U</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
@@ -12480,7 +12480,7 @@
         <v>100</v>
       </c>
       <c r="N79" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
@@ -12491,7 +12491,7 @@
         <v>100</v>
       </c>
       <c r="Q79" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
@@ -12583,7 +12583,7 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -12592,10 +12592,10 @@
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>66.7</v>
+        <v>42.9</v>
       </c>
       <c r="G81" s="4" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
@@ -12603,26 +12603,26 @@
         </is>
       </c>
       <c r="I81" s="3" t="n">
-        <v>50</v>
+        <v>53.6</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M81" s="3" t="n">
-        <v>75</v>
+        <v>46.2</v>
       </c>
       <c r="N81" s="4" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
@@ -12630,10 +12630,10 @@
         </is>
       </c>
       <c r="P81" s="3" t="n">
-        <v>50</v>
+        <v>53.8</v>
       </c>
       <c r="Q81" s="4" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="82">
@@ -12796,19 +12796,19 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F84" s="3" t="n">
-        <v>41.7</v>
+        <v>73.3</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -12816,37 +12816,37 @@
         </is>
       </c>
       <c r="I84" s="3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J84" s="4" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-U</t>
+          <t>N-U-D-N</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="M84" s="3" t="n">
-        <v>80</v>
+        <v>33.3</v>
       </c>
       <c r="N84" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P84" s="3" t="n">
-        <v>40</v>
+        <v>66.7</v>
       </c>
       <c r="Q84" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
@@ -12938,7 +12938,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-U</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -12947,44 +12947,48 @@
         </is>
       </c>
       <c r="F86" s="3" t="n">
-        <v>66.7</v>
+        <v>46.2</v>
       </c>
       <c r="G86" s="4" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I86" s="3" t="n">
-        <v>66.7</v>
+        <v>46.2</v>
       </c>
       <c r="J86" s="4" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>N-U-N-N</t>
+          <t>N-U-N-U</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M86" s="3" t="inlineStr"/>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="M86" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="N86" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P86" s="3" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P86" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="Q86" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
@@ -13289,34 +13293,34 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F91" s="3" t="n">
-        <v>52.6</v>
+        <v>45.9</v>
       </c>
       <c r="G91" s="4" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I91" s="3" t="n">
-        <v>36.8</v>
+        <v>62.2</v>
       </c>
       <c r="J91" s="4" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="L91" s="2" t="inlineStr">
@@ -13325,21 +13329,21 @@
         </is>
       </c>
       <c r="M91" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>46.7</v>
       </c>
       <c r="N91" s="4" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P91" s="3" t="n">
-        <v>42.9</v>
+        <v>60</v>
       </c>
       <c r="Q91" s="4" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="92">
@@ -13431,19 +13435,19 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>U-N-N</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F93" s="3" t="n">
-        <v>55.6</v>
+        <v>42.9</v>
       </c>
       <c r="G93" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
@@ -13451,14 +13455,14 @@
         </is>
       </c>
       <c r="I93" s="3" t="n">
-        <v>55.6</v>
+        <v>42.9</v>
       </c>
       <c r="J93" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-U</t>
+          <t>D-U-N-N</t>
         </is>
       </c>
       <c r="L93" s="2" t="inlineStr">
@@ -13467,21 +13471,21 @@
         </is>
       </c>
       <c r="M93" s="3" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="N93" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="P93" s="3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="Q93" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
@@ -13644,19 +13648,19 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F96" s="3" t="n">
-        <v>48.1</v>
+        <v>61.5</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -13664,14 +13668,14 @@
         </is>
       </c>
       <c r="I96" s="3" t="n">
-        <v>51.9</v>
+        <v>53.8</v>
       </c>
       <c r="J96" s="4" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-U</t>
+          <t>D-U-U-N</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
@@ -13680,10 +13684,10 @@
         </is>
       </c>
       <c r="M96" s="3" t="n">
-        <v>55.6</v>
+        <v>70</v>
       </c>
       <c r="N96" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
@@ -13691,10 +13695,10 @@
         </is>
       </c>
       <c r="P96" s="3" t="n">
-        <v>77.8</v>
+        <v>50</v>
       </c>
       <c r="Q96" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="97">
@@ -13715,19 +13719,19 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F97" s="3" t="n">
-        <v>44.4</v>
+        <v>72.7</v>
       </c>
       <c r="G97" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
@@ -13735,14 +13739,14 @@
         </is>
       </c>
       <c r="I97" s="3" t="n">
-        <v>55.6</v>
+        <v>45.5</v>
       </c>
       <c r="J97" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-N</t>
+          <t>D-U-N-D</t>
         </is>
       </c>
       <c r="L97" s="2" t="inlineStr">
@@ -13751,21 +13755,21 @@
         </is>
       </c>
       <c r="M97" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="N97" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="P97" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="Q97" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98">
@@ -14208,19 +14212,19 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-U</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F104" s="3" t="n">
-        <v>60</v>
+        <v>42.9</v>
       </c>
       <c r="G104" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
@@ -14228,33 +14232,37 @@
         </is>
       </c>
       <c r="I104" s="3" t="n">
-        <v>40</v>
+        <v>57.1</v>
       </c>
       <c r="J104" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>U-N-N-N</t>
+          <t>U-N-N-U</t>
         </is>
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M104" s="3" t="inlineStr"/>
+          <t>N/U</t>
+        </is>
+      </c>
+      <c r="M104" s="3" t="n">
+        <v>50</v>
+      </c>
       <c r="N104" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P104" s="3" t="inlineStr"/>
+          <t>D/N</t>
+        </is>
+      </c>
+      <c r="P104" s="3" t="n">
+        <v>50</v>
+      </c>
       <c r="Q104" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/BIS_tr.xlsx
+++ b/BIS_tr.xlsx
@@ -568,7 +568,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -577,10 +577,10 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>66.7</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -588,14 +588,14 @@
         </is>
       </c>
       <c r="G2" s="3" t="n">
-        <v>41.7</v>
+        <v>47.1</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-N</t>
+          <t>N-N-D-D</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -604,21 +604,21 @@
         </is>
       </c>
       <c r="K2" s="3" t="n">
-        <v>61.5</v>
+        <v>75</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N2" s="3" t="n">
-        <v>46.2</v>
+        <v>50</v>
       </c>
       <c r="O2" s="4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -690,7 +690,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-U</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -699,48 +699,48 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>76.09999999999999</v>
+        <v>66.2</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>N-U-N-U</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
           <t>D/U</t>
         </is>
       </c>
-      <c r="G4" s="3" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>46</v>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>N-U-N-N</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="L4" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
       <c r="N4" s="3" t="n">
-        <v>40</v>
+        <v>46.2</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
@@ -812,7 +812,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -821,25 +821,25 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>58.9</v>
+        <v>68.5</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>175</v>
+        <v>89</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G6" s="3" t="n">
-        <v>39.4</v>
+        <v>43.8</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>175</v>
+        <v>89</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-U</t>
+          <t>N-U-U-N</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -848,10 +848,10 @@
         </is>
       </c>
       <c r="K6" s="3" t="n">
-        <v>53.3</v>
+        <v>68.2</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="N6" s="3" t="n">
-        <v>50</v>
+        <v>45.5</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7">
@@ -934,7 +934,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -943,37 +943,37 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>47.1</v>
+        <v>76.2</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G8" s="3" t="n">
-        <v>50</v>
+        <v>47.6</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K8" s="3" t="n">
-        <v>37.5</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="N8" s="3" t="n">
-        <v>62.5</v>
+        <v>44.4</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1370,25 +1370,25 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>55.9</v>
+        <v>54</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>59</v>
+        <v>163</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G15" s="3" t="n">
-        <v>42.4</v>
+        <v>48.5</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>59</v>
+        <v>163</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1397,21 +1397,21 @@
         </is>
       </c>
       <c r="K15" s="3" t="n">
-        <v>50</v>
+        <v>51.9</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N15" s="3" t="n">
-        <v>55</v>
+        <v>49.4</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>20</v>
+        <v>77</v>
       </c>
     </row>
     <row r="16">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1736,10 +1736,10 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>76.09999999999999</v>
+        <v>61.6</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>71</v>
+        <v>146</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1747,14 +1747,14 @@
         </is>
       </c>
       <c r="G21" s="3" t="n">
-        <v>45.1</v>
+        <v>37.7</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>71</v>
+        <v>146</v>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-N</t>
+          <t>N-U-D-U</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1763,21 +1763,21 @@
         </is>
       </c>
       <c r="K21" s="3" t="n">
-        <v>82.40000000000001</v>
+        <v>66.7</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N21" s="3" t="n">
-        <v>52.9</v>
+        <v>45.8</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1858,37 +1858,37 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>64.3</v>
+        <v>48.3</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G23" s="3" t="n">
-        <v>53.6</v>
+        <v>48.3</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-U</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K23" s="3" t="n">
         <v>55.6</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
@@ -1896,10 +1896,10 @@
         </is>
       </c>
       <c r="N23" s="3" t="n">
-        <v>66.7</v>
+        <v>55.6</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1919,48 +1919,48 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>62.5</v>
+        <v>77.8</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G24" s="3" t="n">
-        <v>41.7</v>
+        <v>55.6</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-N</t>
+          <t>D-D-N-U</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K24" s="3" t="n">
-        <v>45.5</v>
+        <v>100</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N24" s="3" t="n">
-        <v>45.5</v>
+        <v>85.7</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2163,25 +2163,25 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>77.8</v>
+        <v>55.6</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G28" s="3" t="n">
         <v>38.9</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>D-N-D-U</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -2190,21 +2190,21 @@
         </is>
       </c>
       <c r="K28" s="3" t="n">
-        <v>63.6</v>
+        <v>54.1</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N28" s="3" t="n">
-        <v>45.5</v>
+        <v>40.5</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>11</v>
+        <v>37</v>
       </c>
     </row>
     <row r="29">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>U-N-D</t>
+          <t>U-N-N</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2285,25 +2285,25 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>58.6</v>
+        <v>60</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>42.9</v>
+        <v>40</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-D</t>
+          <t>D-U-N-N</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -2312,21 +2312,21 @@
         </is>
       </c>
       <c r="K30" s="3" t="n">
-        <v>63.3</v>
+        <v>63.6</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N30" s="3" t="n">
-        <v>56.7</v>
+        <v>63.6</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>U-N-N</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2529,25 +2529,25 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>66.3</v>
+        <v>86</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>43.4</v>
+        <v>36</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>N-U-N-U</t>
+          <t>N-U-N-N</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="K34" s="3" t="n">
-        <v>68.2</v>
+        <v>93.3</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="N34" s="3" t="n">
-        <v>40.9</v>
+        <v>53.3</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35">
@@ -2581,34 +2581,34 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>50</v>
+        <v>50.7</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v>55</v>
+        <v>44.9</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-U</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -2617,21 +2617,21 @@
         </is>
       </c>
       <c r="K35" s="3" t="n">
-        <v>70</v>
+        <v>53.3</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N35" s="3" t="n">
-        <v>50</v>
+        <v>46.7</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
     <row r="36">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2895,25 +2895,25 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>63.6</v>
+        <v>75.7</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G40" s="3" t="n">
-        <v>52.3</v>
+        <v>43.2</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-U</t>
+          <t>N-U-D-N</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -2922,7 +2922,7 @@
         </is>
       </c>
       <c r="K40" s="3" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="L40" s="4" t="n">
         <v>10</v>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>U-N-N</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3017,10 +3017,10 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>58.3</v>
+        <v>62.5</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -3028,37 +3028,37 @@
         </is>
       </c>
       <c r="G42" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>N-U-N-U</t>
+          <t>N-U-N-N</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K42" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N42" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O42" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -3557,19 +3557,19 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-U</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>90</v>
+        <v>43.8</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3577,37 +3577,37 @@
         </is>
       </c>
       <c r="G51" s="3" t="n">
-        <v>40</v>
+        <v>43.8</v>
       </c>
       <c r="H51" s="4" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>N-N-N-N</t>
+          <t>N-N-N-U</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K51" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="L51" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N51" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="O51" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52">
@@ -3679,34 +3679,34 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>55</v>
+        <v>45.5</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G53" s="3" t="n">
-        <v>50</v>
+        <v>45.5</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -3715,10 +3715,10 @@
         </is>
       </c>
       <c r="K53" s="3" t="n">
-        <v>50</v>
+        <v>47.6</v>
       </c>
       <c r="L53" s="4" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
@@ -3726,10 +3726,10 @@
         </is>
       </c>
       <c r="N53" s="3" t="n">
-        <v>62.5</v>
+        <v>47.6</v>
       </c>
       <c r="O53" s="4" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="54">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3810,10 +3810,10 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>51.6</v>
+        <v>50.6</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3821,14 +3821,14 @@
         </is>
       </c>
       <c r="G55" s="3" t="n">
-        <v>45.7</v>
+        <v>47.1</v>
       </c>
       <c r="H55" s="4" t="n">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-U</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -3837,10 +3837,10 @@
         </is>
       </c>
       <c r="K55" s="3" t="n">
-        <v>60.3</v>
+        <v>54.5</v>
       </c>
       <c r="L55" s="4" t="n">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
@@ -3848,10 +3848,10 @@
         </is>
       </c>
       <c r="N55" s="3" t="n">
-        <v>48.7</v>
+        <v>43.9</v>
       </c>
       <c r="O55" s="4" t="n">
-        <v>78</v>
+        <v>66</v>
       </c>
     </row>
     <row r="56">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3871,25 +3871,25 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>55.6</v>
+        <v>63.5</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G56" s="3" t="n">
-        <v>38.9</v>
+        <v>50</v>
       </c>
       <c r="H56" s="4" t="n">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -3898,10 +3898,10 @@
         </is>
       </c>
       <c r="K56" s="3" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="L56" s="4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
@@ -3909,10 +3909,10 @@
         </is>
       </c>
       <c r="N56" s="3" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="O56" s="4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="57">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3932,25 +3932,25 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>76.8</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G57" s="3" t="n">
-        <v>37.5</v>
+        <v>36.8</v>
       </c>
       <c r="H57" s="4" t="n">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-N</t>
+          <t>D-N-N-D</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -3959,21 +3959,21 @@
         </is>
       </c>
       <c r="K57" s="3" t="n">
-        <v>77.3</v>
+        <v>69.2</v>
       </c>
       <c r="L57" s="4" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N57" s="3" t="n">
-        <v>36.4</v>
+        <v>46.2</v>
       </c>
       <c r="O57" s="4" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="58">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4115,10 +4115,10 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>63.2</v>
+        <v>64.2</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>87</v>
+        <v>159</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -4126,14 +4126,14 @@
         </is>
       </c>
       <c r="G60" s="3" t="n">
-        <v>37.9</v>
+        <v>35.8</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>87</v>
+        <v>159</v>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -4142,21 +4142,21 @@
         </is>
       </c>
       <c r="K60" s="3" t="n">
-        <v>75.8</v>
+        <v>60</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N60" s="3" t="n">
-        <v>36.4</v>
+        <v>41.8</v>
       </c>
       <c r="O60" s="4" t="n">
-        <v>33</v>
+        <v>55</v>
       </c>
     </row>
     <row r="61">
@@ -4228,7 +4228,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4237,10 +4237,10 @@
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>58.9</v>
+        <v>60.8</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>146</v>
+        <v>51</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -4248,14 +4248,14 @@
         </is>
       </c>
       <c r="G62" s="3" t="n">
-        <v>44.5</v>
+        <v>43.1</v>
       </c>
       <c r="H62" s="4" t="n">
-        <v>146</v>
+        <v>51</v>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -4264,21 +4264,21 @@
         </is>
       </c>
       <c r="K62" s="3" t="n">
-        <v>58.2</v>
+        <v>64.7</v>
       </c>
       <c r="L62" s="4" t="n">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N62" s="3" t="n">
-        <v>41.8</v>
+        <v>41.2</v>
       </c>
       <c r="O62" s="4" t="n">
-        <v>55</v>
+        <v>17</v>
       </c>
     </row>
     <row r="63">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -4420,10 +4420,10 @@
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>68.09999999999999</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>94</v>
+        <v>157</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -4431,14 +4431,14 @@
         </is>
       </c>
       <c r="G65" s="3" t="n">
-        <v>43.6</v>
+        <v>44.6</v>
       </c>
       <c r="H65" s="4" t="n">
-        <v>94</v>
+        <v>157</v>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-N</t>
+          <t>U-U-D-U</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -4447,10 +4447,10 @@
         </is>
       </c>
       <c r="K65" s="3" t="n">
-        <v>68.59999999999999</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="L65" s="4" t="n">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
@@ -4458,10 +4458,10 @@
         </is>
       </c>
       <c r="N65" s="3" t="n">
-        <v>48.6</v>
+        <v>45.8</v>
       </c>
       <c r="O65" s="4" t="n">
-        <v>35</v>
+        <v>72</v>
       </c>
     </row>
     <row r="66">
@@ -4472,7 +4472,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-U</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -4481,25 +4481,25 @@
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>71.90000000000001</v>
+        <v>59.4</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G66" s="3" t="n">
-        <v>37.5</v>
+        <v>40.6</v>
       </c>
       <c r="H66" s="4" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>U-U-N-N</t>
+          <t>U-U-N-U</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -4508,21 +4508,21 @@
         </is>
       </c>
       <c r="K66" s="3" t="n">
-        <v>62.5</v>
+        <v>51.7</v>
       </c>
       <c r="L66" s="4" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N66" s="3" t="n">
-        <v>43.8</v>
+        <v>41.4</v>
       </c>
       <c r="O66" s="4" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
     </row>
     <row r="67">
@@ -4533,53 +4533,57 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>75</v>
+        <v>72.7</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G67" s="3" t="n">
-        <v>50</v>
+        <v>45.5</v>
       </c>
       <c r="H67" s="4" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-N</t>
+          <t>N-U-U-D</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="K67" s="3" t="inlineStr"/>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="L67" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N67" s="3" t="inlineStr"/>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="O67" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4590,7 +4594,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -4599,25 +4603,25 @@
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>76.5</v>
+        <v>59.6</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G68" s="3" t="n">
-        <v>47.1</v>
+        <v>46.8</v>
       </c>
       <c r="H68" s="4" t="n">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -4626,21 +4630,21 @@
         </is>
       </c>
       <c r="K68" s="3" t="n">
-        <v>100</v>
+        <v>58.3</v>
       </c>
       <c r="L68" s="4" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N68" s="3" t="n">
-        <v>66.7</v>
+        <v>45.8</v>
       </c>
       <c r="O68" s="4" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
     </row>
     <row r="69">
@@ -4773,7 +4777,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -4782,10 +4786,10 @@
         </is>
       </c>
       <c r="D71" s="3" t="n">
-        <v>51.9</v>
+        <v>61.3</v>
       </c>
       <c r="E71" s="4" t="n">
-        <v>156</v>
+        <v>80</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4793,14 +4797,14 @@
         </is>
       </c>
       <c r="G71" s="3" t="n">
-        <v>44.9</v>
+        <v>43.8</v>
       </c>
       <c r="H71" s="4" t="n">
-        <v>156</v>
+        <v>80</v>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-D</t>
+          <t>N-U-D-N</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -4809,10 +4813,10 @@
         </is>
       </c>
       <c r="K71" s="3" t="n">
-        <v>55.2</v>
+        <v>53.3</v>
       </c>
       <c r="L71" s="4" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
@@ -4820,10 +4824,10 @@
         </is>
       </c>
       <c r="N71" s="3" t="n">
-        <v>44.8</v>
+        <v>46.7</v>
       </c>
       <c r="O71" s="4" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
     </row>
     <row r="72">
@@ -4895,7 +4899,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-U</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -4904,10 +4908,10 @@
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>78.59999999999999</v>
+        <v>64</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4915,14 +4919,14 @@
         </is>
       </c>
       <c r="G73" s="3" t="n">
-        <v>57.1</v>
+        <v>48</v>
       </c>
       <c r="H73" s="4" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>N-N-N-N</t>
+          <t>N-N-N-U</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -4931,21 +4935,21 @@
         </is>
       </c>
       <c r="K73" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="L73" s="4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N73" s="3" t="n">
-        <v>66.7</v>
+        <v>62.5</v>
       </c>
       <c r="O73" s="4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="74">
@@ -5261,7 +5265,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>U-N-N</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -5270,25 +5274,25 @@
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>66.2</v>
+        <v>65.5</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G79" s="3" t="n">
-        <v>33.8</v>
+        <v>45.5</v>
       </c>
       <c r="H79" s="4" t="n">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>N-U-N-U</t>
+          <t>N-U-N-N</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -5297,21 +5301,21 @@
         </is>
       </c>
       <c r="K79" s="3" t="n">
-        <v>63.6</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="L79" s="4" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N79" s="3" t="n">
-        <v>40.9</v>
+        <v>57.1</v>
       </c>
       <c r="O79" s="4" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="80">
@@ -5322,7 +5326,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-U</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -5331,10 +5335,10 @@
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>51.2</v>
+        <v>45.6</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -5342,14 +5346,14 @@
         </is>
       </c>
       <c r="G80" s="3" t="n">
-        <v>41.5</v>
+        <v>44.1</v>
       </c>
       <c r="H80" s="4" t="n">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-N</t>
+          <t>D-U-N-U</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -5358,10 +5362,10 @@
         </is>
       </c>
       <c r="K80" s="3" t="n">
-        <v>42.1</v>
+        <v>52.9</v>
       </c>
       <c r="L80" s="4" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
@@ -5369,10 +5373,10 @@
         </is>
       </c>
       <c r="N80" s="3" t="n">
-        <v>42.1</v>
+        <v>44.1</v>
       </c>
       <c r="O80" s="4" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
     </row>
     <row r="81">
@@ -5444,7 +5448,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -5453,25 +5457,25 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>75</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G82" s="3" t="n">
-        <v>43.8</v>
+        <v>43.5</v>
       </c>
       <c r="H82" s="4" t="n">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -5480,10 +5484,10 @@
         </is>
       </c>
       <c r="K82" s="3" t="n">
-        <v>57.1</v>
+        <v>72.2</v>
       </c>
       <c r="L82" s="4" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
@@ -5491,10 +5495,10 @@
         </is>
       </c>
       <c r="N82" s="3" t="n">
-        <v>57.1</v>
+        <v>50</v>
       </c>
       <c r="O82" s="4" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="83">
@@ -5566,7 +5570,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -5575,25 +5579,25 @@
         </is>
       </c>
       <c r="D84" s="3" t="n">
-        <v>68.09999999999999</v>
+        <v>62.3</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G84" s="3" t="n">
-        <v>39.6</v>
+        <v>40</v>
       </c>
       <c r="H84" s="4" t="n">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-N</t>
+          <t>N-U-D-U</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -5602,21 +5606,21 @@
         </is>
       </c>
       <c r="K84" s="3" t="n">
-        <v>69.2</v>
+        <v>78.3</v>
       </c>
       <c r="L84" s="4" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N84" s="3" t="n">
-        <v>50</v>
+        <v>43.5</v>
       </c>
       <c r="O84" s="4" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="85">
@@ -6115,7 +6119,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-U</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -6124,25 +6128,25 @@
         </is>
       </c>
       <c r="D93" s="3" t="n">
-        <v>64.3</v>
+        <v>60</v>
       </c>
       <c r="E93" s="4" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G93" s="3" t="n">
-        <v>42.9</v>
+        <v>45</v>
       </c>
       <c r="H93" s="4" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-N</t>
+          <t>D-U-N-U</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
@@ -6151,10 +6155,10 @@
         </is>
       </c>
       <c r="K93" s="3" t="n">
-        <v>78.59999999999999</v>
+        <v>71</v>
       </c>
       <c r="L93" s="4" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
@@ -6162,10 +6166,10 @@
         </is>
       </c>
       <c r="N93" s="3" t="n">
-        <v>64.3</v>
+        <v>48.4</v>
       </c>
       <c r="O93" s="4" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
     </row>
     <row r="94">
@@ -6481,7 +6485,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -6490,25 +6494,25 @@
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>58.2</v>
+        <v>50.3</v>
       </c>
       <c r="E99" s="4" t="n">
-        <v>79</v>
+        <v>169</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G99" s="3" t="n">
-        <v>38</v>
+        <v>43.8</v>
       </c>
       <c r="H99" s="4" t="n">
-        <v>79</v>
+        <v>169</v>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
@@ -6517,10 +6521,10 @@
         </is>
       </c>
       <c r="K99" s="3" t="n">
-        <v>50</v>
+        <v>53.6</v>
       </c>
       <c r="L99" s="4" t="n">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
@@ -6528,10 +6532,10 @@
         </is>
       </c>
       <c r="N99" s="3" t="n">
-        <v>53.8</v>
+        <v>44.9</v>
       </c>
       <c r="O99" s="4" t="n">
-        <v>26</v>
+        <v>69</v>
       </c>
     </row>
     <row r="100">
@@ -6725,7 +6729,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -6734,10 +6738,10 @@
         </is>
       </c>
       <c r="D103" s="3" t="n">
-        <v>63.2</v>
+        <v>61.1</v>
       </c>
       <c r="E103" s="4" t="n">
-        <v>87</v>
+        <v>162</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -6745,14 +6749,14 @@
         </is>
       </c>
       <c r="G103" s="3" t="n">
-        <v>39.1</v>
+        <v>41.4</v>
       </c>
       <c r="H103" s="4" t="n">
-        <v>87</v>
+        <v>162</v>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-N</t>
+          <t>N-U-D-U</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
@@ -6761,21 +6765,21 @@
         </is>
       </c>
       <c r="K103" s="3" t="n">
-        <v>65.2</v>
+        <v>56</v>
       </c>
       <c r="L103" s="4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N103" s="3" t="n">
-        <v>43.5</v>
+        <v>60</v>
       </c>
       <c r="O103" s="4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="104">
@@ -7022,7 +7026,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -7031,48 +7035,48 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>57.1</v>
+        <v>58.8</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I2" s="3" t="n">
-        <v>42.9</v>
+        <v>52.9</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-N</t>
+          <t>N-N-D-D</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M2" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P2" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q2" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -7164,34 +7168,34 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-U</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>85.7</v>
+        <v>45.5</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I4" s="3" t="n">
-        <v>42.9</v>
+        <v>54.5</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>N-U-N-N</t>
+          <t>N-U-N-U</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -7302,7 +7306,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -7311,10 +7315,10 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>51.5</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -7322,26 +7326,26 @@
         </is>
       </c>
       <c r="I6" s="3" t="n">
-        <v>39.4</v>
+        <v>57.1</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-U</t>
+          <t>N-U-U-N</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M6" s="3" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -7349,10 +7353,10 @@
         </is>
       </c>
       <c r="P6" s="3" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -7444,39 +7448,39 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="I8" s="3" t="n">
-        <v>62.5</v>
+        <v>42.9</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M8" s="3" t="n">
@@ -7487,11 +7491,11 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P8" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q8" s="4" t="n">
         <v>2</v>
@@ -7941,7 +7945,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -7950,48 +7954,48 @@
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>56.2</v>
+        <v>59.5</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I15" s="3" t="n">
-        <v>56.2</v>
+        <v>59.5</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M15" s="3" t="n">
-        <v>50</v>
+        <v>59.1</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P15" s="3" t="n">
-        <v>75</v>
+        <v>63.6</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16">
@@ -8367,19 +8371,19 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>48.1</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -8387,26 +8391,26 @@
         </is>
       </c>
       <c r="I21" s="3" t="n">
-        <v>57.1</v>
+        <v>55.6</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-N</t>
+          <t>N-U-D-U</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M21" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -8414,10 +8418,10 @@
         </is>
       </c>
       <c r="P21" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -8509,19 +8513,19 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>60</v>
+        <v>42.9</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -8532,11 +8536,11 @@
         <v>50</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-U</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -8545,10 +8549,10 @@
         </is>
       </c>
       <c r="M23" s="3" t="n">
-        <v>66.7</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -8556,10 +8560,10 @@
         </is>
       </c>
       <c r="P23" s="3" t="n">
-        <v>66.7</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -8580,7 +8584,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -8589,10 +8593,10 @@
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>50</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -8600,37 +8604,37 @@
         </is>
       </c>
       <c r="I24" s="3" t="n">
-        <v>40</v>
+        <v>57.1</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-N</t>
+          <t>D-D-N-U</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M24" s="3" t="n">
-        <v>57.1</v>
+        <v>100</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P24" s="3" t="n">
-        <v>57.1</v>
+        <v>100</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -8864,7 +8868,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -8873,48 +8877,48 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>66.7</v>
+        <v>53.3</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I28" s="3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>D-N-D-U</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M28" s="3" t="n">
-        <v>66.7</v>
+        <v>55.6</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P28" s="3" t="n">
-        <v>33.3</v>
+        <v>44.4</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29">
@@ -9006,57 +9010,57 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>U-N-D</t>
+          <t>U-N-N</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="F30" s="3" t="n">
         <v>50</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I30" s="3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-D</t>
+          <t>D-U-N-N</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M30" s="3" t="n">
         <v>100</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P30" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -9290,57 +9294,57 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>U-N-N</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>53.8</v>
+        <v>75</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I34" s="3" t="n">
-        <v>61.5</v>
+        <v>50</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>N-U-N-U</t>
+          <t>N-U-N-N</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M34" s="3" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P34" s="3" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -9361,54 +9365,54 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="J35" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>U-U-U-U</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
           <t>N/U</t>
         </is>
       </c>
-      <c r="F35" s="3" t="n">
+      <c r="M35" s="3" t="n">
         <v>50</v>
-      </c>
-      <c r="G35" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>D/U</t>
-        </is>
-      </c>
-      <c r="I35" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="J35" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>U-U-U-N</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M35" s="3" t="n">
-        <v>100</v>
       </c>
       <c r="N35" s="4" t="n">
         <v>2</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P35" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q35" s="4" t="n">
         <v>2</v>
@@ -9712,7 +9716,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -9721,10 +9725,10 @@
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>62.5</v>
+        <v>80</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -9732,37 +9736,37 @@
         </is>
       </c>
       <c r="I40" s="3" t="n">
-        <v>56.2</v>
+        <v>80</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-U</t>
+          <t>N-U-D-N</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M40" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P40" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q40" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -9850,30 +9854,34 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>U-N-N</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="F42" s="3" t="inlineStr"/>
+          <t>D/N</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>50</v>
+      </c>
       <c r="G42" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="I42" s="3" t="inlineStr"/>
+          <t>N/U</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="n">
+        <v>50</v>
+      </c>
       <c r="J42" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>N-U-N-U</t>
+          <t>N-U-N-N</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -10477,7 +10485,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-U</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -10486,10 +10494,10 @@
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -10497,26 +10505,26 @@
         </is>
       </c>
       <c r="I51" s="3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="J51" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>N-N-N-N</t>
+          <t>N-N-N-U</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="M51" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N51" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
@@ -10527,7 +10535,7 @@
         <v>100</v>
       </c>
       <c r="Q51" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -10619,7 +10627,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -10628,10 +10636,10 @@
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -10639,26 +10647,26 @@
         </is>
       </c>
       <c r="I53" s="3" t="n">
-        <v>100</v>
+        <v>58.3</v>
       </c>
       <c r="J53" s="4" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M53" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N53" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
@@ -10666,10 +10674,10 @@
         </is>
       </c>
       <c r="P53" s="3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="Q53" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54">
@@ -10761,7 +10769,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -10770,10 +10778,10 @@
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>48.5</v>
+        <v>38.9</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -10781,14 +10789,14 @@
         </is>
       </c>
       <c r="I55" s="3" t="n">
-        <v>51.5</v>
+        <v>44.4</v>
       </c>
       <c r="J55" s="4" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-U</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
@@ -10797,10 +10805,10 @@
         </is>
       </c>
       <c r="M55" s="3" t="n">
-        <v>50</v>
+        <v>43.8</v>
       </c>
       <c r="N55" s="4" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
@@ -10808,10 +10816,10 @@
         </is>
       </c>
       <c r="P55" s="3" t="n">
-        <v>75</v>
+        <v>43.8</v>
       </c>
       <c r="Q55" s="4" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="56">
@@ -10832,57 +10840,57 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="G56" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="J56" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>U-U-U-D</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="N56" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I56" s="3" t="n">
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P56" s="3" t="n">
         <v>66.7</v>
       </c>
-      <c r="J56" s="4" t="n">
+      <c r="Q56" s="4" t="n">
         <v>3</v>
-      </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>U-U-U-N</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="inlineStr">
-        <is>
-          <t>N/U</t>
-        </is>
-      </c>
-      <c r="M56" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="N56" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="O56" s="2" t="inlineStr">
-        <is>
-          <t>N/U</t>
-        </is>
-      </c>
-      <c r="P56" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q56" s="4" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -10903,7 +10911,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -10912,25 +10920,25 @@
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>84.59999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I57" s="3" t="n">
-        <v>46.2</v>
+        <v>50</v>
       </c>
       <c r="J57" s="4" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-N</t>
+          <t>D-N-N-D</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
@@ -10939,21 +10947,21 @@
         </is>
       </c>
       <c r="M57" s="3" t="n">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="N57" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P57" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="Q57" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -11116,7 +11124,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -11125,48 +11133,48 @@
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>53.8</v>
+        <v>70.8</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I60" s="3" t="n">
-        <v>46.2</v>
+        <v>41.7</v>
       </c>
       <c r="J60" s="4" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M60" s="3" t="n">
-        <v>50</v>
+        <v>85.7</v>
       </c>
       <c r="N60" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P60" s="3" t="n">
-        <v>50</v>
+        <v>42.9</v>
       </c>
       <c r="Q60" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61">
@@ -11254,7 +11262,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -11263,25 +11271,25 @@
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>57.1</v>
+        <v>50</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="I62" s="3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J62" s="4" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
@@ -11290,21 +11298,21 @@
         </is>
       </c>
       <c r="M62" s="3" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="N62" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P62" s="3" t="n">
-        <v>37.5</v>
+        <v>66.7</v>
       </c>
       <c r="Q62" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63">
@@ -11467,7 +11475,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -11476,10 +11484,10 @@
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>52.6</v>
+        <v>72</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
@@ -11487,14 +11495,14 @@
         </is>
       </c>
       <c r="I65" s="3" t="n">
-        <v>52.6</v>
+        <v>64</v>
       </c>
       <c r="J65" s="4" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-N</t>
+          <t>U-U-D-U</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
@@ -11503,10 +11511,10 @@
         </is>
       </c>
       <c r="M65" s="3" t="n">
-        <v>66.7</v>
+        <v>70</v>
       </c>
       <c r="N65" s="4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
@@ -11514,10 +11522,10 @@
         </is>
       </c>
       <c r="P65" s="3" t="n">
-        <v>66.7</v>
+        <v>70</v>
       </c>
       <c r="Q65" s="4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="66">
@@ -11538,7 +11546,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-U</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -11547,10 +11555,10 @@
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>43.8</v>
+        <v>58.3</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -11558,26 +11566,26 @@
         </is>
       </c>
       <c r="I66" s="3" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="J66" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>U-U-N-U</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>N/U</t>
+        </is>
+      </c>
+      <c r="M66" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="J66" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="K66" s="2" t="inlineStr">
-        <is>
-          <t>U-U-N-N</t>
-        </is>
-      </c>
-      <c r="L66" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M66" s="3" t="n">
-        <v>66.7</v>
-      </c>
       <c r="N66" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
@@ -11585,10 +11593,10 @@
         </is>
       </c>
       <c r="P66" s="3" t="n">
-        <v>66.7</v>
+        <v>75</v>
       </c>
       <c r="Q66" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67">
@@ -11609,49 +11617,57 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="F67" s="3" t="inlineStr"/>
+          <t>N/U</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>50</v>
+      </c>
       <c r="G67" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="I67" s="3" t="inlineStr"/>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="J67" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-N</t>
+          <t>N-U-U-D</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M67" s="3" t="inlineStr"/>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="M67" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="N67" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P67" s="3" t="inlineStr"/>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P67" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="Q67" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -11672,7 +11688,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -11681,25 +11697,25 @@
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I68" s="3" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="J68" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
@@ -11708,21 +11724,21 @@
         </is>
       </c>
       <c r="M68" s="3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="N68" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P68" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q68" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="69">
@@ -11881,19 +11897,19 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>45.8</v>
+        <v>37.5</v>
       </c>
       <c r="G71" s="4" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
@@ -11901,14 +11917,14 @@
         </is>
       </c>
       <c r="I71" s="3" t="n">
-        <v>41.7</v>
+        <v>56.2</v>
       </c>
       <c r="J71" s="4" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-D</t>
+          <t>N-U-D-N</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
@@ -11917,10 +11933,10 @@
         </is>
       </c>
       <c r="M71" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N71" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
@@ -11928,10 +11944,10 @@
         </is>
       </c>
       <c r="P71" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q71" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -12023,7 +12039,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-U</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -12032,7 +12048,7 @@
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="G73" s="4" t="n">
         <v>3</v>
@@ -12043,19 +12059,19 @@
         </is>
       </c>
       <c r="I73" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>3</v>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>N-N-N-N</t>
+          <t>N-N-N-U</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M73" s="3" t="n">
@@ -12066,7 +12082,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P73" s="3" t="n">
@@ -12441,19 +12457,19 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>U-N-N</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="G79" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
@@ -12461,14 +12477,14 @@
         </is>
       </c>
       <c r="I79" s="3" t="n">
-        <v>55.6</v>
+        <v>50</v>
       </c>
       <c r="J79" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>N-U-N-U</t>
+          <t>N-U-N-N</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
@@ -12480,7 +12496,7 @@
         <v>100</v>
       </c>
       <c r="N79" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
@@ -12491,7 +12507,7 @@
         <v>100</v>
       </c>
       <c r="Q79" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -12512,7 +12528,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-U</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -12521,10 +12537,10 @@
         </is>
       </c>
       <c r="F80" s="3" t="n">
-        <v>50</v>
+        <v>69.2</v>
       </c>
       <c r="G80" s="4" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
@@ -12532,14 +12548,14 @@
         </is>
       </c>
       <c r="I80" s="3" t="n">
-        <v>50</v>
+        <v>69.2</v>
       </c>
       <c r="J80" s="4" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-N</t>
+          <t>D-U-N-U</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
@@ -12548,21 +12564,21 @@
         </is>
       </c>
       <c r="M80" s="3" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="N80" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P80" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="Q80" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81">
@@ -12654,19 +12670,19 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>50</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -12674,26 +12690,26 @@
         </is>
       </c>
       <c r="I82" s="3" t="n">
-        <v>100</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="J82" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M82" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="N82" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
@@ -12704,7 +12720,7 @@
         <v>100</v>
       </c>
       <c r="Q82" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -12796,19 +12812,19 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F84" s="3" t="n">
-        <v>73.3</v>
+        <v>41.7</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -12816,37 +12832,37 @@
         </is>
       </c>
       <c r="I84" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="J84" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>N-U-D-U</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M84" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="N84" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>D/N</t>
+        </is>
+      </c>
+      <c r="P84" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="J84" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="K84" s="2" t="inlineStr">
-        <is>
-          <t>N-U-D-N</t>
-        </is>
-      </c>
-      <c r="L84" s="2" t="inlineStr">
-        <is>
-          <t>D/N/U</t>
-        </is>
-      </c>
-      <c r="M84" s="3" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="N84" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="O84" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P84" s="3" t="n">
-        <v>66.7</v>
-      </c>
       <c r="Q84" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85">
@@ -13435,19 +13451,19 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-U</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F93" s="3" t="n">
-        <v>42.9</v>
+        <v>55.6</v>
       </c>
       <c r="G93" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
@@ -13455,14 +13471,14 @@
         </is>
       </c>
       <c r="I93" s="3" t="n">
-        <v>42.9</v>
+        <v>55.6</v>
       </c>
       <c r="J93" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-N</t>
+          <t>D-U-N-U</t>
         </is>
       </c>
       <c r="L93" s="2" t="inlineStr">
@@ -13471,21 +13487,21 @@
         </is>
       </c>
       <c r="M93" s="3" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="N93" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P93" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="Q93" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94">
@@ -13857,57 +13873,57 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>41.7</v>
+        <v>57.1</v>
       </c>
       <c r="G99" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I99" s="3" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="J99" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>D-U-U-U</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M99" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="N99" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="H99" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I99" s="3" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="J99" s="4" t="n">
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P99" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q99" s="4" t="n">
         <v>12</v>
-      </c>
-      <c r="K99" s="2" t="inlineStr">
-        <is>
-          <t>D-U-U-N</t>
-        </is>
-      </c>
-      <c r="L99" s="2" t="inlineStr">
-        <is>
-          <t>D/U</t>
-        </is>
-      </c>
-      <c r="M99" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="N99" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="O99" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P99" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="Q99" s="4" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="100">
@@ -14141,19 +14157,19 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F103" s="3" t="n">
-        <v>59.1</v>
+        <v>48</v>
       </c>
       <c r="G103" s="4" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
@@ -14161,37 +14177,37 @@
         </is>
       </c>
       <c r="I103" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="J103" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>N-U-D-U</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>D/N</t>
+        </is>
+      </c>
+      <c r="M103" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="J103" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="K103" s="2" t="inlineStr">
-        <is>
-          <t>N-U-D-N</t>
-        </is>
-      </c>
-      <c r="L103" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M103" s="3" t="n">
-        <v>83.3</v>
-      </c>
       <c r="N103" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="P103" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="Q103" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">

--- a/BIS_tr.xlsx
+++ b/BIS_tr.xlsx
@@ -690,7 +690,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>U-N-N</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -699,25 +699,25 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>66.2</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G4" s="3" t="n">
-        <v>43.2</v>
+        <v>34.8</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>N-U-N-U</t>
+          <t>N-U-N-N</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -726,21 +726,21 @@
         </is>
       </c>
       <c r="K4" s="3" t="n">
-        <v>61.5</v>
+        <v>80</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N4" s="3" t="n">
-        <v>46.2</v>
+        <v>40</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -751,7 +751,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -760,25 +760,25 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>74.7</v>
+        <v>63.5</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>87</v>
+        <v>167</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G5" s="3" t="n">
-        <v>40.2</v>
+        <v>41.9</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>87</v>
+        <v>167</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="K5" s="3" t="n">
-        <v>64.7</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>34</v>
+        <v>73</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N5" s="3" t="n">
-        <v>38.2</v>
+        <v>43.8</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>34</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6">
@@ -873,7 +873,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -882,48 +882,48 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>68.8</v>
+        <v>53.8</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>96</v>
+        <v>182</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>182</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>U-U-U-U</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="L7" s="4" t="n">
+        <v>78</v>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="G7" s="3" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>96</v>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>U-U-U-N</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>71.8</v>
-      </c>
-      <c r="L7" s="4" t="n">
-        <v>39</v>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
       <c r="N7" s="3" t="n">
-        <v>43.6</v>
+        <v>39.7</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>39</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>N-U-D</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1187,10 +1187,10 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>42.3</v>
+        <v>57.1</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1198,14 +1198,14 @@
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>57.7</v>
+        <v>57.1</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-D</t>
+          <t>D-N-U-N</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1214,21 +1214,21 @@
         </is>
       </c>
       <c r="K12" s="3" t="n">
-        <v>61.5</v>
+        <v>60</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="N12" s="3" t="n">
-        <v>61.5</v>
+        <v>40</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2224,25 +2224,25 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>65.5</v>
+        <v>70.5</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>51.7</v>
+        <v>59.1</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-D</t>
+          <t>D-D-U-U</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -2251,21 +2251,21 @@
         </is>
       </c>
       <c r="K29" s="3" t="n">
-        <v>61.5</v>
+        <v>56.2</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N29" s="3" t="n">
-        <v>61.5</v>
+        <v>56.2</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-U</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2529,25 +2529,25 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>86</v>
+        <v>66.3</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>36</v>
+        <v>43.4</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>N-U-N-N</t>
+          <t>N-U-N-U</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="K34" s="3" t="n">
-        <v>93.3</v>
+        <v>68.2</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="N34" s="3" t="n">
-        <v>53.3</v>
+        <v>40.9</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2895,10 +2895,10 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>75.7</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>37</v>
+        <v>81</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2906,14 +2906,14 @@
         </is>
       </c>
       <c r="G40" s="3" t="n">
-        <v>43.2</v>
+        <v>49.4</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>37</v>
+        <v>81</v>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-N</t>
+          <t>N-U-D-D</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -2922,21 +2922,21 @@
         </is>
       </c>
       <c r="K40" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N40" s="3" t="n">
-        <v>40</v>
+        <v>57.1</v>
       </c>
       <c r="O40" s="4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="41">
@@ -2947,7 +2947,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2956,48 +2956,48 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>42.1</v>
+        <v>52.4</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>19</v>
+        <v>105</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G41" s="3" t="n">
-        <v>36.8</v>
+        <v>47.6</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>19</v>
+        <v>105</v>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K41" s="3" t="n">
-        <v>40</v>
+        <v>47.2</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N41" s="3" t="n">
-        <v>40</v>
+        <v>49.1</v>
       </c>
       <c r="O41" s="4" t="n">
-        <v>5</v>
+        <v>53</v>
       </c>
     </row>
     <row r="42">
@@ -3557,57 +3557,57 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-N-N</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="E51" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="H51" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>N-N-N-N</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
           <t>N/U</t>
         </is>
       </c>
-      <c r="D51" s="3" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="E51" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G51" s="3" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="H51" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>N-N-N-U</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
       <c r="K51" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="L51" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="N51" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="O51" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3749,25 +3749,25 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>64.7</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G54" s="3" t="n">
-        <v>41.2</v>
+        <v>45.5</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-N</t>
+          <t>D-D-N-D</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -3776,10 +3776,10 @@
         </is>
       </c>
       <c r="K54" s="3" t="n">
-        <v>66.7</v>
+        <v>68.2</v>
       </c>
       <c r="L54" s="4" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>50</v>
       </c>
       <c r="O54" s="4" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
     </row>
     <row r="55">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3810,10 +3810,10 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>50.6</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>170</v>
+        <v>78</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3821,14 +3821,14 @@
         </is>
       </c>
       <c r="G55" s="3" t="n">
-        <v>47.1</v>
+        <v>44.9</v>
       </c>
       <c r="H55" s="4" t="n">
-        <v>170</v>
+        <v>78</v>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-D</t>
+          <t>D-U-U-N</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -3837,10 +3837,10 @@
         </is>
       </c>
       <c r="K55" s="3" t="n">
-        <v>54.5</v>
+        <v>64</v>
       </c>
       <c r="L55" s="4" t="n">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
@@ -3848,10 +3848,10 @@
         </is>
       </c>
       <c r="N55" s="3" t="n">
-        <v>43.9</v>
+        <v>48</v>
       </c>
       <c r="O55" s="4" t="n">
-        <v>66</v>
+        <v>25</v>
       </c>
     </row>
     <row r="56">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3871,10 +3871,10 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>63.5</v>
+        <v>48.3</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3882,14 +3882,14 @@
         </is>
       </c>
       <c r="G56" s="3" t="n">
-        <v>50</v>
+        <v>48.3</v>
       </c>
       <c r="H56" s="4" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-D</t>
+          <t>U-U-U-U</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -3898,21 +3898,21 @@
         </is>
       </c>
       <c r="K56" s="3" t="n">
-        <v>70</v>
+        <v>48.1</v>
       </c>
       <c r="L56" s="4" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N56" s="3" t="n">
-        <v>55</v>
+        <v>55.6</v>
       </c>
       <c r="O56" s="4" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="57">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>N-N-D</t>
+          <t>N-N-U</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3932,25 +3932,25 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>71.09999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G57" s="3" t="n">
-        <v>36.8</v>
+        <v>61.9</v>
       </c>
       <c r="H57" s="4" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-D</t>
+          <t>D-N-N-U</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -3959,21 +3959,21 @@
         </is>
       </c>
       <c r="K57" s="3" t="n">
-        <v>69.2</v>
+        <v>66.7</v>
       </c>
       <c r="L57" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N57" s="3" t="n">
-        <v>46.2</v>
+        <v>50</v>
       </c>
       <c r="O57" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="58">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G61" s="3" t="n">
@@ -4194,30 +4194,30 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>N-N-N-N</t>
+          <t>N-N-N-D</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K61" s="3" t="n">
         <v>100</v>
       </c>
       <c r="L61" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N61" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -4472,7 +4472,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>U-N-N</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -4481,25 +4481,25 @@
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>59.4</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G66" s="3" t="n">
-        <v>40.6</v>
+        <v>37.5</v>
       </c>
       <c r="H66" s="4" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>U-U-N-U</t>
+          <t>U-U-N-N</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -4508,21 +4508,21 @@
         </is>
       </c>
       <c r="K66" s="3" t="n">
-        <v>51.7</v>
+        <v>62.5</v>
       </c>
       <c r="L66" s="4" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N66" s="3" t="n">
-        <v>41.4</v>
+        <v>43.8</v>
       </c>
       <c r="O66" s="4" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
     </row>
     <row r="67">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -4603,25 +4603,25 @@
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>59.6</v>
+        <v>71</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G68" s="3" t="n">
-        <v>46.8</v>
+        <v>52.2</v>
       </c>
       <c r="H68" s="4" t="n">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-D</t>
+          <t>U-U-U-U</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -4630,21 +4630,21 @@
         </is>
       </c>
       <c r="K68" s="3" t="n">
-        <v>58.3</v>
+        <v>62.9</v>
       </c>
       <c r="L68" s="4" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N68" s="3" t="n">
-        <v>45.8</v>
+        <v>51.4</v>
       </c>
       <c r="O68" s="4" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="69">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-N-N</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -4908,10 +4908,10 @@
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>64</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4919,14 +4919,14 @@
         </is>
       </c>
       <c r="G73" s="3" t="n">
-        <v>48</v>
+        <v>57.1</v>
       </c>
       <c r="H73" s="4" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>N-N-N-U</t>
+          <t>N-N-N-N</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -4935,21 +4935,21 @@
         </is>
       </c>
       <c r="K73" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="L73" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N73" s="3" t="n">
-        <v>62.5</v>
+        <v>66.7</v>
       </c>
       <c r="O73" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
@@ -5143,7 +5143,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -5152,10 +5152,10 @@
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>58.2</v>
+        <v>64.2</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -5163,14 +5163,14 @@
         </is>
       </c>
       <c r="G77" s="3" t="n">
-        <v>39.9</v>
+        <v>38.7</v>
       </c>
       <c r="H77" s="4" t="n">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -5179,21 +5179,21 @@
         </is>
       </c>
       <c r="K77" s="3" t="n">
-        <v>62.3</v>
+        <v>61.5</v>
       </c>
       <c r="L77" s="4" t="n">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N77" s="3" t="n">
-        <v>45.9</v>
+        <v>44.2</v>
       </c>
       <c r="O77" s="4" t="n">
-        <v>61</v>
+        <v>52</v>
       </c>
     </row>
     <row r="78">
@@ -5204,7 +5204,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -5213,37 +5213,37 @@
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>52.4</v>
+        <v>56.7</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>191</v>
+        <v>60</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G78" s="3" t="n">
-        <v>50.3</v>
+        <v>43.3</v>
       </c>
       <c r="H78" s="4" t="n">
-        <v>191</v>
+        <v>60</v>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-U</t>
+          <t>D-U-U-N</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K78" s="3" t="n">
-        <v>52.8</v>
+        <v>46.4</v>
       </c>
       <c r="L78" s="4" t="n">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="N78" s="3" t="n">
-        <v>50</v>
+        <v>46.4</v>
       </c>
       <c r="O78" s="4" t="n">
-        <v>72</v>
+        <v>28</v>
       </c>
     </row>
     <row r="79">
@@ -5509,7 +5509,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-N-N</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -5518,25 +5518,25 @@
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>63.6</v>
+        <v>83.3</v>
       </c>
       <c r="E83" s="4" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G83" s="3" t="n">
-        <v>56.8</v>
+        <v>36.7</v>
       </c>
       <c r="H83" s="4" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>U-N-N-U</t>
+          <t>U-N-N-N</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
@@ -5545,10 +5545,10 @@
         </is>
       </c>
       <c r="K83" s="3" t="n">
-        <v>61.1</v>
+        <v>77.8</v>
       </c>
       <c r="L83" s="4" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
@@ -5556,10 +5556,10 @@
         </is>
       </c>
       <c r="N83" s="3" t="n">
-        <v>38.9</v>
+        <v>44.4</v>
       </c>
       <c r="O83" s="4" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="84">
@@ -5753,7 +5753,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -5762,10 +5762,10 @@
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>68.40000000000001</v>
+        <v>65.7</v>
       </c>
       <c r="E87" s="4" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5773,37 +5773,37 @@
         </is>
       </c>
       <c r="G87" s="3" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="H87" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>D-N-D-D</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K87" s="3" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="L87" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N87" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="H87" s="4" t="n">
-        <v>38</v>
-      </c>
-      <c r="I87" s="2" t="inlineStr">
-        <is>
-          <t>D-N-D-N</t>
-        </is>
-      </c>
-      <c r="J87" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K87" s="3" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="L87" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="M87" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="N87" s="3" t="n">
-        <v>64.3</v>
-      </c>
       <c r="O87" s="4" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
     </row>
     <row r="88">
@@ -5814,7 +5814,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -5823,10 +5823,10 @@
         </is>
       </c>
       <c r="D88" s="3" t="n">
-        <v>49.4</v>
+        <v>57.7</v>
       </c>
       <c r="E88" s="4" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5834,14 +5834,14 @@
         </is>
       </c>
       <c r="G88" s="3" t="n">
-        <v>40</v>
+        <v>42.3</v>
       </c>
       <c r="H88" s="4" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-U</t>
+          <t>D-U-N-D</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
@@ -5850,21 +5850,21 @@
         </is>
       </c>
       <c r="K88" s="3" t="n">
-        <v>48.6</v>
+        <v>58.8</v>
       </c>
       <c r="L88" s="4" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N88" s="3" t="n">
-        <v>43.2</v>
+        <v>44.1</v>
       </c>
       <c r="O88" s="4" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="89">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -5884,25 +5884,25 @@
         </is>
       </c>
       <c r="D89" s="3" t="n">
-        <v>50.3</v>
+        <v>57.5</v>
       </c>
       <c r="E89" s="4" t="n">
-        <v>193</v>
+        <v>80</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G89" s="3" t="n">
-        <v>42.5</v>
+        <v>45</v>
       </c>
       <c r="H89" s="4" t="n">
-        <v>193</v>
+        <v>80</v>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
@@ -5911,21 +5911,21 @@
         </is>
       </c>
       <c r="K89" s="3" t="n">
-        <v>54.7</v>
+        <v>47.1</v>
       </c>
       <c r="L89" s="4" t="n">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N89" s="3" t="n">
-        <v>46.7</v>
+        <v>47.1</v>
       </c>
       <c r="O89" s="4" t="n">
-        <v>75</v>
+        <v>34</v>
       </c>
     </row>
     <row r="90">
@@ -6302,7 +6302,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -6311,10 +6311,10 @@
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>51.6</v>
+        <v>52.6</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>64</v>
+        <v>171</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -6322,14 +6322,14 @@
         </is>
       </c>
       <c r="G96" s="3" t="n">
-        <v>42.2</v>
+        <v>39.2</v>
       </c>
       <c r="H96" s="4" t="n">
-        <v>64</v>
+        <v>171</v>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
@@ -6338,10 +6338,10 @@
         </is>
       </c>
       <c r="K96" s="3" t="n">
-        <v>50</v>
+        <v>55.8</v>
       </c>
       <c r="L96" s="4" t="n">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
@@ -6349,10 +6349,10 @@
         </is>
       </c>
       <c r="N96" s="3" t="n">
-        <v>43.8</v>
+        <v>42.3</v>
       </c>
       <c r="O96" s="4" t="n">
-        <v>32</v>
+        <v>52</v>
       </c>
     </row>
     <row r="97">
@@ -6485,7 +6485,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -6494,25 +6494,25 @@
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>50.3</v>
+        <v>58.2</v>
       </c>
       <c r="E99" s="4" t="n">
-        <v>169</v>
+        <v>79</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G99" s="3" t="n">
-        <v>43.8</v>
+        <v>38</v>
       </c>
       <c r="H99" s="4" t="n">
-        <v>169</v>
+        <v>79</v>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-U</t>
+          <t>D-U-U-N</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
@@ -6521,10 +6521,10 @@
         </is>
       </c>
       <c r="K99" s="3" t="n">
-        <v>53.6</v>
+        <v>50</v>
       </c>
       <c r="L99" s="4" t="n">
-        <v>69</v>
+        <v>26</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
@@ -6532,10 +6532,10 @@
         </is>
       </c>
       <c r="N99" s="3" t="n">
-        <v>44.9</v>
+        <v>53.8</v>
       </c>
       <c r="O99" s="4" t="n">
-        <v>69</v>
+        <v>26</v>
       </c>
     </row>
     <row r="100">
@@ -7168,34 +7168,34 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>U-N-N</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>45.5</v>
+        <v>85.7</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I4" s="3" t="n">
-        <v>54.5</v>
+        <v>42.9</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>N-U-N-U</t>
+          <t>N-U-N-N</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -7235,7 +7235,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>58.3</v>
+        <v>50</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -7255,37 +7255,37 @@
         </is>
       </c>
       <c r="I5" s="3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M5" s="3" t="n">
-        <v>60</v>
+        <v>53.3</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P5" s="3" t="n">
         <v>40</v>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -7377,19 +7377,19 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>65</v>
+        <v>57.1</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -7400,34 +7400,34 @@
         <v>40</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-U</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M7" s="3" t="n">
-        <v>62.5</v>
+        <v>66.7</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="P7" s="3" t="n">
-        <v>37.5</v>
+        <v>33.3</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
@@ -7732,57 +7732,57 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>N-U-D</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>45.5</v>
+        <v>100</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I12" s="3" t="n">
-        <v>54.5</v>
+        <v>100</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-D</t>
+          <t>D-N-U-N</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M12" s="3" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P12" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -8939,7 +8939,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I29" s="3" t="n">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-D</t>
+          <t>D-D-U-U</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -8978,7 +8978,7 @@
         <v>50</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -8989,7 +8989,7 @@
         <v>50</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -9294,57 +9294,57 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-U</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>75</v>
+        <v>53.8</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I34" s="3" t="n">
-        <v>50</v>
+        <v>61.5</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>N-U-N-N</t>
+          <t>N-U-N-U</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M34" s="3" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P34" s="3" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -9725,25 +9725,25 @@
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>80</v>
+        <v>66.7</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I40" s="3" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-N</t>
+          <t>N-U-D-D</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -9755,7 +9755,7 @@
         <v>100</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>100</v>
       </c>
       <c r="Q40" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -9787,53 +9787,57 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F41" s="3" t="n">
         <v>50</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I41" s="3" t="n">
         <v>50</v>
       </c>
       <c r="J41" s="4" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M41" s="3" t="inlineStr"/>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="n">
+        <v>80</v>
+      </c>
       <c r="N41" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P41" s="3" t="inlineStr"/>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="n">
+        <v>80</v>
+      </c>
       <c r="Q41" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42">
@@ -10485,7 +10489,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-N-N</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -10494,10 +10498,10 @@
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -10505,26 +10509,26 @@
         </is>
       </c>
       <c r="I51" s="3" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="J51" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>N-N-N-U</t>
+          <t>N-N-N-N</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M51" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N51" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
@@ -10535,7 +10539,7 @@
         <v>100</v>
       </c>
       <c r="Q51" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -10698,46 +10702,46 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>50</v>
+        <v>44.4</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I54" s="3" t="n">
-        <v>50</v>
+        <v>44.4</v>
       </c>
       <c r="J54" s="4" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-N</t>
+          <t>D-D-N-D</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="M54" s="3" t="n">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
@@ -10745,10 +10749,10 @@
         </is>
       </c>
       <c r="P54" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="Q54" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55">
@@ -10769,7 +10773,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -10778,48 +10782,48 @@
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>38.9</v>
+        <v>60</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I55" s="3" t="n">
-        <v>44.4</v>
+        <v>40</v>
       </c>
       <c r="J55" s="4" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-D</t>
+          <t>D-U-U-N</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M55" s="3" t="n">
-        <v>43.8</v>
+        <v>50</v>
       </c>
       <c r="N55" s="4" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="P55" s="3" t="n">
-        <v>43.8</v>
+        <v>50</v>
       </c>
       <c r="Q55" s="4" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -10840,7 +10844,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -10849,10 +10853,10 @@
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>50</v>
+        <v>55.6</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -10860,14 +10864,14 @@
         </is>
       </c>
       <c r="I56" s="3" t="n">
-        <v>58.3</v>
+        <v>66.7</v>
       </c>
       <c r="J56" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-D</t>
+          <t>U-U-U-U</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
@@ -10876,10 +10880,10 @@
         </is>
       </c>
       <c r="M56" s="3" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
       <c r="N56" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
@@ -10887,10 +10891,10 @@
         </is>
       </c>
       <c r="P56" s="3" t="n">
-        <v>66.7</v>
+        <v>80</v>
       </c>
       <c r="Q56" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57">
@@ -10911,7 +10915,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>N-N-D</t>
+          <t>N-N-U</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -10920,25 +10924,25 @@
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>83.3</v>
+        <v>42.9</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I57" s="3" t="n">
-        <v>50</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="J57" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-D</t>
+          <t>D-N-N-U</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
@@ -10950,18 +10954,18 @@
         <v>100</v>
       </c>
       <c r="N57" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P57" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="Q57" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -11195,19 +11199,19 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -11218,30 +11222,34 @@
         <v>100</v>
       </c>
       <c r="J61" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>N-N-N-D</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="M61" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N61" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="K61" s="2" t="inlineStr">
-        <is>
-          <t>N-N-N-N</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M61" s="3" t="inlineStr"/>
-      <c r="N61" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P61" s="3" t="inlineStr"/>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P61" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="Q61" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -11546,7 +11554,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>U-N-N</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -11555,10 +11563,10 @@
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>58.3</v>
+        <v>43.8</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -11566,26 +11574,26 @@
         </is>
       </c>
       <c r="I66" s="3" t="n">
-        <v>41.7</v>
+        <v>50</v>
       </c>
       <c r="J66" s="4" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>U-U-N-U</t>
+          <t>U-U-N-N</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M66" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="N66" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
@@ -11593,10 +11601,10 @@
         </is>
       </c>
       <c r="P66" s="3" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="Q66" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67">
@@ -11688,7 +11696,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -11697,10 +11705,10 @@
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>60</v>
+        <v>61.5</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -11708,37 +11716,37 @@
         </is>
       </c>
       <c r="I68" s="3" t="n">
-        <v>60</v>
+        <v>53.8</v>
       </c>
       <c r="J68" s="4" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-D</t>
+          <t>U-U-U-U</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="M68" s="3" t="n">
-        <v>75</v>
+        <v>42.9</v>
       </c>
       <c r="N68" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P68" s="3" t="n">
-        <v>50</v>
+        <v>42.9</v>
       </c>
       <c r="Q68" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69">
@@ -12039,7 +12047,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-N-N</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -12048,7 +12056,7 @@
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="G73" s="4" t="n">
         <v>3</v>
@@ -12059,19 +12067,19 @@
         </is>
       </c>
       <c r="I73" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>3</v>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>N-N-N-U</t>
+          <t>N-N-N-N</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M73" s="3" t="n">
@@ -12082,7 +12090,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P73" s="3" t="n">
@@ -12315,7 +12323,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -12324,10 +12332,10 @@
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>60</v>
+        <v>57.1</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
@@ -12335,37 +12343,37 @@
         </is>
       </c>
       <c r="I77" s="3" t="n">
-        <v>45</v>
+        <v>42.9</v>
       </c>
       <c r="J77" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M77" s="3" t="n">
-        <v>80</v>
+        <v>55.6</v>
       </c>
       <c r="N77" s="4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P77" s="3" t="n">
-        <v>60</v>
+        <v>55.6</v>
       </c>
       <c r="Q77" s="4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="78">
@@ -12386,46 +12394,46 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>54.5</v>
+        <v>55.6</v>
       </c>
       <c r="G78" s="4" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I78" s="3" t="n">
-        <v>60.6</v>
+        <v>44.4</v>
       </c>
       <c r="J78" s="4" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-U</t>
+          <t>D-U-U-N</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M78" s="3" t="n">
-        <v>63.6</v>
+        <v>40</v>
       </c>
       <c r="N78" s="4" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
@@ -12433,10 +12441,10 @@
         </is>
       </c>
       <c r="P78" s="3" t="n">
-        <v>54.5</v>
+        <v>60</v>
       </c>
       <c r="Q78" s="4" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79">
@@ -12741,7 +12749,7 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-N-N</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -12750,48 +12758,48 @@
         </is>
       </c>
       <c r="F83" s="3" t="n">
-        <v>66.7</v>
+        <v>57.1</v>
       </c>
       <c r="G83" s="4" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I83" s="3" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="J83" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>U-N-N-N</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>D/N</t>
+        </is>
+      </c>
+      <c r="M83" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="N83" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
           <t>D/U</t>
         </is>
       </c>
-      <c r="I83" s="3" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="J83" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="K83" s="2" t="inlineStr">
-        <is>
-          <t>U-N-N-U</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M83" s="3" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="N83" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="O83" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
       <c r="P83" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="Q83" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
@@ -13025,7 +13033,7 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -13034,10 +13042,10 @@
         </is>
       </c>
       <c r="F87" s="3" t="n">
-        <v>57.1</v>
+        <v>63.6</v>
       </c>
       <c r="G87" s="4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
@@ -13045,26 +13053,26 @@
         </is>
       </c>
       <c r="I87" s="3" t="n">
-        <v>57.1</v>
+        <v>54.5</v>
       </c>
       <c r="J87" s="4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>D-N-D-D</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M87" s="3" t="n">
-        <v>33.3</v>
+        <v>80</v>
       </c>
       <c r="N87" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
@@ -13072,10 +13080,10 @@
         </is>
       </c>
       <c r="P87" s="3" t="n">
-        <v>66.7</v>
+        <v>80</v>
       </c>
       <c r="Q87" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="88">
@@ -13096,57 +13104,57 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F88" s="3" t="n">
-        <v>58.3</v>
+        <v>53.3</v>
       </c>
       <c r="G88" s="4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I88" s="3" t="n">
-        <v>66.7</v>
+        <v>46.7</v>
       </c>
       <c r="J88" s="4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-U</t>
+          <t>D-U-N-D</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M88" s="3" t="n">
-        <v>66.7</v>
+        <v>62.5</v>
       </c>
       <c r="N88" s="4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P88" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="Q88" s="4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="89">
@@ -13167,57 +13175,57 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F89" s="3" t="n">
-        <v>43.5</v>
+        <v>46.7</v>
       </c>
       <c r="G89" s="4" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I89" s="3" t="n">
-        <v>52.2</v>
+        <v>53.3</v>
       </c>
       <c r="J89" s="4" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M89" s="3" t="n">
-        <v>45.5</v>
+        <v>50</v>
       </c>
       <c r="N89" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P89" s="3" t="n">
-        <v>45.5</v>
+        <v>62.5</v>
       </c>
       <c r="Q89" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="90">
@@ -13664,7 +13672,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -13673,10 +13681,10 @@
         </is>
       </c>
       <c r="F96" s="3" t="n">
-        <v>61.5</v>
+        <v>59.5</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -13684,14 +13692,14 @@
         </is>
       </c>
       <c r="I96" s="3" t="n">
-        <v>53.8</v>
+        <v>43.2</v>
       </c>
       <c r="J96" s="4" t="n">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
@@ -13700,10 +13708,10 @@
         </is>
       </c>
       <c r="M96" s="3" t="n">
-        <v>70</v>
+        <v>64.3</v>
       </c>
       <c r="N96" s="4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
@@ -13711,10 +13719,10 @@
         </is>
       </c>
       <c r="P96" s="3" t="n">
-        <v>50</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="Q96" s="4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="97">
@@ -13873,19 +13881,19 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>57.1</v>
+        <v>41.7</v>
       </c>
       <c r="G99" s="4" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
@@ -13893,26 +13901,26 @@
         </is>
       </c>
       <c r="I99" s="3" t="n">
-        <v>60.7</v>
+        <v>66.7</v>
       </c>
       <c r="J99" s="4" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-U</t>
+          <t>D-U-U-N</t>
         </is>
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="M99" s="3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="N99" s="4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
@@ -13920,10 +13928,10 @@
         </is>
       </c>
       <c r="P99" s="3" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="Q99" s="4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="100">

--- a/BIS_tr.xlsx
+++ b/BIS_tr.xlsx
@@ -568,7 +568,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -577,10 +577,10 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>66.7</v>
+        <v>61.9</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -588,14 +588,14 @@
         </is>
       </c>
       <c r="G2" s="3" t="n">
-        <v>46.2</v>
+        <v>46.9</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-N</t>
+          <t>N-D-D-D</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -604,21 +604,21 @@
         </is>
       </c>
       <c r="K2" s="3" t="n">
-        <v>64.7</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N2" s="3" t="n">
-        <v>41.2</v>
+        <v>50</v>
       </c>
       <c r="O2" s="4" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
@@ -934,7 +934,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -943,25 +943,25 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>100</v>
+        <v>77.8</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G8" s="3" t="n">
-        <v>40</v>
+        <v>55.6</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-N</t>
+          <t>D-U-N-D</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -970,21 +970,21 @@
         </is>
       </c>
       <c r="K8" s="3" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N8" s="3" t="n">
         <v>50</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1065,10 +1065,10 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>76.09999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>88</v>
+        <v>151</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -1076,14 +1076,14 @@
         </is>
       </c>
       <c r="G10" s="3" t="n">
-        <v>40.9</v>
+        <v>37.1</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>88</v>
+        <v>151</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-N</t>
+          <t>U-U-D-D</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1092,10 +1092,10 @@
         </is>
       </c>
       <c r="K10" s="3" t="n">
-        <v>74.3</v>
+        <v>62.5</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="N10" s="3" t="n">
-        <v>45.7</v>
+        <v>42.9</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>35</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1126,25 +1126,25 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>79.59999999999999</v>
+        <v>74</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G11" s="3" t="n">
-        <v>46.9</v>
+        <v>37</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-N</t>
+          <t>D-U-N-D</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1153,21 +1153,21 @@
         </is>
       </c>
       <c r="K11" s="3" t="n">
-        <v>80</v>
+        <v>77.8</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N11" s="3" t="n">
-        <v>45</v>
+        <v>36.1</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1187,25 +1187,25 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>58.8</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>52.9</v>
+        <v>46.4</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>N-U-N-U</t>
+          <t>N-U-N-D</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1217,18 +1217,18 @@
         <v>100</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N12" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1309,25 +1309,25 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>69.09999999999999</v>
+        <v>70.8</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G14" s="3" t="n">
-        <v>39.7</v>
+        <v>44.4</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>N-D-N-N</t>
+          <t>N-D-N-D</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1336,7 +1336,7 @@
         </is>
       </c>
       <c r="K14" s="3" t="n">
-        <v>72.7</v>
+        <v>81.8</v>
       </c>
       <c r="L14" s="4" t="n">
         <v>22</v>
@@ -1347,7 +1347,7 @@
         </is>
       </c>
       <c r="N14" s="3" t="n">
-        <v>50</v>
+        <v>40.9</v>
       </c>
       <c r="O14" s="4" t="n">
         <v>22</v>
@@ -1727,7 +1727,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1736,25 +1736,25 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>64</v>
+        <v>57.1</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>86</v>
+        <v>140</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G21" s="3" t="n">
-        <v>37.2</v>
+        <v>42.1</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>86</v>
+        <v>140</v>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1763,10 +1763,10 @@
         </is>
       </c>
       <c r="K21" s="3" t="n">
-        <v>51.4</v>
+        <v>61.1</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
@@ -1774,10 +1774,10 @@
         </is>
       </c>
       <c r="N21" s="3" t="n">
-        <v>54.1</v>
+        <v>38.9</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>37</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22">
@@ -1971,7 +1971,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>83.3</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1991,14 +1991,14 @@
         </is>
       </c>
       <c r="G25" s="3" t="n">
-        <v>43.8</v>
+        <v>61.9</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>N-N-N-N</t>
+          <t>N-N-N-D</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -2007,10 +2007,10 @@
         </is>
       </c>
       <c r="K25" s="3" t="n">
-        <v>92.90000000000001</v>
+        <v>61.9</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
@@ -2018,10 +2018,10 @@
         </is>
       </c>
       <c r="N25" s="3" t="n">
-        <v>50</v>
+        <v>52.4</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2163,25 +2163,25 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>72.5</v>
+        <v>60.6</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>69</v>
+        <v>180</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G28" s="3" t="n">
-        <v>43.5</v>
+        <v>47.8</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>69</v>
+        <v>180</v>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-N</t>
+          <t>N-D-U-U</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -2190,10 +2190,10 @@
         </is>
       </c>
       <c r="K28" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>75</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
@@ -2201,10 +2201,10 @@
         </is>
       </c>
       <c r="N28" s="3" t="n">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-N-N</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2285,25 +2285,25 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>61.4</v>
+        <v>74.2</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>45.5</v>
+        <v>41.9</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>U-N-N-U</t>
+          <t>U-N-N-N</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -2312,21 +2312,21 @@
         </is>
       </c>
       <c r="K30" s="3" t="n">
-        <v>61.5</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N30" s="3" t="n">
-        <v>46.2</v>
+        <v>42.9</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>63.1</v>
+        <v>59.6</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>84</v>
+        <v>57</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2540,14 +2540,14 @@
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>44</v>
+        <v>40.4</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>84</v>
+        <v>57</v>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-U</t>
+          <t>U-N-U-N</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="K34" s="3" t="n">
-        <v>60.7</v>
+        <v>47.4</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="N34" s="3" t="n">
-        <v>46.4</v>
+        <v>57.9</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35">
@@ -2581,34 +2581,34 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D35" s="3" t="n">
         <v>50</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v>55</v>
+        <v>45.7</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-U</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -2617,21 +2617,21 @@
         </is>
       </c>
       <c r="K35" s="3" t="n">
-        <v>70</v>
+        <v>54.8</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N35" s="3" t="n">
-        <v>50</v>
+        <v>45.2</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>10</v>
+        <v>31</v>
       </c>
     </row>
     <row r="36">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>N-U-D</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2651,48 +2651,48 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>51.6</v>
+        <v>63</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>48.4</v>
+        <v>48.1</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-D</t>
+          <t>D-N-U-U</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="K36" s="3" t="n">
-        <v>41.7</v>
+        <v>44.4</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N36" s="3" t="n">
-        <v>50</v>
+        <v>55.6</v>
       </c>
       <c r="O36" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2895,25 +2895,25 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>64.8</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G40" s="3" t="n">
-        <v>40.5</v>
+        <v>40.9</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -2922,21 +2922,21 @@
         </is>
       </c>
       <c r="K40" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>70</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N40" s="3" t="n">
-        <v>47.1</v>
+        <v>45</v>
       </c>
       <c r="O40" s="4" t="n">
-        <v>17</v>
+        <v>40</v>
       </c>
     </row>
     <row r="41">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3017,48 +3017,48 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>62.5</v>
+        <v>50</v>
       </c>
       <c r="E42" s="4" t="n">
         <v>8</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G42" s="3" t="n">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="H42" s="4" t="n">
         <v>8</v>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>U-N-N-U</t>
+          <t>U-N-N-D</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="K42" s="3" t="n">
         <v>50</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N42" s="3" t="n">
         <v>50</v>
       </c>
       <c r="O42" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3200,48 +3200,48 @@
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>47.2</v>
+        <v>51.1</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G45" s="3" t="n">
-        <v>47.7</v>
+        <v>44.6</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-U</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K45" s="3" t="n">
-        <v>42.7</v>
+        <v>51.3</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N45" s="3" t="n">
-        <v>51.7</v>
+        <v>42.3</v>
       </c>
       <c r="O45" s="4" t="n">
-        <v>89</v>
+        <v>78</v>
       </c>
     </row>
     <row r="46">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -3444,25 +3444,25 @@
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>73.2</v>
+        <v>61.8</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G49" s="3" t="n">
-        <v>39</v>
+        <v>48.5</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-N</t>
+          <t>U-D-N-D</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -3471,10 +3471,10 @@
         </is>
       </c>
       <c r="K49" s="3" t="n">
-        <v>87.5</v>
+        <v>65.7</v>
       </c>
       <c r="L49" s="4" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
@@ -3482,10 +3482,10 @@
         </is>
       </c>
       <c r="N49" s="3" t="n">
-        <v>37.5</v>
+        <v>51.4</v>
       </c>
       <c r="O49" s="4" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
     </row>
     <row r="50">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3688,10 +3688,10 @@
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>56.2</v>
+        <v>61.5</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3699,26 +3699,26 @@
         </is>
       </c>
       <c r="G53" s="3" t="n">
-        <v>56.2</v>
+        <v>46.2</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K53" s="3" t="n">
-        <v>57.1</v>
+        <v>58.8</v>
       </c>
       <c r="L53" s="4" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
@@ -3726,10 +3726,10 @@
         </is>
       </c>
       <c r="N53" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>52.9</v>
       </c>
       <c r="O53" s="4" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="54">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3749,10 +3749,10 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>83.3</v>
+        <v>64.7</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3760,37 +3760,37 @@
         </is>
       </c>
       <c r="G54" s="3" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>D-N-D-D</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K54" s="3" t="n">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="L54" s="4" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N54" s="3" t="n">
-        <v>57.1</v>
+        <v>45</v>
       </c>
       <c r="O54" s="4" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="55">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3932,25 +3932,25 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>57.1</v>
+        <v>81.8</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>77</v>
+        <v>33</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G57" s="3" t="n">
-        <v>44.2</v>
+        <v>48.5</v>
       </c>
       <c r="H57" s="4" t="n">
-        <v>77</v>
+        <v>33</v>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>N-N-U-U</t>
+          <t>N-N-U-N</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -3959,21 +3959,21 @@
         </is>
       </c>
       <c r="K57" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L57" s="4" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="N57" s="3" t="n">
-        <v>38.5</v>
+        <v>37.5</v>
       </c>
       <c r="O57" s="4" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
     </row>
     <row r="58">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4054,25 +4054,25 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>70.7</v>
+        <v>63.2</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>92</v>
+        <v>125</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G59" s="3" t="n">
-        <v>44.6</v>
+        <v>41.6</v>
       </c>
       <c r="H59" s="4" t="n">
-        <v>92</v>
+        <v>125</v>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -4081,10 +4081,10 @@
         </is>
       </c>
       <c r="K59" s="3" t="n">
-        <v>67.90000000000001</v>
+        <v>62.5</v>
       </c>
       <c r="L59" s="4" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
@@ -4092,10 +4092,10 @@
         </is>
       </c>
       <c r="N59" s="3" t="n">
-        <v>53.6</v>
+        <v>42.9</v>
       </c>
       <c r="O59" s="4" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
     </row>
     <row r="60">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4115,10 +4115,10 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>70.2</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>94</v>
+        <v>145</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -4126,14 +4126,14 @@
         </is>
       </c>
       <c r="G60" s="3" t="n">
-        <v>42.6</v>
+        <v>42.1</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>94</v>
+        <v>145</v>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-N</t>
+          <t>U-U-D-D</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -4142,21 +4142,21 @@
         </is>
       </c>
       <c r="K60" s="3" t="n">
-        <v>58.7</v>
+        <v>62.5</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N60" s="3" t="n">
-        <v>41.3</v>
+        <v>42.9</v>
       </c>
       <c r="O60" s="4" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
     </row>
     <row r="61">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4176,10 +4176,10 @@
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>80</v>
+        <v>62.5</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -4187,37 +4187,37 @@
         </is>
       </c>
       <c r="G61" s="3" t="n">
-        <v>66.7</v>
+        <v>52.5</v>
       </c>
       <c r="H61" s="4" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-N</t>
+          <t>N-N-D-D</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K61" s="3" t="n">
         <v>100</v>
       </c>
       <c r="L61" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N61" s="3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="62">
@@ -4472,7 +4472,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -4481,10 +4481,10 @@
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>87.90000000000001</v>
+        <v>66.2</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>124</v>
+        <v>68</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -4492,14 +4492,14 @@
         </is>
       </c>
       <c r="G66" s="3" t="n">
-        <v>53.2</v>
+        <v>39.7</v>
       </c>
       <c r="H66" s="4" t="n">
-        <v>124</v>
+        <v>68</v>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>U-N-N-N</t>
+          <t>U-N-N-D</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -4508,10 +4508,10 @@
         </is>
       </c>
       <c r="K66" s="3" t="n">
-        <v>90.5</v>
+        <v>52.6</v>
       </c>
       <c r="L66" s="4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
@@ -4519,10 +4519,10 @@
         </is>
       </c>
       <c r="N66" s="3" t="n">
-        <v>61.9</v>
+        <v>47.4</v>
       </c>
       <c r="O66" s="4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="67">
@@ -4533,7 +4533,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -4542,25 +4542,25 @@
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>100</v>
+        <v>47.1</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G67" s="3" t="n">
-        <v>50</v>
+        <v>47.1</v>
       </c>
       <c r="H67" s="4" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-N</t>
+          <t>U-U-D-D</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -4569,21 +4569,21 @@
         </is>
       </c>
       <c r="K67" s="3" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="L67" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N67" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="O67" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68">
@@ -4838,19 +4838,19 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>48.5</v>
+        <v>53.3</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>33</v>
+        <v>90</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4858,14 +4858,14 @@
         </is>
       </c>
       <c r="G72" s="3" t="n">
-        <v>42.4</v>
+        <v>43.3</v>
       </c>
       <c r="H72" s="4" t="n">
-        <v>33</v>
+        <v>90</v>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -4874,10 +4874,10 @@
         </is>
       </c>
       <c r="K72" s="3" t="n">
-        <v>70</v>
+        <v>45.7</v>
       </c>
       <c r="L72" s="4" t="n">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
@@ -4885,10 +4885,10 @@
         </is>
       </c>
       <c r="N72" s="3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="O72" s="4" t="n">
-        <v>10</v>
+        <v>46</v>
       </c>
     </row>
     <row r="73">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-U</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -5091,25 +5091,25 @@
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>72.7</v>
+        <v>72.2</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G76" s="3" t="n">
-        <v>34.1</v>
+        <v>55.6</v>
       </c>
       <c r="H76" s="4" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>N-N-N-N</t>
+          <t>N-N-N-U</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -5118,10 +5118,10 @@
         </is>
       </c>
       <c r="K76" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>80</v>
       </c>
       <c r="L76" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
@@ -5129,10 +5129,10 @@
         </is>
       </c>
       <c r="N76" s="3" t="n">
-        <v>50</v>
+        <v>46.7</v>
       </c>
       <c r="O76" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="77">
@@ -5387,7 +5387,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -5396,37 +5396,37 @@
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>59.3</v>
+        <v>59.7</v>
       </c>
       <c r="E81" s="4" t="n">
-        <v>59</v>
+        <v>119</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G81" s="3" t="n">
-        <v>45.8</v>
+        <v>42</v>
       </c>
       <c r="H81" s="4" t="n">
-        <v>59</v>
+        <v>119</v>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K81" s="3" t="n">
-        <v>42.9</v>
+        <v>59.6</v>
       </c>
       <c r="L81" s="4" t="n">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
@@ -5434,10 +5434,10 @@
         </is>
       </c>
       <c r="N81" s="3" t="n">
-        <v>57.1</v>
+        <v>42.3</v>
       </c>
       <c r="O81" s="4" t="n">
-        <v>21</v>
+        <v>52</v>
       </c>
     </row>
     <row r="82">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -5579,25 +5579,25 @@
         </is>
       </c>
       <c r="D84" s="3" t="n">
-        <v>61.4</v>
+        <v>56.2</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G84" s="3" t="n">
-        <v>42.9</v>
+        <v>39.2</v>
       </c>
       <c r="H84" s="4" t="n">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -5606,10 +5606,10 @@
         </is>
       </c>
       <c r="K84" s="3" t="n">
-        <v>67.90000000000001</v>
+        <v>55.8</v>
       </c>
       <c r="L84" s="4" t="n">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
@@ -5617,10 +5617,10 @@
         </is>
       </c>
       <c r="N84" s="3" t="n">
-        <v>46.4</v>
+        <v>38.5</v>
       </c>
       <c r="O84" s="4" t="n">
-        <v>28</v>
+        <v>52</v>
       </c>
     </row>
     <row r="85">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -6067,10 +6067,10 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>73.2</v>
+        <v>57.9</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -6078,14 +6078,14 @@
         </is>
       </c>
       <c r="G92" s="3" t="n">
-        <v>36.6</v>
+        <v>40.4</v>
       </c>
       <c r="H92" s="4" t="n">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-N</t>
+          <t>U-D-N-D</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
@@ -6094,21 +6094,21 @@
         </is>
       </c>
       <c r="K92" s="3" t="n">
-        <v>70</v>
+        <v>64.5</v>
       </c>
       <c r="L92" s="4" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N92" s="3" t="n">
-        <v>45</v>
+        <v>38.7</v>
       </c>
       <c r="O92" s="4" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="93">
@@ -6302,7 +6302,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -6311,10 +6311,10 @@
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>51.2</v>
+        <v>50.6</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>84</v>
+        <v>168</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -6322,14 +6322,14 @@
         </is>
       </c>
       <c r="G96" s="3" t="n">
-        <v>42.9</v>
+        <v>41.7</v>
       </c>
       <c r="H96" s="4" t="n">
-        <v>84</v>
+        <v>168</v>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-N</t>
+          <t>U-U-D-D</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
@@ -6338,21 +6338,21 @@
         </is>
       </c>
       <c r="K96" s="3" t="n">
-        <v>57.9</v>
+        <v>55.2</v>
       </c>
       <c r="L96" s="4" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N96" s="3" t="n">
-        <v>42.1</v>
+        <v>44.8</v>
       </c>
       <c r="O96" s="4" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
     </row>
     <row r="97">
@@ -6363,7 +6363,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -6372,10 +6372,10 @@
         </is>
       </c>
       <c r="D97" s="3" t="n">
-        <v>65.5</v>
+        <v>59.8</v>
       </c>
       <c r="E97" s="4" t="n">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -6383,14 +6383,14 @@
         </is>
       </c>
       <c r="G97" s="3" t="n">
-        <v>38.2</v>
+        <v>37.8</v>
       </c>
       <c r="H97" s="4" t="n">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-N</t>
+          <t>U-N-D-D</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
@@ -6399,18 +6399,18 @@
         </is>
       </c>
       <c r="K97" s="3" t="n">
-        <v>65.40000000000001</v>
+        <v>61.5</v>
       </c>
       <c r="L97" s="4" t="n">
         <v>26</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N97" s="3" t="n">
-        <v>38.5</v>
+        <v>42.3</v>
       </c>
       <c r="O97" s="4" t="n">
         <v>26</v>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -6616,10 +6616,10 @@
         </is>
       </c>
       <c r="D101" s="3" t="n">
-        <v>68.40000000000001</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="E101" s="4" t="n">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -6627,14 +6627,14 @@
         </is>
       </c>
       <c r="G101" s="3" t="n">
-        <v>43.9</v>
+        <v>45.1</v>
       </c>
       <c r="H101" s="4" t="n">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-N</t>
+          <t>U-D-N-D</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
@@ -6643,10 +6643,10 @@
         </is>
       </c>
       <c r="K101" s="3" t="n">
-        <v>66.7</v>
+        <v>61.3</v>
       </c>
       <c r="L101" s="4" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
@@ -6654,10 +6654,10 @@
         </is>
       </c>
       <c r="N101" s="3" t="n">
-        <v>40.7</v>
+        <v>35.5</v>
       </c>
       <c r="O101" s="4" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="102">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -6677,25 +6677,25 @@
         </is>
       </c>
       <c r="D102" s="3" t="n">
-        <v>75.8</v>
+        <v>62.5</v>
       </c>
       <c r="E102" s="4" t="n">
-        <v>120</v>
+        <v>56</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G102" s="3" t="n">
-        <v>40</v>
+        <v>35.7</v>
       </c>
       <c r="H102" s="4" t="n">
-        <v>120</v>
+        <v>56</v>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-N</t>
+          <t>U-N-U-D</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
@@ -6704,21 +6704,21 @@
         </is>
       </c>
       <c r="K102" s="3" t="n">
-        <v>69.8</v>
+        <v>55.6</v>
       </c>
       <c r="L102" s="4" t="n">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="N102" s="3" t="n">
-        <v>45.3</v>
+        <v>37</v>
       </c>
       <c r="O102" s="4" t="n">
-        <v>53</v>
+        <v>27</v>
       </c>
     </row>
     <row r="103">
@@ -6790,7 +6790,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="D104" s="3" t="n">
-        <v>57.6</v>
+        <v>51.4</v>
       </c>
       <c r="E104" s="4" t="n">
-        <v>33</v>
+        <v>74</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -6810,14 +6810,14 @@
         </is>
       </c>
       <c r="G104" s="3" t="n">
-        <v>42.4</v>
+        <v>41.9</v>
       </c>
       <c r="H104" s="4" t="n">
-        <v>33</v>
+        <v>74</v>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>N-N-U-N</t>
+          <t>N-N-U-D</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
@@ -6826,21 +6826,21 @@
         </is>
       </c>
       <c r="K104" s="3" t="n">
-        <v>61.5</v>
+        <v>60</v>
       </c>
       <c r="L104" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N104" s="3" t="n">
-        <v>38.5</v>
+        <v>46.7</v>
       </c>
       <c r="O104" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -7035,10 +7035,10 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>90</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -7046,26 +7046,26 @@
         </is>
       </c>
       <c r="I2" s="3" t="n">
-        <v>50</v>
+        <v>60.9</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-N</t>
+          <t>N-D-D-D</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M2" s="3" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
@@ -7073,10 +7073,10 @@
         </is>
       </c>
       <c r="P2" s="3" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
       <c r="Q2" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -7452,7 +7452,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -7461,41 +7461,41 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I8" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>D-U-N-D</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="n">
         <v>66.7</v>
-      </c>
-      <c r="J8" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>D-U-N-N</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="n">
-        <v>100</v>
       </c>
       <c r="N8" s="4" t="n">
         <v>3</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P8" s="3" t="n">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -7603,10 +7603,10 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>78.3</v>
+        <v>88.2</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -7614,14 +7614,14 @@
         </is>
       </c>
       <c r="I10" s="3" t="n">
-        <v>43.5</v>
+        <v>44.1</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-N</t>
+          <t>U-U-D-D</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -7630,21 +7630,21 @@
         </is>
       </c>
       <c r="M10" s="3" t="n">
-        <v>75</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P10" s="3" t="n">
-        <v>50</v>
+        <v>38.5</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
@@ -7665,7 +7665,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -7674,25 +7674,25 @@
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>70</v>
+        <v>81.2</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I11" s="3" t="n">
-        <v>50</v>
+        <v>43.8</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-N</t>
+          <t>D-U-N-D</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -7701,21 +7701,21 @@
         </is>
       </c>
       <c r="M11" s="3" t="n">
-        <v>66.7</v>
+        <v>87.5</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="P11" s="3" t="n">
-        <v>50</v>
+        <v>37.5</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -7745,10 +7745,10 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -7756,14 +7756,14 @@
         </is>
       </c>
       <c r="I12" s="3" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>N-U-N-U</t>
+          <t>N-U-N-D</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -7883,25 +7883,25 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>90.90000000000001</v>
+        <v>75</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I14" s="3" t="n">
-        <v>36.4</v>
+        <v>41.7</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>N-D-N-N</t>
+          <t>N-D-N-D</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -7910,10 +7910,10 @@
         </is>
       </c>
       <c r="M14" s="3" t="n">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -7921,10 +7921,10 @@
         </is>
       </c>
       <c r="P14" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -8380,10 +8380,10 @@
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>61.1</v>
+        <v>55</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -8394,11 +8394,11 @@
         <v>50</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -8407,21 +8407,21 @@
         </is>
       </c>
       <c r="M21" s="3" t="n">
-        <v>62.5</v>
+        <v>50</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="P21" s="3" t="n">
-        <v>37.5</v>
+        <v>33.3</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22">
@@ -8655,7 +8655,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -8664,10 +8664,10 @@
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>87.5</v>
+        <v>86.7</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -8675,14 +8675,14 @@
         </is>
       </c>
       <c r="I25" s="3" t="n">
-        <v>62.5</v>
+        <v>66.7</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>N-N-N-N</t>
+          <t>N-N-N-D</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -8691,10 +8691,10 @@
         </is>
       </c>
       <c r="M25" s="3" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -8702,10 +8702,10 @@
         </is>
       </c>
       <c r="P25" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
@@ -8868,7 +8868,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -8877,25 +8877,25 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>91.7</v>
+        <v>63.2</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I28" s="3" t="n">
-        <v>41.7</v>
+        <v>55.3</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-N</t>
+          <t>N-D-U-U</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -8904,21 +8904,21 @@
         </is>
       </c>
       <c r="M28" s="3" t="n">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P28" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-N-N</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -9019,48 +9019,44 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>61.5</v>
+        <v>100</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I30" s="3" t="n">
-        <v>46.2</v>
+        <v>60</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>U-N-N-U</t>
+          <t>U-N-N-N</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M30" s="3" t="n">
-        <v>66.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr"/>
       <c r="N30" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P30" s="3" t="n">
-        <v>66.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr"/>
       <c r="Q30" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -9294,7 +9290,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -9303,25 +9299,25 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>66.7</v>
+        <v>63.6</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="I34" s="3" t="n">
-        <v>54.2</v>
+        <v>36.4</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-U</t>
+          <t>U-N-U-N</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -9330,21 +9326,21 @@
         </is>
       </c>
       <c r="M34" s="3" t="n">
-        <v>77.8</v>
+        <v>75</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P34" s="3" t="n">
-        <v>55.6</v>
+        <v>75</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
@@ -9365,19 +9361,19 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>50</v>
+        <v>52.6</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -9385,26 +9381,26 @@
         </is>
       </c>
       <c r="I35" s="3" t="n">
-        <v>83.3</v>
+        <v>63.2</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-U</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M35" s="3" t="n">
-        <v>50</v>
+        <v>62.5</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -9412,10 +9408,10 @@
         </is>
       </c>
       <c r="P35" s="3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36">
@@ -9436,7 +9432,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>N-U-D</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -9445,48 +9441,48 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>D/U</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="G36" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I36" s="3" t="n">
-        <v>62.5</v>
-      </c>
       <c r="J36" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-D</t>
+          <t>D-N-U-U</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M36" s="3" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P36" s="3" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="Q36" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -9720,7 +9716,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -9729,48 +9725,48 @@
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>100</v>
+        <v>76.5</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I40" s="3" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="J40" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>U-D-D-D</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="N40" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="J40" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>U-D-D-N</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M40" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="N40" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P40" s="3" t="n">
-        <v>100</v>
-      </c>
       <c r="Q40" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41">
@@ -9858,7 +9854,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -9870,7 +9866,7 @@
         <v>100</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -9881,34 +9877,30 @@
         <v>100</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>U-N-N-U</t>
+          <t>U-N-N-D</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M42" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr"/>
       <c r="N42" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P42" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr"/>
       <c r="Q42" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -10071,19 +10063,19 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>55.6</v>
+        <v>57.6</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -10091,26 +10083,26 @@
         </is>
       </c>
       <c r="I45" s="3" t="n">
-        <v>55.6</v>
+        <v>48.5</v>
       </c>
       <c r="J45" s="4" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-U</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M45" s="3" t="n">
-        <v>63.6</v>
+        <v>53.3</v>
       </c>
       <c r="N45" s="4" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
@@ -10118,10 +10110,10 @@
         </is>
       </c>
       <c r="P45" s="3" t="n">
-        <v>54.5</v>
+        <v>46.7</v>
       </c>
       <c r="Q45" s="4" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="46">
@@ -10351,7 +10343,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -10360,25 +10352,25 @@
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>100</v>
+        <v>61.1</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I49" s="3" t="n">
-        <v>60</v>
+        <v>61.1</v>
       </c>
       <c r="J49" s="4" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-N</t>
+          <t>U-D-N-D</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
@@ -10387,10 +10379,10 @@
         </is>
       </c>
       <c r="M49" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="N49" s="4" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
@@ -10398,10 +10390,10 @@
         </is>
       </c>
       <c r="P49" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="Q49" s="4" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="50">
@@ -10635,7 +10627,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -10644,10 +10636,10 @@
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>66.7</v>
+        <v>77.8</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -10655,14 +10647,14 @@
         </is>
       </c>
       <c r="I53" s="3" t="n">
-        <v>66.7</v>
+        <v>55.6</v>
       </c>
       <c r="J53" s="4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
@@ -10674,7 +10666,7 @@
         <v>100</v>
       </c>
       <c r="N53" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
@@ -10682,10 +10674,10 @@
         </is>
       </c>
       <c r="P53" s="3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="Q53" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54">
@@ -10706,7 +10698,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -10715,48 +10707,48 @@
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="G54" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="J54" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>D-N-D-D</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="N54" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I54" s="3" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="J54" s="4" t="n">
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>D/N/U</t>
+        </is>
+      </c>
+      <c r="P54" s="3" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="Q54" s="4" t="n">
         <v>3</v>
-      </c>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>D-N-D-N</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M54" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="N54" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="O54" s="2" t="inlineStr">
-        <is>
-          <t>D/N</t>
-        </is>
-      </c>
-      <c r="P54" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q54" s="4" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -10919,7 +10911,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -10928,10 +10920,10 @@
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>60</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -10939,37 +10931,37 @@
         </is>
       </c>
       <c r="I57" s="3" t="n">
-        <v>40</v>
+        <v>42.9</v>
       </c>
       <c r="J57" s="4" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>N-N-U-U</t>
+          <t>N-N-U-N</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M57" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="N57" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P57" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q57" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -11061,7 +11053,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -11070,25 +11062,25 @@
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>76.90000000000001</v>
+        <v>57.1</v>
       </c>
       <c r="G59" s="4" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I59" s="3" t="n">
-        <v>38.5</v>
+        <v>38.1</v>
       </c>
       <c r="J59" s="4" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
@@ -11097,10 +11089,10 @@
         </is>
       </c>
       <c r="M59" s="3" t="n">
-        <v>66.7</v>
+        <v>53.3</v>
       </c>
       <c r="N59" s="4" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
@@ -11108,10 +11100,10 @@
         </is>
       </c>
       <c r="P59" s="3" t="n">
-        <v>66.7</v>
+        <v>40</v>
       </c>
       <c r="Q59" s="4" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="60">
@@ -11132,7 +11124,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -11141,37 +11133,37 @@
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>78.59999999999999</v>
+        <v>54.8</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I60" s="3" t="n">
-        <v>57.1</v>
+        <v>45.2</v>
       </c>
       <c r="J60" s="4" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-N</t>
+          <t>U-U-D-D</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M60" s="3" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
       <c r="N60" s="4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
@@ -11179,10 +11171,10 @@
         </is>
       </c>
       <c r="P60" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q60" s="4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="61">
@@ -11203,7 +11195,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -11212,25 +11204,25 @@
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I61" s="3" t="n">
-        <v>100</v>
+        <v>62.5</v>
       </c>
       <c r="J61" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-N</t>
+          <t>N-N-D-D</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
@@ -11554,7 +11546,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -11563,25 +11555,25 @@
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>100</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="I66" s="3" t="n">
-        <v>60.9</v>
+        <v>38.5</v>
       </c>
       <c r="J66" s="4" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>U-N-N-N</t>
+          <t>U-N-N-D</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
@@ -11593,7 +11585,7 @@
         <v>100</v>
       </c>
       <c r="N66" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
@@ -11601,10 +11593,10 @@
         </is>
       </c>
       <c r="P66" s="3" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="Q66" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67">
@@ -11625,49 +11617,57 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="F67" s="3" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>75</v>
+      </c>
       <c r="G67" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="I67" s="3" t="inlineStr"/>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="n">
+        <v>75</v>
+      </c>
       <c r="J67" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-N</t>
+          <t>U-U-D-D</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M67" s="3" t="inlineStr"/>
+          <t>N/U</t>
+        </is>
+      </c>
+      <c r="M67" s="3" t="n">
+        <v>50</v>
+      </c>
       <c r="N67" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P67" s="3" t="inlineStr"/>
+          <t>D/U</t>
+        </is>
+      </c>
+      <c r="P67" s="3" t="n">
+        <v>50</v>
+      </c>
       <c r="Q67" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -11972,57 +11972,57 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F72" s="3" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I72" s="3" t="n">
-        <v>66.7</v>
+        <v>57.1</v>
       </c>
       <c r="J72" s="4" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M72" s="3" t="n">
-        <v>100</v>
+        <v>37.5</v>
       </c>
       <c r="N72" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P72" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q72" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="73">
@@ -12248,7 +12248,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-U</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -12257,25 +12257,25 @@
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>75</v>
+        <v>93.3</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I76" s="3" t="n">
-        <v>62.5</v>
+        <v>46.7</v>
       </c>
       <c r="J76" s="4" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>N-N-N-N</t>
+          <t>N-N-N-U</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
@@ -12284,14 +12284,14 @@
         </is>
       </c>
       <c r="M76" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="N76" s="4" t="n">
         <v>3</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P76" s="3" t="n">
@@ -12599,7 +12599,7 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -12608,25 +12608,25 @@
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>77.8</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="G81" s="4" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I81" s="3" t="n">
         <v>44.4</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
@@ -12635,10 +12635,10 @@
         </is>
       </c>
       <c r="M81" s="3" t="n">
-        <v>50</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="N81" s="4" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
@@ -12649,7 +12649,7 @@
         <v>50</v>
       </c>
       <c r="Q81" s="4" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="82">
@@ -12812,7 +12812,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -12821,48 +12821,48 @@
         </is>
       </c>
       <c r="F84" s="3" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="G84" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I84" s="3" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="J84" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>U-D-U-D</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M84" s="3" t="n">
         <v>66.7</v>
       </c>
-      <c r="G84" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I84" s="3" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="J84" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="K84" s="2" t="inlineStr">
-        <is>
-          <t>U-D-U-N</t>
-        </is>
-      </c>
-      <c r="L84" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M84" s="3" t="n">
-        <v>75</v>
-      </c>
       <c r="N84" s="4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="P84" s="3" t="n">
-        <v>100</v>
+        <v>41.7</v>
       </c>
       <c r="Q84" s="4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="85">
@@ -13380,7 +13380,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -13389,48 +13389,48 @@
         </is>
       </c>
       <c r="F92" s="3" t="n">
-        <v>70</v>
+        <v>54.5</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I92" s="3" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="J92" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>U-D-N-D</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M92" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N92" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>N/U</t>
+        </is>
+      </c>
+      <c r="P92" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="J92" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="K92" s="2" t="inlineStr">
-        <is>
-          <t>U-D-N-N</t>
-        </is>
-      </c>
-      <c r="L92" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M92" s="3" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="N92" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="O92" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P92" s="3" t="n">
-        <v>66.7</v>
-      </c>
       <c r="Q92" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -13673,10 +13673,10 @@
         </is>
       </c>
       <c r="F96" s="3" t="n">
-        <v>57.1</v>
+        <v>70</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -13684,14 +13684,14 @@
         </is>
       </c>
       <c r="I96" s="3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J96" s="4" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-N</t>
+          <t>U-U-D-D</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
@@ -13700,21 +13700,21 @@
         </is>
       </c>
       <c r="M96" s="3" t="n">
-        <v>57.1</v>
+        <v>81.2</v>
       </c>
       <c r="N96" s="4" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P96" s="3" t="n">
-        <v>42.9</v>
+        <v>56.2</v>
       </c>
       <c r="Q96" s="4" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="97">
@@ -13735,7 +13735,7 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -13744,25 +13744,25 @@
         </is>
       </c>
       <c r="F97" s="3" t="n">
-        <v>100</v>
+        <v>57.1</v>
       </c>
       <c r="G97" s="4" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I97" s="3" t="n">
-        <v>33.3</v>
+        <v>38.1</v>
       </c>
       <c r="J97" s="4" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-N</t>
+          <t>U-N-D-D</t>
         </is>
       </c>
       <c r="L97" s="2" t="inlineStr">
@@ -13771,21 +13771,21 @@
         </is>
       </c>
       <c r="M97" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="N97" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P97" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="Q97" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="98">
@@ -14019,57 +14019,57 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F101" s="3" t="n">
-        <v>63.6</v>
+        <v>56.2</v>
       </c>
       <c r="G101" s="4" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I101" s="3" t="n">
-        <v>36.4</v>
+        <v>62.5</v>
       </c>
       <c r="J101" s="4" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-N</t>
+          <t>U-D-N-D</t>
         </is>
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M101" s="3" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="N101" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P101" s="3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="Q101" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="102">
@@ -14090,7 +14090,7 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -14099,25 +14099,25 @@
         </is>
       </c>
       <c r="F102" s="3" t="n">
-        <v>80</v>
+        <v>55.6</v>
       </c>
       <c r="G102" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I102" s="3" t="n">
-        <v>40</v>
+        <v>44.4</v>
       </c>
       <c r="J102" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-N</t>
+          <t>U-N-U-D</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
@@ -14129,18 +14129,18 @@
         <v>66.7</v>
       </c>
       <c r="N102" s="4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P102" s="3" t="n">
-        <v>55.6</v>
+        <v>100</v>
       </c>
       <c r="Q102" s="4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="103">
@@ -14232,7 +14232,7 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -14241,48 +14241,48 @@
         </is>
       </c>
       <c r="F104" s="3" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="G104" s="4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I104" s="3" t="n">
         <v>50</v>
       </c>
       <c r="J104" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>N-N-U-D</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M104" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="N104" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="K104" s="2" t="inlineStr">
-        <is>
-          <t>N-N-U-N</t>
-        </is>
-      </c>
-      <c r="L104" s="2" t="inlineStr">
-        <is>
-          <t>N/U</t>
-        </is>
-      </c>
-      <c r="M104" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="N104" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P104" s="3" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="Q104" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/BIS_tr.xlsx
+++ b/BIS_tr.xlsx
@@ -690,7 +690,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -699,10 +699,10 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>61.1</v>
+        <v>54.2</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -713,11 +713,11 @@
         <v>41.7</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>U-N-N-N</t>
+          <t>U-N-N-D</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -726,21 +726,21 @@
         </is>
       </c>
       <c r="K4" s="3" t="n">
-        <v>64.3</v>
+        <v>56.2</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N4" s="3" t="n">
-        <v>35.7</v>
+        <v>43.8</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1370,25 +1370,25 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>74.40000000000001</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G15" s="3" t="n">
-        <v>39.7</v>
+        <v>48.8</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1397,21 +1397,21 @@
         </is>
       </c>
       <c r="K15" s="3" t="n">
-        <v>76.90000000000001</v>
+        <v>63.3</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>26</v>
+        <v>79</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N15" s="3" t="n">
-        <v>46.2</v>
+        <v>57</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>26</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1431,25 +1431,25 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>83.5</v>
+        <v>75</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>91</v>
+        <v>52</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>50.5</v>
+        <v>40.4</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>91</v>
+        <v>52</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-N</t>
+          <t>D-N-N-D</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1458,21 +1458,21 @@
         </is>
       </c>
       <c r="K16" s="3" t="n">
-        <v>69</v>
+        <v>64.3</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="N16" s="3" t="n">
-        <v>48.3</v>
+        <v>35.7</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1675,25 +1675,25 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>70.3</v>
+        <v>66.7</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>53.1</v>
+        <v>44.4</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-N</t>
+          <t>U-D-N-D</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1702,10 +1702,10 @@
         </is>
       </c>
       <c r="K20" s="3" t="n">
-        <v>72</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="N20" s="3" t="n">
-        <v>72</v>
+        <v>38.5</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1797,10 +1797,10 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>50</v>
+        <v>67.8</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1808,37 +1808,37 @@
         </is>
       </c>
       <c r="G22" s="3" t="n">
-        <v>45.5</v>
+        <v>50.8</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K22" s="3" t="n">
-        <v>50</v>
+        <v>81.5</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N22" s="3" t="n">
-        <v>41.7</v>
+        <v>51.9</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23">
@@ -2093,57 +2093,57 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>54.2</v>
+        <v>33.3</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>45.8</v>
+        <v>50</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-U</t>
+          <t>U-D-D-N</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K27" s="3" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N27" s="3" t="n">
-        <v>80</v>
+        <v>66.7</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>60.6</v>
+        <v>58.3</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -2174,14 +2174,14 @@
         </is>
       </c>
       <c r="G28" s="3" t="n">
-        <v>47.8</v>
+        <v>42.3</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-U</t>
+          <t>N-D-U-D</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -2190,21 +2190,21 @@
         </is>
       </c>
       <c r="K28" s="3" t="n">
-        <v>75</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N28" s="3" t="n">
-        <v>50</v>
+        <v>43.5</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>74.2</v>
+        <v>56.8</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2296,14 +2296,14 @@
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>41.9</v>
+        <v>37.8</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>U-N-N-N</t>
+          <t>U-N-N-D</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -2312,21 +2312,21 @@
         </is>
       </c>
       <c r="K30" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>75</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="N30" s="3" t="n">
-        <v>42.9</v>
+        <v>37.5</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2346,25 +2346,25 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>67.09999999999999</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>50.7</v>
+        <v>44.6</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-U</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -2373,21 +2373,21 @@
         </is>
       </c>
       <c r="K31" s="3" t="n">
-        <v>66.7</v>
+        <v>68</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N31" s="3" t="n">
-        <v>55.6</v>
+        <v>44</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
     </row>
     <row r="32">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>59.6</v>
+        <v>63.6</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>57</v>
+        <v>99</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2540,14 +2540,14 @@
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>40.4</v>
+        <v>44.4</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>57</v>
+        <v>99</v>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-N</t>
+          <t>U-N-U-D</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="K34" s="3" t="n">
-        <v>47.4</v>
+        <v>58.3</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="N34" s="3" t="n">
-        <v>57.9</v>
+        <v>41.7</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
     </row>
     <row r="35">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2651,48 +2651,48 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>63</v>
+        <v>51.6</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>48.1</v>
+        <v>48.4</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-U</t>
+          <t>D-N-U-D</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K36" s="3" t="n">
-        <v>44.4</v>
+        <v>41.7</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N36" s="3" t="n">
-        <v>55.6</v>
+        <v>50</v>
       </c>
       <c r="O36" s="4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="37">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2773,25 +2773,25 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>72.3</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G38" s="3" t="n">
-        <v>36.2</v>
+        <v>46</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-N</t>
+          <t>U-D-N-D</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -2800,21 +2800,21 @@
         </is>
       </c>
       <c r="K38" s="3" t="n">
-        <v>65</v>
+        <v>77.3</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N38" s="3" t="n">
-        <v>45</v>
+        <v>45.5</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="39">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -3505,25 +3505,25 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>65.40000000000001</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G50" s="3" t="n">
-        <v>42.9</v>
+        <v>47.8</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-U</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -3532,21 +3532,21 @@
         </is>
       </c>
       <c r="K50" s="3" t="n">
-        <v>62.3</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="L50" s="4" t="n">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N50" s="3" t="n">
-        <v>39.3</v>
+        <v>43.9</v>
       </c>
       <c r="O50" s="4" t="n">
-        <v>61</v>
+        <v>41</v>
       </c>
     </row>
     <row r="51">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-N-N</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3627,25 +3627,25 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>65.40000000000001</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G52" s="3" t="n">
-        <v>38.5</v>
+        <v>41</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-U</t>
+          <t>D-N-N-N</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -3654,21 +3654,21 @@
         </is>
       </c>
       <c r="K52" s="3" t="n">
-        <v>66.7</v>
+        <v>72.7</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N52" s="3" t="n">
-        <v>38.9</v>
+        <v>63.6</v>
       </c>
       <c r="O52" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="53">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3993,10 +3993,10 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>70.90000000000001</v>
+        <v>61.4</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>134</v>
+        <v>101</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -4004,14 +4004,14 @@
         </is>
       </c>
       <c r="G58" s="3" t="n">
-        <v>50.7</v>
+        <v>49.5</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>134</v>
+        <v>101</v>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-U</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -4020,10 +4020,10 @@
         </is>
       </c>
       <c r="K58" s="3" t="n">
-        <v>64.2</v>
+        <v>68.2</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
@@ -4031,10 +4031,10 @@
         </is>
       </c>
       <c r="N58" s="3" t="n">
-        <v>47.8</v>
+        <v>52.3</v>
       </c>
       <c r="O58" s="4" t="n">
-        <v>67</v>
+        <v>44</v>
       </c>
     </row>
     <row r="59">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -4359,25 +4359,25 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>46.6</v>
+        <v>45.2</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G64" s="3" t="n">
-        <v>48.3</v>
+        <v>48.9</v>
       </c>
       <c r="H64" s="4" t="n">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-U</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -4386,21 +4386,21 @@
         </is>
       </c>
       <c r="K64" s="3" t="n">
-        <v>48.6</v>
+        <v>45.7</v>
       </c>
       <c r="L64" s="4" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N64" s="3" t="n">
-        <v>51.4</v>
+        <v>50</v>
       </c>
       <c r="O64" s="4" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="65">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -4725,10 +4725,10 @@
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>61.3</v>
+        <v>53.8</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4736,14 +4736,14 @@
         </is>
       </c>
       <c r="G70" s="3" t="n">
-        <v>45.8</v>
+        <v>42.5</v>
       </c>
       <c r="H70" s="4" t="n">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-U</t>
+          <t>U-D-U-N</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -4752,10 +4752,10 @@
         </is>
       </c>
       <c r="K70" s="3" t="n">
-        <v>62.5</v>
+        <v>50</v>
       </c>
       <c r="L70" s="4" t="n">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
@@ -4763,10 +4763,10 @@
         </is>
       </c>
       <c r="N70" s="3" t="n">
-        <v>45.3</v>
+        <v>44.4</v>
       </c>
       <c r="O70" s="4" t="n">
-        <v>64</v>
+        <v>36</v>
       </c>
     </row>
     <row r="71">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -4969,25 +4969,25 @@
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>55.4</v>
+        <v>54.4</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>65</v>
+        <v>171</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G74" s="3" t="n">
-        <v>40</v>
+        <v>46.8</v>
       </c>
       <c r="H74" s="4" t="n">
-        <v>65</v>
+        <v>171</v>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-N</t>
+          <t>N-D-U-U</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -4996,21 +4996,21 @@
         </is>
       </c>
       <c r="K74" s="3" t="n">
-        <v>73.3</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="L74" s="4" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N74" s="3" t="n">
-        <v>46.7</v>
+        <v>39.3</v>
       </c>
       <c r="O74" s="4" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="75">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -5091,10 +5091,10 @@
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>72.2</v>
+        <v>77.5</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -5102,14 +5102,14 @@
         </is>
       </c>
       <c r="G76" s="3" t="n">
-        <v>55.6</v>
+        <v>40</v>
       </c>
       <c r="H76" s="4" t="n">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>N-N-N-U</t>
+          <t>N-N-N-D</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -5118,21 +5118,21 @@
         </is>
       </c>
       <c r="K76" s="3" t="n">
-        <v>80</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="L76" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N76" s="3" t="n">
-        <v>46.7</v>
+        <v>35.7</v>
       </c>
       <c r="O76" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="77">
@@ -5204,7 +5204,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -5213,25 +5213,25 @@
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>75</v>
+        <v>64.2</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G78" s="3" t="n">
-        <v>38.9</v>
+        <v>41.8</v>
       </c>
       <c r="H78" s="4" t="n">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>U-U-N-N</t>
+          <t>U-U-N-D</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -5240,21 +5240,21 @@
         </is>
       </c>
       <c r="K78" s="3" t="n">
-        <v>80</v>
+        <v>61.5</v>
       </c>
       <c r="L78" s="4" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N78" s="3" t="n">
-        <v>40</v>
+        <v>46.2</v>
       </c>
       <c r="O78" s="4" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
     </row>
     <row r="79">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -5274,48 +5274,48 @@
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>68</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="E79" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="H79" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>U-N-N-D</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K79" s="3" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="L79" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G79" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="H79" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="I79" s="2" t="inlineStr">
-        <is>
-          <t>U-N-N-N</t>
-        </is>
-      </c>
-      <c r="J79" s="2" t="inlineStr">
-        <is>
-          <t>N<